--- a/AT/Materials.xlsx
+++ b/AT/Materials.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wellspan-my.sharepoint.com/personal/dsmith14_wellspan_org/Documents/Documents/GitHub/dps/AT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1416" documentId="8_{DFBDE19A-4092-4537-AB95-BEF979D4F74F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B481EB9C-76C3-4D1D-9E0A-5FB3267A8FCC}"/>
+  <xr:revisionPtr revIDLastSave="2319" documentId="13_ncr:1_{7E8DFDA2-3B81-4DBD-A379-3D4479E4AEB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7853741-BF2A-4710-9A01-2732E3FB3EDF}"/>
   <bookViews>
-    <workbookView xWindow="6330" yWindow="465" windowWidth="21705" windowHeight="14670" activeTab="1" xr2:uid="{362FB22F-6BD6-431B-94C9-F0870D854534}"/>
+    <workbookView xWindow="900" yWindow="1200" windowWidth="26625" windowHeight="14610" activeTab="2" xr2:uid="{362FB22F-6BD6-431B-94C9-F0870D854534}"/>
   </bookViews>
   <sheets>
     <sheet name="Materials" sheetId="1" r:id="rId1"/>
     <sheet name="ToDo" sheetId="2" r:id="rId2"/>
-    <sheet name="Notes" sheetId="3" r:id="rId3"/>
+    <sheet name="Make" sheetId="4" r:id="rId3"/>
+    <sheet name="Notes" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -72,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="483">
   <si>
     <t>piping slide</t>
   </si>
@@ -80,9 +81,6 @@
     <t>1/2" Ladder lock</t>
   </si>
   <si>
-    <t>user existing orange hood</t>
-  </si>
-  <si>
     <t>Pockets size 8" tall x 6" wide x 1 1/2" deep. Shape like blue pack.  7" zipper #3 (have)</t>
   </si>
   <si>
@@ -581,9 +579,6 @@
     <t>300d</t>
   </si>
   <si>
-    <t>21d</t>
-  </si>
-  <si>
     <t>5yds</t>
   </si>
   <si>
@@ -611,9 +606,6 @@
     <t>existing</t>
   </si>
   <si>
-    <t>both</t>
-  </si>
-  <si>
     <t>Kilt</t>
   </si>
   <si>
@@ -855,16 +847,693 @@
   </si>
   <si>
     <t>Quilt $58.50 - $92.00</t>
+  </si>
+  <si>
+    <t>Sq inches per yard</t>
+  </si>
+  <si>
+    <t>Width</t>
+  </si>
+  <si>
+    <t>Length</t>
+  </si>
+  <si>
+    <t>Wt/yd</t>
+  </si>
+  <si>
+    <t>total sq. yds</t>
+  </si>
+  <si>
+    <t>Total weight</t>
+  </si>
+  <si>
+    <t>(F-32) * 5/9 - F to C formula</t>
+  </si>
+  <si>
+    <t>Wt Oz</t>
+  </si>
+  <si>
+    <t>Wt. gm</t>
+  </si>
+  <si>
+    <t>210d</t>
+  </si>
+  <si>
+    <t>20 F</t>
+  </si>
+  <si>
+    <t>Top Quilt</t>
+  </si>
+  <si>
+    <t>Materials</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Griz Ariel Hammock</t>
+  </si>
+  <si>
+    <t>Ripstop by the Roll</t>
+  </si>
+  <si>
+    <t>Gathered End Hammock</t>
+  </si>
+  <si>
+    <t>Climashield 6oz</t>
+  </si>
+  <si>
+    <t>Climashield 5oz</t>
+  </si>
+  <si>
+    <t>Climashield 3.6oz</t>
+  </si>
+  <si>
+    <t>Back Pack</t>
+  </si>
+  <si>
+    <t>Hexon 1.6</t>
+  </si>
+  <si>
+    <t>Dutchware</t>
+  </si>
+  <si>
+    <t>Total Wt</t>
+  </si>
+  <si>
+    <t>Buckles 1"</t>
+  </si>
+  <si>
+    <t>Buckles 3/4"</t>
+  </si>
+  <si>
+    <t>Amsteel 7/64</t>
+  </si>
+  <si>
+    <t>Shock Cord</t>
+  </si>
+  <si>
+    <t>Sleeping Bag Liner</t>
+  </si>
+  <si>
+    <t>Ditty Bags (See ToDo)</t>
+  </si>
+  <si>
+    <t>Kilt (Use ION)</t>
+  </si>
+  <si>
+    <t>shock cord</t>
+  </si>
+  <si>
+    <t>HyperD 1.6</t>
+  </si>
+  <si>
+    <t>Membrane 10 .66oz</t>
+  </si>
+  <si>
+    <t>Membrane 15 .9oz</t>
+  </si>
+  <si>
+    <t>wt</t>
+  </si>
+  <si>
+    <t>HyperD 1.0</t>
+  </si>
+  <si>
+    <t>Ripstop 1.1oz</t>
+  </si>
+  <si>
+    <t>Thread Mara 50</t>
+  </si>
+  <si>
+    <t>Thread Mara 70</t>
+  </si>
+  <si>
+    <t>Tension Lock 12</t>
+  </si>
+  <si>
+    <t>Tri-Glide 12</t>
+  </si>
+  <si>
+    <t>cord locks mini</t>
+  </si>
+  <si>
+    <t>cord locks regular 12</t>
+  </si>
+  <si>
+    <t>cord locks mini 12</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>HHH zipper #5 /ft</t>
+  </si>
+  <si>
+    <t>HHH pull #5</t>
+  </si>
+  <si>
+    <t>1/8" 25' (gm/in)</t>
+  </si>
+  <si>
+    <t>3/32" 25' (gm/in)</t>
+  </si>
+  <si>
+    <t>yellow 25' (gm/ft)</t>
+  </si>
+  <si>
+    <t>blue 25' (gm/ft)</t>
+  </si>
+  <si>
+    <t>red 25' (gm/ft)</t>
+  </si>
+  <si>
+    <t>pocket mesh 4oz</t>
+  </si>
+  <si>
+    <t>420D Robic</t>
+  </si>
+  <si>
+    <t>HyperD 300</t>
+  </si>
+  <si>
+    <t>Hex 2.2 PU3000</t>
+  </si>
+  <si>
+    <t>102x46</t>
+  </si>
+  <si>
+    <t>cord lock</t>
+  </si>
+  <si>
+    <t>78x48</t>
+  </si>
+  <si>
+    <t>no-seem .5 oz</t>
+  </si>
+  <si>
+    <t>no-seem .67 oz</t>
+  </si>
+  <si>
+    <t>no-seem .9 oz</t>
+  </si>
+  <si>
+    <t>Grossgrain 3/4" 25'</t>
+  </si>
+  <si>
+    <t>Grossgrain 1/2" 25'</t>
+  </si>
+  <si>
+    <t>gm/yd</t>
+  </si>
+  <si>
+    <t>Grossgrain 1/2" 5yd</t>
+  </si>
+  <si>
+    <t>Grossgrain 3/4" 5 yd</t>
+  </si>
+  <si>
+    <t>Grossgrain 1" 5 yd</t>
+  </si>
+  <si>
+    <t>gm/ft</t>
+  </si>
+  <si>
+    <t>gm/in</t>
+  </si>
+  <si>
+    <t>mil-spec webbing 1" 25'</t>
+  </si>
+  <si>
+    <t>mil-spec webbing 2" 25'</t>
+  </si>
+  <si>
+    <t>polyester webbing 1" 25'</t>
+  </si>
+  <si>
+    <t>mil-spec webbing 3/4" 25'</t>
+  </si>
+  <si>
+    <t>xeon sil .9 oz</t>
+  </si>
+  <si>
+    <t>hexon 1.0 oz</t>
+  </si>
+  <si>
+    <t>thread</t>
+  </si>
+  <si>
+    <t>pocket mesh</t>
+  </si>
+  <si>
+    <t>Hexon 1.2</t>
+  </si>
+  <si>
+    <t>webbing 2" polypro per foot</t>
+  </si>
+  <si>
+    <t>webbing 3/4" polyester 25'</t>
+  </si>
+  <si>
+    <t>webbing 1/2" polyester 25'</t>
+  </si>
+  <si>
+    <t>webbing 1" polyester 25'</t>
+  </si>
+  <si>
+    <t>Buckles 2"</t>
+  </si>
+  <si>
+    <t>Velcro 2" per foot</t>
+  </si>
+  <si>
+    <t>Velcro 1" per foot</t>
+  </si>
+  <si>
+    <t>unavailable</t>
+  </si>
+  <si>
+    <t>ykk waterproff #3 zipper /ft</t>
+  </si>
+  <si>
+    <t>YKK waterproff pull #3</t>
+  </si>
+  <si>
+    <t>.665 pole tip</t>
+  </si>
+  <si>
+    <t>magic buckle 1"</t>
+  </si>
+  <si>
+    <t>54x78</t>
+  </si>
+  <si>
+    <t>spacer mesh 1/8" 1/2yd</t>
+  </si>
+  <si>
+    <t>nano no-seem .67 oz</t>
+  </si>
+  <si>
+    <t>nano noseeum tarp sleeves</t>
+  </si>
+  <si>
+    <t>amsteel</t>
+  </si>
+  <si>
+    <t>amsteel (2@16')</t>
+  </si>
+  <si>
+    <t>cannot find</t>
+  </si>
+  <si>
+    <t>Argon .49</t>
+  </si>
+  <si>
+    <t>210D Robic</t>
+  </si>
+  <si>
+    <t>spacer mesh 1/4" per foot</t>
+  </si>
+  <si>
+    <t>spacer mesh 1/8" per foot</t>
+  </si>
+  <si>
+    <t>Rain Pants</t>
+  </si>
+  <si>
+    <t>Dyneema .51 oz 1/2 yd</t>
+  </si>
+  <si>
+    <t>Rain Kilt (30L x 48W)</t>
+  </si>
+  <si>
+    <t>Bug Net</t>
+  </si>
+  <si>
+    <t>58 x 72</t>
+  </si>
+  <si>
+    <t>Food Bag (12.5 x 22)</t>
+  </si>
+  <si>
+    <t>1.4 oz 10D waterproof/breathable</t>
+  </si>
+  <si>
+    <t>make pattern</t>
+  </si>
+  <si>
+    <t>Pack Cover (new pack)</t>
+  </si>
+  <si>
+    <t>existing orange material</t>
+  </si>
+  <si>
+    <t>existing ION material</t>
+  </si>
+  <si>
+    <t>See ToDo</t>
+  </si>
+  <si>
+    <t>1" PET PSA seam seal tape /yd</t>
+  </si>
+  <si>
+    <t>Xenon 1.1</t>
+  </si>
+  <si>
+    <t>PET Seam seal 1"</t>
+  </si>
+  <si>
+    <t>LineLoc 3 - 12</t>
+  </si>
+  <si>
+    <t>shock cord (3/32 15')</t>
+  </si>
+  <si>
+    <t>cord lock (4)</t>
+  </si>
+  <si>
+    <t>shock cord (1/8 6')</t>
+  </si>
+  <si>
+    <t>Linelocs 3 (4)</t>
+  </si>
+  <si>
+    <t>shock cord (1/8 15')</t>
+  </si>
+  <si>
+    <t>cord lock (3)</t>
+  </si>
+  <si>
+    <t>cord lock (5)</t>
+  </si>
+  <si>
+    <t>TQ</t>
+  </si>
+  <si>
+    <t>UQ</t>
+  </si>
+  <si>
+    <t>LineLocs</t>
+  </si>
+  <si>
+    <t>with half bug net</t>
+  </si>
+  <si>
+    <t>Griz</t>
+  </si>
+  <si>
+    <t>shock cord 3/32</t>
+  </si>
+  <si>
+    <t>shock cord 1/8</t>
+  </si>
+  <si>
+    <t>Order</t>
+  </si>
+  <si>
+    <t>Bugnet</t>
+  </si>
+  <si>
+    <t>webbing 1" - 2'</t>
+  </si>
+  <si>
+    <t>Buckle 1"</t>
+  </si>
+  <si>
+    <t>elastic / 1/8" chock cord (36")</t>
+  </si>
+  <si>
+    <t>FB</t>
+  </si>
+  <si>
+    <t>RK</t>
+  </si>
+  <si>
+    <t>RP</t>
+  </si>
+  <si>
+    <t>Pack</t>
+  </si>
+  <si>
+    <t>Webbing 1"</t>
+  </si>
+  <si>
+    <t>cord lock (1)</t>
+  </si>
+  <si>
+    <t>cord lock - regular</t>
+  </si>
+  <si>
+    <t>cord lock - small</t>
+  </si>
+  <si>
+    <t>1-3</t>
+  </si>
+  <si>
+    <t>Order 1</t>
+  </si>
+  <si>
+    <t>Order 3</t>
+  </si>
+  <si>
+    <t>Order 2</t>
+  </si>
+  <si>
+    <t>Order 4</t>
+  </si>
+  <si>
+    <t>Order 5</t>
+  </si>
+  <si>
+    <t>mini plastic hook (3/32)</t>
+  </si>
+  <si>
+    <t>Order Items</t>
+  </si>
+  <si>
+    <t>mini combo hook - 12</t>
+  </si>
+  <si>
+    <t>120x55</t>
+  </si>
+  <si>
+    <t>Dyneema 1.3 oz 1/2 yd</t>
+  </si>
+  <si>
+    <t>Dyneema 1.43 oz 1/2 yd</t>
+  </si>
+  <si>
+    <t>11,12</t>
+  </si>
+  <si>
+    <t>8,9</t>
+  </si>
+  <si>
+    <t>use existing orange hood</t>
+  </si>
+  <si>
+    <t>* Work on quantities</t>
+  </si>
+  <si>
+    <t>D rings 1" - 12</t>
+  </si>
+  <si>
+    <t>Beastee Dee rings 1/2" - 12</t>
+  </si>
+  <si>
+    <t>D rings 1" (2)</t>
+  </si>
+  <si>
+    <t>Tri-Glide (2)</t>
+  </si>
+  <si>
+    <t>Tension Lock (6)</t>
+  </si>
+  <si>
+    <t>Buckles 1" (2)</t>
+  </si>
+  <si>
+    <t>cord locks regular (4)</t>
+  </si>
+  <si>
+    <t>Amazon $6.99 for 4</t>
+  </si>
+  <si>
+    <t>do not carry</t>
+  </si>
+  <si>
+    <t>Beastee Dee rings 1/2" (6)</t>
+  </si>
+  <si>
+    <t>Robic 210D 1/2 yd (3)</t>
+  </si>
+  <si>
+    <t>300D 1/2 yd (3)</t>
+  </si>
+  <si>
+    <t>regeneration 420 1/2 yd (1)</t>
+  </si>
+  <si>
+    <t>X-Pac VX25 1/2 yd (1)</t>
+  </si>
+  <si>
+    <t>RS &amp; Dutch</t>
+  </si>
+  <si>
+    <t>Order 1-4</t>
+  </si>
+  <si>
+    <t>-OR- 36L x 56W</t>
+  </si>
+  <si>
+    <t>Spreader bar 28.5"</t>
+  </si>
+  <si>
+    <t>Tent</t>
+  </si>
+  <si>
+    <t>matress</t>
+  </si>
+  <si>
+    <t>sleeping bag</t>
+  </si>
+  <si>
+    <t>hammock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spreader </t>
+  </si>
+  <si>
+    <t>Tent vs Hammock Weight</t>
+  </si>
+  <si>
+    <t>bugnet</t>
+  </si>
+  <si>
+    <t>tyvek</t>
+  </si>
+  <si>
+    <t>120 x 96</t>
+  </si>
+  <si>
+    <t>pounds</t>
+  </si>
+  <si>
+    <t>ounces</t>
+  </si>
+  <si>
+    <t>stakes</t>
+  </si>
+  <si>
+    <t>straps</t>
+  </si>
+  <si>
+    <t>down</t>
+  </si>
+  <si>
+    <t>down saves</t>
+  </si>
+  <si>
+    <t>$50 / lb down - $13 more</t>
+  </si>
+  <si>
+    <t>down (Amazon)</t>
+  </si>
+  <si>
+    <t>Make pullover/hoodie patern</t>
+  </si>
+  <si>
+    <t>Make jacket patern</t>
+  </si>
+  <si>
+    <t>Polartec Alpha Direct 4008</t>
+  </si>
+  <si>
+    <t>slate blue 4008</t>
+  </si>
+  <si>
+    <t>mara 70 thread</t>
+  </si>
+  <si>
+    <t>Mango yellow</t>
+  </si>
+  <si>
+    <t>pattern</t>
+  </si>
+  <si>
+    <t>pullover hoodie Alpha Direct 4008</t>
+  </si>
+  <si>
+    <t>gm          =</t>
+  </si>
+  <si>
+    <t>Amzn 6 + webbing 11.99</t>
+  </si>
+  <si>
+    <t>TQ Wt</t>
+  </si>
+  <si>
+    <t>UQ Wt</t>
+  </si>
+  <si>
+    <t>Total lb</t>
+  </si>
+  <si>
+    <t>4,5</t>
+  </si>
+  <si>
+    <t>7,10</t>
+  </si>
+  <si>
+    <t>RS</t>
+  </si>
+  <si>
+    <t>Pullover/hoodie</t>
+  </si>
+  <si>
+    <t>6,13</t>
+  </si>
+  <si>
+    <t>4048 with wool</t>
+  </si>
+  <si>
+    <t>Alpha Direct 4028</t>
+  </si>
+  <si>
+    <t>Alpha Direct 4004</t>
+  </si>
+  <si>
+    <t>Alpha Direct 4008</t>
+  </si>
+  <si>
+    <t>Alpha Direct 4024</t>
+  </si>
+  <si>
+    <t>Alpha Direct 4048 w/ wool</t>
+  </si>
+  <si>
+    <t>gsm</t>
+  </si>
+  <si>
+    <t>oz per 2 yds</t>
+  </si>
+  <si>
+    <t>4004</t>
+  </si>
+  <si>
+    <t>L</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="3">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -918,8 +1587,24 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -980,8 +1665,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -989,12 +1692,222 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="168">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1040,6 +1953,267 @@
     <xf numFmtId="2" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="8" fillId="5" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="16" fontId="8" fillId="6" borderId="6" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="16" fontId="8" fillId="12" borderId="6" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1059,9 +2233,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1099,7 +2273,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1205,7 +2379,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1347,7 +2521,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1373,42 +2547,42 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F1" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K1" s="18" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>9</v>
-      </c>
       <c r="F2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>9</v>
-      </c>
       <c r="K2" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
@@ -1430,10 +2604,10 @@
       </c>
       <c r="G3" s="3"/>
       <c r="J3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K3" s="16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L3">
         <v>3</v>
@@ -1446,7 +2620,7 @@
         <v>19.5</v>
       </c>
       <c r="O3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
@@ -1465,10 +2639,10 @@
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="J4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K4" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L4">
         <v>1</v>
@@ -1481,12 +2655,12 @@
         <v>4.25</v>
       </c>
       <c r="O4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C5" s="3">
         <v>16.5</v>
@@ -1500,13 +2674,13 @@
         <v>10</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L5">
         <v>1</v>
@@ -1519,12 +2693,12 @@
         <v>3.7</v>
       </c>
       <c r="O5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C6" s="3">
         <v>6.95</v>
@@ -1535,10 +2709,10 @@
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="J6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="L6">
         <v>1</v>
@@ -1553,7 +2727,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3">
@@ -1564,7 +2738,7 @@
       <c r="H7" s="13"/>
       <c r="I7" s="3"/>
       <c r="K7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -1579,7 +2753,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B8">
         <v>2</v>
@@ -1593,7 +2767,7 @@
       <c r="H8" s="13"/>
       <c r="J8" s="3"/>
       <c r="K8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -1608,7 +2782,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C9" s="3">
         <v>0</v>
@@ -1623,7 +2797,7 @@
       </c>
       <c r="J9" s="3"/>
       <c r="K9" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -1638,10 +2812,10 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C10" s="3">
         <v>6</v>
@@ -1655,10 +2829,10 @@
         <v>11</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K10" s="16" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L10">
         <v>2</v>
@@ -1673,10 +2847,10 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C11" s="3">
         <v>7.25</v>
@@ -1687,10 +2861,10 @@
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -1705,7 +2879,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3">
@@ -1714,10 +2888,10 @@
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -1732,10 +2906,10 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C13" s="3">
         <v>7.75</v>
@@ -1745,10 +2919,10 @@
       <c r="G13" s="3"/>
       <c r="H13" s="9"/>
       <c r="J13" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L13">
         <v>12</v>
@@ -1763,10 +2937,10 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3">
@@ -1778,13 +2952,13 @@
         <v>15</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J14" t="s">
+        <v>125</v>
+      </c>
+      <c r="K14" t="s">
         <v>126</v>
-      </c>
-      <c r="K14" t="s">
-        <v>127</v>
       </c>
       <c r="L14">
         <v>2</v>
@@ -1799,10 +2973,10 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" s="3">
         <v>4.75</v>
@@ -1816,13 +2990,13 @@
       </c>
       <c r="G15" s="12"/>
       <c r="H15" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L15">
         <v>1</v>
@@ -1837,10 +3011,10 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C16" s="3">
         <v>6</v>
@@ -1851,13 +3025,13 @@
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J16" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L16">
         <v>2</v>
@@ -1872,7 +3046,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B17">
         <v>4</v>
@@ -1884,13 +3058,13 @@
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J17" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K17" s="16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L17">
         <v>3</v>
@@ -1905,7 +3079,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B18">
         <v>4</v>
@@ -1917,17 +3091,17 @@
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B19">
         <v>6</v>
@@ -1943,7 +3117,7 @@
       </c>
       <c r="H19" s="9"/>
       <c r="M19" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N19" s="3">
         <f>SUM(N3:N18)</f>
@@ -1953,7 +3127,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B20">
         <v>4</v>
@@ -1965,18 +3139,18 @@
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K20" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" t="s">
         <v>55</v>
-      </c>
-      <c r="B21" t="s">
-        <v>56</v>
       </c>
       <c r="C21" s="3">
         <v>4</v>
@@ -1988,7 +3162,7 @@
       <c r="G21" s="3"/>
       <c r="H21" s="9"/>
       <c r="K21" s="25" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L21">
         <v>5</v>
@@ -2004,10 +3178,10 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B22" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D22" s="3">
         <v>1.75</v>
@@ -2018,7 +3192,7 @@
       </c>
       <c r="H22" s="9"/>
       <c r="K22" s="25" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M22" s="3">
         <v>4.5</v>
@@ -2030,14 +3204,14 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="K23" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L23">
         <v>1</v>
@@ -2053,10 +3227,10 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B24" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C24" s="3">
         <v>7.5</v>
@@ -2065,7 +3239,7 @@
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="K24" s="25" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L24">
         <v>2</v>
@@ -2084,10 +3258,10 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C25" s="3"/>
       <c r="D25" s="3">
@@ -2099,10 +3273,10 @@
         <v>52</v>
       </c>
       <c r="H25" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -2117,10 +3291,10 @@
     </row>
     <row r="26" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C26" s="3">
         <v>5.5</v>
@@ -2131,7 +3305,7 @@
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
       <c r="K26" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="L26">
         <v>4</v>
@@ -2146,7 +3320,7 @@
     </row>
     <row r="27" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C27" s="3">
         <v>8.5</v>
@@ -2161,7 +3335,7 @@
       </c>
       <c r="J27" s="3"/>
       <c r="K27" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L27">
         <v>1</v>
@@ -2176,10 +3350,10 @@
     </row>
     <row r="28" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3">
@@ -2191,7 +3365,7 @@
         <v>2.1</v>
       </c>
       <c r="K28" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L28">
         <v>8</v>
@@ -2210,7 +3384,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
@@ -2225,10 +3399,10 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B30" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C30" s="3">
         <v>4.75</v>
@@ -2245,7 +3419,7 @@
       <c r="I30" s="3"/>
       <c r="K30" s="10"/>
       <c r="M30" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N30" s="3">
         <f>SUM(N21:N28)</f>
@@ -2254,10 +3428,10 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B31" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C31" s="3">
         <v>6.5</v>
@@ -2268,7 +3442,7 @@
       <c r="H31" s="10"/>
       <c r="I31" s="3"/>
       <c r="K31" s="23" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L31" s="23"/>
       <c r="M31" s="19"/>
@@ -2276,10 +3450,10 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B32" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C32" s="3"/>
       <c r="D32" s="3">
@@ -2292,15 +3466,15 @@
         <v>DG Future 18.00</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K32" s="23" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B33">
         <v>2</v>
@@ -2316,18 +3490,18 @@
         <v>DG Future 30.00</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M33" s="25" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B34" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3">
@@ -2340,18 +3514,18 @@
         <v>DG Future 12.00</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M34" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B35" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C35" s="3"/>
       <c r="D35" s="3">
@@ -2364,18 +3538,18 @@
         <v>DG Future 6.25</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L35" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="M35" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C36" s="3"/>
       <c r="D36" s="3">
@@ -2388,18 +3562,18 @@
         <v>DG Future 22.00</v>
       </c>
       <c r="I36" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M36" s="26" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B37" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C37" s="3"/>
       <c r="D37" s="3">
@@ -2409,13 +3583,13 @@
       <c r="G37" s="13"/>
       <c r="H37" s="13"/>
       <c r="M37" s="16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N37" s="16"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="26" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B38">
         <v>6</v>
@@ -2452,57 +3626,57 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>2</v>
+        <v>418</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -2531,47 +3705,47 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -2580,31 +3754,31 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="21" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>88</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -2612,150 +3786,153 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C15" s="1"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="22" t="s">
-        <v>104</v>
+      <c r="A18" s="2" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B19" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B20" t="s">
-        <v>112</v>
+        <v>111</v>
+      </c>
+      <c r="C20" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>106</v>
+      </c>
+      <c r="B21" t="s">
         <v>107</v>
       </c>
-      <c r="B21" t="s">
-        <v>108</v>
-      </c>
       <c r="C21" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B22" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C22" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>109</v>
+      </c>
+      <c r="B23" t="s">
         <v>110</v>
-      </c>
-      <c r="B23" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>112</v>
+      </c>
+      <c r="B24" t="s">
         <v>113</v>
-      </c>
-      <c r="B24" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B25" t="s">
+        <v>117</v>
+      </c>
+      <c r="C25" t="s">
         <v>118</v>
-      </c>
-      <c r="C25" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B26" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B27" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C27" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F27" s="21" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B28" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C28" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G28" s="18" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="G29" s="2" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F30" s="20" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G30" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="H30">
         <v>5</v>
@@ -2768,18 +3945,18 @@
         <v>22.5</v>
       </c>
       <c r="K30" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F31" s="20" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="G31" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H31">
         <v>3</v>
@@ -2794,16 +3971,16 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B32" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F32" s="20" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="G32" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="H32">
         <v>3</v>
@@ -2818,16 +3995,16 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B33" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F33" s="20" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="G33" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H33">
         <v>3</v>
@@ -2842,22 +4019,22 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B34" t="s">
+        <v>188</v>
+      </c>
+      <c r="C34" t="s">
+        <v>189</v>
+      </c>
+      <c r="D34" t="s">
         <v>191</v>
       </c>
-      <c r="C34" t="s">
-        <v>192</v>
-      </c>
-      <c r="D34" t="s">
-        <v>194</v>
-      </c>
       <c r="F34" s="20" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="G34" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="H34">
         <v>5</v>
@@ -2872,16 +4049,16 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C35" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F35" s="20" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="G35" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="H35">
         <v>5</v>
@@ -2896,13 +4073,13 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F36" s="20" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="G36" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I36" s="30">
         <v>6.5</v>
@@ -2914,19 +4091,19 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B37" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C37" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F37" s="20" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="G37" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="H37">
         <v>4</v>
@@ -2941,11 +4118,11 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F38" s="20"/>
       <c r="G38" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H38">
         <v>1</v>
@@ -2958,13 +4135,16 @@
         <v>3.7</v>
       </c>
       <c r="K38" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>462</v>
+      </c>
       <c r="F39" s="20"/>
       <c r="G39" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="I39" s="30">
         <v>4.25</v>
@@ -2977,7 +4157,7 @@
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="F40" s="20"/>
       <c r="G40" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I40" s="30">
         <v>5.5</v>
@@ -2987,13 +4167,13 @@
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="F41" s="20"/>
       <c r="G41" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="I41" s="30">
         <v>5.5</v>
@@ -3003,16 +4183,16 @@
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B42" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="F42" s="20"/>
       <c r="G42" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H42">
         <v>4</v>
@@ -3025,22 +4205,22 @@
         <v>19</v>
       </c>
       <c r="K42" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C43" s="30">
         <v>13.5</v>
       </c>
       <c r="D43" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="F43" s="20"/>
       <c r="G43" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="I43" s="30">
         <v>2.1</v>
@@ -3050,22 +4230,22 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C44" s="30">
         <v>13.5</v>
       </c>
       <c r="D44" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="F44" s="20"/>
       <c r="G44" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I44" s="30">
         <v>2.1</v>
@@ -3077,17 +4257,17 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C45" s="30">
         <v>13.5</v>
       </c>
       <c r="D45" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F45" s="20"/>
       <c r="G45" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="I45" s="30">
         <v>3.75</v>
@@ -3099,17 +4279,17 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C46" s="30">
         <v>13.5</v>
       </c>
       <c r="D46" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="F46" s="20"/>
       <c r="G46" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="I46" s="30">
         <v>7</v>
@@ -3121,10 +4301,10 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="F47" s="20" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="G47" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="H47">
         <v>2</v>
@@ -3137,18 +4317,18 @@
         <v>12.5</v>
       </c>
       <c r="K47" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B48" s="2" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F48" s="20" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G48" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="H48">
         <v>1</v>
@@ -3161,18 +4341,18 @@
         <v>12</v>
       </c>
       <c r="K48" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="49" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="F49" s="20" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G49" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="H49">
         <v>2</v>
@@ -3185,18 +4365,18 @@
         <v>27</v>
       </c>
       <c r="K49" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="50" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="F50" s="20" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="G50" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I50" s="30">
         <v>3.9</v>
@@ -3206,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="L50" s="30">
         <f>J30+J38+SUM(J40:J43)+SUM(J47:J50)</f>
@@ -3215,11 +4395,11 @@
     </row>
     <row r="51" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="F51" s="20"/>
       <c r="G51" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="I51" s="30">
         <v>2</v>
@@ -3231,7 +4411,7 @@
     </row>
     <row r="52" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="F52" s="20"/>
       <c r="I52" s="30"/>
@@ -3242,12 +4422,12 @@
     </row>
     <row r="53" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="54" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
   </sheetData>
@@ -3269,8 +4449,5081 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{458BE52D-397A-4267-A4EC-33DE3608C71C}">
+  <dimension ref="A1:AB124"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.5703125" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="6" width="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="1.7109375" customWidth="1"/>
+    <col min="10" max="10" width="22.5703125" style="10" customWidth="1"/>
+    <col min="11" max="11" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7" customWidth="1"/>
+    <col min="13" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.5703125" customWidth="1"/>
+    <col min="19" max="19" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.28515625" customWidth="1"/>
+    <col min="22" max="22" width="5.140625" customWidth="1"/>
+    <col min="23" max="23" width="5.28515625" customWidth="1"/>
+    <col min="24" max="24" width="7" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="3.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="3.28515625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B1" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="I1" s="34"/>
+      <c r="K1" s="18" t="s">
+        <v>273</v>
+      </c>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+      <c r="S1" s="62"/>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="B2" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="I2" s="34"/>
+      <c r="K2" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="S2" s="4"/>
+      <c r="U2" s="4"/>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="B3" s="38" t="s">
+        <v>275</v>
+      </c>
+      <c r="C3" s="20">
+        <v>6</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E3" s="36">
+        <f>C3*$A$5</f>
+        <v>19.5</v>
+      </c>
+      <c r="F3" s="33">
+        <v>2.5</v>
+      </c>
+      <c r="G3" s="35">
+        <v>14.98</v>
+      </c>
+      <c r="H3" s="35">
+        <f>IF((G3*F3)=0,"",G3*F3)</f>
+        <v>37.450000000000003</v>
+      </c>
+      <c r="I3" s="34"/>
+      <c r="J3" s="147" t="str">
+        <f>IF(ISBLANK(A3),"",A3)</f>
+        <v>Top Quilt</v>
+      </c>
+      <c r="K3" t="s">
+        <v>276</v>
+      </c>
+      <c r="L3" s="20">
+        <v>5</v>
+      </c>
+      <c r="M3" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="N3" s="36">
+        <f>L3*$A$5</f>
+        <v>16.25</v>
+      </c>
+      <c r="O3" s="33">
+        <v>2.5</v>
+      </c>
+      <c r="P3" s="35">
+        <v>14.25</v>
+      </c>
+      <c r="Q3" s="35">
+        <f>IF((P3*O3)=0,"",P3*O3)</f>
+        <v>35.625</v>
+      </c>
+      <c r="T3" s="3"/>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A4" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="B4" s="38" t="s">
+        <v>277</v>
+      </c>
+      <c r="C4" s="20">
+        <v>3.6</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E4" s="36">
+        <f t="shared" ref="E4" si="0">C4*$A$5</f>
+        <v>11.700000000000001</v>
+      </c>
+      <c r="F4" s="33"/>
+      <c r="G4" s="35">
+        <v>9.6300000000000008</v>
+      </c>
+      <c r="H4" s="35" t="str">
+        <f t="shared" ref="H4:H84" si="1">IF((G4*F4)=0,"",G4*F4)</f>
+        <v/>
+      </c>
+      <c r="I4" s="34"/>
+      <c r="J4" s="148" t="str">
+        <f t="shared" ref="J4:J68" si="2">IF(ISBLANK(A4),"",A4)</f>
+        <v>54x78</v>
+      </c>
+      <c r="K4" t="s">
+        <v>277</v>
+      </c>
+      <c r="L4" s="20">
+        <v>3.6</v>
+      </c>
+      <c r="M4" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="N4" s="36">
+        <f t="shared" ref="N4:N10" si="3">L4*$A$5</f>
+        <v>11.700000000000001</v>
+      </c>
+      <c r="O4" s="33"/>
+      <c r="P4" s="35">
+        <v>12</v>
+      </c>
+      <c r="Q4" s="35" t="str">
+        <f t="shared" ref="Q4:Q84" si="4">IF((P4*O4)=0,"",P4*O4)</f>
+        <v/>
+      </c>
+      <c r="T4" s="3">
+        <f>E3+E7</f>
+        <v>23.855</v>
+      </c>
+      <c r="U4" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A5" s="37">
+        <f>(54*78)/(36*36)</f>
+        <v>3.25</v>
+      </c>
+      <c r="B5" s="38" t="s">
+        <v>451</v>
+      </c>
+      <c r="C5" s="20"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I5" s="34"/>
+      <c r="J5" s="148">
+        <f t="shared" si="2"/>
+        <v>3.25</v>
+      </c>
+      <c r="K5" s="66" t="s">
+        <v>451</v>
+      </c>
+      <c r="L5" s="20"/>
+      <c r="M5" s="21"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="33"/>
+      <c r="P5" s="35"/>
+      <c r="Q5" s="35" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="T5" s="3">
+        <f>E16+E17</f>
+        <v>21.204444444444444</v>
+      </c>
+      <c r="U5" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="B6" s="38" t="s">
+        <v>454</v>
+      </c>
+      <c r="C6" s="20"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I6" s="34"/>
+      <c r="J6" s="148" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K6" s="66" t="s">
+        <v>454</v>
+      </c>
+      <c r="L6" s="20"/>
+      <c r="M6" s="21"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="33"/>
+      <c r="P6" s="35"/>
+      <c r="Q6" s="35" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="T6" s="3">
+        <f>(T4+T5)/16</f>
+        <v>2.8162152777777778</v>
+      </c>
+      <c r="U6" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A7" s="20"/>
+      <c r="B7" s="38" t="s">
+        <v>213</v>
+      </c>
+      <c r="C7" s="20">
+        <v>0.67</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E7" s="36">
+        <f>C7*$A$5*2</f>
+        <v>4.3550000000000004</v>
+      </c>
+      <c r="F7" s="33"/>
+      <c r="G7" s="35">
+        <v>10.7</v>
+      </c>
+      <c r="H7" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I7" s="34"/>
+      <c r="J7" s="148" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K7" t="s">
+        <v>291</v>
+      </c>
+      <c r="L7" s="20">
+        <v>0.66</v>
+      </c>
+      <c r="M7" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="N7" s="36">
+        <f t="shared" si="3"/>
+        <v>2.145</v>
+      </c>
+      <c r="O7" s="33"/>
+      <c r="P7" s="35">
+        <v>12.75</v>
+      </c>
+      <c r="Q7" s="35" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A8" s="20"/>
+      <c r="B8" s="38" t="s">
+        <v>214</v>
+      </c>
+      <c r="C8" s="20">
+        <v>0.9</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E8" s="36">
+        <f>C8*$A$5*2</f>
+        <v>5.8500000000000005</v>
+      </c>
+      <c r="F8" s="33">
+        <v>5</v>
+      </c>
+      <c r="G8" s="35">
+        <v>8.0299999999999994</v>
+      </c>
+      <c r="H8" s="35">
+        <f>IF((G8*F8)=0,"",G8*F8)</f>
+        <v>40.15</v>
+      </c>
+      <c r="I8" s="34"/>
+      <c r="J8" s="148" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K8" t="s">
+        <v>292</v>
+      </c>
+      <c r="L8" s="20">
+        <v>0.9</v>
+      </c>
+      <c r="M8" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="N8" s="36">
+        <f t="shared" si="3"/>
+        <v>2.9250000000000003</v>
+      </c>
+      <c r="O8" s="33">
+        <v>5</v>
+      </c>
+      <c r="P8" s="35">
+        <v>10</v>
+      </c>
+      <c r="Q8" s="35">
+        <f t="shared" si="4"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A9" s="20"/>
+      <c r="B9" s="38" t="s">
+        <v>333</v>
+      </c>
+      <c r="C9" s="20">
+        <v>0.93</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E9" s="36">
+        <f>C9*$A$5*2</f>
+        <v>6.0449999999999999</v>
+      </c>
+      <c r="F9" s="33"/>
+      <c r="G9" s="35">
+        <v>6.42</v>
+      </c>
+      <c r="H9" s="35" t="str">
+        <f t="shared" ref="H9:H25" si="5">IF((G9*F9)=0,"",G9*F9)</f>
+        <v/>
+      </c>
+      <c r="I9" s="34"/>
+      <c r="J9" s="148" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K9" t="s">
+        <v>294</v>
+      </c>
+      <c r="L9" s="20">
+        <v>1</v>
+      </c>
+      <c r="M9" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="N9" s="36">
+        <f t="shared" si="3"/>
+        <v>3.25</v>
+      </c>
+      <c r="O9" s="33"/>
+      <c r="P9" s="35">
+        <v>6.6</v>
+      </c>
+      <c r="Q9" s="35" t="str">
+        <f t="shared" ref="Q9:Q12" si="6">IF((P9*O9)=0,"",P9*O9)</f>
+        <v/>
+      </c>
+      <c r="U9" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="V9" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="W9" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="X9" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="Y9" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="Z9" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="AA9" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="AB9" s="2" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A10" s="20"/>
+      <c r="B10" s="38" t="s">
+        <v>334</v>
+      </c>
+      <c r="C10" s="20">
+        <v>1.05</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E10" s="36">
+        <f>C10*$A$5*2</f>
+        <v>6.8250000000000002</v>
+      </c>
+      <c r="F10" s="33"/>
+      <c r="G10" s="35">
+        <v>7.22</v>
+      </c>
+      <c r="H10" s="35" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="I10" s="34"/>
+      <c r="J10" s="148" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K10" t="s">
+        <v>295</v>
+      </c>
+      <c r="L10" s="20">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M10" s="21">
+        <v>7</v>
+      </c>
+      <c r="N10" s="36">
+        <f t="shared" si="3"/>
+        <v>3.5750000000000002</v>
+      </c>
+      <c r="O10" s="33"/>
+      <c r="P10" s="35">
+        <v>6.5</v>
+      </c>
+      <c r="Q10" s="35" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="S10" s="70" t="s">
+        <v>389</v>
+      </c>
+      <c r="T10" s="75">
+        <f>SUM(U10:AB10)</f>
+        <v>23</v>
+      </c>
+      <c r="X10">
+        <v>15</v>
+      </c>
+      <c r="AB10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A11" s="20"/>
+      <c r="B11" s="38" t="s">
+        <v>296</v>
+      </c>
+      <c r="C11" s="20"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="36"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="35">
+        <v>3.96</v>
+      </c>
+      <c r="H11" s="35" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="I11" s="34"/>
+      <c r="J11" s="148" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K11" t="s">
+        <v>296</v>
+      </c>
+      <c r="L11" s="20"/>
+      <c r="M11" s="21"/>
+      <c r="N11" s="36"/>
+      <c r="O11" s="33">
+        <v>1</v>
+      </c>
+      <c r="P11" s="35">
+        <v>5.25</v>
+      </c>
+      <c r="Q11" s="35">
+        <f t="shared" si="6"/>
+        <v>5.25</v>
+      </c>
+      <c r="S11" s="70" t="s">
+        <v>390</v>
+      </c>
+      <c r="T11" s="75">
+        <f t="shared" ref="T11:T17" si="7">SUM(U11:AB11)</f>
+        <v>39</v>
+      </c>
+      <c r="U11">
+        <v>6</v>
+      </c>
+      <c r="V11">
+        <v>15</v>
+      </c>
+      <c r="Z11">
+        <v>4</v>
+      </c>
+      <c r="AA11">
+        <v>6</v>
+      </c>
+      <c r="AB11">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A12" s="20"/>
+      <c r="B12" s="38" t="s">
+        <v>297</v>
+      </c>
+      <c r="C12" s="20"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="33">
+        <v>1</v>
+      </c>
+      <c r="G12" s="35">
+        <v>4.55</v>
+      </c>
+      <c r="H12" s="35">
+        <f t="shared" si="5"/>
+        <v>4.55</v>
+      </c>
+      <c r="I12" s="34"/>
+      <c r="J12" s="148" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K12" t="s">
+        <v>297</v>
+      </c>
+      <c r="L12" s="20"/>
+      <c r="M12" s="21"/>
+      <c r="N12" s="36"/>
+      <c r="O12" s="33"/>
+      <c r="P12" s="35">
+        <v>4.5</v>
+      </c>
+      <c r="Q12" s="35" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="S12" s="71" t="s">
+        <v>402</v>
+      </c>
+      <c r="T12" s="75">
+        <f t="shared" si="7"/>
+        <v>13</v>
+      </c>
+      <c r="U12">
+        <v>3</v>
+      </c>
+      <c r="V12">
+        <v>5</v>
+      </c>
+      <c r="Z12">
+        <v>1</v>
+      </c>
+      <c r="AA12">
+        <v>1</v>
+      </c>
+      <c r="AB12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A13" s="20"/>
+      <c r="B13" s="46" t="s">
+        <v>379</v>
+      </c>
+      <c r="C13" s="20"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="35" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="I13" s="34"/>
+      <c r="J13" s="148" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K13" s="139" t="s">
+        <v>289</v>
+      </c>
+      <c r="L13" s="20"/>
+      <c r="M13" s="21"/>
+      <c r="N13" s="36"/>
+      <c r="O13" s="33"/>
+      <c r="P13" s="35">
+        <v>5</v>
+      </c>
+      <c r="Q13" s="35"/>
+      <c r="S13" s="71" t="s">
+        <v>403</v>
+      </c>
+      <c r="T13" s="75">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="X13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="20"/>
+      <c r="B14" s="50" t="s">
+        <v>382</v>
+      </c>
+      <c r="C14" s="20"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="33">
+        <v>2</v>
+      </c>
+      <c r="G14" s="35"/>
+      <c r="H14" s="35" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="I14" s="34"/>
+      <c r="J14" s="148" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K14" s="140" t="s">
+        <v>316</v>
+      </c>
+      <c r="L14" s="20"/>
+      <c r="M14" s="21"/>
+      <c r="N14" s="36"/>
+      <c r="O14" s="33">
+        <v>2</v>
+      </c>
+      <c r="P14" s="35"/>
+      <c r="Q14" s="35"/>
+      <c r="S14" s="72" t="s">
+        <v>386</v>
+      </c>
+      <c r="T14" s="75">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="V14">
+        <v>4</v>
+      </c>
+      <c r="AB14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="20"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="H15" s="65">
+        <f>SUM(H3:H14)</f>
+        <v>82.149999999999991</v>
+      </c>
+      <c r="I15" s="34"/>
+      <c r="J15" s="148" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K15" s="66"/>
+      <c r="L15" s="20"/>
+      <c r="M15" s="21"/>
+      <c r="N15" s="36"/>
+      <c r="O15" s="33"/>
+      <c r="P15" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q15" s="65">
+        <f>SUM(Q3:Q14)</f>
+        <v>90.875</v>
+      </c>
+      <c r="S15" s="73" t="s">
+        <v>354</v>
+      </c>
+      <c r="T15" s="75">
+        <f t="shared" si="7"/>
+        <v>32</v>
+      </c>
+      <c r="W15">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="B16" s="38" t="s">
+        <v>275</v>
+      </c>
+      <c r="C16" s="20">
+        <v>6</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E16" s="36">
+        <f>C16*$A$18</f>
+        <v>17.333333333333332</v>
+      </c>
+      <c r="F16" s="33">
+        <v>2.5</v>
+      </c>
+      <c r="G16" s="35">
+        <v>14.98</v>
+      </c>
+      <c r="H16" s="35">
+        <f t="shared" si="5"/>
+        <v>37.450000000000003</v>
+      </c>
+      <c r="I16" s="34"/>
+      <c r="J16" s="147" t="str">
+        <f t="shared" si="2"/>
+        <v>Under Quilt</v>
+      </c>
+      <c r="K16" s="66" t="s">
+        <v>276</v>
+      </c>
+      <c r="L16" s="20">
+        <v>5</v>
+      </c>
+      <c r="M16" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="N16" s="36"/>
+      <c r="O16" s="33">
+        <v>2.5</v>
+      </c>
+      <c r="P16" s="35">
+        <v>14.25</v>
+      </c>
+      <c r="Q16" s="35">
+        <f t="shared" si="4"/>
+        <v>35.625</v>
+      </c>
+      <c r="S16" s="74" t="s">
+        <v>394</v>
+      </c>
+      <c r="T16" s="75">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="Y16">
+        <v>1</v>
+      </c>
+      <c r="AB16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A17" s="20" t="s">
+        <v>317</v>
+      </c>
+      <c r="B17" s="38" t="s">
+        <v>213</v>
+      </c>
+      <c r="C17" s="20">
+        <v>0.67</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E17" s="36">
+        <f>C17*$A$18*2</f>
+        <v>3.8711111111111114</v>
+      </c>
+      <c r="F17" s="33"/>
+      <c r="G17" s="35">
+        <v>10.7</v>
+      </c>
+      <c r="H17" s="35" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="I17" s="34"/>
+      <c r="J17" s="148" t="str">
+        <f t="shared" si="2"/>
+        <v>78x48</v>
+      </c>
+      <c r="K17" s="66" t="s">
+        <v>291</v>
+      </c>
+      <c r="L17" s="20">
+        <v>0.66</v>
+      </c>
+      <c r="M17" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="N17" s="36">
+        <f t="shared" ref="N17:N18" si="8">L17*$A$5</f>
+        <v>2.145</v>
+      </c>
+      <c r="O17" s="33"/>
+      <c r="P17" s="35">
+        <v>12.75</v>
+      </c>
+      <c r="Q17" s="35" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="S17" s="74" t="s">
+        <v>400</v>
+      </c>
+      <c r="T17" s="75">
+        <f t="shared" si="7"/>
+        <v>17</v>
+      </c>
+      <c r="Y17">
+        <v>2</v>
+      </c>
+      <c r="AB17">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A18" s="37">
+        <f>(78*48)/(36*36)</f>
+        <v>2.8888888888888888</v>
+      </c>
+      <c r="B18" s="38" t="s">
+        <v>214</v>
+      </c>
+      <c r="C18" s="20">
+        <v>0.9</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E18" s="36">
+        <f>C18*$A$18*2</f>
+        <v>5.2</v>
+      </c>
+      <c r="F18" s="33">
+        <v>5</v>
+      </c>
+      <c r="G18" s="35">
+        <v>8.0299999999999994</v>
+      </c>
+      <c r="H18" s="35">
+        <f t="shared" si="5"/>
+        <v>40.15</v>
+      </c>
+      <c r="I18" s="34"/>
+      <c r="J18" s="148">
+        <f t="shared" si="2"/>
+        <v>2.8888888888888888</v>
+      </c>
+      <c r="K18" s="66" t="s">
+        <v>292</v>
+      </c>
+      <c r="L18" s="20">
+        <v>0.9</v>
+      </c>
+      <c r="M18" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="N18" s="36">
+        <f t="shared" si="8"/>
+        <v>2.9250000000000003</v>
+      </c>
+      <c r="O18" s="33">
+        <v>5</v>
+      </c>
+      <c r="P18" s="35">
+        <v>10</v>
+      </c>
+      <c r="Q18" s="35">
+        <f t="shared" si="4"/>
+        <v>50</v>
+      </c>
+      <c r="S18" s="74"/>
+      <c r="T18" s="75"/>
+    </row>
+    <row r="19" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="38" t="s">
+        <v>79</v>
+      </c>
+      <c r="C19" s="20"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="33">
+        <v>1</v>
+      </c>
+      <c r="G19" s="35">
+        <v>3.96</v>
+      </c>
+      <c r="H19" s="35">
+        <f t="shared" si="5"/>
+        <v>3.96</v>
+      </c>
+      <c r="I19" s="34"/>
+      <c r="J19" s="148" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K19" s="66" t="s">
+        <v>335</v>
+      </c>
+      <c r="L19" s="20"/>
+      <c r="M19" s="21"/>
+      <c r="N19" s="36"/>
+      <c r="O19" s="33">
+        <v>1</v>
+      </c>
+      <c r="P19" s="35">
+        <v>4.5</v>
+      </c>
+      <c r="Q19" s="35">
+        <f t="shared" si="4"/>
+        <v>4.5</v>
+      </c>
+      <c r="S19" s="107" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A20" s="20"/>
+      <c r="B20" s="38" t="s">
+        <v>326</v>
+      </c>
+      <c r="C20" s="20">
+        <v>49.9</v>
+      </c>
+      <c r="D20" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="G20" s="35">
+        <v>4.01</v>
+      </c>
+      <c r="H20" s="35" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="I20" s="34"/>
+      <c r="J20" s="148" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K20" s="66" t="s">
+        <v>326</v>
+      </c>
+      <c r="L20" s="20">
+        <v>6.6</v>
+      </c>
+      <c r="M20" s="21" t="s">
+        <v>323</v>
+      </c>
+      <c r="N20" s="36"/>
+      <c r="O20" s="33"/>
+      <c r="P20" s="35">
+        <v>6.25</v>
+      </c>
+      <c r="Q20" s="35" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="R20" s="5"/>
+      <c r="S20" s="76" t="s">
+        <v>18</v>
+      </c>
+      <c r="T20" s="77" t="s">
+        <v>65</v>
+      </c>
+      <c r="U20" s="78" t="s">
+        <v>391</v>
+      </c>
+      <c r="V20" s="79"/>
+      <c r="W20" s="80"/>
+    </row>
+    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A21" s="20"/>
+      <c r="B21" s="38" t="s">
+        <v>321</v>
+      </c>
+      <c r="C21" s="20">
+        <v>43.94</v>
+      </c>
+      <c r="D21" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="E21" s="36"/>
+      <c r="F21" s="33"/>
+      <c r="G21" s="35">
+        <v>3.16</v>
+      </c>
+      <c r="H21" s="35" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="I21" s="34"/>
+      <c r="J21" s="148" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K21" s="66" t="s">
+        <v>325</v>
+      </c>
+      <c r="L21" s="20">
+        <v>5</v>
+      </c>
+      <c r="M21" s="21" t="s">
+        <v>323</v>
+      </c>
+      <c r="N21" s="36"/>
+      <c r="O21" s="33"/>
+      <c r="P21" s="35">
+        <v>5.75</v>
+      </c>
+      <c r="Q21" s="35" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="R21" s="5"/>
+      <c r="S21" s="81" t="str">
+        <f>A3</f>
+        <v>Top Quilt</v>
+      </c>
+      <c r="T21" s="82">
+        <f>H15</f>
+        <v>82.149999999999991</v>
+      </c>
+      <c r="U21" s="83">
+        <v>4</v>
+      </c>
+      <c r="V21" s="84" t="s">
+        <v>280</v>
+      </c>
+      <c r="W21" s="85"/>
+    </row>
+    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A22" s="20"/>
+      <c r="B22" s="38" t="s">
+        <v>322</v>
+      </c>
+      <c r="C22" s="20">
+        <v>27.49</v>
+      </c>
+      <c r="D22" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="E22" s="36"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="35">
+        <v>2.25</v>
+      </c>
+      <c r="H22" s="35" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="I22" s="34"/>
+      <c r="J22" s="148" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K22" s="66" t="s">
+        <v>324</v>
+      </c>
+      <c r="L22" s="20">
+        <v>3.6</v>
+      </c>
+      <c r="M22" s="21" t="s">
+        <v>323</v>
+      </c>
+      <c r="N22" s="36"/>
+      <c r="O22" s="33"/>
+      <c r="P22" s="35">
+        <v>5.25</v>
+      </c>
+      <c r="Q22" s="35" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="R22" s="5"/>
+      <c r="S22" s="81" t="str">
+        <f>A16</f>
+        <v>Under Quilt</v>
+      </c>
+      <c r="T22" s="82">
+        <f>H26</f>
+        <v>82.999999999999986</v>
+      </c>
+      <c r="U22" s="83">
+        <v>5</v>
+      </c>
+      <c r="V22" s="84" t="s">
+        <v>280</v>
+      </c>
+      <c r="W22" s="85"/>
+    </row>
+    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A23" s="20"/>
+      <c r="B23" s="46" t="s">
+        <v>381</v>
+      </c>
+      <c r="C23" s="20"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="33"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="35" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="I23" s="34"/>
+      <c r="J23" s="148" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K23" s="139" t="s">
+        <v>289</v>
+      </c>
+      <c r="L23" s="20"/>
+      <c r="M23" s="21"/>
+      <c r="N23" s="36"/>
+      <c r="O23" s="33"/>
+      <c r="P23" s="35"/>
+      <c r="Q23" s="35" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="R23" s="5"/>
+      <c r="S23" s="86" t="str">
+        <f>A27</f>
+        <v>Griz Ariel Hammock</v>
+      </c>
+      <c r="T23" s="87">
+        <f>H36</f>
+        <v>38.440000000000005</v>
+      </c>
+      <c r="U23" s="88">
+        <v>3</v>
+      </c>
+      <c r="V23" s="89" t="s">
+        <v>280</v>
+      </c>
+      <c r="W23" s="90"/>
+    </row>
+    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A24" s="20"/>
+      <c r="B24" s="50" t="s">
+        <v>383</v>
+      </c>
+      <c r="C24" s="20"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="33"/>
+      <c r="G24" s="35"/>
+      <c r="H24" s="35" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="I24" s="34"/>
+      <c r="J24" s="148" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K24" s="140" t="s">
+        <v>316</v>
+      </c>
+      <c r="L24" s="20"/>
+      <c r="M24" s="21"/>
+      <c r="N24" s="36"/>
+      <c r="O24" s="33"/>
+      <c r="P24" s="35"/>
+      <c r="Q24" s="35" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="R24" s="167" t="s">
+        <v>482</v>
+      </c>
+      <c r="S24" s="91" t="str">
+        <f>A37</f>
+        <v>Gathered End Hammock</v>
+      </c>
+      <c r="T24" s="92">
+        <f>H41</f>
+        <v>40.340000000000003</v>
+      </c>
+      <c r="U24" s="93">
+        <v>8</v>
+      </c>
+      <c r="V24" s="94" t="s">
+        <v>280</v>
+      </c>
+      <c r="W24" s="95"/>
+    </row>
+    <row r="25" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="20"/>
+      <c r="B25" s="38" t="s">
+        <v>380</v>
+      </c>
+      <c r="C25" s="20">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="D25" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="E25" s="36"/>
+      <c r="F25" s="33">
+        <v>4</v>
+      </c>
+      <c r="G25" s="35">
+        <v>0.36</v>
+      </c>
+      <c r="H25" s="35">
+        <f t="shared" si="5"/>
+        <v>1.44</v>
+      </c>
+      <c r="I25" s="34"/>
+      <c r="J25" s="148" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K25" s="66" t="s">
+        <v>376</v>
+      </c>
+      <c r="L25" s="20"/>
+      <c r="M25" s="21"/>
+      <c r="N25" s="36"/>
+      <c r="O25" s="33">
+        <v>1</v>
+      </c>
+      <c r="P25" s="35">
+        <v>5</v>
+      </c>
+      <c r="Q25" s="35">
+        <f t="shared" ref="Q25" si="9">IF((P25*O25)=0,"",P25*O25)</f>
+        <v>5</v>
+      </c>
+      <c r="R25" s="167" t="s">
+        <v>482</v>
+      </c>
+      <c r="S25" s="91" t="str">
+        <f>A42</f>
+        <v>Bug Net</v>
+      </c>
+      <c r="T25" s="92">
+        <f>H47</f>
+        <v>29.189999999999998</v>
+      </c>
+      <c r="U25" s="93">
+        <v>9</v>
+      </c>
+      <c r="V25" s="94" t="s">
+        <v>280</v>
+      </c>
+      <c r="W25" s="95"/>
+    </row>
+    <row r="26" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="20"/>
+      <c r="B26" s="38"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="36"/>
+      <c r="F26" s="33"/>
+      <c r="G26" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="H26" s="65">
+        <f>SUM(H16:H25)</f>
+        <v>82.999999999999986</v>
+      </c>
+      <c r="I26" s="34"/>
+      <c r="J26" s="148" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K26" s="66"/>
+      <c r="L26" s="20"/>
+      <c r="M26" s="21"/>
+      <c r="N26" s="36"/>
+      <c r="O26" s="33"/>
+      <c r="P26" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q26" s="65">
+        <f>SUM(Q16:Q25)</f>
+        <v>95.125</v>
+      </c>
+      <c r="R26" s="167" t="s">
+        <v>482</v>
+      </c>
+      <c r="S26" s="96" t="str">
+        <f>A49</f>
+        <v>Back Pack</v>
+      </c>
+      <c r="T26" s="97">
+        <f>Q77+H77</f>
+        <v>65.52000000000001</v>
+      </c>
+      <c r="U26" s="98">
+        <v>6</v>
+      </c>
+      <c r="V26" s="99" t="s">
+        <v>434</v>
+      </c>
+      <c r="W26" s="100"/>
+      <c r="X26" s="30"/>
+    </row>
+    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A27" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B27" s="38" t="s">
+        <v>279</v>
+      </c>
+      <c r="C27" s="20">
+        <v>1.6</v>
+      </c>
+      <c r="D27" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E27" s="36">
+        <f>$A$29*C27</f>
+        <v>5.7925925925925927</v>
+      </c>
+      <c r="F27" s="33">
+        <v>3</v>
+      </c>
+      <c r="G27" s="35">
+        <v>6.42</v>
+      </c>
+      <c r="H27" s="35">
+        <f t="shared" si="1"/>
+        <v>19.259999999999998</v>
+      </c>
+      <c r="I27" s="34"/>
+      <c r="J27" s="147" t="str">
+        <f t="shared" si="2"/>
+        <v>Griz Ariel Hammock</v>
+      </c>
+      <c r="K27" s="66" t="s">
+        <v>290</v>
+      </c>
+      <c r="L27" s="20">
+        <v>1.6</v>
+      </c>
+      <c r="M27" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="N27" s="36"/>
+      <c r="O27" s="33">
+        <v>3</v>
+      </c>
+      <c r="P27" s="35">
+        <v>7.5</v>
+      </c>
+      <c r="Q27" s="35">
+        <f t="shared" si="4"/>
+        <v>22.5</v>
+      </c>
+      <c r="R27" s="167" t="s">
+        <v>482</v>
+      </c>
+      <c r="S27" s="101" t="str">
+        <f>A86</f>
+        <v>Sleeping Bag Liner</v>
+      </c>
+      <c r="T27" s="102">
+        <f>H90</f>
+        <v>25.36</v>
+      </c>
+      <c r="U27" s="103">
+        <v>10</v>
+      </c>
+      <c r="V27" s="104" t="s">
+        <v>280</v>
+      </c>
+      <c r="W27" s="105"/>
+    </row>
+    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A28" s="20" t="s">
+        <v>315</v>
+      </c>
+      <c r="B28" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="C28" s="20">
+        <v>1.2</v>
+      </c>
+      <c r="D28" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E28" s="36">
+        <f>$A$29*C28</f>
+        <v>4.3444444444444441</v>
+      </c>
+      <c r="F28" s="33"/>
+      <c r="G28" s="35">
+        <v>6.69</v>
+      </c>
+      <c r="H28" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I28" s="34"/>
+      <c r="J28" s="148" t="str">
+        <f t="shared" si="2"/>
+        <v>102x46</v>
+      </c>
+      <c r="K28" s="66"/>
+      <c r="L28" s="20"/>
+      <c r="M28" s="21"/>
+      <c r="N28" s="36"/>
+      <c r="O28" s="33"/>
+      <c r="P28" s="35"/>
+      <c r="Q28" s="35" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="R28" s="167" t="s">
+        <v>482</v>
+      </c>
+      <c r="S28" s="121" t="str">
+        <f>A91</f>
+        <v>Food Bag (12.5 x 22)</v>
+      </c>
+      <c r="T28" s="122">
+        <f>H95</f>
+        <v>27.560000000000002</v>
+      </c>
+      <c r="U28" s="123">
+        <v>11</v>
+      </c>
+      <c r="V28" s="118" t="s">
+        <v>280</v>
+      </c>
+      <c r="W28" s="124"/>
+    </row>
+    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A29" s="37">
+        <f>(102*46)/(36*36)</f>
+        <v>3.6203703703703702</v>
+      </c>
+      <c r="B29" s="38" t="s">
+        <v>79</v>
+      </c>
+      <c r="C29" s="20"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="36"/>
+      <c r="F29" s="33">
+        <v>1</v>
+      </c>
+      <c r="G29" s="35">
+        <v>3.96</v>
+      </c>
+      <c r="H29" s="35">
+        <f t="shared" si="1"/>
+        <v>3.96</v>
+      </c>
+      <c r="I29" s="34"/>
+      <c r="J29" s="148">
+        <f t="shared" si="2"/>
+        <v>3.6203703703703702</v>
+      </c>
+      <c r="K29" s="66" t="s">
+        <v>79</v>
+      </c>
+      <c r="L29" s="20"/>
+      <c r="M29" s="21"/>
+      <c r="N29" s="36"/>
+      <c r="O29" s="33">
+        <v>1</v>
+      </c>
+      <c r="P29" s="35">
+        <v>5.25</v>
+      </c>
+      <c r="Q29" s="35">
+        <f t="shared" si="4"/>
+        <v>5.25</v>
+      </c>
+      <c r="R29" s="167" t="s">
+        <v>482</v>
+      </c>
+      <c r="S29" s="121" t="str">
+        <f>A98</f>
+        <v>Rain Kilt (30L x 48W)</v>
+      </c>
+      <c r="T29" s="122">
+        <f>H102</f>
+        <v>48.163000000000004</v>
+      </c>
+      <c r="U29" s="123">
+        <v>12</v>
+      </c>
+      <c r="V29" s="118" t="s">
+        <v>280</v>
+      </c>
+      <c r="W29" s="124"/>
+    </row>
+    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A30" s="20" t="s">
+        <v>387</v>
+      </c>
+      <c r="B30" s="38" t="s">
+        <v>322</v>
+      </c>
+      <c r="C30" s="20">
+        <v>27.49</v>
+      </c>
+      <c r="D30" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="E30" s="36"/>
+      <c r="F30" s="33"/>
+      <c r="G30" s="35">
+        <v>2.25</v>
+      </c>
+      <c r="H30" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I30" s="34"/>
+      <c r="J30" s="148" t="str">
+        <f t="shared" si="2"/>
+        <v>with half bug net</v>
+      </c>
+      <c r="K30" s="66" t="s">
+        <v>324</v>
+      </c>
+      <c r="L30" s="20">
+        <v>3.6</v>
+      </c>
+      <c r="M30" s="21" t="s">
+        <v>323</v>
+      </c>
+      <c r="N30" s="36"/>
+      <c r="O30" s="33"/>
+      <c r="P30" s="35">
+        <v>5.25</v>
+      </c>
+      <c r="Q30" s="35" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="R30" s="167" t="s">
+        <v>482</v>
+      </c>
+      <c r="S30" s="101" t="str">
+        <f>A103</f>
+        <v>Rain Pants</v>
+      </c>
+      <c r="T30" s="102">
+        <f>H108</f>
+        <v>17.88</v>
+      </c>
+      <c r="U30" s="103">
+        <v>7</v>
+      </c>
+      <c r="V30" s="104" t="s">
+        <v>280</v>
+      </c>
+      <c r="W30" s="105"/>
+    </row>
+    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A31" s="20"/>
+      <c r="B31" s="52" t="s">
+        <v>348</v>
+      </c>
+      <c r="C31">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D31" t="s">
+        <v>161</v>
+      </c>
+      <c r="F31">
+        <v>4</v>
+      </c>
+      <c r="G31" s="35">
+        <v>1.5</v>
+      </c>
+      <c r="H31" s="35">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="I31" s="34"/>
+      <c r="J31" s="148" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K31" s="66"/>
+      <c r="L31" s="20"/>
+      <c r="M31" s="21"/>
+      <c r="N31" s="36"/>
+      <c r="O31" s="33"/>
+      <c r="P31" s="35"/>
+      <c r="Q31" s="35" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="R31" s="167" t="s">
+        <v>482</v>
+      </c>
+      <c r="S31" s="86" t="str">
+        <f>A78</f>
+        <v>Amsteel 7/64</v>
+      </c>
+      <c r="T31" s="87">
+        <f>H81</f>
+        <v>24.6</v>
+      </c>
+      <c r="U31" s="88">
+        <v>1</v>
+      </c>
+      <c r="V31" s="89" t="s">
+        <v>280</v>
+      </c>
+      <c r="W31" s="90"/>
+    </row>
+    <row r="32" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A32" s="20"/>
+      <c r="B32" s="52" t="s">
+        <v>437</v>
+      </c>
+      <c r="G32" s="35"/>
+      <c r="H32" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I32" s="34"/>
+      <c r="J32" s="148" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K32" s="118" t="s">
+        <v>437</v>
+      </c>
+      <c r="L32" s="20"/>
+      <c r="M32" s="21"/>
+      <c r="N32" s="36"/>
+      <c r="O32" s="33"/>
+      <c r="P32" s="35"/>
+      <c r="Q32" s="35" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="R32" s="167" t="s">
+        <v>482</v>
+      </c>
+      <c r="S32" s="86" t="str">
+        <f>A82</f>
+        <v>Shock Cord</v>
+      </c>
+      <c r="T32" s="87">
+        <f>H85</f>
+        <v>9.1</v>
+      </c>
+      <c r="U32" s="88">
+        <v>2</v>
+      </c>
+      <c r="V32" s="89" t="s">
+        <v>280</v>
+      </c>
+      <c r="W32" s="90"/>
+    </row>
+    <row r="33" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="20"/>
+      <c r="B33" s="53" t="s">
+        <v>355</v>
+      </c>
+      <c r="F33" s="33"/>
+      <c r="G33" s="35">
+        <v>6.15</v>
+      </c>
+      <c r="H33" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I33" s="34"/>
+      <c r="J33" s="148" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K33" s="141" t="s">
+        <v>354</v>
+      </c>
+      <c r="L33" s="20"/>
+      <c r="M33" s="21"/>
+      <c r="N33" s="36"/>
+      <c r="O33" s="33"/>
+      <c r="P33" s="35">
+        <v>7.5</v>
+      </c>
+      <c r="Q33" s="35" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="R33" s="167" t="s">
+        <v>482</v>
+      </c>
+      <c r="S33" s="150" t="str">
+        <f>A113</f>
+        <v>Pullover/hoodie</v>
+      </c>
+      <c r="T33" s="151">
+        <f>Q113</f>
+        <v>54.5</v>
+      </c>
+      <c r="U33" s="152">
+        <v>13</v>
+      </c>
+      <c r="V33" s="153" t="s">
+        <v>470</v>
+      </c>
+      <c r="W33" s="106"/>
+    </row>
+    <row r="34" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="20"/>
+      <c r="B34" s="38" t="s">
+        <v>352</v>
+      </c>
+      <c r="C34" s="20">
+        <v>0.67</v>
+      </c>
+      <c r="D34" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E34" s="36"/>
+      <c r="F34" s="33">
+        <v>2</v>
+      </c>
+      <c r="G34" s="35">
+        <v>4.17</v>
+      </c>
+      <c r="H34" s="35">
+        <f t="shared" si="1"/>
+        <v>8.34</v>
+      </c>
+      <c r="I34" s="34"/>
+      <c r="J34" s="148" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K34" s="66" t="s">
+        <v>319</v>
+      </c>
+      <c r="L34" s="20">
+        <v>0.67</v>
+      </c>
+      <c r="M34" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="N34" s="36"/>
+      <c r="O34" s="33">
+        <v>2</v>
+      </c>
+      <c r="P34" s="35">
+        <v>5.5</v>
+      </c>
+      <c r="Q34" s="35">
+        <f t="shared" si="4"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="20"/>
+      <c r="B35" s="38" t="s">
+        <v>410</v>
+      </c>
+      <c r="C35" s="20">
+        <v>0.3</v>
+      </c>
+      <c r="D35" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="E35" s="36"/>
+      <c r="F35" s="33">
+        <v>4</v>
+      </c>
+      <c r="G35" s="35">
+        <v>0.22</v>
+      </c>
+      <c r="H35" s="35">
+        <f t="shared" si="1"/>
+        <v>0.88</v>
+      </c>
+      <c r="I35" s="34"/>
+      <c r="J35" s="148" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K35" s="56" t="s">
+        <v>412</v>
+      </c>
+      <c r="L35" s="20"/>
+      <c r="M35" s="21"/>
+      <c r="N35" s="36"/>
+      <c r="O35" s="33">
+        <v>1</v>
+      </c>
+      <c r="P35" s="35">
+        <v>4.25</v>
+      </c>
+      <c r="Q35" s="35">
+        <f t="shared" si="4"/>
+        <v>4.25</v>
+      </c>
+      <c r="S35" s="116" t="s">
+        <v>65</v>
+      </c>
+      <c r="T35" s="117">
+        <f>SUM(T21:T33)</f>
+        <v>545.80300000000011</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="20"/>
+      <c r="B36" s="55"/>
+      <c r="F36" s="33"/>
+      <c r="G36" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="H36" s="65">
+        <f>SUM(H27:H35)</f>
+        <v>38.440000000000005</v>
+      </c>
+      <c r="I36" s="34"/>
+      <c r="J36" s="148" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K36" s="56"/>
+      <c r="L36" s="20"/>
+      <c r="M36" s="21"/>
+      <c r="N36" s="36"/>
+      <c r="O36" s="33"/>
+      <c r="P36" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q36" s="65">
+        <f>SUM(Q27:Q35)</f>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="B37" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="C37" s="20">
+        <v>1.2</v>
+      </c>
+      <c r="D37" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E37" s="36">
+        <f>$A$39*C37</f>
+        <v>6.1111111111111107</v>
+      </c>
+      <c r="F37" s="33">
+        <v>4</v>
+      </c>
+      <c r="G37" s="35">
+        <v>6.42</v>
+      </c>
+      <c r="H37" s="35">
+        <f t="shared" si="1"/>
+        <v>25.68</v>
+      </c>
+      <c r="I37" s="34"/>
+      <c r="J37" s="147" t="str">
+        <f t="shared" si="2"/>
+        <v>Gathered End Hammock</v>
+      </c>
+      <c r="K37" s="66" t="s">
+        <v>290</v>
+      </c>
+      <c r="L37" s="20">
+        <v>1.6</v>
+      </c>
+      <c r="M37" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="N37" s="36"/>
+      <c r="O37" s="33">
+        <v>4</v>
+      </c>
+      <c r="P37" s="35">
+        <v>7.5</v>
+      </c>
+      <c r="Q37" s="35">
+        <f t="shared" si="4"/>
+        <v>30</v>
+      </c>
+      <c r="S37" s="108" t="s">
+        <v>405</v>
+      </c>
+      <c r="T37" s="109">
+        <f>T31+T32+T23</f>
+        <v>72.140000000000015</v>
+      </c>
+      <c r="U37" s="110" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="20" t="s">
+        <v>413</v>
+      </c>
+      <c r="B38" s="38" t="s">
+        <v>279</v>
+      </c>
+      <c r="C38" s="20">
+        <v>1.6</v>
+      </c>
+      <c r="D38" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E38" s="36">
+        <f>$A$39*C38</f>
+        <v>8.1481481481481488</v>
+      </c>
+      <c r="F38" s="33"/>
+      <c r="G38" s="35">
+        <v>6.69</v>
+      </c>
+      <c r="H38" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I38" s="34"/>
+      <c r="J38" s="148" t="str">
+        <f t="shared" si="2"/>
+        <v>120x55</v>
+      </c>
+      <c r="K38" s="66"/>
+      <c r="L38" s="20"/>
+      <c r="M38" s="21"/>
+      <c r="N38" s="36"/>
+      <c r="O38" s="33"/>
+      <c r="P38" s="35"/>
+      <c r="Q38" s="35" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="S38" s="111" t="s">
+        <v>407</v>
+      </c>
+      <c r="T38" s="82">
+        <f>T21+T22</f>
+        <v>165.14999999999998</v>
+      </c>
+      <c r="U38" s="112" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="37">
+        <f>(120*55)/(36*36)</f>
+        <v>5.0925925925925926</v>
+      </c>
+      <c r="B39" s="38" t="s">
+        <v>79</v>
+      </c>
+      <c r="C39" s="20"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="36"/>
+      <c r="F39" s="33">
+        <v>1</v>
+      </c>
+      <c r="G39" s="35">
+        <v>3.96</v>
+      </c>
+      <c r="H39" s="35">
+        <f t="shared" si="1"/>
+        <v>3.96</v>
+      </c>
+      <c r="I39" s="34"/>
+      <c r="J39" s="148">
+        <f t="shared" si="2"/>
+        <v>5.0925925925925926</v>
+      </c>
+      <c r="K39" s="66" t="s">
+        <v>79</v>
+      </c>
+      <c r="L39" s="20"/>
+      <c r="M39" s="21"/>
+      <c r="N39" s="36"/>
+      <c r="O39" s="33">
+        <v>1</v>
+      </c>
+      <c r="P39" s="35">
+        <v>5.25</v>
+      </c>
+      <c r="Q39" s="35">
+        <f t="shared" si="4"/>
+        <v>5.25</v>
+      </c>
+      <c r="S39" s="111" t="s">
+        <v>406</v>
+      </c>
+      <c r="T39" s="97">
+        <f>T26+T33</f>
+        <v>120.02000000000001</v>
+      </c>
+      <c r="U39" s="114" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="37"/>
+      <c r="B40" s="52" t="s">
+        <v>353</v>
+      </c>
+      <c r="C40" s="20">
+        <v>27</v>
+      </c>
+      <c r="D40" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="E40" s="36"/>
+      <c r="F40" s="33">
+        <v>1</v>
+      </c>
+      <c r="G40" s="35">
+        <v>10.7</v>
+      </c>
+      <c r="H40" s="35">
+        <f t="shared" si="1"/>
+        <v>10.7</v>
+      </c>
+      <c r="I40" s="34"/>
+      <c r="J40" s="148" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="Q40" s="35" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="S40" s="111" t="s">
+        <v>406</v>
+      </c>
+      <c r="T40" s="102">
+        <f>T27+T30</f>
+        <v>43.239999999999995</v>
+      </c>
+      <c r="U40" s="113" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="37"/>
+      <c r="B41" s="54"/>
+      <c r="C41" s="20"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="36"/>
+      <c r="F41" s="33"/>
+      <c r="G41" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="H41" s="63">
+        <f>SUM(H37:H40)</f>
+        <v>40.340000000000003</v>
+      </c>
+      <c r="I41" s="34"/>
+      <c r="J41" s="148" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="P41" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q41" s="63">
+        <f>SUM(Q37:Q40)</f>
+        <v>35.25</v>
+      </c>
+      <c r="S41" s="111" t="s">
+        <v>408</v>
+      </c>
+      <c r="T41" s="92">
+        <f>T25+T24</f>
+        <v>69.53</v>
+      </c>
+      <c r="U41" s="125" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="B42" s="38" t="s">
+        <v>352</v>
+      </c>
+      <c r="C42" s="20">
+        <v>0.67</v>
+      </c>
+      <c r="D42" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E42" s="36">
+        <f>C42*$A$44</f>
+        <v>5.9555555555555566</v>
+      </c>
+      <c r="F42" s="33">
+        <v>7</v>
+      </c>
+      <c r="G42" s="35">
+        <v>4.17</v>
+      </c>
+      <c r="H42" s="35">
+        <f t="shared" si="1"/>
+        <v>29.189999999999998</v>
+      </c>
+      <c r="I42" s="34"/>
+      <c r="J42" s="147" t="str">
+        <f t="shared" si="2"/>
+        <v>Bug Net</v>
+      </c>
+      <c r="K42" s="66" t="s">
+        <v>319</v>
+      </c>
+      <c r="L42" s="20">
+        <v>0.67</v>
+      </c>
+      <c r="M42" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="N42" s="36"/>
+      <c r="O42" s="33">
+        <v>7</v>
+      </c>
+      <c r="P42" s="35">
+        <v>5.5</v>
+      </c>
+      <c r="Q42" s="35">
+        <f t="shared" ref="Q42" si="10">IF((P42*O42)=0,"",P42*O42)</f>
+        <v>38.5</v>
+      </c>
+      <c r="S42" s="115" t="s">
+        <v>409</v>
+      </c>
+      <c r="T42" s="119">
+        <f>T28+T29</f>
+        <v>75.723000000000013</v>
+      </c>
+      <c r="U42" s="120" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A43" s="20" t="s">
+        <v>446</v>
+      </c>
+      <c r="B43" s="38" t="s">
+        <v>320</v>
+      </c>
+      <c r="C43" s="20">
+        <v>0.9</v>
+      </c>
+      <c r="D43" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E43" s="36">
+        <f>C43*$A$44</f>
+        <v>8</v>
+      </c>
+      <c r="F43" s="33"/>
+      <c r="G43" s="35">
+        <v>4.17</v>
+      </c>
+      <c r="H43" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I43" s="34"/>
+      <c r="J43" s="148" t="str">
+        <f t="shared" si="2"/>
+        <v>120 x 96</v>
+      </c>
+      <c r="K43" s="66" t="s">
+        <v>320</v>
+      </c>
+      <c r="L43" s="20">
+        <v>0.9</v>
+      </c>
+      <c r="M43" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="N43" s="36"/>
+      <c r="O43" s="33"/>
+      <c r="P43" s="35">
+        <v>5</v>
+      </c>
+      <c r="Q43" s="35" t="str">
+        <f t="shared" ref="Q43" si="11">IF((P43*O43)=0,"",P43*O43)</f>
+        <v/>
+      </c>
+      <c r="S43" s="128" t="s">
+        <v>435</v>
+      </c>
+      <c r="T43" s="30">
+        <f>SUM(T37:T42)</f>
+        <v>545.80300000000011</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A44" s="20">
+        <f>(120*96)/(36*36)</f>
+        <v>8.8888888888888893</v>
+      </c>
+      <c r="B44" s="38"/>
+      <c r="H44" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I44" s="34"/>
+      <c r="J44" s="148">
+        <f t="shared" si="2"/>
+        <v>8.8888888888888893</v>
+      </c>
+      <c r="K44" s="66" t="s">
+        <v>318</v>
+      </c>
+      <c r="L44" s="20">
+        <v>0.5</v>
+      </c>
+      <c r="M44" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="N44" s="36">
+        <f>(55*36)/(36*36)</f>
+        <v>1.5277777777777777</v>
+      </c>
+      <c r="O44" s="33">
+        <v>7</v>
+      </c>
+      <c r="P44" s="35">
+        <v>8.75</v>
+      </c>
+      <c r="Q44" s="35"/>
+      <c r="T44" s="30"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="20"/>
+      <c r="B45" s="46" t="s">
+        <v>377</v>
+      </c>
+      <c r="C45" s="20"/>
+      <c r="D45" s="21"/>
+      <c r="E45" s="36"/>
+      <c r="F45" s="33"/>
+      <c r="G45" s="35"/>
+      <c r="H45" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I45" s="34"/>
+      <c r="J45" s="148" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K45" s="139" t="s">
+        <v>289</v>
+      </c>
+      <c r="L45" s="20"/>
+      <c r="M45" s="21"/>
+      <c r="N45" s="36"/>
+      <c r="O45" s="33"/>
+      <c r="P45" s="35"/>
+      <c r="Q45" s="35"/>
+      <c r="T45" s="30"/>
+    </row>
+    <row r="46" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="20"/>
+      <c r="B46" s="50" t="s">
+        <v>378</v>
+      </c>
+      <c r="C46" s="20"/>
+      <c r="D46" s="21"/>
+      <c r="E46" s="36"/>
+      <c r="F46" s="33"/>
+      <c r="G46" s="35"/>
+      <c r="H46" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I46" s="34"/>
+      <c r="J46" s="148" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K46" s="140" t="s">
+        <v>316</v>
+      </c>
+      <c r="L46" s="20"/>
+      <c r="M46" s="21"/>
+      <c r="N46" s="36"/>
+      <c r="O46" s="33"/>
+      <c r="P46" s="35"/>
+      <c r="Q46" s="35"/>
+      <c r="T46" s="30"/>
+    </row>
+    <row r="47" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="20"/>
+      <c r="B47" s="54"/>
+      <c r="C47" s="20"/>
+      <c r="D47" s="21"/>
+      <c r="E47" s="36"/>
+      <c r="F47" s="33"/>
+      <c r="G47" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="H47" s="65">
+        <f>SUM(H42:H46)</f>
+        <v>29.189999999999998</v>
+      </c>
+      <c r="I47" s="34"/>
+      <c r="J47" s="148" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K47" s="66"/>
+      <c r="L47" s="20"/>
+      <c r="M47" s="21"/>
+      <c r="N47" s="36"/>
+      <c r="O47" s="33"/>
+      <c r="P47" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q47" s="65">
+        <f>SUM(Q42:Q46)</f>
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="20"/>
+      <c r="B48" s="54"/>
+      <c r="C48" s="20"/>
+      <c r="D48" s="21"/>
+      <c r="E48" s="36"/>
+      <c r="F48" s="33"/>
+      <c r="G48" s="64"/>
+      <c r="H48" s="145"/>
+      <c r="I48" s="34"/>
+      <c r="J48" s="148"/>
+      <c r="K48" s="66"/>
+      <c r="L48" s="20"/>
+      <c r="M48" s="21"/>
+      <c r="N48" s="36"/>
+      <c r="O48" s="33"/>
+      <c r="P48" s="64"/>
+      <c r="Q48" s="145"/>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A49" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="B49" s="38" t="s">
+        <v>430</v>
+      </c>
+      <c r="C49" s="20">
+        <f>(4.85+5.85)/2</f>
+        <v>5.35</v>
+      </c>
+      <c r="D49" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E49" s="36"/>
+      <c r="F49" s="33"/>
+      <c r="G49" s="35">
+        <v>12.84</v>
+      </c>
+      <c r="H49" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I49" s="34"/>
+      <c r="J49" s="147" t="str">
+        <f t="shared" si="2"/>
+        <v>Back Pack</v>
+      </c>
+      <c r="K49" s="142" t="s">
+        <v>358</v>
+      </c>
+      <c r="L49" s="20">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="M49" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="N49" s="36"/>
+      <c r="O49" s="33">
+        <v>2</v>
+      </c>
+      <c r="P49" s="35">
+        <v>14.5</v>
+      </c>
+      <c r="Q49" s="35">
+        <f t="shared" si="4"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A50" s="60" t="s">
+        <v>419</v>
+      </c>
+      <c r="B50" s="38" t="s">
+        <v>431</v>
+      </c>
+      <c r="C50" s="20">
+        <v>3.2</v>
+      </c>
+      <c r="D50" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E50" s="36"/>
+      <c r="F50" s="33"/>
+      <c r="G50" s="35">
+        <v>5.08</v>
+      </c>
+      <c r="H50" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I50" s="34"/>
+      <c r="J50" s="148" t="str">
+        <f t="shared" si="2"/>
+        <v>* Work on quantities</v>
+      </c>
+      <c r="K50" s="66" t="s">
+        <v>314</v>
+      </c>
+      <c r="L50" s="20">
+        <v>3.2</v>
+      </c>
+      <c r="M50" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="N50" s="36"/>
+      <c r="O50" s="33"/>
+      <c r="P50" s="35">
+        <v>10</v>
+      </c>
+      <c r="Q50" s="35" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B51" s="38" t="s">
+        <v>432</v>
+      </c>
+      <c r="C51" s="20">
+        <v>6.73</v>
+      </c>
+      <c r="D51" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E51" s="36"/>
+      <c r="F51" s="33"/>
+      <c r="G51" s="35">
+        <v>3.75</v>
+      </c>
+      <c r="H51" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I51" s="34"/>
+      <c r="J51" s="148" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K51" s="66" t="s">
+        <v>313</v>
+      </c>
+      <c r="L51" s="20">
+        <v>3.9</v>
+      </c>
+      <c r="M51" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="N51" s="36"/>
+      <c r="O51" s="33"/>
+      <c r="P51" s="35">
+        <v>12.75</v>
+      </c>
+      <c r="Q51" s="35" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B52" s="38" t="s">
+        <v>433</v>
+      </c>
+      <c r="C52" s="20">
+        <v>7.9</v>
+      </c>
+      <c r="D52" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E52" s="36"/>
+      <c r="F52" s="33"/>
+      <c r="G52" s="35">
+        <v>12.84</v>
+      </c>
+      <c r="H52" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I52" s="34"/>
+      <c r="J52" s="148" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K52" s="142" t="s">
+        <v>312</v>
+      </c>
+      <c r="L52" s="20">
+        <v>6.1</v>
+      </c>
+      <c r="M52" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="N52" s="36"/>
+      <c r="O52" s="33"/>
+      <c r="P52" s="35">
+        <v>15</v>
+      </c>
+      <c r="Q52" s="35" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B53" s="38" t="s">
+        <v>335</v>
+      </c>
+      <c r="C53" s="20"/>
+      <c r="D53" s="21"/>
+      <c r="E53" s="36"/>
+      <c r="F53" s="33"/>
+      <c r="G53" s="35">
+        <v>3.96</v>
+      </c>
+      <c r="H53" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I53" s="34"/>
+      <c r="J53" s="148" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K53" s="66" t="s">
+        <v>335</v>
+      </c>
+      <c r="L53" s="20"/>
+      <c r="M53" s="21"/>
+      <c r="N53" s="36"/>
+      <c r="O53" s="33">
+        <v>1</v>
+      </c>
+      <c r="P53" s="35">
+        <v>4.5</v>
+      </c>
+      <c r="Q53" s="35">
+        <f t="shared" si="4"/>
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B54" s="38" t="s">
+        <v>351</v>
+      </c>
+      <c r="C54" s="20">
+        <v>212.5</v>
+      </c>
+      <c r="D54" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="E54" s="36"/>
+      <c r="F54" s="33"/>
+      <c r="G54" s="35">
+        <v>13.91</v>
+      </c>
+      <c r="H54" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I54" s="34"/>
+      <c r="J54" s="148" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K54" s="118" t="s">
+        <v>360</v>
+      </c>
+      <c r="L54" s="20">
+        <v>10</v>
+      </c>
+      <c r="M54" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="N54" s="36"/>
+      <c r="O54" s="33"/>
+      <c r="P54" s="35">
+        <v>14</v>
+      </c>
+      <c r="Q54" s="35" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B55" s="38"/>
+      <c r="C55" s="20"/>
+      <c r="D55" s="21"/>
+      <c r="E55" s="36"/>
+      <c r="F55" s="33"/>
+      <c r="G55" s="35"/>
+      <c r="H55" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I55" s="34"/>
+      <c r="J55" s="148" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K55" s="142" t="s">
+        <v>359</v>
+      </c>
+      <c r="L55" s="20">
+        <v>14.36</v>
+      </c>
+      <c r="M55" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="N55" s="36"/>
+      <c r="O55" s="33"/>
+      <c r="P55" s="35">
+        <v>12.88</v>
+      </c>
+      <c r="Q55" s="35" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B56" s="38" t="s">
+        <v>336</v>
+      </c>
+      <c r="C56" s="21" t="s">
+        <v>356</v>
+      </c>
+      <c r="D56" s="21"/>
+      <c r="E56" s="36"/>
+      <c r="F56" s="33"/>
+      <c r="G56" s="35"/>
+      <c r="H56" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I56" s="34"/>
+      <c r="J56" s="148" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K56" s="142" t="s">
+        <v>311</v>
+      </c>
+      <c r="L56" s="20">
+        <v>4</v>
+      </c>
+      <c r="M56" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="N56" s="3"/>
+      <c r="O56" s="33"/>
+      <c r="P56" s="35">
+        <v>8</v>
+      </c>
+      <c r="Q56" s="35" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>7</v>
+      </c>
+      <c r="B57" s="38" t="s">
+        <v>422</v>
+      </c>
+      <c r="C57" s="20">
+        <v>1.7</v>
+      </c>
+      <c r="D57" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="E57" s="36"/>
+      <c r="F57" s="33"/>
+      <c r="G57" s="35">
+        <v>0.16</v>
+      </c>
+      <c r="H57" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I57" s="34"/>
+      <c r="J57" s="148">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="K57" s="66" t="s">
+        <v>420</v>
+      </c>
+      <c r="L57" s="20">
+        <v>2.6</v>
+      </c>
+      <c r="M57" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="N57" s="36"/>
+      <c r="O57" s="33"/>
+      <c r="P57" s="35">
+        <v>4.5</v>
+      </c>
+      <c r="Q57" s="35" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B58" s="38" t="s">
+        <v>429</v>
+      </c>
+      <c r="C58" s="20">
+        <v>0.42</v>
+      </c>
+      <c r="D58" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="E58" s="36"/>
+      <c r="F58" s="33">
+        <v>12</v>
+      </c>
+      <c r="G58" s="35">
+        <v>0.16</v>
+      </c>
+      <c r="H58" s="35">
+        <f t="shared" si="1"/>
+        <v>1.92</v>
+      </c>
+      <c r="I58" s="34"/>
+      <c r="J58" s="148" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K58" s="66" t="s">
+        <v>421</v>
+      </c>
+      <c r="L58" s="20">
+        <v>0.5</v>
+      </c>
+      <c r="M58" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="N58" s="36"/>
+      <c r="O58" s="33"/>
+      <c r="P58" s="35">
+        <v>4</v>
+      </c>
+      <c r="Q58" s="35" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>10</v>
+      </c>
+      <c r="B59" s="38" t="s">
+        <v>423</v>
+      </c>
+      <c r="C59" s="20"/>
+      <c r="D59" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="E59" s="36"/>
+      <c r="F59" s="33"/>
+      <c r="G59" s="35"/>
+      <c r="H59" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I59" s="34"/>
+      <c r="J59" s="148">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="K59" s="66" t="s">
+        <v>299</v>
+      </c>
+      <c r="L59" s="20">
+        <v>2.33</v>
+      </c>
+      <c r="M59" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="N59" s="36"/>
+      <c r="O59" s="33"/>
+      <c r="P59" s="35">
+        <v>5</v>
+      </c>
+      <c r="Q59" s="35" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>9</v>
+      </c>
+      <c r="B60" s="38" t="s">
+        <v>424</v>
+      </c>
+      <c r="C60" s="20">
+        <v>3.96</v>
+      </c>
+      <c r="D60" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="E60" s="36"/>
+      <c r="F60" s="33">
+        <v>3</v>
+      </c>
+      <c r="G60" s="35">
+        <v>0.34</v>
+      </c>
+      <c r="H60" s="35">
+        <f t="shared" si="1"/>
+        <v>1.02</v>
+      </c>
+      <c r="I60" s="34"/>
+      <c r="J60" s="148">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="K60" s="66" t="s">
+        <v>298</v>
+      </c>
+      <c r="L60" s="20">
+        <v>4</v>
+      </c>
+      <c r="M60" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="N60" s="36"/>
+      <c r="O60" s="33"/>
+      <c r="P60" s="35">
+        <v>4.75</v>
+      </c>
+      <c r="Q60" s="35" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="S60" s="10"/>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B61" s="38" t="s">
+        <v>380</v>
+      </c>
+      <c r="C61" s="20">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="D61" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="E61" s="36"/>
+      <c r="F61" s="33">
+        <v>14</v>
+      </c>
+      <c r="G61" s="35">
+        <v>0.36</v>
+      </c>
+      <c r="H61" s="35">
+        <f t="shared" si="1"/>
+        <v>5.04</v>
+      </c>
+      <c r="I61" s="34"/>
+      <c r="J61" s="148" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K61" s="66" t="s">
+        <v>376</v>
+      </c>
+      <c r="L61" s="20"/>
+      <c r="M61" s="21"/>
+      <c r="N61" s="36"/>
+      <c r="O61" s="33"/>
+      <c r="P61" s="35">
+        <v>5</v>
+      </c>
+      <c r="Q61" s="35" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A62" s="23" t="s">
+        <v>427</v>
+      </c>
+      <c r="B62" s="38" t="s">
+        <v>342</v>
+      </c>
+      <c r="C62" s="126" t="s">
+        <v>428</v>
+      </c>
+      <c r="D62" s="126"/>
+      <c r="E62" s="36"/>
+      <c r="F62" s="33"/>
+      <c r="G62" s="35"/>
+      <c r="H62" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I62" s="34"/>
+      <c r="J62" s="149" t="s">
+        <v>464</v>
+      </c>
+      <c r="K62" s="142" t="s">
+        <v>342</v>
+      </c>
+      <c r="L62" s="20">
+        <v>33</v>
+      </c>
+      <c r="M62" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="N62" s="36"/>
+      <c r="O62" s="33">
+        <v>3</v>
+      </c>
+      <c r="P62" s="35">
+        <v>0.65</v>
+      </c>
+      <c r="Q62" s="35">
+        <f t="shared" si="4"/>
+        <v>1.9500000000000002</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B63" s="38" t="s">
+        <v>349</v>
+      </c>
+      <c r="C63" s="20">
+        <v>11.62</v>
+      </c>
+      <c r="D63" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="E63" s="36"/>
+      <c r="F63" s="33"/>
+      <c r="G63" s="35">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="H63" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I63" s="34"/>
+      <c r="J63" s="148" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K63" s="66"/>
+      <c r="L63" s="20"/>
+      <c r="M63" s="21"/>
+      <c r="N63" s="36"/>
+      <c r="O63" s="33"/>
+      <c r="P63" s="35"/>
+      <c r="Q63" s="35" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>5</v>
+      </c>
+      <c r="B64" s="38" t="s">
+        <v>425</v>
+      </c>
+      <c r="C64" s="20">
+        <v>15.1</v>
+      </c>
+      <c r="D64" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="E64" s="36"/>
+      <c r="F64" s="33"/>
+      <c r="G64" s="35">
+        <v>0.8</v>
+      </c>
+      <c r="H64" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I64" s="34"/>
+      <c r="J64" s="148">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="K64" s="66" t="s">
+        <v>282</v>
+      </c>
+      <c r="L64" s="20">
+        <v>15</v>
+      </c>
+      <c r="M64" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="N64" s="36"/>
+      <c r="O64" s="33"/>
+      <c r="P64" s="35">
+        <v>0.9</v>
+      </c>
+      <c r="Q64" s="35" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B65" s="38" t="s">
+        <v>283</v>
+      </c>
+      <c r="C65" s="20">
+        <v>8.5</v>
+      </c>
+      <c r="D65" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="E65" s="127"/>
+      <c r="F65" s="33"/>
+      <c r="G65" s="35">
+        <v>0.8</v>
+      </c>
+      <c r="H65" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I65" s="34"/>
+      <c r="J65" s="148" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K65" s="66" t="s">
+        <v>283</v>
+      </c>
+      <c r="L65" s="20">
+        <v>6</v>
+      </c>
+      <c r="M65" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="N65" s="36"/>
+      <c r="O65" s="33"/>
+      <c r="P65" s="35">
+        <v>0.65</v>
+      </c>
+      <c r="Q65" s="35" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>9</v>
+      </c>
+      <c r="B66" s="50" t="s">
+        <v>426</v>
+      </c>
+      <c r="C66" s="20">
+        <v>1.58</v>
+      </c>
+      <c r="D66" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="E66" s="36"/>
+      <c r="F66" s="33"/>
+      <c r="G66" s="35">
+        <v>0.22</v>
+      </c>
+      <c r="H66" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I66" s="34"/>
+      <c r="J66" s="148">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="K66" s="140" t="s">
+        <v>301</v>
+      </c>
+      <c r="L66" s="20">
+        <v>5.4</v>
+      </c>
+      <c r="M66" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="N66" s="36"/>
+      <c r="O66" s="33"/>
+      <c r="P66" s="35">
+        <v>4.5</v>
+      </c>
+      <c r="Q66" s="35" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>8</v>
+      </c>
+      <c r="B67" s="50" t="s">
+        <v>300</v>
+      </c>
+      <c r="C67" s="20">
+        <v>1.58</v>
+      </c>
+      <c r="D67" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="E67" s="36"/>
+      <c r="F67" s="33"/>
+      <c r="G67" s="35">
+        <v>0.22</v>
+      </c>
+      <c r="H67" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I67" s="34"/>
+      <c r="J67" s="148">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="K67" s="140" t="s">
+        <v>302</v>
+      </c>
+      <c r="L67" s="20">
+        <v>6.2</v>
+      </c>
+      <c r="M67" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="N67" s="36"/>
+      <c r="O67" s="33"/>
+      <c r="P67" s="35">
+        <v>5</v>
+      </c>
+      <c r="Q67" s="35" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B68" s="38" t="s">
+        <v>338</v>
+      </c>
+      <c r="C68" s="20">
+        <v>14.79</v>
+      </c>
+      <c r="D68" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="E68" s="36"/>
+      <c r="F68" s="33">
+        <v>8</v>
+      </c>
+      <c r="G68" s="35">
+        <v>0.21</v>
+      </c>
+      <c r="H68" s="35">
+        <f t="shared" si="1"/>
+        <v>1.68</v>
+      </c>
+      <c r="I68" s="34"/>
+      <c r="J68" s="148" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K68" s="66" t="s">
+        <v>330</v>
+      </c>
+      <c r="L68" s="20">
+        <v>11.2</v>
+      </c>
+      <c r="M68" s="21" t="s">
+        <v>327</v>
+      </c>
+      <c r="N68" s="36"/>
+      <c r="O68" s="33"/>
+      <c r="P68" s="35">
+        <v>7.75</v>
+      </c>
+      <c r="Q68" s="35" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B69" s="38" t="s">
+        <v>341</v>
+      </c>
+      <c r="C69" s="20">
+        <v>7</v>
+      </c>
+      <c r="D69" s="21" t="s">
+        <v>327</v>
+      </c>
+      <c r="E69" s="36"/>
+      <c r="F69" s="33">
+        <v>1</v>
+      </c>
+      <c r="G69" s="35">
+        <v>7.49</v>
+      </c>
+      <c r="H69" s="35">
+        <f t="shared" si="1"/>
+        <v>7.49</v>
+      </c>
+      <c r="I69" s="34"/>
+      <c r="J69" s="148" t="str">
+        <f t="shared" ref="J69:J114" si="12">IF(ISBLANK(A69),"",A69)</f>
+        <v/>
+      </c>
+      <c r="K69" s="66" t="s">
+        <v>331</v>
+      </c>
+      <c r="L69" s="20">
+        <v>7.6</v>
+      </c>
+      <c r="M69" s="21" t="s">
+        <v>327</v>
+      </c>
+      <c r="N69" s="3"/>
+      <c r="P69" s="35">
+        <v>9</v>
+      </c>
+      <c r="Q69" s="35" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B70" s="38" t="s">
+        <v>339</v>
+      </c>
+      <c r="C70" s="20">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="D70" s="21" t="s">
+        <v>327</v>
+      </c>
+      <c r="E70" s="36"/>
+      <c r="F70" s="33"/>
+      <c r="G70" s="35">
+        <v>9.36</v>
+      </c>
+      <c r="H70" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I70" s="34"/>
+      <c r="J70" s="148" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="K70" s="66" t="s">
+        <v>332</v>
+      </c>
+      <c r="L70" s="20">
+        <v>3.9</v>
+      </c>
+      <c r="M70" s="21" t="s">
+        <v>327</v>
+      </c>
+      <c r="N70" s="3"/>
+      <c r="P70" s="35">
+        <v>5.5</v>
+      </c>
+      <c r="Q70" s="35" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B71" s="38" t="s">
+        <v>340</v>
+      </c>
+      <c r="C71" s="20">
+        <v>2.8</v>
+      </c>
+      <c r="D71" s="21" t="s">
+        <v>327</v>
+      </c>
+      <c r="E71" s="3"/>
+      <c r="G71" s="35">
+        <v>6.69</v>
+      </c>
+      <c r="H71" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I71" s="34"/>
+      <c r="J71" s="148" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="K71" s="142" t="s">
+        <v>329</v>
+      </c>
+      <c r="L71" s="20">
+        <v>4.5</v>
+      </c>
+      <c r="M71" s="21" t="s">
+        <v>327</v>
+      </c>
+      <c r="N71" s="36"/>
+      <c r="O71" s="33">
+        <v>1</v>
+      </c>
+      <c r="P71" s="35">
+        <v>6.5</v>
+      </c>
+      <c r="Q71" s="35">
+        <f t="shared" si="4"/>
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B72" s="52" t="s">
+        <v>343</v>
+      </c>
+      <c r="C72" s="20">
+        <v>10.3</v>
+      </c>
+      <c r="D72" s="21" t="s">
+        <v>327</v>
+      </c>
+      <c r="E72" s="3"/>
+      <c r="F72">
+        <v>2</v>
+      </c>
+      <c r="G72" s="35">
+        <v>3.21</v>
+      </c>
+      <c r="H72" s="35">
+        <f t="shared" si="1"/>
+        <v>6.42</v>
+      </c>
+      <c r="I72" s="34"/>
+      <c r="J72" s="148" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="K72" s="66" t="s">
+        <v>343</v>
+      </c>
+      <c r="L72" s="21" t="s">
+        <v>345</v>
+      </c>
+      <c r="M72" s="21"/>
+      <c r="N72" s="36"/>
+      <c r="O72" s="33"/>
+      <c r="P72" s="35"/>
+      <c r="Q72" s="35" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B73" s="52" t="s">
+        <v>344</v>
+      </c>
+      <c r="C73" s="20">
+        <v>8</v>
+      </c>
+      <c r="D73" s="21" t="s">
+        <v>327</v>
+      </c>
+      <c r="E73" s="3"/>
+      <c r="G73" s="35">
+        <v>0.86</v>
+      </c>
+      <c r="H73" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I73" s="34"/>
+      <c r="J73" s="148" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="K73" s="66" t="s">
+        <v>344</v>
+      </c>
+      <c r="L73" s="21" t="s">
+        <v>345</v>
+      </c>
+      <c r="M73" s="21"/>
+      <c r="N73" s="36"/>
+      <c r="O73" s="33"/>
+      <c r="P73" s="35"/>
+      <c r="Q73" s="35" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B74" s="46" t="s">
+        <v>289</v>
+      </c>
+      <c r="C74" s="20"/>
+      <c r="D74" s="21"/>
+      <c r="E74" s="3"/>
+      <c r="G74" s="35"/>
+      <c r="H74" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I74" s="34"/>
+      <c r="J74" s="148" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="K74" s="139" t="s">
+        <v>289</v>
+      </c>
+      <c r="L74" s="20"/>
+      <c r="M74" s="21"/>
+      <c r="N74" s="3"/>
+      <c r="P74" s="30"/>
+      <c r="Q74" s="35" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B75" s="38" t="s">
+        <v>346</v>
+      </c>
+      <c r="C75" s="20">
+        <v>4.3</v>
+      </c>
+      <c r="D75" s="21" t="s">
+        <v>327</v>
+      </c>
+      <c r="E75" s="3"/>
+      <c r="G75" s="35">
+        <v>2.94</v>
+      </c>
+      <c r="H75" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I75" s="34"/>
+      <c r="J75" s="148" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="K75" s="66" t="s">
+        <v>304</v>
+      </c>
+      <c r="L75" s="20">
+        <v>8</v>
+      </c>
+      <c r="M75" s="21" t="s">
+        <v>327</v>
+      </c>
+      <c r="N75" s="3"/>
+      <c r="P75" s="35">
+        <v>3.75</v>
+      </c>
+      <c r="Q75" s="35" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="S75" s="30"/>
+    </row>
+    <row r="76" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B76" s="38" t="s">
+        <v>347</v>
+      </c>
+      <c r="C76" s="20">
+        <v>1.41</v>
+      </c>
+      <c r="D76" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="E76" s="3"/>
+      <c r="G76" s="35">
+        <v>0.54</v>
+      </c>
+      <c r="H76" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I76" s="51"/>
+      <c r="J76" s="148" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="K76" s="140" t="s">
+        <v>305</v>
+      </c>
+      <c r="L76" s="20" t="s">
+        <v>303</v>
+      </c>
+      <c r="M76" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="N76" s="3"/>
+      <c r="P76" s="35">
+        <v>0.95</v>
+      </c>
+      <c r="Q76" s="35" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="77" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C77" s="20"/>
+      <c r="D77" s="21"/>
+      <c r="E77" s="3"/>
+      <c r="G77" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="H77" s="65">
+        <f>SUM(H49:H76)</f>
+        <v>23.57</v>
+      </c>
+      <c r="I77" s="34"/>
+      <c r="J77" s="148" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="K77" s="118"/>
+      <c r="L77" s="20"/>
+      <c r="M77" s="21"/>
+      <c r="N77" s="3"/>
+      <c r="P77" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q77" s="65">
+        <f>SUM(Q49:Q76)</f>
+        <v>41.95</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A78" s="39" t="s">
+        <v>284</v>
+      </c>
+      <c r="B78" s="40" t="s">
+        <v>308</v>
+      </c>
+      <c r="C78" s="41">
+        <v>1.36</v>
+      </c>
+      <c r="D78" s="42" t="s">
+        <v>161</v>
+      </c>
+      <c r="E78" s="11"/>
+      <c r="F78" s="43">
+        <v>2</v>
+      </c>
+      <c r="G78" s="44">
+        <v>6.15</v>
+      </c>
+      <c r="H78" s="44">
+        <f t="shared" si="1"/>
+        <v>12.3</v>
+      </c>
+      <c r="I78" s="34"/>
+      <c r="J78" s="148" t="str">
+        <f t="shared" si="12"/>
+        <v>Amsteel 7/64</v>
+      </c>
+      <c r="K78" s="143" t="s">
+        <v>308</v>
+      </c>
+      <c r="L78" s="41">
+        <v>1.36</v>
+      </c>
+      <c r="M78" s="42" t="s">
+        <v>327</v>
+      </c>
+      <c r="N78" s="11"/>
+      <c r="O78" s="43">
+        <v>1</v>
+      </c>
+      <c r="P78" s="44">
+        <v>7.5</v>
+      </c>
+      <c r="Q78" s="44">
+        <f t="shared" si="4"/>
+        <v>7.5</v>
+      </c>
+      <c r="S78" s="30"/>
+    </row>
+    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A79" s="43"/>
+      <c r="B79" s="40" t="s">
+        <v>309</v>
+      </c>
+      <c r="C79" s="41">
+        <v>1.36</v>
+      </c>
+      <c r="D79" s="42" t="s">
+        <v>161</v>
+      </c>
+      <c r="E79" s="11"/>
+      <c r="F79" s="43">
+        <v>1</v>
+      </c>
+      <c r="G79" s="44">
+        <v>6.15</v>
+      </c>
+      <c r="H79" s="44">
+        <f t="shared" si="1"/>
+        <v>6.15</v>
+      </c>
+      <c r="I79" s="34"/>
+      <c r="J79" s="148" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="K79" s="143" t="s">
+        <v>309</v>
+      </c>
+      <c r="L79" s="41">
+        <v>1.36</v>
+      </c>
+      <c r="M79" s="42" t="s">
+        <v>327</v>
+      </c>
+      <c r="N79" s="11"/>
+      <c r="O79" s="43">
+        <v>1</v>
+      </c>
+      <c r="P79" s="44">
+        <v>7.5</v>
+      </c>
+      <c r="Q79" s="44">
+        <f t="shared" si="4"/>
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="39"/>
+      <c r="B80" s="40" t="s">
+        <v>310</v>
+      </c>
+      <c r="C80" s="41">
+        <v>1.36</v>
+      </c>
+      <c r="D80" s="42" t="s">
+        <v>161</v>
+      </c>
+      <c r="E80" s="11"/>
+      <c r="F80" s="43">
+        <v>1</v>
+      </c>
+      <c r="G80" s="44">
+        <v>6.15</v>
+      </c>
+      <c r="H80" s="44">
+        <f t="shared" si="1"/>
+        <v>6.15</v>
+      </c>
+      <c r="I80" s="34"/>
+      <c r="J80" s="148" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="K80" s="143" t="s">
+        <v>310</v>
+      </c>
+      <c r="L80" s="41">
+        <v>1.36</v>
+      </c>
+      <c r="M80" s="42" t="s">
+        <v>327</v>
+      </c>
+      <c r="N80" s="11"/>
+      <c r="O80" s="43">
+        <v>1</v>
+      </c>
+      <c r="P80" s="44">
+        <v>7.5</v>
+      </c>
+      <c r="Q80" s="44">
+        <f t="shared" si="4"/>
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="39"/>
+      <c r="B81" s="40"/>
+      <c r="C81" s="41"/>
+      <c r="D81" s="42"/>
+      <c r="E81" s="11"/>
+      <c r="F81" s="43"/>
+      <c r="G81" s="69" t="s">
+        <v>65</v>
+      </c>
+      <c r="H81" s="67">
+        <f>SUM(H78:H80)</f>
+        <v>24.6</v>
+      </c>
+      <c r="I81" s="34"/>
+      <c r="J81" s="148" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="K81" s="143"/>
+      <c r="L81" s="41"/>
+      <c r="M81" s="42"/>
+      <c r="N81" s="11"/>
+      <c r="O81" s="43"/>
+      <c r="P81" s="69" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q81" s="67">
+        <f>SUM(Q78:Q80)</f>
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A82" s="45" t="s">
+        <v>285</v>
+      </c>
+      <c r="B82" s="46" t="s">
+        <v>306</v>
+      </c>
+      <c r="C82" s="47">
+        <v>1.9</v>
+      </c>
+      <c r="D82" s="48" t="s">
+        <v>161</v>
+      </c>
+      <c r="E82" s="8"/>
+      <c r="F82" s="7">
+        <v>1</v>
+      </c>
+      <c r="G82" s="49">
+        <v>4.55</v>
+      </c>
+      <c r="H82" s="49">
+        <f t="shared" si="1"/>
+        <v>4.55</v>
+      </c>
+      <c r="I82" s="34"/>
+      <c r="J82" s="148" t="str">
+        <f t="shared" si="12"/>
+        <v>Shock Cord</v>
+      </c>
+      <c r="K82" s="139" t="s">
+        <v>306</v>
+      </c>
+      <c r="L82" s="47">
+        <v>1.9</v>
+      </c>
+      <c r="M82" s="48" t="s">
+        <v>328</v>
+      </c>
+      <c r="N82" s="8"/>
+      <c r="O82" s="7">
+        <v>1</v>
+      </c>
+      <c r="P82" s="49">
+        <v>5.75</v>
+      </c>
+      <c r="Q82" s="49">
+        <f t="shared" si="4"/>
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A83" s="7"/>
+      <c r="B83" s="46" t="s">
+        <v>307</v>
+      </c>
+      <c r="C83" s="47">
+        <v>1.2</v>
+      </c>
+      <c r="D83" s="48" t="s">
+        <v>161</v>
+      </c>
+      <c r="E83" s="8"/>
+      <c r="F83" s="7">
+        <v>1</v>
+      </c>
+      <c r="G83" s="49">
+        <v>4.55</v>
+      </c>
+      <c r="H83" s="49">
+        <f t="shared" si="1"/>
+        <v>4.55</v>
+      </c>
+      <c r="I83" s="34"/>
+      <c r="J83" s="148" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="K83" s="139" t="s">
+        <v>307</v>
+      </c>
+      <c r="L83" s="47">
+        <v>1.2</v>
+      </c>
+      <c r="M83" s="48" t="s">
+        <v>328</v>
+      </c>
+      <c r="N83" s="8"/>
+      <c r="O83" s="7">
+        <v>1</v>
+      </c>
+      <c r="P83" s="49">
+        <v>5.75</v>
+      </c>
+      <c r="Q83" s="49">
+        <f t="shared" si="4"/>
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="10"/>
+      <c r="B84" s="54" t="s">
+        <v>373</v>
+      </c>
+      <c r="C84" s="57">
+        <v>4.7</v>
+      </c>
+      <c r="D84" s="58" t="s">
+        <v>323</v>
+      </c>
+      <c r="E84" s="13"/>
+      <c r="F84" s="10"/>
+      <c r="G84" s="59">
+        <v>1.61</v>
+      </c>
+      <c r="H84" s="59" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I84" s="34"/>
+      <c r="J84" s="148" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="K84" s="118" t="s">
+        <v>375</v>
+      </c>
+      <c r="L84" s="57">
+        <v>1.9</v>
+      </c>
+      <c r="M84" s="58" t="s">
+        <v>327</v>
+      </c>
+      <c r="N84" s="13"/>
+      <c r="O84" s="10"/>
+      <c r="P84" s="59">
+        <v>2.5</v>
+      </c>
+      <c r="Q84" s="59" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="85" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="10"/>
+      <c r="B85" s="54"/>
+      <c r="C85" s="57"/>
+      <c r="D85" s="58"/>
+      <c r="E85" s="13"/>
+      <c r="F85" s="10"/>
+      <c r="G85" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="H85" s="68">
+        <f>SUM(H82:H84)</f>
+        <v>9.1</v>
+      </c>
+      <c r="I85" s="34"/>
+      <c r="J85" s="148" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="K85" s="118"/>
+      <c r="L85" s="57"/>
+      <c r="M85" s="58"/>
+      <c r="N85" s="13"/>
+      <c r="O85" s="10"/>
+      <c r="P85" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q85" s="68">
+        <f>SUM(Q82:Q84)</f>
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A86" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="B86" s="38" t="s">
+        <v>357</v>
+      </c>
+      <c r="C86" s="20">
+        <v>0.49</v>
+      </c>
+      <c r="D86" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E86" s="36">
+        <f>C86*((58*72)/(36*36))</f>
+        <v>1.578888888888889</v>
+      </c>
+      <c r="F86" s="33"/>
+      <c r="G86" s="35">
+        <v>13.38</v>
+      </c>
+      <c r="H86" s="59" t="str">
+        <f t="shared" ref="H86:H115" si="13">IF((G86*F86)=0,"",G86*F86)</f>
+        <v/>
+      </c>
+      <c r="I86" s="34"/>
+      <c r="J86" s="148" t="str">
+        <f t="shared" si="12"/>
+        <v>Sleeping Bag Liner</v>
+      </c>
+      <c r="P86" s="33"/>
+      <c r="Q86" s="59" t="str">
+        <f t="shared" ref="Q86:Q103" si="14">IF((P86*O86)=0,"",P86*O86)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A87" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="B87" s="54" t="s">
+        <v>213</v>
+      </c>
+      <c r="C87" s="20">
+        <v>0.67</v>
+      </c>
+      <c r="D87" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E87" s="36">
+        <f>C87*((58*72)/(36*36))</f>
+        <v>2.1588888888888893</v>
+      </c>
+      <c r="F87" s="33">
+        <v>2</v>
+      </c>
+      <c r="G87" s="35">
+        <v>10.7</v>
+      </c>
+      <c r="H87" s="59">
+        <f t="shared" si="13"/>
+        <v>21.4</v>
+      </c>
+      <c r="I87" s="34"/>
+      <c r="J87" s="148" t="str">
+        <f t="shared" si="12"/>
+        <v>58 x 72</v>
+      </c>
+      <c r="K87" s="66" t="s">
+        <v>291</v>
+      </c>
+      <c r="L87" s="20">
+        <v>0.66</v>
+      </c>
+      <c r="M87" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="N87" s="36">
+        <f t="shared" ref="N87" si="15">L87*$A$5</f>
+        <v>2.145</v>
+      </c>
+      <c r="O87" s="33">
+        <v>2</v>
+      </c>
+      <c r="P87" s="35">
+        <v>12.75</v>
+      </c>
+      <c r="Q87" s="59">
+        <f t="shared" si="14"/>
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A88" s="5"/>
+      <c r="B88" s="38" t="s">
+        <v>214</v>
+      </c>
+      <c r="C88" s="20">
+        <v>0.9</v>
+      </c>
+      <c r="D88" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E88" s="36">
+        <f>C88*((58*72)/(36*36))</f>
+        <v>2.9000000000000004</v>
+      </c>
+      <c r="F88" s="33"/>
+      <c r="G88" s="35">
+        <v>8.0299999999999994</v>
+      </c>
+      <c r="H88" s="59" t="str">
+        <f t="shared" ref="H88:H103" si="16">IF((G88*F88)=0,"",G88*F88)</f>
+        <v/>
+      </c>
+      <c r="I88" s="34"/>
+      <c r="J88" s="148" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="P88" s="33"/>
+      <c r="Q88" s="59" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+    </row>
+    <row r="89" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="5"/>
+      <c r="B89" s="38" t="s">
+        <v>335</v>
+      </c>
+      <c r="C89" s="20"/>
+      <c r="D89" s="21"/>
+      <c r="E89" s="36"/>
+      <c r="F89" s="33">
+        <v>1</v>
+      </c>
+      <c r="G89" s="35">
+        <v>3.96</v>
+      </c>
+      <c r="H89" s="59">
+        <f t="shared" si="16"/>
+        <v>3.96</v>
+      </c>
+      <c r="I89" s="34"/>
+      <c r="J89" s="148" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="K89" t="s">
+        <v>335</v>
+      </c>
+      <c r="O89">
+        <v>1</v>
+      </c>
+      <c r="P89" s="33">
+        <v>4.5</v>
+      </c>
+      <c r="Q89" s="59">
+        <f t="shared" si="14"/>
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="5"/>
+      <c r="B90" s="38"/>
+      <c r="C90" s="20"/>
+      <c r="D90" s="21"/>
+      <c r="E90" s="36"/>
+      <c r="F90" s="33"/>
+      <c r="G90" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="H90" s="68">
+        <f>SUM(H86:H89)</f>
+        <v>25.36</v>
+      </c>
+      <c r="I90" s="34"/>
+      <c r="J90" s="148" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="P90" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q90" s="68">
+        <f>SUM(Q86:Q89)</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A91" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="B91" s="38" t="s">
+        <v>414</v>
+      </c>
+      <c r="C91" s="20">
+        <v>1.3</v>
+      </c>
+      <c r="D91" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E91" s="36">
+        <f>C91*((12.5*22)/(36*36))</f>
+        <v>0.2758487654320988</v>
+      </c>
+      <c r="F91" s="33">
+        <v>1</v>
+      </c>
+      <c r="G91" s="35">
+        <v>20.6</v>
+      </c>
+      <c r="H91" s="59">
+        <f t="shared" si="16"/>
+        <v>20.6</v>
+      </c>
+      <c r="I91" s="34"/>
+      <c r="J91" s="148" t="str">
+        <f t="shared" si="12"/>
+        <v>Food Bag (12.5 x 22)</v>
+      </c>
+      <c r="K91" s="66" t="s">
+        <v>415</v>
+      </c>
+      <c r="L91" s="20">
+        <v>1.43</v>
+      </c>
+      <c r="M91" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="N91" s="36">
+        <f>L91*((12.5*22)/(36*36))</f>
+        <v>0.30343364197530864</v>
+      </c>
+      <c r="O91" s="33">
+        <v>1</v>
+      </c>
+      <c r="P91" s="35">
+        <v>27</v>
+      </c>
+      <c r="Q91" s="59">
+        <f t="shared" si="14"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A92" s="5"/>
+      <c r="B92" s="38" t="s">
+        <v>374</v>
+      </c>
+      <c r="C92" s="20">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D92" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E92" s="36">
+        <f>C92*((12.5*22)/(36*36))</f>
+        <v>0.2334104938271605</v>
+      </c>
+      <c r="F92" s="33">
+        <v>1</v>
+      </c>
+      <c r="G92" s="35">
+        <v>6.96</v>
+      </c>
+      <c r="H92" s="59">
+        <f t="shared" si="16"/>
+        <v>6.96</v>
+      </c>
+      <c r="I92" s="34"/>
+      <c r="J92" s="148" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="P92" s="35"/>
+      <c r="Q92" s="59" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A93" s="5"/>
+      <c r="B93" s="38" t="s">
+        <v>393</v>
+      </c>
+      <c r="C93" s="20"/>
+      <c r="D93" s="21"/>
+      <c r="E93" s="36"/>
+      <c r="F93" s="33"/>
+      <c r="G93" s="35"/>
+      <c r="H93" s="59"/>
+      <c r="I93" s="34"/>
+      <c r="J93" s="148" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="P93" s="35"/>
+      <c r="Q93" s="59"/>
+    </row>
+    <row r="94" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="5"/>
+      <c r="B94" s="38" t="s">
+        <v>282</v>
+      </c>
+      <c r="C94" s="20">
+        <v>15.1</v>
+      </c>
+      <c r="D94" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="E94" s="36"/>
+      <c r="F94" s="33">
+        <v>1</v>
+      </c>
+      <c r="G94" s="35">
+        <v>0.8</v>
+      </c>
+      <c r="H94" s="59"/>
+      <c r="I94" s="34"/>
+      <c r="J94" s="148" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="P94" s="35"/>
+      <c r="Q94" s="59"/>
+    </row>
+    <row r="95" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="5"/>
+      <c r="B95" s="38"/>
+      <c r="C95" s="20"/>
+      <c r="D95" s="21"/>
+      <c r="E95" s="36"/>
+      <c r="F95" s="33"/>
+      <c r="G95" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="H95" s="68">
+        <f>SUM(H91:H92)</f>
+        <v>27.560000000000002</v>
+      </c>
+      <c r="I95" s="34"/>
+      <c r="J95" s="148" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="P95" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q95" s="68">
+        <f>SUM(Q91:Q92)</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A96" s="5"/>
+      <c r="B96" s="38"/>
+      <c r="C96" s="20"/>
+      <c r="D96" s="21"/>
+      <c r="E96" s="36"/>
+      <c r="F96" s="33"/>
+      <c r="G96" s="64"/>
+      <c r="H96" s="146"/>
+      <c r="I96" s="34"/>
+      <c r="J96" s="148"/>
+      <c r="P96" s="64"/>
+      <c r="Q96" s="146"/>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A97" s="5"/>
+      <c r="B97" s="38"/>
+      <c r="C97" s="20"/>
+      <c r="D97" s="21"/>
+      <c r="E97" s="36"/>
+      <c r="F97" s="33"/>
+      <c r="G97" s="64"/>
+      <c r="H97" s="146"/>
+      <c r="I97" s="34"/>
+      <c r="J97" s="148"/>
+      <c r="P97" s="64"/>
+      <c r="Q97" s="146"/>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A98" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="B98" s="38" t="s">
+        <v>362</v>
+      </c>
+      <c r="C98" s="20">
+        <v>0.51</v>
+      </c>
+      <c r="D98" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E98" s="36">
+        <f>C98*((36*56)/(36*36))</f>
+        <v>0.79333333333333333</v>
+      </c>
+      <c r="F98" s="33">
+        <v>2</v>
+      </c>
+      <c r="G98" s="35">
+        <v>20.6</v>
+      </c>
+      <c r="H98" s="59">
+        <f t="shared" si="16"/>
+        <v>41.2</v>
+      </c>
+      <c r="I98" s="34"/>
+      <c r="J98" s="147" t="str">
+        <f t="shared" si="12"/>
+        <v>Rain Kilt (30L x 48W)</v>
+      </c>
+      <c r="K98" s="66" t="s">
+        <v>362</v>
+      </c>
+      <c r="L98" s="20">
+        <v>0.51</v>
+      </c>
+      <c r="M98" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="N98" s="36">
+        <f>L98*((36*56)/(36*36))</f>
+        <v>0.79333333333333333</v>
+      </c>
+      <c r="O98" s="33">
+        <v>2</v>
+      </c>
+      <c r="P98" s="35">
+        <v>20.5</v>
+      </c>
+      <c r="Q98" s="59">
+        <f t="shared" si="14"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A99" s="129" t="s">
+        <v>436</v>
+      </c>
+      <c r="B99" s="38" t="s">
+        <v>374</v>
+      </c>
+      <c r="C99" s="20">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D99" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E99" s="36">
+        <f>C99*((36*56)/(36*36))</f>
+        <v>1.7111111111111112</v>
+      </c>
+      <c r="F99" s="33">
+        <v>1</v>
+      </c>
+      <c r="G99" s="35">
+        <v>6.9630000000000001</v>
+      </c>
+      <c r="H99" s="59">
+        <f t="shared" si="16"/>
+        <v>6.9630000000000001</v>
+      </c>
+      <c r="I99" s="34"/>
+      <c r="J99" s="148" t="str">
+        <f t="shared" si="12"/>
+        <v>-OR- 36L x 56W</v>
+      </c>
+      <c r="P99" s="35"/>
+      <c r="Q99" s="59" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A100" s="5"/>
+      <c r="B100" s="38" t="s">
+        <v>395</v>
+      </c>
+      <c r="C100" s="20"/>
+      <c r="D100" s="21"/>
+      <c r="E100" s="36"/>
+      <c r="F100" s="33"/>
+      <c r="G100" s="35"/>
+      <c r="H100" s="59"/>
+      <c r="I100" s="34"/>
+      <c r="J100" s="148" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="P100" s="35"/>
+      <c r="Q100" s="59"/>
+    </row>
+    <row r="101" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="5"/>
+      <c r="B101" s="38" t="s">
+        <v>401</v>
+      </c>
+      <c r="C101" s="20"/>
+      <c r="D101" s="21"/>
+      <c r="E101" s="36"/>
+      <c r="F101" s="33"/>
+      <c r="G101" s="35"/>
+      <c r="H101" s="59"/>
+      <c r="I101" s="34"/>
+      <c r="J101" s="148" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="P101" s="35"/>
+      <c r="Q101" s="59"/>
+    </row>
+    <row r="102" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="5"/>
+      <c r="B102" s="38"/>
+      <c r="C102" s="20"/>
+      <c r="D102" s="21"/>
+      <c r="E102" s="36"/>
+      <c r="F102" s="33"/>
+      <c r="G102" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="H102" s="68">
+        <f>SUM(H98:H99)</f>
+        <v>48.163000000000004</v>
+      </c>
+      <c r="I102" s="34"/>
+      <c r="J102" s="148" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="P102" s="35"/>
+      <c r="Q102" s="59"/>
+    </row>
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A103" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="B103" s="38" t="s">
+        <v>374</v>
+      </c>
+      <c r="C103" s="20">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D103" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E103" s="36">
+        <f>C103*((72*54)/(36*36))</f>
+        <v>3.3000000000000003</v>
+      </c>
+      <c r="F103" s="33">
+        <v>2</v>
+      </c>
+      <c r="G103" s="35">
+        <v>6.96</v>
+      </c>
+      <c r="H103" s="59">
+        <f t="shared" si="16"/>
+        <v>13.92</v>
+      </c>
+      <c r="I103" s="34"/>
+      <c r="J103" s="147" t="str">
+        <f t="shared" si="12"/>
+        <v>Rain Pants</v>
+      </c>
+      <c r="K103" t="s">
+        <v>367</v>
+      </c>
+      <c r="N103" s="36">
+        <f>1.4*((72*54)/(36*36))</f>
+        <v>4.1999999999999993</v>
+      </c>
+      <c r="O103" s="33">
+        <v>2</v>
+      </c>
+      <c r="P103" s="35">
+        <v>20</v>
+      </c>
+      <c r="Q103" s="59">
+        <f t="shared" si="14"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A104" s="60" t="s">
+        <v>368</v>
+      </c>
+      <c r="B104" s="38" t="s">
+        <v>362</v>
+      </c>
+      <c r="C104" s="20">
+        <v>0.51</v>
+      </c>
+      <c r="D104" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E104" s="36">
+        <f>C104*((30*48)/(36*36))</f>
+        <v>0.56666666666666665</v>
+      </c>
+      <c r="F104" s="33"/>
+      <c r="G104" s="35">
+        <v>20.6</v>
+      </c>
+      <c r="H104" s="59" t="str">
+        <f t="shared" ref="H104" si="17">IF((G104*F104)=0,"",G104*F104)</f>
+        <v/>
+      </c>
+      <c r="I104" s="34"/>
+      <c r="J104" s="148" t="str">
+        <f t="shared" si="12"/>
+        <v>make pattern</v>
+      </c>
+      <c r="K104" s="66" t="s">
+        <v>362</v>
+      </c>
+      <c r="L104" s="20">
+        <v>0.51</v>
+      </c>
+      <c r="M104" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="N104" s="36">
+        <f>L104*((12.5*22)/(36*36))</f>
+        <v>0.10821759259259259</v>
+      </c>
+      <c r="O104" s="33"/>
+      <c r="P104" s="35">
+        <v>20.5</v>
+      </c>
+      <c r="Q104" s="59" t="str">
+        <f t="shared" ref="Q104" si="18">IF((P104*O104)=0,"",P104*O104)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A105" s="60"/>
+      <c r="B105" s="46" t="s">
+        <v>379</v>
+      </c>
+      <c r="C105" s="20"/>
+      <c r="D105" s="21"/>
+      <c r="E105" s="36"/>
+      <c r="F105" s="33"/>
+      <c r="G105" s="35"/>
+      <c r="H105" s="59"/>
+      <c r="I105" s="34"/>
+      <c r="J105" s="148" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="K105" s="66"/>
+      <c r="L105" s="20"/>
+      <c r="M105" s="21"/>
+      <c r="N105" s="36"/>
+      <c r="O105" s="33"/>
+      <c r="P105" s="35"/>
+      <c r="Q105" s="59"/>
+    </row>
+    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A106" s="60"/>
+      <c r="B106" s="50" t="s">
+        <v>316</v>
+      </c>
+      <c r="C106" s="20"/>
+      <c r="D106" s="21"/>
+      <c r="E106" s="36"/>
+      <c r="F106" s="33"/>
+      <c r="G106" s="35"/>
+      <c r="H106" s="59"/>
+      <c r="I106" s="34"/>
+      <c r="J106" s="148" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="K106" s="66"/>
+      <c r="L106" s="20"/>
+      <c r="M106" s="21"/>
+      <c r="N106" s="36"/>
+      <c r="O106" s="33"/>
+      <c r="P106" s="35"/>
+      <c r="Q106" s="59"/>
+    </row>
+    <row r="107" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="60"/>
+      <c r="B107" s="38" t="s">
+        <v>335</v>
+      </c>
+      <c r="C107" s="20"/>
+      <c r="D107" s="21"/>
+      <c r="E107" s="36"/>
+      <c r="F107" s="33">
+        <v>1</v>
+      </c>
+      <c r="G107" s="35">
+        <v>3.96</v>
+      </c>
+      <c r="H107" s="59">
+        <f t="shared" ref="H107" si="19">IF((G107*F107)=0,"",G107*F107)</f>
+        <v>3.96</v>
+      </c>
+      <c r="I107" s="34"/>
+      <c r="J107" s="148" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="K107" t="s">
+        <v>335</v>
+      </c>
+      <c r="O107">
+        <v>1</v>
+      </c>
+      <c r="P107" s="138">
+        <v>4.5</v>
+      </c>
+      <c r="Q107" s="59">
+        <f t="shared" ref="Q107" si="20">IF((P107*O107)=0,"",P107*O107)</f>
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="108" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="60"/>
+      <c r="B108" s="38"/>
+      <c r="C108" s="20"/>
+      <c r="D108" s="21"/>
+      <c r="E108" s="36"/>
+      <c r="F108" s="33"/>
+      <c r="G108" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="H108" s="68">
+        <f>SUM(H103:H107)</f>
+        <v>17.88</v>
+      </c>
+      <c r="I108" s="34"/>
+      <c r="J108" s="148" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="K108" s="66"/>
+      <c r="L108" s="20"/>
+      <c r="M108" s="21"/>
+      <c r="N108" s="36"/>
+      <c r="O108" s="33"/>
+      <c r="P108" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q108" s="68">
+        <f>SUM(Q103:Q107)</f>
+        <v>44.5</v>
+      </c>
+    </row>
+    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A109" s="18" t="s">
+        <v>369</v>
+      </c>
+      <c r="B109" s="38" t="s">
+        <v>370</v>
+      </c>
+      <c r="C109" s="20"/>
+      <c r="D109" s="21"/>
+      <c r="E109" s="36"/>
+      <c r="F109" s="33"/>
+      <c r="G109" s="35"/>
+      <c r="H109" s="59"/>
+      <c r="I109" s="34"/>
+      <c r="J109" s="147" t="str">
+        <f t="shared" si="12"/>
+        <v>Pack Cover (new pack)</v>
+      </c>
+      <c r="P109" s="33"/>
+      <c r="Q109" s="10"/>
+    </row>
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A110" s="18" t="s">
+        <v>287</v>
+      </c>
+      <c r="B110" s="61" t="s">
+        <v>372</v>
+      </c>
+      <c r="H110" s="59" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="I110" s="34"/>
+      <c r="J110" s="147" t="str">
+        <f t="shared" si="12"/>
+        <v>Ditty Bags (See ToDo)</v>
+      </c>
+    </row>
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A111" s="18" t="s">
+        <v>288</v>
+      </c>
+      <c r="B111" s="38" t="s">
+        <v>371</v>
+      </c>
+      <c r="H111" s="59" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="I111" s="34"/>
+      <c r="J111" s="147" t="str">
+        <f t="shared" si="12"/>
+        <v>Kilt (Use ION)</v>
+      </c>
+    </row>
+    <row r="112" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B112" s="38"/>
+      <c r="H112" s="59" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="I112" s="34"/>
+      <c r="J112" s="148" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="Q112" s="20"/>
+    </row>
+    <row r="113" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="18" t="s">
+        <v>471</v>
+      </c>
+      <c r="B113" s="54" t="s">
+        <v>457</v>
+      </c>
+      <c r="C113">
+        <f>C114*F118</f>
+        <v>6.8078820000000002</v>
+      </c>
+      <c r="D113" t="s">
+        <v>159</v>
+      </c>
+      <c r="E113" s="36">
+        <f>C113*((30*48)/(36*36))</f>
+        <v>7.5643133333333337</v>
+      </c>
+      <c r="F113">
+        <v>2</v>
+      </c>
+      <c r="G113">
+        <v>29</v>
+      </c>
+      <c r="H113" s="59">
+        <f t="shared" si="13"/>
+        <v>58</v>
+      </c>
+      <c r="I113" s="34"/>
+      <c r="J113" s="147" t="str">
+        <f t="shared" si="12"/>
+        <v>Pullover/hoodie</v>
+      </c>
+      <c r="K113" t="s">
+        <v>458</v>
+      </c>
+      <c r="L113">
+        <v>4.8</v>
+      </c>
+      <c r="M113" t="s">
+        <v>159</v>
+      </c>
+      <c r="N113" s="36">
+        <f>1.4*((72*54)/(36*36))</f>
+        <v>4.1999999999999993</v>
+      </c>
+      <c r="O113">
+        <v>2</v>
+      </c>
+      <c r="P113" s="137">
+        <v>27.25</v>
+      </c>
+      <c r="Q113" s="68">
+        <f t="shared" ref="Q113" si="21">IF((P113*O113)=0,"",P113*O113)</f>
+        <v>54.5</v>
+      </c>
+    </row>
+    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B114" s="54" t="s">
+        <v>460</v>
+      </c>
+      <c r="C114">
+        <v>193</v>
+      </c>
+      <c r="D114" t="s">
+        <v>161</v>
+      </c>
+      <c r="I114" s="34"/>
+      <c r="J114" s="144" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="K114" t="s">
+        <v>459</v>
+      </c>
+      <c r="L114">
+        <v>135.62</v>
+      </c>
+      <c r="M114" t="s">
+        <v>161</v>
+      </c>
+      <c r="N114" s="36"/>
+    </row>
+    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B115" s="118">
+        <v>4004</v>
+      </c>
+      <c r="C115">
+        <v>119</v>
+      </c>
+      <c r="F115">
+        <v>2</v>
+      </c>
+      <c r="G115">
+        <v>28</v>
+      </c>
+      <c r="H115" s="59">
+        <f t="shared" si="13"/>
+        <v>56</v>
+      </c>
+      <c r="I115" s="34"/>
+      <c r="K115" t="s">
+        <v>461</v>
+      </c>
+      <c r="P115" s="137">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A116" s="132" t="s">
+        <v>455</v>
+      </c>
+      <c r="K116" t="s">
+        <v>473</v>
+      </c>
+      <c r="L116">
+        <v>152.58000000000001</v>
+      </c>
+      <c r="M116" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="117" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="18" t="s">
+        <v>456</v>
+      </c>
+      <c r="L117">
+        <f>L116*F118</f>
+        <v>5.38210692</v>
+      </c>
+      <c r="M117" t="s">
+        <v>159</v>
+      </c>
+      <c r="O117">
+        <v>2</v>
+      </c>
+      <c r="P117" s="137">
+        <v>31.5</v>
+      </c>
+      <c r="Q117" s="59">
+        <f t="shared" ref="Q117:Q118" si="22">IF((P117*O117)=0,"",P117*O117)</f>
+        <v>63</v>
+      </c>
+    </row>
+    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="D118" s="133">
+        <v>1</v>
+      </c>
+      <c r="E118" s="79" t="s">
+        <v>463</v>
+      </c>
+      <c r="F118" s="79">
+        <v>3.5274E-2</v>
+      </c>
+      <c r="G118" s="80" t="s">
+        <v>159</v>
+      </c>
+      <c r="K118" s="31" t="s">
+        <v>481</v>
+      </c>
+      <c r="O118">
+        <v>2</v>
+      </c>
+      <c r="P118" s="137">
+        <v>26.25</v>
+      </c>
+      <c r="Q118" s="59">
+        <f t="shared" si="22"/>
+        <v>52.5</v>
+      </c>
+    </row>
+    <row r="119" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D119" s="134">
+        <v>28.349499999999999</v>
+      </c>
+      <c r="E119" s="135" t="s">
+        <v>463</v>
+      </c>
+      <c r="F119" s="135">
+        <v>1</v>
+      </c>
+      <c r="G119" s="136" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K120" s="166"/>
+      <c r="L120" s="66"/>
+      <c r="M120" s="66"/>
+      <c r="N120" s="159"/>
+      <c r="O120" s="66"/>
+      <c r="P120" s="66"/>
+    </row>
+    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K121" s="166"/>
+      <c r="L121" s="66"/>
+      <c r="M121" s="66"/>
+      <c r="N121" s="159"/>
+      <c r="O121" s="66"/>
+      <c r="P121" s="66"/>
+    </row>
+    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K122" s="166"/>
+      <c r="L122" s="66"/>
+      <c r="M122" s="66"/>
+      <c r="N122" s="159"/>
+      <c r="O122" s="66"/>
+      <c r="P122" s="66"/>
+    </row>
+    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K123" s="166"/>
+      <c r="L123" s="66"/>
+      <c r="M123" s="66"/>
+      <c r="N123" s="159"/>
+      <c r="O123" s="66"/>
+      <c r="P123" s="66"/>
+    </row>
+    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K124" s="166"/>
+      <c r="L124" s="66"/>
+      <c r="M124" s="66"/>
+      <c r="N124" s="159"/>
+      <c r="O124" s="66"/>
+      <c r="P124" s="66"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B110" location="ToDo!A19" display="See ToDo" xr:uid="{CE28C4E6-45D1-4C5D-A0AF-3ACF169C0D5B}"/>
+    <hyperlink ref="R31" location="Make!A81" display="L" xr:uid="{F2445477-C9B7-447F-944F-160D21ACEB18}"/>
+    <hyperlink ref="R32" location="Make!A85" display="L" xr:uid="{D614D32D-E4C7-4ABC-8AEA-2A0D20F4C1EC}"/>
+    <hyperlink ref="R27" location="Make!A90" display="L" xr:uid="{786E7206-F76A-4474-B631-F01E095CA8FB}"/>
+    <hyperlink ref="R28" location="Make!A95" display="L" xr:uid="{A288F02B-8AE6-4CE7-9B7F-6DD8E549C8E8}"/>
+    <hyperlink ref="R29" location="Make!A102" display="L" xr:uid="{C7F86928-456B-47CA-B030-99A0CE694B65}"/>
+    <hyperlink ref="R30" location="Make!A108" display="L" xr:uid="{E0FEEF9A-7979-41D4-9772-139EF091D5CD}"/>
+    <hyperlink ref="R33" location="Make!A115" display="L" xr:uid="{9AA833A4-D1DB-483F-A7AF-3C44DA0808E7}"/>
+    <hyperlink ref="R26" location="Make!A77" display="L" xr:uid="{E64E53CA-419A-4BC2-9BE5-AAA6BFB2DE02}"/>
+    <hyperlink ref="R24" location="Make!A41" display="L" xr:uid="{25449295-6A81-450D-82CB-5908B642E8DB}"/>
+    <hyperlink ref="R25" location="Make!A48" display="L" xr:uid="{A66F585E-5359-4692-A61E-3AC13DCE42DB}"/>
+  </hyperlinks>
+  <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3D8ADF0-8E94-4902-A1F9-3D27383A1516}">
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:T31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -3280,154 +9533,302 @@
     <col min="6" max="6" width="7.28515625" customWidth="1"/>
     <col min="7" max="7" width="5.42578125" customWidth="1"/>
     <col min="8" max="8" width="8" customWidth="1"/>
+    <col min="12" max="12" width="10.5703125" customWidth="1"/>
+    <col min="14" max="14" width="1.7109375" customWidth="1"/>
+    <col min="15" max="15" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E1">
         <v>3.5274E-2</v>
       </c>
       <c r="F1" t="s">
+        <v>159</v>
+      </c>
+      <c r="G1" t="s">
         <v>160</v>
-      </c>
-      <c r="G1" t="s">
-        <v>161</v>
       </c>
       <c r="H1">
         <v>28.349499999999999</v>
       </c>
       <c r="I1" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B2" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="C2" s="24" t="s">
         <v>140</v>
-      </c>
-      <c r="C2" s="24" t="s">
-        <v>141</v>
       </c>
       <c r="E2">
         <f>2.72*H1</f>
         <v>77.110640000000004</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G2" s="31" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B3" s="16">
         <v>50</v>
       </c>
-      <c r="C3" s="16">
+      <c r="C3" s="165">
+        <f>(B3-32)*5/9</f>
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B4">
         <v>40</v>
       </c>
-      <c r="C4">
-        <v>4.4000000000000004</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C4" s="165">
+        <f t="shared" ref="C4:C8" si="0">(B4-32)*5/9</f>
+        <v>4.4444444444444446</v>
+      </c>
+      <c r="K4" s="26">
+        <f>36*36</f>
+        <v>1296</v>
+      </c>
+      <c r="L4" s="26" t="s">
+        <v>258</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="29" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B5" s="29">
         <v>30</v>
       </c>
-      <c r="C5" s="29">
-        <v>-1</v>
+      <c r="C5" s="165">
+        <f t="shared" si="0"/>
+        <v>-1.1111111111111112</v>
       </c>
       <c r="D5" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+        <v>176</v>
+      </c>
+      <c r="K5" s="7">
+        <v>54</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="O5" s="20" t="s">
+        <v>438</v>
+      </c>
+      <c r="P5">
+        <v>32</v>
+      </c>
+      <c r="Q5" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="R5">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="29" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B6" s="29">
         <v>20</v>
       </c>
-      <c r="C6" s="29"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C6" s="165">
+        <f t="shared" si="0"/>
+        <v>-6.666666666666667</v>
+      </c>
+      <c r="D6" t="s">
+        <v>175</v>
+      </c>
+      <c r="K6" s="7">
+        <v>78</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="O6" s="20" t="s">
+        <v>439</v>
+      </c>
+      <c r="P6">
+        <v>16</v>
+      </c>
+      <c r="Q6" s="20" t="s">
+        <v>441</v>
+      </c>
+      <c r="R6">
+        <v>8.1999999999999993</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B7">
         <v>10</v>
       </c>
-      <c r="C7">
-        <v>-12.2</v>
-      </c>
-      <c r="D7" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C7" s="165">
+        <f t="shared" si="0"/>
+        <v>-12.222222222222221</v>
+      </c>
+      <c r="K7" s="7">
+        <v>1.83</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="O7" s="20" t="s">
+        <v>440</v>
+      </c>
+      <c r="P7">
+        <v>44.8</v>
+      </c>
+      <c r="Q7" s="20" t="s">
+        <v>384</v>
+      </c>
+      <c r="R7">
+        <v>26</v>
+      </c>
+      <c r="S7">
+        <v>22</v>
+      </c>
+      <c r="T7" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="25" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B8" s="25">
         <v>-5</v>
       </c>
-      <c r="C8" s="25">
-        <v>-20.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C8" s="165">
+        <f t="shared" si="0"/>
+        <v>-20.555555555555557</v>
+      </c>
+      <c r="K8" s="9">
+        <f>(K5*K6)/K4</f>
+        <v>3.25</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="O8" s="20" t="s">
+        <v>445</v>
+      </c>
+      <c r="P8">
+        <v>4.2</v>
+      </c>
+      <c r="Q8" s="20" t="s">
+        <v>385</v>
+      </c>
+      <c r="R8">
+        <v>23</v>
+      </c>
+      <c r="S8">
+        <v>20</v>
+      </c>
+      <c r="T8" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="E9" s="22" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+      <c r="K9" s="9">
+        <f>K8*K7</f>
+        <v>5.9474999999999998</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="O9" s="20" t="s">
+        <v>449</v>
+      </c>
+      <c r="P9">
+        <v>4</v>
+      </c>
+      <c r="Q9" s="20" t="s">
+        <v>442</v>
+      </c>
+      <c r="R9">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="L10" s="32" t="s">
+        <v>266</v>
+      </c>
+      <c r="M10" s="32" t="s">
+        <v>265</v>
+      </c>
+      <c r="O10" s="20"/>
+      <c r="Q10" s="20" t="s">
+        <v>450</v>
+      </c>
+      <c r="R10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B11" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E11">
         <v>51.89</v>
@@ -3437,29 +9838,70 @@
         <v>1.83036786</v>
       </c>
       <c r="G11" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H11" s="3">
-        <f>F11*5</f>
-        <v>9.1518392999999989</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+        <f>F11*2</f>
+        <v>3.6607357199999999</v>
+      </c>
+      <c r="J11" s="7">
+        <v>54</v>
+      </c>
+      <c r="K11" s="7">
+        <v>78</v>
+      </c>
+      <c r="L11" s="12">
+        <f>(J11*K11/$K$4)*E11</f>
+        <v>168.64250000000001</v>
+      </c>
+      <c r="M11" s="12">
+        <f>(J11*K11/$K$4)*F11</f>
+        <v>5.9486955449999996</v>
+      </c>
+      <c r="Q11" s="20" t="s">
+        <v>444</v>
+      </c>
+      <c r="R11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>144</v>
+      </c>
+      <c r="B12" t="s">
         <v>145</v>
-      </c>
-      <c r="B12" t="s">
-        <v>146</v>
       </c>
       <c r="F12" s="3"/>
       <c r="H12" s="3"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="12">
+        <f t="shared" ref="L12:L28" si="1">(J12*K12/$K$4)*E12</f>
+        <v>0</v>
+      </c>
+      <c r="M12" s="12">
+        <f t="shared" ref="M12:M28" si="2">(J12*K12/$K$4)*F12</f>
+        <v>0</v>
+      </c>
+      <c r="P12" s="130">
+        <f>SUM(P5:P11)</f>
+        <v>101</v>
+      </c>
+      <c r="Q12" s="131" t="s">
+        <v>65</v>
+      </c>
+      <c r="R12" s="130">
+        <f>SUM(R5:R11)</f>
+        <v>93.2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>67</v>
       </c>
       <c r="B13" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E13">
         <v>31.48</v>
@@ -3469,19 +9911,44 @@
         <v>1.1104255199999999</v>
       </c>
       <c r="G13" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H13" s="3">
         <f>F13*5</f>
         <v>5.5521275999999995</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J13" s="7">
+        <v>54</v>
+      </c>
+      <c r="K13" s="7">
+        <v>74</v>
+      </c>
+      <c r="L13" s="12">
+        <f t="shared" si="1"/>
+        <v>97.063333333333333</v>
+      </c>
+      <c r="M13" s="12">
+        <f t="shared" si="2"/>
+        <v>3.4238120200000002</v>
+      </c>
+      <c r="P13">
+        <f>INT(P12/16)</f>
+        <v>6</v>
+      </c>
+      <c r="Q13" s="20" t="s">
+        <v>447</v>
+      </c>
+      <c r="R13">
+        <f>INT(R12/16)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>90</v>
       </c>
       <c r="B14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E14">
         <v>43</v>
@@ -3491,22 +9958,54 @@
         <v>1.5167820000000001</v>
       </c>
       <c r="G14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H14" s="3">
         <f>F14*5</f>
         <v>7.5839100000000004</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J14" s="7">
+        <v>54</v>
+      </c>
+      <c r="K14" s="7">
+        <v>74</v>
+      </c>
+      <c r="L14" s="12">
+        <f t="shared" si="1"/>
+        <v>132.58333333333334</v>
+      </c>
+      <c r="M14" s="12">
+        <f t="shared" si="2"/>
+        <v>4.6767445000000007</v>
+      </c>
+      <c r="P14">
+        <f>P12-(P13*16)</f>
+        <v>5</v>
+      </c>
+      <c r="Q14" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="R14">
+        <f>R12-(R13*16)</f>
+        <v>13.200000000000003</v>
+      </c>
+      <c r="S14">
+        <f>R7-S7+R8-S8</f>
+        <v>7</v>
+      </c>
+      <c r="T14" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B15" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C15" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E15">
         <v>51.89</v>
@@ -3516,29 +10015,52 @@
         <v>1.83036786</v>
       </c>
       <c r="G15" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H15" s="3">
         <f>F15*3</f>
         <v>5.4911035799999999</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M15" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S15" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>146</v>
+      </c>
+      <c r="B16" t="s">
         <v>147</v>
-      </c>
-      <c r="B16" t="s">
-        <v>148</v>
       </c>
       <c r="F16" s="3"/>
       <c r="H16" s="3"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M16" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>1.2</v>
       </c>
       <c r="B17" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E17">
         <v>54</v>
@@ -3548,22 +10070,33 @@
         <v>1.9047959999999999</v>
       </c>
       <c r="G17" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H17" s="3">
         <f>F17*4</f>
         <v>7.6191839999999997</v>
       </c>
-      <c r="J17" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J17" s="7">
+        <v>54</v>
+      </c>
+      <c r="K17" s="7">
+        <v>120</v>
+      </c>
+      <c r="L17" s="12">
+        <f t="shared" si="1"/>
+        <v>270</v>
+      </c>
+      <c r="M17" s="12">
+        <f t="shared" si="2"/>
+        <v>9.5239799999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>1.6</v>
       </c>
       <c r="B18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E18">
         <v>80.47</v>
@@ -3573,193 +10106,419 @@
         <v>2.8384987800000001</v>
       </c>
       <c r="G18" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H18" s="3">
         <f>F18*3</f>
         <v>8.5154963400000003</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="J18" s="7">
+        <v>54</v>
+      </c>
+      <c r="K18" s="7">
+        <v>120</v>
+      </c>
+      <c r="L18" s="12">
+        <f t="shared" si="1"/>
+        <v>402.35</v>
+      </c>
+      <c r="M18" s="12">
+        <f t="shared" si="2"/>
+        <v>14.192493900000001</v>
+      </c>
+      <c r="O18" s="154" t="s">
+        <v>474</v>
+      </c>
+      <c r="P18" s="155">
+        <v>60</v>
+      </c>
+      <c r="Q18" s="155" t="s">
+        <v>479</v>
+      </c>
+      <c r="R18" s="156">
+        <f>P18*2*$E$1</f>
+        <v>4.2328799999999998</v>
+      </c>
+      <c r="S18" s="155" t="s">
+        <v>480</v>
+      </c>
+      <c r="T18" s="157"/>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>179</v>
+      </c>
+      <c r="F19" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="H19" s="3"/>
+      <c r="J19" s="7">
+        <v>48</v>
+      </c>
+      <c r="K19" s="7">
+        <v>86</v>
+      </c>
+      <c r="L19" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M19" s="12">
+        <f t="shared" si="2"/>
+        <v>3.822222222222222</v>
+      </c>
+      <c r="O19" s="158" t="s">
+        <v>475</v>
+      </c>
+      <c r="P19" s="66">
+        <v>90</v>
+      </c>
+      <c r="Q19" s="66" t="s">
+        <v>479</v>
+      </c>
+      <c r="R19" s="159">
+        <f t="shared" ref="R19:R22" si="3">P19*2*$E$1</f>
+        <v>6.3493199999999996</v>
+      </c>
+      <c r="S19" s="66" t="s">
+        <v>480</v>
+      </c>
+      <c r="T19" s="160"/>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>148</v>
+      </c>
+      <c r="B20" t="s">
         <v>149</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C20" t="s">
         <v>150</v>
       </c>
-      <c r="C19" t="s">
+      <c r="F20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M20" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O20" s="158" t="s">
+        <v>476</v>
+      </c>
+      <c r="P20" s="66">
+        <v>120</v>
+      </c>
+      <c r="Q20" s="66" t="s">
+        <v>479</v>
+      </c>
+      <c r="R20" s="159">
+        <f t="shared" si="3"/>
+        <v>8.4657599999999995</v>
+      </c>
+      <c r="S20" s="66" t="s">
+        <v>480</v>
+      </c>
+      <c r="T20" s="160"/>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>0.9</v>
+      </c>
+      <c r="B21" t="s">
+        <v>163</v>
+      </c>
+      <c r="C21" t="s">
         <v>151</v>
       </c>
-      <c r="F19" s="3"/>
-      <c r="H19" s="3"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>0.9</v>
-      </c>
-      <c r="B20" t="s">
-        <v>164</v>
-      </c>
-      <c r="C20" t="s">
-        <v>152</v>
-      </c>
-      <c r="E20">
+      <c r="E21">
         <v>44.59</v>
-      </c>
-      <c r="F20" s="3">
-        <f>E20*$E$1</f>
-        <v>1.57286766</v>
-      </c>
-      <c r="G20" t="s">
-        <v>172</v>
-      </c>
-      <c r="H20" s="3"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B21" t="s">
-        <v>166</v>
-      </c>
-      <c r="C21">
-        <v>4000</v>
-      </c>
-      <c r="E21">
-        <v>58.21</v>
       </c>
       <c r="F21" s="3">
         <f>E21*$E$1</f>
+        <v>1.57286766</v>
+      </c>
+      <c r="G21" t="s">
+        <v>170</v>
+      </c>
+      <c r="H21" s="3"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M21" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O21" s="158" t="s">
+        <v>478</v>
+      </c>
+      <c r="P21" s="66">
+        <v>150</v>
+      </c>
+      <c r="Q21" s="66" t="s">
+        <v>479</v>
+      </c>
+      <c r="R21" s="159">
+        <f t="shared" si="3"/>
+        <v>10.5822</v>
+      </c>
+      <c r="S21" s="66" t="s">
+        <v>480</v>
+      </c>
+      <c r="T21" s="160"/>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B22" t="s">
+        <v>165</v>
+      </c>
+      <c r="C22">
+        <v>4000</v>
+      </c>
+      <c r="E22">
+        <v>58.21</v>
+      </c>
+      <c r="F22" s="3">
+        <f>E22*$E$1</f>
         <v>2.0532995399999998</v>
       </c>
-      <c r="G21" t="s">
-        <v>172</v>
-      </c>
-      <c r="H21" s="3">
-        <f>F21*8</f>
+      <c r="G22" t="s">
+        <v>170</v>
+      </c>
+      <c r="H22" s="3">
+        <f>F22*8</f>
         <v>16.426396319999998</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="H22" s="3"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="J22" s="7"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M22" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O22" s="161" t="s">
+        <v>477</v>
+      </c>
+      <c r="P22" s="162">
+        <v>190</v>
+      </c>
+      <c r="Q22" s="162" t="s">
+        <v>479</v>
+      </c>
+      <c r="R22" s="163">
+        <f t="shared" si="3"/>
+        <v>13.404120000000001</v>
+      </c>
+      <c r="S22" s="162" t="s">
+        <v>480</v>
+      </c>
+      <c r="T22" s="164"/>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="H23" s="3"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M23" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>152</v>
+      </c>
+      <c r="B24" t="s">
         <v>153</v>
       </c>
-      <c r="B23" t="s">
-        <v>154</v>
-      </c>
-      <c r="D23" t="s">
-        <v>168</v>
-      </c>
-      <c r="E23">
+      <c r="D24" t="s">
+        <v>167</v>
+      </c>
+      <c r="E24">
         <v>90</v>
-      </c>
-      <c r="F23" s="3">
-        <f>E23*$E$1</f>
-        <v>3.1746599999999998</v>
-      </c>
-      <c r="H23" s="3"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>156</v>
-      </c>
-      <c r="B24" t="s">
-        <v>155</v>
-      </c>
-      <c r="D24" t="s">
-        <v>169</v>
-      </c>
-      <c r="E24">
-        <v>135</v>
       </c>
       <c r="F24" s="3">
         <f>E24*$E$1</f>
-        <v>4.7619899999999999</v>
+        <v>3.1746599999999998</v>
       </c>
       <c r="H24" s="3"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J24" s="7"/>
+      <c r="K24" s="7"/>
+      <c r="L24" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M24" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>167</v>
-      </c>
-      <c r="B25">
-        <v>2.5</v>
+        <v>155</v>
+      </c>
+      <c r="B25" t="s">
+        <v>154</v>
       </c>
       <c r="D25" t="s">
-        <v>206</v>
+        <v>267</v>
       </c>
       <c r="E25">
-        <v>119.44</v>
+        <v>135</v>
       </c>
       <c r="F25" s="3">
         <f>E25*$E$1</f>
-        <v>4.2131265600000001</v>
-      </c>
-      <c r="G25" t="s">
-        <v>174</v>
-      </c>
-      <c r="H25" s="3">
-        <f>F25*2</f>
-        <v>8.4262531200000002</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+        <v>4.7619899999999999</v>
+      </c>
+      <c r="H25" s="3"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="7"/>
+      <c r="L25" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M25" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>166</v>
+      </c>
       <c r="B26">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="D26" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="E26">
-        <v>180</v>
+        <v>119.44</v>
       </c>
       <c r="F26" s="3">
         <f>E26*$E$1</f>
-        <v>6.3493199999999996</v>
+        <v>4.2131265600000001</v>
       </c>
       <c r="G26" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H26" s="3">
         <f>F26*2</f>
-        <v>12.698639999999999</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+        <v>8.4262531200000002</v>
+      </c>
+      <c r="J26" s="7"/>
+      <c r="K26" s="7"/>
+      <c r="L26" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M26" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B27">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="D27" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="E27">
-        <v>238.88</v>
+        <v>180</v>
       </c>
       <c r="F27" s="3">
         <f>E27*$E$1</f>
-        <v>8.4262531200000002</v>
+        <v>6.3493199999999996</v>
       </c>
       <c r="G27" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H27" s="3">
         <f>F27*2</f>
+        <v>12.698639999999999</v>
+      </c>
+      <c r="J27" s="7"/>
+      <c r="K27" s="7"/>
+      <c r="L27" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M27" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B28">
+        <v>5</v>
+      </c>
+      <c r="D28" t="s">
+        <v>205</v>
+      </c>
+      <c r="E28">
+        <v>238.88</v>
+      </c>
+      <c r="F28" s="3">
+        <f>E28*$E$1</f>
+        <v>8.4262531200000002</v>
+      </c>
+      <c r="G28" t="s">
+        <v>172</v>
+      </c>
+      <c r="H28" s="3">
+        <f>F28*2</f>
         <v>16.85250624</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>184</v>
-      </c>
-      <c r="C28" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J28" s="7"/>
+      <c r="K28" s="7"/>
+      <c r="L28" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M28" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B29">
+        <v>6</v>
+      </c>
+      <c r="D29" t="s">
+        <v>268</v>
+      </c>
       <c r="F29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="J29" s="7"/>
+      <c r="K29" s="7"/>
+      <c r="L29" s="12"/>
+      <c r="M29" s="12"/>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>181</v>
+      </c>
+      <c r="C30" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="F31" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AT/Materials.xlsx
+++ b/AT/Materials.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wellspan-my.sharepoint.com/personal/dsmith14_wellspan_org/Documents/Documents/GitHub/dps/AT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2319" documentId="13_ncr:1_{7E8DFDA2-3B81-4DBD-A379-3D4479E4AEB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7853741-BF2A-4710-9A01-2732E3FB3EDF}"/>
+  <xr:revisionPtr revIDLastSave="131" documentId="8_{C7F6FACF-983A-4174-A2EA-A87A6F163CFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED8533CD-84E2-4911-A449-642EC21D6D95}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="1200" windowWidth="26625" windowHeight="14610" activeTab="2" xr2:uid="{362FB22F-6BD6-431B-94C9-F0870D854534}"/>
+    <workbookView xWindow="885" yWindow="510" windowWidth="27525" windowHeight="15225" activeTab="2" xr2:uid="{362FB22F-6BD6-431B-94C9-F0870D854534}"/>
   </bookViews>
   <sheets>
     <sheet name="Materials" sheetId="1" r:id="rId1"/>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="508">
   <si>
     <t>piping slide</t>
   </si>
@@ -1014,12 +1014,6 @@
     <t>420D Robic</t>
   </si>
   <si>
-    <t>HyperD 300</t>
-  </si>
-  <si>
-    <t>Hex 2.2 PU3000</t>
-  </si>
-  <si>
     <t>102x46</t>
   </si>
   <si>
@@ -1074,9 +1068,6 @@
     <t>mil-spec webbing 3/4" 25'</t>
   </si>
   <si>
-    <t>xeon sil .9 oz</t>
-  </si>
-  <si>
     <t>hexon 1.0 oz</t>
   </si>
   <si>
@@ -1146,12 +1137,6 @@
     <t>cannot find</t>
   </si>
   <si>
-    <t>Argon .49</t>
-  </si>
-  <si>
-    <t>210D Robic</t>
-  </si>
-  <si>
     <t>spacer mesh 1/4" per foot</t>
   </si>
   <si>
@@ -1254,9 +1239,6 @@
     <t>Bugnet</t>
   </si>
   <si>
-    <t>webbing 1" - 2'</t>
-  </si>
-  <si>
     <t>Buckle 1"</t>
   </si>
   <si>
@@ -1290,15 +1272,6 @@
     <t>1-3</t>
   </si>
   <si>
-    <t>Order 1</t>
-  </si>
-  <si>
-    <t>Order 3</t>
-  </si>
-  <si>
-    <t>Order 2</t>
-  </si>
-  <si>
     <t>Order 4</t>
   </si>
   <si>
@@ -1380,9 +1353,6 @@
     <t>RS &amp; Dutch</t>
   </si>
   <si>
-    <t>Order 1-4</t>
-  </si>
-  <si>
     <t>-OR- 36L x 56W</t>
   </si>
   <si>
@@ -1522,6 +1492,111 @@
   </si>
   <si>
     <t>L</t>
+  </si>
+  <si>
+    <t>Order 6</t>
+  </si>
+  <si>
+    <t>36x58</t>
+  </si>
+  <si>
+    <t>sq yds</t>
+  </si>
+  <si>
+    <t>1,2,3</t>
+  </si>
+  <si>
+    <t>velcro</t>
+  </si>
+  <si>
+    <t>Argon 90 charcoal</t>
+  </si>
+  <si>
+    <t>Argon 67</t>
+  </si>
+  <si>
+    <t>Argon 49</t>
+  </si>
+  <si>
+    <t>Argon 90</t>
+  </si>
+  <si>
+    <t>both</t>
+  </si>
+  <si>
+    <t>and use current 5oz UQ</t>
+  </si>
+  <si>
+    <t>make this a TQ. See above</t>
+  </si>
+  <si>
+    <t>make 2nd top quilt 3.5oz</t>
+  </si>
+  <si>
+    <t>3yd 6oz &amp; 2 yd 3.5oz</t>
+  </si>
+  <si>
+    <t>add 1/2yd 6oz to 3.5oz TQ</t>
+  </si>
+  <si>
+    <t>tapperd &amp; sewn waist down</t>
+  </si>
+  <si>
+    <t>future if 5oz UQ is not warm</t>
+  </si>
+  <si>
+    <t>Total $129.33</t>
+  </si>
+  <si>
+    <t>Ordered 7/25/25 #245630</t>
+  </si>
+  <si>
+    <t>food bag and rain kilt optional</t>
+  </si>
+  <si>
+    <t>Hex 2.2 PU3000 - 70d</t>
+  </si>
+  <si>
+    <t>HyperD 300 - 300d</t>
+  </si>
+  <si>
+    <t>210D Robic - 210d</t>
+  </si>
+  <si>
+    <t>RSBTR $87.46</t>
+  </si>
+  <si>
+    <t>13, 6 partial</t>
+  </si>
+  <si>
+    <t>+6</t>
+  </si>
+  <si>
+    <t>Redesign to make it partial</t>
+  </si>
+  <si>
+    <t>cover head to waist only</t>
+  </si>
+  <si>
+    <t>nano no-seem .67 oz (7 yds)</t>
+  </si>
+  <si>
+    <t>The Ultimate Hang half bug net 72" x 55" (.67 noseeum)</t>
+  </si>
+  <si>
+    <t>webbing 1" - 2' ( or 1/2")</t>
+  </si>
+  <si>
+    <t>Xenon sil .9 oz</t>
+  </si>
+  <si>
+    <t>Xenon waterproof for bottom</t>
+  </si>
+  <si>
+    <t>D rings 1/2" (2)</t>
+  </si>
+  <si>
+    <t>Make items above plus</t>
   </si>
 </sst>
 </file>
@@ -1604,7 +1679,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1680,6 +1755,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1907,7 +1994,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="168">
+  <cellXfs count="179">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2098,9 +2185,6 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="8" fillId="5" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -2213,6 +2297,36 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2841,7 +2955,7 @@
         <v>13.5</v>
       </c>
       <c r="N10" s="3">
-        <f t="shared" ref="N10" si="1">M10*L10</f>
+        <f>M10*L10</f>
         <v>27</v>
       </c>
     </row>
@@ -3171,7 +3285,7 @@
         <v>7.5</v>
       </c>
       <c r="N21" s="3">
-        <f t="shared" ref="N21:N29" si="2">M21*L21</f>
+        <f t="shared" ref="N21:N29" si="1">M21*L21</f>
         <v>37.5</v>
       </c>
       <c r="O21" s="3"/>
@@ -3198,7 +3312,7 @@
         <v>4.5</v>
       </c>
       <c r="N22" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3248,7 +3362,7 @@
         <v>7</v>
       </c>
       <c r="N24" s="3">
-        <f t="shared" ref="N24" si="3">M24*L24</f>
+        <f>M24*L24</f>
         <v>14</v>
       </c>
       <c r="O24" s="12">
@@ -3374,7 +3488,7 @@
         <v>3.9</v>
       </c>
       <c r="N28" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>31.2</v>
       </c>
       <c r="O28" s="12">
@@ -3393,7 +3507,7 @@
       <c r="K29" s="10"/>
       <c r="M29" s="3"/>
       <c r="N29" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3641,7 +3755,7 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
@@ -4140,7 +4254,7 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="F39" s="20"/>
       <c r="G39" t="s">
@@ -4295,7 +4409,7 @@
         <v>7</v>
       </c>
       <c r="J46" s="30">
-        <f t="shared" ref="J46" si="1">I46*H46</f>
+        <f>I46*H46</f>
         <v>0</v>
       </c>
     </row>
@@ -4382,7 +4496,7 @@
         <v>3.9</v>
       </c>
       <c r="J50" s="30">
-        <f t="shared" ref="J50:J51" si="2">I50*H50</f>
+        <f>I50*H50</f>
         <v>0</v>
       </c>
       <c r="K50" t="s">
@@ -4405,7 +4519,7 @@
         <v>2</v>
       </c>
       <c r="J51" s="30">
-        <f t="shared" si="2"/>
+        <f>I51*H51</f>
         <v>0</v>
       </c>
     </row>
@@ -4450,10 +4564,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{458BE52D-397A-4267-A4EC-33DE3608C71C}">
-  <dimension ref="A1:AB124"/>
+  <dimension ref="A1:AB127"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.28515625" customWidth="1"/>
     <col min="2" max="2" width="26.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.5703125" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -4472,8 +4586,8 @@
     <col min="20" max="20" width="7.5703125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="7.28515625" customWidth="1"/>
     <col min="22" max="22" width="5.140625" customWidth="1"/>
-    <col min="23" max="23" width="5.28515625" customWidth="1"/>
-    <col min="24" max="24" width="7" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.28515625" customWidth="1"/>
+    <col min="24" max="24" width="7.5703125" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="3.140625" bestFit="1" customWidth="1"/>
     <col min="26" max="27" width="3.28515625" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="5" bestFit="1" customWidth="1"/>
@@ -4555,18 +4669,16 @@
         <f>C3*$A$5</f>
         <v>19.5</v>
       </c>
-      <c r="F3" s="33">
-        <v>2.5</v>
-      </c>
+      <c r="F3" s="33"/>
       <c r="G3" s="35">
         <v>14.98</v>
       </c>
-      <c r="H3" s="35">
+      <c r="H3" s="35" t="str">
         <f>IF((G3*F3)=0,"",G3*F3)</f>
-        <v>37.450000000000003</v>
+        <v/>
       </c>
       <c r="I3" s="34"/>
-      <c r="J3" s="147" t="str">
+      <c r="J3" s="146" t="str">
         <f>IF(ISBLANK(A3),"",A3)</f>
         <v>Top Quilt</v>
       </c>
@@ -4597,7 +4709,7 @@
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" s="20" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B4" s="38" t="s">
         <v>277</v>
@@ -4609,20 +4721,22 @@
         <v>159</v>
       </c>
       <c r="E4" s="36">
-        <f t="shared" ref="E4" si="0">C4*$A$5</f>
+        <f>C4*$A$5</f>
         <v>11.700000000000001</v>
       </c>
-      <c r="F4" s="33"/>
+      <c r="F4" s="33">
+        <v>0</v>
+      </c>
       <c r="G4" s="35">
         <v>9.6300000000000008</v>
       </c>
       <c r="H4" s="35" t="str">
-        <f t="shared" ref="H4:H84" si="1">IF((G4*F4)=0,"",G4*F4)</f>
+        <f t="shared" ref="H4:H86" si="0">IF((G4*F4)=0,"",G4*F4)</f>
         <v/>
       </c>
       <c r="I4" s="34"/>
-      <c r="J4" s="148" t="str">
-        <f t="shared" ref="J4:J68" si="2">IF(ISBLANK(A4),"",A4)</f>
+      <c r="J4" s="147" t="str">
+        <f t="shared" ref="J4:J40" si="1">IF(ISBLANK(A4),"",A4)</f>
         <v>54x78</v>
       </c>
       <c r="K4" t="s">
@@ -4635,7 +4749,7 @@
         <v>159</v>
       </c>
       <c r="N4" s="36">
-        <f t="shared" ref="N4:N10" si="3">L4*$A$5</f>
+        <f t="shared" ref="N4:N10" si="2">L4*$A$5</f>
         <v>11.700000000000001</v>
       </c>
       <c r="O4" s="33"/>
@@ -4643,7 +4757,7 @@
         <v>12</v>
       </c>
       <c r="Q4" s="35" t="str">
-        <f t="shared" ref="Q4:Q84" si="4">IF((P4*O4)=0,"",P4*O4)</f>
+        <f t="shared" ref="Q4:Q86" si="3">IF((P4*O4)=0,"",P4*O4)</f>
         <v/>
       </c>
       <c r="T4" s="3">
@@ -4651,7 +4765,7 @@
         <v>23.855</v>
       </c>
       <c r="U4" t="s">
-        <v>465</v>
+        <v>455</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.25">
@@ -4660,7 +4774,7 @@
         <v>3.25</v>
       </c>
       <c r="B5" s="38" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="C5" s="20"/>
       <c r="D5" s="21"/>
@@ -4668,16 +4782,16 @@
       <c r="F5" s="33"/>
       <c r="G5" s="35"/>
       <c r="H5" s="35" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I5" s="34"/>
+      <c r="J5" s="147">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I5" s="34"/>
-      <c r="J5" s="148">
-        <f t="shared" si="2"/>
         <v>3.25</v>
       </c>
       <c r="K5" s="66" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="L5" s="20"/>
       <c r="M5" s="21"/>
@@ -4685,20 +4799,24 @@
       <c r="O5" s="33"/>
       <c r="P5" s="35"/>
       <c r="Q5" s="35" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="S5" s="30"/>
       <c r="T5" s="3">
         <f>E16+E17</f>
         <v>21.204444444444444</v>
       </c>
       <c r="U5" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>488</v>
+      </c>
       <c r="B6" s="38" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="C6" s="20"/>
       <c r="D6" s="21"/>
@@ -4706,16 +4824,16 @@
       <c r="F6" s="33"/>
       <c r="G6" s="35"/>
       <c r="H6" s="35" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I6" s="34"/>
+      <c r="J6" s="147" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I6" s="34"/>
-      <c r="J6" s="148" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>tapperd &amp; sewn waist down</v>
       </c>
       <c r="K6" s="66" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="L6" s="20"/>
       <c r="M6" s="21"/>
@@ -4723,7 +4841,7 @@
       <c r="O6" s="33"/>
       <c r="P6" s="35"/>
       <c r="Q6" s="35" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="T6" s="3">
@@ -4731,13 +4849,15 @@
         <v>2.8162152777777778</v>
       </c>
       <c r="U6" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A7" s="20"/>
+      <c r="A7" s="20" t="s">
+        <v>485</v>
+      </c>
       <c r="B7" s="38" t="s">
-        <v>213</v>
+        <v>479</v>
       </c>
       <c r="C7" s="20">
         <v>0.67</v>
@@ -4751,16 +4871,16 @@
       </c>
       <c r="F7" s="33"/>
       <c r="G7" s="35">
-        <v>10.7</v>
+        <v>11.45</v>
       </c>
       <c r="H7" s="35" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I7" s="34"/>
+      <c r="J7" s="147" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I7" s="34"/>
-      <c r="J7" s="148" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>make 2nd top quilt 3.5oz</v>
       </c>
       <c r="K7" t="s">
         <v>291</v>
@@ -4772,22 +4892,26 @@
         <v>159</v>
       </c>
       <c r="N7" s="36">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2.145</v>
       </c>
-      <c r="O7" s="33"/>
+      <c r="O7" s="33">
+        <v>5</v>
+      </c>
       <c r="P7" s="35">
         <v>12.75</v>
       </c>
-      <c r="Q7" s="35" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+      <c r="Q7" s="35">
+        <f t="shared" si="3"/>
+        <v>63.75</v>
       </c>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A8" s="20"/>
+      <c r="A8" s="20" t="s">
+        <v>483</v>
+      </c>
       <c r="B8" s="38" t="s">
-        <v>214</v>
+        <v>481</v>
       </c>
       <c r="C8" s="20">
         <v>0.9</v>
@@ -4803,16 +4927,16 @@
         <v>5</v>
       </c>
       <c r="G8" s="35">
-        <v>8.0299999999999994</v>
+        <v>8.59</v>
       </c>
       <c r="H8" s="35">
         <f>IF((G8*F8)=0,"",G8*F8)</f>
-        <v>40.15</v>
+        <v>42.95</v>
       </c>
       <c r="I8" s="34"/>
-      <c r="J8" s="148" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="J8" s="147" t="str">
+        <f t="shared" si="1"/>
+        <v>and use current 5oz UQ</v>
       </c>
       <c r="K8" t="s">
         <v>292</v>
@@ -4824,24 +4948,24 @@
         <v>159</v>
       </c>
       <c r="N8" s="36">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2.9250000000000003</v>
       </c>
-      <c r="O8" s="33">
-        <v>5</v>
-      </c>
+      <c r="O8" s="33"/>
       <c r="P8" s="35">
         <v>10</v>
       </c>
-      <c r="Q8" s="35">
-        <f t="shared" si="4"/>
-        <v>50</v>
+      <c r="Q8" s="35" t="str">
+        <f t="shared" si="3"/>
+        <v/>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A9" s="20"/>
+      <c r="A9" s="21" t="s">
+        <v>486</v>
+      </c>
       <c r="B9" s="38" t="s">
-        <v>333</v>
+        <v>504</v>
       </c>
       <c r="C9" s="20">
         <v>0.93</v>
@@ -4858,13 +4982,13 @@
         <v>6.42</v>
       </c>
       <c r="H9" s="35" t="str">
-        <f t="shared" ref="H9:H25" si="5">IF((G9*F9)=0,"",G9*F9)</f>
+        <f t="shared" ref="H9:H26" si="4">IF((G9*F9)=0,"",G9*F9)</f>
         <v/>
       </c>
       <c r="I9" s="34"/>
-      <c r="J9" s="148" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="J9" s="147" t="str">
+        <f t="shared" si="1"/>
+        <v>3yd 6oz &amp; 2 yd 3.5oz</v>
       </c>
       <c r="K9" t="s">
         <v>294</v>
@@ -4876,7 +5000,7 @@
         <v>159</v>
       </c>
       <c r="N9" s="36">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>3.25</v>
       </c>
       <c r="O9" s="33"/>
@@ -4884,38 +5008,40 @@
         <v>6.6</v>
       </c>
       <c r="Q9" s="35" t="str">
-        <f t="shared" ref="Q9:Q12" si="6">IF((P9*O9)=0,"",P9*O9)</f>
+        <f>IF((P9*O9)=0,"",P9*O9)</f>
         <v/>
       </c>
       <c r="U9" s="2" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="V9" s="2" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="X9" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="Y9" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="Z9" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="AA9" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="Y9" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="Z9" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="AA9" s="2" t="s">
-        <v>398</v>
-      </c>
       <c r="AB9" s="2" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A10" s="20"/>
+      <c r="A10" s="21" t="s">
+        <v>487</v>
+      </c>
       <c r="B10" s="38" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C10" s="20">
         <v>1.05</v>
@@ -4932,13 +5058,13 @@
         <v>7.22</v>
       </c>
       <c r="H10" s="35" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I10" s="34"/>
-      <c r="J10" s="148" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="J10" s="147" t="str">
+        <f t="shared" si="1"/>
+        <v>add 1/2yd 6oz to 3.5oz TQ</v>
       </c>
       <c r="K10" t="s">
         <v>295</v>
@@ -4950,7 +5076,7 @@
         <v>7</v>
       </c>
       <c r="N10" s="36">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>3.5750000000000002</v>
       </c>
       <c r="O10" s="33"/>
@@ -4958,11 +5084,11 @@
         <v>6.5</v>
       </c>
       <c r="Q10" s="35" t="str">
-        <f t="shared" si="6"/>
+        <f>IF((P10*O10)=0,"",P10*O10)</f>
         <v/>
       </c>
       <c r="S10" s="70" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="T10" s="75">
         <f>SUM(U10:AB10)</f>
@@ -4988,12 +5114,12 @@
         <v>3.96</v>
       </c>
       <c r="H11" s="35" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I11" s="34"/>
-      <c r="J11" s="148" t="str">
-        <f t="shared" si="2"/>
+      <c r="J11" s="147" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K11" t="s">
@@ -5009,14 +5135,14 @@
         <v>5.25</v>
       </c>
       <c r="Q11" s="35">
-        <f t="shared" si="6"/>
+        <f>IF((P11*O11)=0,"",P11*O11)</f>
         <v>5.25</v>
       </c>
       <c r="S11" s="70" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="T11" s="75">
-        <f t="shared" ref="T11:T17" si="7">SUM(U11:AB11)</f>
+        <f t="shared" ref="T11:T17" si="5">SUM(U11:AB11)</f>
         <v>39</v>
       </c>
       <c r="U11">
@@ -5050,12 +5176,12 @@
         <v>4.55</v>
       </c>
       <c r="H12" s="35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>4.55</v>
       </c>
       <c r="I12" s="34"/>
-      <c r="J12" s="148" t="str">
-        <f t="shared" si="2"/>
+      <c r="J12" s="147" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K12" t="s">
@@ -5069,14 +5195,14 @@
         <v>4.5</v>
       </c>
       <c r="Q12" s="35" t="str">
-        <f t="shared" si="6"/>
+        <f>IF((P12*O12)=0,"",P12*O12)</f>
         <v/>
       </c>
       <c r="S12" s="71" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="T12" s="75">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>13</v>
       </c>
       <c r="U12">
@@ -5098,7 +5224,7 @@
     <row r="13" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A13" s="20"/>
       <c r="B13" s="46" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="C13" s="20"/>
       <c r="D13" s="21"/>
@@ -5106,15 +5232,15 @@
       <c r="F13" s="33"/>
       <c r="G13" s="35"/>
       <c r="H13" s="35" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I13" s="34"/>
-      <c r="J13" s="148" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K13" s="139" t="s">
+      <c r="J13" s="147" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K13" s="138" t="s">
         <v>289</v>
       </c>
       <c r="L13" s="20"/>
@@ -5126,10 +5252,10 @@
       </c>
       <c r="Q13" s="35"/>
       <c r="S13" s="71" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="T13" s="75">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="X13">
@@ -5139,7 +5265,7 @@
     <row r="14" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="20"/>
       <c r="B14" s="50" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="21"/>
@@ -5149,16 +5275,16 @@
       </c>
       <c r="G14" s="35"/>
       <c r="H14" s="35" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I14" s="34"/>
-      <c r="J14" s="148" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K14" s="140" t="s">
-        <v>316</v>
+      <c r="J14" s="147" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K14" s="139" t="s">
+        <v>314</v>
       </c>
       <c r="L14" s="20"/>
       <c r="M14" s="21"/>
@@ -5169,10 +5295,10 @@
       <c r="P14" s="35"/>
       <c r="Q14" s="35"/>
       <c r="S14" s="72" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="T14" s="75">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>8</v>
       </c>
       <c r="V14">
@@ -5194,11 +5320,11 @@
       </c>
       <c r="H15" s="65">
         <f>SUM(H3:H14)</f>
-        <v>82.149999999999991</v>
+        <v>47.5</v>
       </c>
       <c r="I15" s="34"/>
-      <c r="J15" s="148" t="str">
-        <f t="shared" si="2"/>
+      <c r="J15" s="147" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K15" s="66"/>
@@ -5211,13 +5337,13 @@
       </c>
       <c r="Q15" s="65">
         <f>SUM(Q3:Q14)</f>
-        <v>90.875</v>
+        <v>104.625</v>
       </c>
       <c r="S15" s="73" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="T15" s="75">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>32</v>
       </c>
       <c r="W15">
@@ -5242,18 +5368,18 @@
         <v>17.333333333333332</v>
       </c>
       <c r="F16" s="33">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="G16" s="35">
         <v>14.98</v>
       </c>
       <c r="H16" s="35">
-        <f t="shared" si="5"/>
-        <v>37.450000000000003</v>
+        <f t="shared" si="4"/>
+        <v>44.94</v>
       </c>
       <c r="I16" s="34"/>
-      <c r="J16" s="147" t="str">
-        <f t="shared" si="2"/>
+      <c r="J16" s="146" t="str">
+        <f t="shared" si="1"/>
         <v>Under Quilt</v>
       </c>
       <c r="K16" s="66" t="s">
@@ -5273,14 +5399,14 @@
         <v>14.25</v>
       </c>
       <c r="Q16" s="35">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>35.625</v>
       </c>
       <c r="S16" s="74" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="T16" s="75">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="Y16">
@@ -5292,10 +5418,10 @@
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A17" s="20" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>213</v>
+        <v>479</v>
       </c>
       <c r="C17" s="20">
         <v>0.67</v>
@@ -5309,15 +5435,15 @@
       </c>
       <c r="F17" s="33"/>
       <c r="G17" s="35">
-        <v>10.7</v>
+        <v>11.45</v>
       </c>
       <c r="H17" s="35" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I17" s="34"/>
-      <c r="J17" s="148" t="str">
-        <f t="shared" si="2"/>
+      <c r="J17" s="147" t="str">
+        <f t="shared" si="1"/>
         <v>78x48</v>
       </c>
       <c r="K17" s="66" t="s">
@@ -5330,22 +5456,24 @@
         <v>159</v>
       </c>
       <c r="N17" s="36">
-        <f t="shared" ref="N17:N18" si="8">L17*$A$5</f>
+        <f>L17*$A$5</f>
         <v>2.145</v>
       </c>
-      <c r="O17" s="33"/>
+      <c r="O17" s="33">
+        <v>5</v>
+      </c>
       <c r="P17" s="35">
         <v>12.75</v>
       </c>
-      <c r="Q17" s="35" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+      <c r="Q17" s="35">
+        <f t="shared" si="3"/>
+        <v>63.75</v>
       </c>
       <c r="S17" s="74" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="T17" s="75">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>17</v>
       </c>
       <c r="Y17">
@@ -5361,7 +5489,7 @@
         <v>2.8888888888888888</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>214</v>
+        <v>481</v>
       </c>
       <c r="C18" s="20">
         <v>0.9</v>
@@ -5377,15 +5505,15 @@
         <v>5</v>
       </c>
       <c r="G18" s="35">
-        <v>8.0299999999999994</v>
+        <v>8.59</v>
       </c>
       <c r="H18" s="35">
-        <f t="shared" si="5"/>
-        <v>40.15</v>
+        <f t="shared" si="4"/>
+        <v>42.95</v>
       </c>
       <c r="I18" s="34"/>
-      <c r="J18" s="148">
-        <f t="shared" si="2"/>
+      <c r="J18" s="147">
+        <f t="shared" si="1"/>
         <v>2.8888888888888888</v>
       </c>
       <c r="K18" s="66" t="s">
@@ -5398,46 +5526,52 @@
         <v>159</v>
       </c>
       <c r="N18" s="36">
-        <f t="shared" si="8"/>
+        <f>L18*$A$5</f>
         <v>2.9250000000000003</v>
       </c>
-      <c r="O18" s="33">
-        <v>5</v>
-      </c>
+      <c r="O18" s="33"/>
       <c r="P18" s="35">
         <v>10</v>
       </c>
-      <c r="Q18" s="35">
-        <f t="shared" si="4"/>
-        <v>50</v>
+      <c r="Q18" s="35" t="str">
+        <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="S18" s="74"/>
       <c r="T18" s="75"/>
     </row>
     <row r="19" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>484</v>
+      </c>
       <c r="B19" s="38" t="s">
-        <v>79</v>
-      </c>
-      <c r="C19" s="20"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="33">
-        <v>1</v>
-      </c>
+        <v>504</v>
+      </c>
+      <c r="C19" s="20">
+        <v>0.93</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E19" s="36">
+        <f>C19*$A$5*2</f>
+        <v>6.0449999999999999</v>
+      </c>
+      <c r="F19" s="33"/>
       <c r="G19" s="35">
-        <v>3.96</v>
-      </c>
-      <c r="H19" s="35">
-        <f t="shared" si="5"/>
-        <v>3.96</v>
+        <v>6.42</v>
+      </c>
+      <c r="H19" s="35" t="str">
+        <f t="shared" si="4"/>
+        <v/>
       </c>
       <c r="I19" s="34"/>
-      <c r="J19" s="148" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="J19" s="147" t="str">
+        <f t="shared" si="1"/>
+        <v>make this a TQ. See above</v>
       </c>
       <c r="K19" s="66" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="L19" s="20"/>
       <c r="M19" s="21"/>
@@ -5449,44 +5583,46 @@
         <v>4.5</v>
       </c>
       <c r="Q19" s="35">
+        <f t="shared" si="3"/>
+        <v>4.5</v>
+      </c>
+      <c r="S19" s="107" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A20" s="20" t="s">
+        <v>489</v>
+      </c>
+      <c r="B20" s="38" t="s">
+        <v>79</v>
+      </c>
+      <c r="C20" s="20"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="33">
+        <v>1</v>
+      </c>
+      <c r="G20" s="35">
+        <v>3.96</v>
+      </c>
+      <c r="H20" s="35">
         <f t="shared" si="4"/>
-        <v>4.5</v>
-      </c>
-      <c r="S19" s="107" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A20" s="20"/>
-      <c r="B20" s="38" t="s">
-        <v>326</v>
-      </c>
-      <c r="C20" s="20">
-        <v>49.9</v>
-      </c>
-      <c r="D20" s="21" t="s">
-        <v>161</v>
-      </c>
-      <c r="G20" s="35">
-        <v>4.01</v>
-      </c>
-      <c r="H20" s="35" t="str">
-        <f t="shared" si="5"/>
-        <v/>
+        <v>3.96</v>
       </c>
       <c r="I20" s="34"/>
-      <c r="J20" s="148" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="J20" s="147" t="str">
+        <f t="shared" si="1"/>
+        <v>future if 5oz UQ is not warm</v>
       </c>
       <c r="K20" s="66" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="L20" s="20">
         <v>6.6</v>
       </c>
       <c r="M20" s="21" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="N20" s="36"/>
       <c r="O20" s="33"/>
@@ -5494,7 +5630,7 @@
         <v>6.25</v>
       </c>
       <c r="Q20" s="35" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="R20" s="5"/>
@@ -5505,44 +5641,44 @@
         <v>65</v>
       </c>
       <c r="U20" s="78" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="V20" s="79"/>
       <c r="W20" s="80"/>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A21" s="20"/>
+      <c r="A21" s="20" t="s">
+        <v>505</v>
+      </c>
       <c r="B21" s="38" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C21" s="20">
-        <v>43.94</v>
+        <v>49.9</v>
       </c>
       <c r="D21" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="E21" s="36"/>
-      <c r="F21" s="33"/>
       <c r="G21" s="35">
-        <v>3.16</v>
+        <v>4.01</v>
       </c>
       <c r="H21" s="35" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I21" s="34"/>
-      <c r="J21" s="148" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="J21" s="147" t="str">
+        <f t="shared" si="1"/>
+        <v>Xenon waterproof for bottom</v>
       </c>
       <c r="K21" s="66" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="L21" s="20">
         <v>5</v>
       </c>
       <c r="M21" s="21" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="N21" s="36"/>
       <c r="O21" s="33"/>
@@ -5550,7 +5686,7 @@
         <v>5.75</v>
       </c>
       <c r="Q21" s="35" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="R21" s="5"/>
@@ -5560,7 +5696,7 @@
       </c>
       <c r="T21" s="82">
         <f>H15</f>
-        <v>82.149999999999991</v>
+        <v>47.5</v>
       </c>
       <c r="U21" s="83">
         <v>4</v>
@@ -5573,10 +5709,10 @@
     <row r="22" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A22" s="20"/>
       <c r="B22" s="38" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C22" s="20">
-        <v>27.49</v>
+        <v>43.94</v>
       </c>
       <c r="D22" s="21" t="s">
         <v>161</v>
@@ -5584,25 +5720,25 @@
       <c r="E22" s="36"/>
       <c r="F22" s="33"/>
       <c r="G22" s="35">
-        <v>2.25</v>
+        <v>3.16</v>
       </c>
       <c r="H22" s="35" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I22" s="34"/>
-      <c r="J22" s="148" t="str">
-        <f t="shared" si="2"/>
+      <c r="J22" s="147" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K22" s="66" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="L22" s="20">
         <v>3.6</v>
       </c>
       <c r="M22" s="21" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="N22" s="36"/>
       <c r="O22" s="33"/>
@@ -5610,7 +5746,7 @@
         <v>5.25</v>
       </c>
       <c r="Q22" s="35" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="R22" s="5"/>
@@ -5619,8 +5755,8 @@
         <v>Under Quilt</v>
       </c>
       <c r="T22" s="82">
-        <f>H26</f>
-        <v>82.999999999999986</v>
+        <f>H27</f>
+        <v>93.289999999999992</v>
       </c>
       <c r="U22" s="83">
         <v>5</v>
@@ -5632,24 +5768,30 @@
     </row>
     <row r="23" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A23" s="20"/>
-      <c r="B23" s="46" t="s">
-        <v>381</v>
-      </c>
-      <c r="C23" s="20"/>
-      <c r="D23" s="21"/>
+      <c r="B23" s="38" t="s">
+        <v>320</v>
+      </c>
+      <c r="C23" s="20">
+        <v>27.49</v>
+      </c>
+      <c r="D23" s="21" t="s">
+        <v>161</v>
+      </c>
       <c r="E23" s="36"/>
       <c r="F23" s="33"/>
-      <c r="G23" s="35"/>
+      <c r="G23" s="35">
+        <v>2.25</v>
+      </c>
       <c r="H23" s="35" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I23" s="34"/>
-      <c r="J23" s="148" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K23" s="139" t="s">
+      <c r="J23" s="147" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K23" s="138" t="s">
         <v>289</v>
       </c>
       <c r="L23" s="20"/>
@@ -5658,7 +5800,7 @@
       <c r="O23" s="33"/>
       <c r="P23" s="35"/>
       <c r="Q23" s="35" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="R23" s="5"/>
@@ -5667,8 +5809,8 @@
         <v>Griz Ariel Hammock</v>
       </c>
       <c r="T23" s="87">
-        <f>H36</f>
-        <v>38.440000000000005</v>
+        <f>H37</f>
+        <v>42.089999999999996</v>
       </c>
       <c r="U23" s="88">
         <v>3</v>
@@ -5680,8 +5822,8 @@
     </row>
     <row r="24" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A24" s="20"/>
-      <c r="B24" s="50" t="s">
-        <v>383</v>
+      <c r="B24" s="46" t="s">
+        <v>376</v>
       </c>
       <c r="C24" s="20"/>
       <c r="D24" s="21"/>
@@ -5689,16 +5831,16 @@
       <c r="F24" s="33"/>
       <c r="G24" s="35"/>
       <c r="H24" s="35" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I24" s="34"/>
-      <c r="J24" s="148" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K24" s="140" t="s">
-        <v>316</v>
+      <c r="J24" s="147" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K24" s="139" t="s">
+        <v>314</v>
       </c>
       <c r="L24" s="20"/>
       <c r="M24" s="21"/>
@@ -5706,19 +5848,19 @@
       <c r="O24" s="33"/>
       <c r="P24" s="35"/>
       <c r="Q24" s="35" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="R24" s="167" t="s">
-        <v>482</v>
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="R24" s="166" t="s">
+        <v>472</v>
       </c>
       <c r="S24" s="91" t="str">
         <f>A37</f>
         <v>Gathered End Hammock</v>
       </c>
       <c r="T24" s="92">
-        <f>H41</f>
-        <v>40.340000000000003</v>
+        <f>H43</f>
+        <v>38.56</v>
       </c>
       <c r="U24" s="93">
         <v>8</v>
@@ -5730,33 +5872,25 @@
     </row>
     <row r="25" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="20"/>
-      <c r="B25" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="C25" s="20">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="D25" s="21" t="s">
-        <v>161</v>
-      </c>
+      <c r="B25" s="50" t="s">
+        <v>378</v>
+      </c>
+      <c r="C25" s="20"/>
+      <c r="D25" s="21"/>
       <c r="E25" s="36"/>
-      <c r="F25" s="33">
-        <v>4</v>
-      </c>
-      <c r="G25" s="35">
-        <v>0.36</v>
-      </c>
-      <c r="H25" s="35">
-        <f t="shared" si="5"/>
-        <v>1.44</v>
+      <c r="F25" s="33"/>
+      <c r="G25" s="35"/>
+      <c r="H25" s="35" t="str">
+        <f t="shared" si="4"/>
+        <v/>
       </c>
       <c r="I25" s="34"/>
-      <c r="J25" s="148" t="str">
-        <f t="shared" si="2"/>
+      <c r="J25" s="147" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K25" s="66" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="L25" s="20"/>
       <c r="M25" s="21"/>
@@ -5768,19 +5902,19 @@
         <v>5</v>
       </c>
       <c r="Q25" s="35">
-        <f t="shared" ref="Q25" si="9">IF((P25*O25)=0,"",P25*O25)</f>
+        <f>IF((P25*O25)=0,"",P25*O25)</f>
         <v>5</v>
       </c>
-      <c r="R25" s="167" t="s">
-        <v>482</v>
+      <c r="R25" s="166" t="s">
+        <v>472</v>
       </c>
       <c r="S25" s="91" t="str">
-        <f>A42</f>
+        <f>A43</f>
         <v>Bug Net</v>
       </c>
       <c r="T25" s="92">
-        <f>H47</f>
-        <v>29.189999999999998</v>
+        <f>H49</f>
+        <v>31.22</v>
       </c>
       <c r="U25" s="93">
         <v>9</v>
@@ -5792,21 +5926,29 @@
     </row>
     <row r="26" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="20"/>
-      <c r="B26" s="38"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="21"/>
+      <c r="B26" s="38" t="s">
+        <v>375</v>
+      </c>
+      <c r="C26" s="20">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="D26" s="21" t="s">
+        <v>161</v>
+      </c>
       <c r="E26" s="36"/>
-      <c r="F26" s="33"/>
-      <c r="G26" s="64" t="s">
-        <v>65</v>
-      </c>
-      <c r="H26" s="65">
-        <f>SUM(H16:H25)</f>
-        <v>82.999999999999986</v>
+      <c r="F26" s="33">
+        <v>4</v>
+      </c>
+      <c r="G26" s="35">
+        <v>0.36</v>
+      </c>
+      <c r="H26" s="35">
+        <f t="shared" si="4"/>
+        <v>1.44</v>
       </c>
       <c r="I26" s="34"/>
-      <c r="J26" s="148" t="str">
-        <f t="shared" si="2"/>
+      <c r="J26" s="147" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K26" s="66"/>
@@ -5819,58 +5961,47 @@
       </c>
       <c r="Q26" s="65">
         <f>SUM(Q16:Q25)</f>
-        <v>95.125</v>
-      </c>
-      <c r="R26" s="167" t="s">
-        <v>482</v>
+        <v>108.875</v>
+      </c>
+      <c r="R26" s="166" t="s">
+        <v>472</v>
       </c>
       <c r="S26" s="96" t="str">
-        <f>A49</f>
+        <f>A50</f>
         <v>Back Pack</v>
       </c>
       <c r="T26" s="97">
-        <f>Q77+H77</f>
-        <v>65.52000000000001</v>
+        <f>Q79+H79</f>
+        <v>61.769999999999996</v>
       </c>
       <c r="U26" s="98">
         <v>6</v>
       </c>
       <c r="V26" s="99" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="W26" s="100"/>
       <c r="X26" s="30"/>
     </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="B27" s="38" t="s">
-        <v>279</v>
-      </c>
-      <c r="C27" s="20">
-        <v>1.6</v>
-      </c>
-      <c r="D27" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="E27" s="36">
-        <f>$A$29*C27</f>
-        <v>5.7925925925925927</v>
-      </c>
-      <c r="F27" s="33">
-        <v>3</v>
-      </c>
-      <c r="G27" s="35">
-        <v>6.42</v>
-      </c>
-      <c r="H27" s="35">
+      <c r="B27" s="38"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="36"/>
+      <c r="F27" s="33"/>
+      <c r="G27" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="H27" s="65">
+        <f>SUM(H16:H26)</f>
+        <v>93.289999999999992</v>
+      </c>
+      <c r="I27" s="34"/>
+      <c r="J27" s="146" t="str">
         <f t="shared" si="1"/>
-        <v>19.259999999999998</v>
-      </c>
-      <c r="I27" s="34"/>
-      <c r="J27" s="147" t="str">
-        <f t="shared" si="2"/>
         <v>Griz Ariel Hammock</v>
       </c>
       <c r="K27" s="66" t="s">
@@ -5890,19 +6021,19 @@
         <v>7.5</v>
       </c>
       <c r="Q27" s="35">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>22.5</v>
       </c>
-      <c r="R27" s="167" t="s">
-        <v>482</v>
+      <c r="R27" s="166" t="s">
+        <v>472</v>
       </c>
       <c r="S27" s="101" t="str">
-        <f>A86</f>
+        <f>A87</f>
         <v>Sleeping Bag Liner</v>
       </c>
       <c r="T27" s="102">
-        <f>H90</f>
-        <v>25.36</v>
+        <f>H92</f>
+        <v>26.86</v>
       </c>
       <c r="U27" s="103">
         <v>10</v>
@@ -5914,32 +6045,32 @@
     </row>
     <row r="28" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A28" s="20" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B28" s="38" t="s">
-        <v>337</v>
+        <v>279</v>
       </c>
       <c r="C28" s="20">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="D28" s="21" t="s">
         <v>159</v>
       </c>
       <c r="E28" s="36">
         <f>$A$29*C28</f>
-        <v>4.3444444444444441</v>
+        <v>5.7925925925925927</v>
       </c>
       <c r="F28" s="33"/>
       <c r="G28" s="35">
-        <v>6.69</v>
+        <v>6.87</v>
       </c>
       <c r="H28" s="35" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I28" s="34"/>
+      <c r="J28" s="147" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I28" s="34"/>
-      <c r="J28" s="148" t="str">
-        <f t="shared" si="2"/>
         <v>102x46</v>
       </c>
       <c r="K28" s="66"/>
@@ -5949,27 +6080,27 @@
       <c r="O28" s="33"/>
       <c r="P28" s="35"/>
       <c r="Q28" s="35" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="R28" s="167" t="s">
-        <v>482</v>
-      </c>
-      <c r="S28" s="121" t="str">
-        <f>A91</f>
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="R28" s="166" t="s">
+        <v>472</v>
+      </c>
+      <c r="S28" s="120" t="str">
+        <f>A92</f>
         <v>Food Bag (12.5 x 22)</v>
       </c>
-      <c r="T28" s="122">
-        <f>H95</f>
-        <v>27.560000000000002</v>
-      </c>
-      <c r="U28" s="123">
+      <c r="T28" s="121">
+        <f>H97</f>
+        <v>6.96</v>
+      </c>
+      <c r="U28" s="122">
         <v>11</v>
       </c>
-      <c r="V28" s="118" t="s">
+      <c r="V28" s="117" t="s">
         <v>280</v>
       </c>
-      <c r="W28" s="124"/>
+      <c r="W28" s="123"/>
     </row>
     <row r="29" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A29" s="37">
@@ -5977,24 +6108,31 @@
         <v>3.6203703703703702</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>79</v>
-      </c>
-      <c r="C29" s="20"/>
-      <c r="D29" s="21"/>
-      <c r="E29" s="36"/>
+        <v>334</v>
+      </c>
+      <c r="C29" s="20">
+        <v>1.2</v>
+      </c>
+      <c r="D29" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E29" s="36">
+        <f>$A$29*C29</f>
+        <v>4.3444444444444441</v>
+      </c>
       <c r="F29" s="33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G29" s="35">
-        <v>3.96</v>
+        <v>7.45</v>
       </c>
       <c r="H29" s="35">
+        <f t="shared" si="0"/>
+        <v>22.35</v>
+      </c>
+      <c r="I29" s="34"/>
+      <c r="J29" s="147">
         <f t="shared" si="1"/>
-        <v>3.96</v>
-      </c>
-      <c r="I29" s="34"/>
-      <c r="J29" s="148">
-        <f t="shared" si="2"/>
         <v>3.6203703703703702</v>
       </c>
       <c r="K29" s="66" t="s">
@@ -6010,63 +6148,61 @@
         <v>5.25</v>
       </c>
       <c r="Q29" s="35">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>5.25</v>
       </c>
-      <c r="R29" s="167" t="s">
-        <v>482</v>
-      </c>
-      <c r="S29" s="121" t="str">
-        <f>A98</f>
+      <c r="R29" s="166" t="s">
+        <v>472</v>
+      </c>
+      <c r="S29" s="120" t="str">
+        <f>A99</f>
         <v>Rain Kilt (30L x 48W)</v>
       </c>
-      <c r="T29" s="122">
-        <f>H102</f>
-        <v>48.163000000000004</v>
-      </c>
-      <c r="U29" s="123">
+      <c r="T29" s="121">
+        <f>H104</f>
+        <v>6.9630000000000001</v>
+      </c>
+      <c r="U29" s="122">
         <v>12</v>
       </c>
-      <c r="V29" s="118" t="s">
+      <c r="V29" s="117" t="s">
         <v>280</v>
       </c>
-      <c r="W29" s="124"/>
+      <c r="W29" s="123"/>
     </row>
     <row r="30" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A30" s="20" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="B30" s="38" t="s">
+        <v>79</v>
+      </c>
+      <c r="C30" s="20"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="36"/>
+      <c r="F30" s="33">
+        <v>1</v>
+      </c>
+      <c r="G30" s="35">
+        <v>3.96</v>
+      </c>
+      <c r="H30" s="35">
+        <f t="shared" si="0"/>
+        <v>3.96</v>
+      </c>
+      <c r="I30" s="34"/>
+      <c r="J30" s="147" t="str">
+        <f t="shared" si="1"/>
+        <v>with half bug net</v>
+      </c>
+      <c r="K30" s="66" t="s">
         <v>322</v>
-      </c>
-      <c r="C30" s="20">
-        <v>27.49</v>
-      </c>
-      <c r="D30" s="21" t="s">
-        <v>161</v>
-      </c>
-      <c r="E30" s="36"/>
-      <c r="F30" s="33"/>
-      <c r="G30" s="35">
-        <v>2.25</v>
-      </c>
-      <c r="H30" s="35" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I30" s="34"/>
-      <c r="J30" s="148" t="str">
-        <f t="shared" si="2"/>
-        <v>with half bug net</v>
-      </c>
-      <c r="K30" s="66" t="s">
-        <v>324</v>
       </c>
       <c r="L30" s="20">
         <v>3.6</v>
       </c>
       <c r="M30" s="21" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="N30" s="36"/>
       <c r="O30" s="33"/>
@@ -6074,19 +6210,19 @@
         <v>5.25</v>
       </c>
       <c r="Q30" s="35" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="R30" s="167" t="s">
-        <v>482</v>
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="R30" s="166" t="s">
+        <v>472</v>
       </c>
       <c r="S30" s="101" t="str">
-        <f>A103</f>
+        <f>A104</f>
         <v>Rain Pants</v>
       </c>
       <c r="T30" s="102">
-        <f>H108</f>
-        <v>17.88</v>
+        <f>H111</f>
+        <v>13.92</v>
       </c>
       <c r="U30" s="103">
         <v>7</v>
@@ -6098,28 +6234,27 @@
     </row>
     <row r="31" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A31" s="20"/>
-      <c r="B31" s="52" t="s">
-        <v>348</v>
-      </c>
-      <c r="C31">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="D31" t="s">
+      <c r="B31" s="38" t="s">
+        <v>320</v>
+      </c>
+      <c r="C31" s="20">
+        <v>27.49</v>
+      </c>
+      <c r="D31" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="F31">
-        <v>4</v>
-      </c>
+      <c r="E31" s="36"/>
+      <c r="F31" s="33"/>
       <c r="G31" s="35">
-        <v>1.5</v>
-      </c>
-      <c r="H31" s="35">
+        <v>2.25</v>
+      </c>
+      <c r="H31" s="35" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I31" s="34"/>
+      <c r="J31" s="147" t="str">
         <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="I31" s="34"/>
-      <c r="J31" s="148" t="str">
-        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K31" s="66"/>
@@ -6129,19 +6264,19 @@
       <c r="O31" s="33"/>
       <c r="P31" s="35"/>
       <c r="Q31" s="35" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="R31" s="167" t="s">
-        <v>482</v>
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="R31" s="166" t="s">
+        <v>472</v>
       </c>
       <c r="S31" s="86" t="str">
-        <f>A78</f>
+        <f>A79</f>
         <v>Amsteel 7/64</v>
       </c>
       <c r="T31" s="87">
-        <f>H81</f>
-        <v>24.6</v>
+        <f>H83</f>
+        <v>26.32</v>
       </c>
       <c r="U31" s="88">
         <v>1</v>
@@ -6154,20 +6289,31 @@
     <row r="32" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A32" s="20"/>
       <c r="B32" s="52" t="s">
-        <v>437</v>
-      </c>
-      <c r="G32" s="35"/>
+        <v>345</v>
+      </c>
+      <c r="C32">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D32" t="s">
+        <v>161</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32" s="35">
+        <v>1.61</v>
+      </c>
       <c r="H32" s="35" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I32" s="34"/>
+      <c r="J32" s="147" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I32" s="34"/>
-      <c r="J32" s="148" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K32" s="118" t="s">
-        <v>437</v>
+      <c r="K32" s="117" t="s">
+        <v>427</v>
       </c>
       <c r="L32" s="20"/>
       <c r="M32" s="21"/>
@@ -6175,19 +6321,19 @@
       <c r="O32" s="33"/>
       <c r="P32" s="35"/>
       <c r="Q32" s="35" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="R32" s="167" t="s">
-        <v>482</v>
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="R32" s="166" t="s">
+        <v>472</v>
       </c>
       <c r="S32" s="86" t="str">
-        <f>A82</f>
+        <f>A83</f>
         <v>Shock Cord</v>
       </c>
       <c r="T32" s="87">
-        <f>H85</f>
-        <v>9.1</v>
+        <f>H87</f>
+        <v>9.74</v>
       </c>
       <c r="U32" s="88">
         <v>2</v>
@@ -6197,26 +6343,23 @@
       </c>
       <c r="W32" s="90"/>
     </row>
-    <row r="33" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="20"/>
-      <c r="B33" s="53" t="s">
-        <v>355</v>
-      </c>
-      <c r="F33" s="33"/>
-      <c r="G33" s="35">
-        <v>6.15</v>
-      </c>
+      <c r="B33" s="52" t="s">
+        <v>427</v>
+      </c>
+      <c r="G33" s="35"/>
       <c r="H33" s="35" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I33" s="34"/>
+      <c r="J33" s="147" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I33" s="34"/>
-      <c r="J33" s="148" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K33" s="141" t="s">
-        <v>354</v>
+      <c r="K33" s="140" t="s">
+        <v>351</v>
       </c>
       <c r="L33" s="20"/>
       <c r="M33" s="21"/>
@@ -6226,57 +6369,48 @@
         <v>7.5</v>
       </c>
       <c r="Q33" s="35" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="R33" s="167" t="s">
-        <v>482</v>
-      </c>
-      <c r="S33" s="150" t="str">
-        <f>A113</f>
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="R33" s="166" t="s">
+        <v>472</v>
+      </c>
+      <c r="S33" s="149" t="str">
+        <f>A115</f>
         <v>Pullover/hoodie</v>
       </c>
-      <c r="T33" s="151">
-        <f>Q113</f>
+      <c r="T33" s="150">
+        <f>Q116</f>
         <v>54.5</v>
       </c>
-      <c r="U33" s="152">
+      <c r="U33" s="151">
         <v>13</v>
       </c>
-      <c r="V33" s="153" t="s">
-        <v>470</v>
+      <c r="V33" s="152" t="s">
+        <v>460</v>
       </c>
       <c r="W33" s="106"/>
     </row>
-    <row r="34" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="20"/>
-      <c r="B34" s="38" t="s">
+      <c r="B34" s="53" t="s">
         <v>352</v>
       </c>
-      <c r="C34" s="20">
-        <v>0.67</v>
-      </c>
-      <c r="D34" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="E34" s="36"/>
-      <c r="F34" s="33">
-        <v>2</v>
-      </c>
+      <c r="F34" s="33"/>
       <c r="G34" s="35">
-        <v>4.17</v>
-      </c>
-      <c r="H34" s="35">
+        <v>6.15</v>
+      </c>
+      <c r="H34" s="35" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I34" s="34"/>
+      <c r="J34" s="147" t="str">
         <f t="shared" si="1"/>
-        <v>8.34</v>
-      </c>
-      <c r="I34" s="34"/>
-      <c r="J34" s="148" t="str">
-        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K34" s="66" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="L34" s="20">
         <v>0.67</v>
@@ -6292,39 +6426,39 @@
         <v>5.5</v>
       </c>
       <c r="Q34" s="35">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>11</v>
       </c>
     </row>
-    <row r="35" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="20"/>
       <c r="B35" s="38" t="s">
-        <v>410</v>
+        <v>349</v>
       </c>
       <c r="C35" s="20">
-        <v>0.3</v>
+        <v>0.67</v>
       </c>
       <c r="D35" s="21" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E35" s="36"/>
       <c r="F35" s="33">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G35" s="35">
-        <v>0.22</v>
+        <v>4.46</v>
       </c>
       <c r="H35" s="35">
+        <f t="shared" si="0"/>
+        <v>13.379999999999999</v>
+      </c>
+      <c r="I35" s="34"/>
+      <c r="J35" s="147" t="str">
         <f t="shared" si="1"/>
-        <v>0.88</v>
-      </c>
-      <c r="I35" s="34"/>
-      <c r="J35" s="148" t="str">
-        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K35" s="56" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="L35" s="20"/>
       <c r="M35" s="21"/>
@@ -6336,31 +6470,42 @@
         <v>4.25</v>
       </c>
       <c r="Q35" s="35">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>4.25</v>
       </c>
-      <c r="S35" s="116" t="s">
+      <c r="S35" s="115" t="s">
         <v>65</v>
       </c>
-      <c r="T35" s="117">
+      <c r="T35" s="116">
         <f>SUM(T21:T33)</f>
-        <v>545.80300000000011</v>
-      </c>
-    </row>
-    <row r="36" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>459.69300000000004</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="20"/>
-      <c r="B36" s="55"/>
-      <c r="F36" s="33"/>
-      <c r="G36" s="64" t="s">
-        <v>65</v>
-      </c>
-      <c r="H36" s="65">
-        <f>SUM(H27:H35)</f>
-        <v>38.440000000000005</v>
+      <c r="B36" s="38" t="s">
+        <v>401</v>
+      </c>
+      <c r="C36" s="20">
+        <v>0.3</v>
+      </c>
+      <c r="D36" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="E36" s="36"/>
+      <c r="F36" s="33">
+        <v>10</v>
+      </c>
+      <c r="G36" s="35">
+        <v>0.24</v>
+      </c>
+      <c r="H36" s="35">
+        <f t="shared" si="0"/>
+        <v>2.4</v>
       </c>
       <c r="I36" s="34"/>
-      <c r="J36" s="148" t="str">
-        <f t="shared" si="2"/>
+      <c r="J36" s="147" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K36" s="56"/>
@@ -6375,37 +6520,24 @@
         <f>SUM(Q27:Q35)</f>
         <v>43</v>
       </c>
-    </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T36" s="30"/>
+    </row>
+    <row r="37" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="B37" s="38" t="s">
-        <v>337</v>
-      </c>
-      <c r="C37" s="20">
-        <v>1.2</v>
-      </c>
-      <c r="D37" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="E37" s="36">
-        <f>$A$39*C37</f>
-        <v>6.1111111111111107</v>
-      </c>
-      <c r="F37" s="33">
-        <v>4</v>
-      </c>
-      <c r="G37" s="35">
-        <v>6.42</v>
-      </c>
-      <c r="H37" s="35">
+      <c r="B37" s="55"/>
+      <c r="F37" s="33"/>
+      <c r="G37" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="H37" s="65">
+        <f>SUM(H28:H36)</f>
+        <v>42.089999999999996</v>
+      </c>
+      <c r="I37" s="34"/>
+      <c r="J37" s="146" t="str">
         <f t="shared" si="1"/>
-        <v>25.68</v>
-      </c>
-      <c r="I37" s="34"/>
-      <c r="J37" s="147" t="str">
-        <f t="shared" si="2"/>
         <v>Gathered End Hammock</v>
       </c>
       <c r="K37" s="66" t="s">
@@ -6425,48 +6557,57 @@
         <v>7.5</v>
       </c>
       <c r="Q37" s="35">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
-      <c r="S37" s="108" t="s">
-        <v>405</v>
-      </c>
-      <c r="T37" s="109">
+      <c r="S37" s="169" t="s">
+        <v>491</v>
+      </c>
+      <c r="T37" s="108">
         <f>T31+T32+T23</f>
-        <v>72.140000000000015</v>
-      </c>
-      <c r="U37" s="110" t="s">
+        <v>78.150000000000006</v>
+      </c>
+      <c r="U37" s="109" t="s">
+        <v>398</v>
+      </c>
+      <c r="V37" s="31" t="s">
+        <v>476</v>
+      </c>
+      <c r="W37" t="s">
+        <v>482</v>
+      </c>
+      <c r="X37" s="30"/>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A38" s="20" t="s">
         <v>404</v>
       </c>
-    </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A38" s="20" t="s">
-        <v>413</v>
-      </c>
       <c r="B38" s="38" t="s">
-        <v>279</v>
+        <v>334</v>
       </c>
       <c r="C38" s="20">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="D38" s="21" t="s">
         <v>159</v>
       </c>
       <c r="E38" s="36">
         <f>$A$39*C38</f>
-        <v>8.1481481481481488</v>
-      </c>
-      <c r="F38" s="33"/>
+        <v>6.1111111111111107</v>
+      </c>
+      <c r="F38" s="33">
+        <v>4</v>
+      </c>
       <c r="G38" s="35">
-        <v>6.69</v>
-      </c>
-      <c r="H38" s="35" t="str">
+        <v>6.42</v>
+      </c>
+      <c r="H38" s="35">
+        <f t="shared" si="0"/>
+        <v>25.68</v>
+      </c>
+      <c r="I38" s="34"/>
+      <c r="J38" s="147" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I38" s="34"/>
-      <c r="J38" s="148" t="str">
-        <f t="shared" si="2"/>
         <v>120x55</v>
       </c>
       <c r="K38" s="66"/>
@@ -6476,44 +6617,56 @@
       <c r="O38" s="33"/>
       <c r="P38" s="35"/>
       <c r="Q38" s="35" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="S38" s="111" t="s">
-        <v>407</v>
-      </c>
-      <c r="T38" s="82">
-        <f>T21+T22</f>
-        <v>165.14999999999998</v>
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="S38" s="170" t="s">
+        <v>490</v>
+      </c>
+      <c r="T38" s="102">
+        <f>T27+T30</f>
+        <v>40.78</v>
       </c>
       <c r="U38" s="112" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+        <v>459</v>
+      </c>
+      <c r="V38" s="31" t="s">
+        <v>459</v>
+      </c>
+      <c r="W38" s="3">
+        <v>129.33000000000001</v>
+      </c>
+      <c r="X38" s="30"/>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A39" s="37">
         <f>(120*55)/(36*36)</f>
         <v>5.0925925925925926</v>
       </c>
       <c r="B39" s="38" t="s">
-        <v>79</v>
-      </c>
-      <c r="C39" s="20"/>
-      <c r="D39" s="21"/>
-      <c r="E39" s="36"/>
-      <c r="F39" s="33">
-        <v>1</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="C39" s="20">
+        <v>1.6</v>
+      </c>
+      <c r="D39" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E39" s="36">
+        <f>$A$39*C39</f>
+        <v>8.1481481481481488</v>
+      </c>
+      <c r="F39" s="33"/>
       <c r="G39" s="35">
-        <v>3.96</v>
-      </c>
-      <c r="H39" s="35">
+        <v>6.69</v>
+      </c>
+      <c r="H39" s="35" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I39" s="34"/>
+      <c r="J39" s="147">
         <f t="shared" si="1"/>
-        <v>3.96</v>
-      </c>
-      <c r="I39" s="34"/>
-      <c r="J39" s="148">
-        <f t="shared" si="2"/>
         <v>5.0925925925925926</v>
       </c>
       <c r="K39" s="66" t="s">
@@ -6529,105 +6682,109 @@
         <v>5.25</v>
       </c>
       <c r="Q39" s="35">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>5.25</v>
       </c>
-      <c r="S39" s="111" t="s">
-        <v>406</v>
+      <c r="S39" s="110" t="s">
+        <v>496</v>
       </c>
       <c r="T39" s="97">
         <f>T26+T33</f>
-        <v>120.02000000000001</v>
-      </c>
-      <c r="U39" s="114" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="40" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>116.27</v>
+      </c>
+      <c r="U39" s="113" t="s">
+        <v>462</v>
+      </c>
+      <c r="V39" s="25" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A40" s="37"/>
-      <c r="B40" s="52" t="s">
-        <v>353</v>
-      </c>
-      <c r="C40" s="20">
-        <v>27</v>
-      </c>
-      <c r="D40" s="21" t="s">
-        <v>161</v>
-      </c>
+      <c r="B40" s="38" t="s">
+        <v>79</v>
+      </c>
+      <c r="C40" s="20"/>
+      <c r="D40" s="21"/>
       <c r="E40" s="36"/>
       <c r="F40" s="33">
         <v>1</v>
       </c>
       <c r="G40" s="35">
-        <v>10.7</v>
+        <v>3.96</v>
       </c>
       <c r="H40" s="35">
+        <f t="shared" si="0"/>
+        <v>3.96</v>
+      </c>
+      <c r="I40" s="34"/>
+      <c r="J40" s="147" t="str">
         <f t="shared" si="1"/>
-        <v>10.7</v>
-      </c>
-      <c r="I40" s="34"/>
-      <c r="J40" s="148" t="str">
-        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Q40" s="35" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="S40" s="111" t="s">
-        <v>406</v>
-      </c>
-      <c r="T40" s="102">
-        <f>T27+T30</f>
-        <v>43.239999999999995</v>
-      </c>
-      <c r="U40" s="113" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="41" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="S40" s="110" t="s">
+        <v>399</v>
+      </c>
+      <c r="T40" s="82">
+        <f>T21+T22</f>
+        <v>140.79</v>
+      </c>
+      <c r="U40" s="111" t="s">
+        <v>458</v>
+      </c>
+      <c r="V40" s="174" t="s">
+        <v>498</v>
+      </c>
+      <c r="W40" s="177">
+        <f>H79</f>
+        <v>25.02</v>
+      </c>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A41" s="37"/>
-      <c r="B41" s="54"/>
-      <c r="C41" s="20"/>
-      <c r="D41" s="21"/>
+      <c r="B41" s="52" t="s">
+        <v>350</v>
+      </c>
+      <c r="C41" s="20">
+        <v>27</v>
+      </c>
+      <c r="D41" s="21" t="s">
+        <v>161</v>
+      </c>
       <c r="E41" s="36"/>
-      <c r="F41" s="33"/>
-      <c r="G41" s="64" t="s">
-        <v>65</v>
-      </c>
-      <c r="H41" s="63">
-        <f>SUM(H37:H40)</f>
-        <v>40.340000000000003</v>
+      <c r="F41" s="33">
+        <v>0</v>
+      </c>
+      <c r="G41" s="35">
+        <v>11.45</v>
+      </c>
+      <c r="H41" s="35" t="str">
+        <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="I41" s="34"/>
-      <c r="J41" s="148" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="P41" s="64" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q41" s="63">
-        <f>SUM(Q37:Q40)</f>
-        <v>35.25</v>
-      </c>
-      <c r="S41" s="111" t="s">
-        <v>408</v>
+      <c r="J41" s="147"/>
+      <c r="Q41" s="35"/>
+      <c r="S41" s="110" t="s">
+        <v>400</v>
       </c>
       <c r="T41" s="92">
         <f>T25+T24</f>
-        <v>69.53</v>
-      </c>
-      <c r="U41" s="125" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="42" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="5" t="s">
-        <v>364</v>
-      </c>
+        <v>69.78</v>
+      </c>
+      <c r="U41" s="124" t="s">
+        <v>408</v>
+      </c>
+      <c r="X41" s="30"/>
+    </row>
+    <row r="42" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="37"/>
       <c r="B42" s="38" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C42" s="20">
         <v>0.67</v>
@@ -6635,361 +6792,355 @@
       <c r="D42" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="E42" s="36">
-        <f>C42*$A$44</f>
+      <c r="E42" s="36"/>
+      <c r="F42" s="33">
+        <v>2</v>
+      </c>
+      <c r="G42" s="35">
+        <v>4.46</v>
+      </c>
+      <c r="H42" s="35">
+        <f t="shared" ref="H42" si="6">IF((G42*F42)=0,"",G42*F42)</f>
+        <v>8.92</v>
+      </c>
+      <c r="I42" s="34"/>
+      <c r="J42" s="147"/>
+      <c r="Q42" s="35"/>
+      <c r="S42" s="114" t="s">
+        <v>473</v>
+      </c>
+      <c r="T42" s="118">
+        <f>T28+T29</f>
+        <v>13.923</v>
+      </c>
+      <c r="U42" s="119" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="43" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="B43" s="54"/>
+      <c r="C43" s="20"/>
+      <c r="D43" s="21"/>
+      <c r="E43" s="36"/>
+      <c r="F43" s="33"/>
+      <c r="G43" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="H43" s="63">
+        <f>SUM(H38:H42)</f>
+        <v>38.56</v>
+      </c>
+      <c r="I43" s="34"/>
+      <c r="J43" s="147" t="str">
+        <f>IF(ISBLANK(A41),"",A41)</f>
+        <v/>
+      </c>
+      <c r="P43" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q43" s="63">
+        <f>SUM(Q37:Q42)</f>
+        <v>35.25</v>
+      </c>
+      <c r="S43" s="127"/>
+      <c r="T43" s="30"/>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A44" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="B44" s="38" t="s">
+        <v>501</v>
+      </c>
+      <c r="C44" s="20">
+        <v>0.67</v>
+      </c>
+      <c r="D44" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E44" s="36">
+        <f>C44*$A$45</f>
         <v>5.9555555555555566</v>
       </c>
-      <c r="F42" s="33">
+      <c r="F44" s="33">
+        <v>5</v>
+      </c>
+      <c r="G44" s="35">
+        <v>4.46</v>
+      </c>
+      <c r="H44" s="35">
+        <f t="shared" si="0"/>
+        <v>22.3</v>
+      </c>
+      <c r="I44" s="34"/>
+      <c r="J44" s="146" t="str">
+        <f t="shared" ref="J44:J49" si="7">IF(ISBLANK(A43),"",A43)</f>
+        <v>Bug Net</v>
+      </c>
+      <c r="K44" s="66" t="s">
+        <v>317</v>
+      </c>
+      <c r="L44" s="20">
+        <v>0.67</v>
+      </c>
+      <c r="M44" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="N44" s="36"/>
+      <c r="O44" s="33">
         <v>7</v>
       </c>
-      <c r="G42" s="35">
-        <v>4.17</v>
-      </c>
-      <c r="H42" s="35">
-        <f t="shared" si="1"/>
-        <v>29.189999999999998</v>
-      </c>
-      <c r="I42" s="34"/>
-      <c r="J42" s="147" t="str">
-        <f t="shared" si="2"/>
-        <v>Bug Net</v>
-      </c>
-      <c r="K42" s="66" t="s">
-        <v>319</v>
-      </c>
-      <c r="L42" s="20">
-        <v>0.67</v>
-      </c>
-      <c r="M42" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="N42" s="36"/>
-      <c r="O42" s="33">
-        <v>7</v>
-      </c>
-      <c r="P42" s="35">
+      <c r="P44" s="35">
         <v>5.5</v>
       </c>
-      <c r="Q42" s="35">
-        <f t="shared" ref="Q42" si="10">IF((P42*O42)=0,"",P42*O42)</f>
+      <c r="Q44" s="35">
+        <f>IF((P44*O44)=0,"",P44*O44)</f>
         <v>38.5</v>
       </c>
-      <c r="S42" s="115" t="s">
-        <v>409</v>
-      </c>
-      <c r="T42" s="119">
-        <f>T28+T29</f>
-        <v>75.723000000000013</v>
-      </c>
-      <c r="U42" s="120" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A43" s="20" t="s">
-        <v>446</v>
-      </c>
-      <c r="B43" s="38" t="s">
-        <v>320</v>
-      </c>
-      <c r="C43" s="20">
-        <v>0.9</v>
-      </c>
-      <c r="D43" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="E43" s="36">
-        <f>C43*$A$44</f>
-        <v>8</v>
-      </c>
-      <c r="F43" s="33"/>
-      <c r="G43" s="35">
-        <v>4.17</v>
-      </c>
-      <c r="H43" s="35" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I43" s="34"/>
-      <c r="J43" s="148" t="str">
-        <f t="shared" si="2"/>
-        <v>120 x 96</v>
-      </c>
-      <c r="K43" s="66" t="s">
-        <v>320</v>
-      </c>
-      <c r="L43" s="20">
-        <v>0.9</v>
-      </c>
-      <c r="M43" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="N43" s="36"/>
-      <c r="O43" s="33"/>
-      <c r="P43" s="35">
-        <v>5</v>
-      </c>
-      <c r="Q43" s="35" t="str">
-        <f t="shared" ref="Q43" si="11">IF((P43*O43)=0,"",P43*O43)</f>
-        <v/>
-      </c>
-      <c r="S43" s="128" t="s">
-        <v>435</v>
-      </c>
-      <c r="T43" s="30">
-        <f>SUM(T37:T42)</f>
-        <v>545.80300000000011</v>
-      </c>
-    </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A44" s="20">
+      <c r="S44" s="167" t="s">
+        <v>507</v>
+      </c>
+      <c r="T44" s="30"/>
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A45" s="20">
         <f>(120*96)/(36*36)</f>
         <v>8.8888888888888893</v>
       </c>
-      <c r="B44" s="38"/>
-      <c r="H44" s="35" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I44" s="34"/>
-      <c r="J44" s="148">
-        <f t="shared" si="2"/>
+      <c r="B45" s="38" t="s">
+        <v>318</v>
+      </c>
+      <c r="C45" s="20">
+        <v>0.9</v>
+      </c>
+      <c r="D45" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E45" s="36">
+        <f>C45*$A$45</f>
+        <v>8</v>
+      </c>
+      <c r="F45" s="33"/>
+      <c r="G45" s="35">
+        <v>4.17</v>
+      </c>
+      <c r="H45" s="35" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I45" s="34"/>
+      <c r="J45" s="147" t="str">
+        <f t="shared" si="7"/>
+        <v>120 x 96</v>
+      </c>
+      <c r="K45" s="66" t="s">
+        <v>318</v>
+      </c>
+      <c r="L45" s="20">
+        <v>0.9</v>
+      </c>
+      <c r="M45" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="N45" s="36"/>
+      <c r="O45" s="33"/>
+      <c r="P45" s="35">
+        <v>5</v>
+      </c>
+      <c r="Q45" s="35" t="str">
+        <f>IF((P45*O45)=0,"",P45*O45)</f>
+        <v/>
+      </c>
+      <c r="S45" s="20" t="str">
+        <f>A111</f>
+        <v>Pack Cover (new pack)</v>
+      </c>
+      <c r="T45" s="30"/>
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A46" s="20" t="s">
+        <v>499</v>
+      </c>
+      <c r="B46" s="38"/>
+      <c r="H46" s="35" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I46" s="34"/>
+      <c r="J46" s="147">
+        <f t="shared" si="7"/>
         <v>8.8888888888888893</v>
       </c>
-      <c r="K44" s="66" t="s">
-        <v>318</v>
-      </c>
-      <c r="L44" s="20">
+      <c r="K46" s="66" t="s">
+        <v>316</v>
+      </c>
+      <c r="L46" s="20">
         <v>0.5</v>
       </c>
-      <c r="M44" s="21" t="s">
+      <c r="M46" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="N44" s="36">
+      <c r="N46" s="36">
         <f>(55*36)/(36*36)</f>
         <v>1.5277777777777777</v>
       </c>
-      <c r="O44" s="33">
+      <c r="O46" s="33">
         <v>7</v>
       </c>
-      <c r="P44" s="35">
+      <c r="P46" s="35">
         <v>8.75</v>
       </c>
-      <c r="Q44" s="35"/>
-      <c r="T44" s="30"/>
-    </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A45" s="20"/>
-      <c r="B45" s="46" t="s">
-        <v>377</v>
-      </c>
-      <c r="C45" s="20"/>
-      <c r="D45" s="21"/>
-      <c r="E45" s="36"/>
-      <c r="F45" s="33"/>
-      <c r="G45" s="35"/>
-      <c r="H45" s="35" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I45" s="34"/>
-      <c r="J45" s="148" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K45" s="139" t="s">
-        <v>289</v>
-      </c>
-      <c r="L45" s="20"/>
-      <c r="M45" s="21"/>
-      <c r="N45" s="36"/>
-      <c r="O45" s="33"/>
-      <c r="P45" s="35"/>
-      <c r="Q45" s="35"/>
-      <c r="T45" s="30"/>
-    </row>
-    <row r="46" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="20"/>
-      <c r="B46" s="50" t="s">
-        <v>378</v>
-      </c>
-      <c r="C46" s="20"/>
-      <c r="D46" s="21"/>
-      <c r="E46" s="36"/>
-      <c r="F46" s="33"/>
-      <c r="G46" s="35"/>
-      <c r="H46" s="35" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I46" s="34"/>
-      <c r="J46" s="148" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K46" s="140" t="s">
-        <v>316</v>
-      </c>
-      <c r="L46" s="20"/>
-      <c r="M46" s="21"/>
-      <c r="N46" s="36"/>
-      <c r="O46" s="33"/>
-      <c r="P46" s="35"/>
       <c r="Q46" s="35"/>
+      <c r="S46" s="20" t="str">
+        <f>A112</f>
+        <v>Ditty Bags (See ToDo)</v>
+      </c>
       <c r="T46" s="30"/>
     </row>
-    <row r="47" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="20"/>
-      <c r="B47" s="54"/>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A47" s="20" t="s">
+        <v>500</v>
+      </c>
+      <c r="B47" s="46" t="s">
+        <v>372</v>
+      </c>
       <c r="C47" s="20"/>
       <c r="D47" s="21"/>
       <c r="E47" s="36"/>
       <c r="F47" s="33"/>
-      <c r="G47" s="64" t="s">
-        <v>65</v>
-      </c>
-      <c r="H47" s="65">
-        <f>SUM(H42:H46)</f>
-        <v>29.189999999999998</v>
+      <c r="G47" s="35"/>
+      <c r="H47" s="35" t="str">
+        <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="I47" s="34"/>
-      <c r="J47" s="148" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K47" s="66"/>
+      <c r="J47" s="147" t="str">
+        <f t="shared" si="7"/>
+        <v>Redesign to make it partial</v>
+      </c>
+      <c r="K47" s="138" t="s">
+        <v>289</v>
+      </c>
       <c r="L47" s="20"/>
       <c r="M47" s="21"/>
       <c r="N47" s="36"/>
       <c r="O47" s="33"/>
-      <c r="P47" s="64" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q47" s="65">
-        <f>SUM(Q42:Q46)</f>
-        <v>38.5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A48" s="20"/>
-      <c r="B48" s="54"/>
+      <c r="P47" s="35"/>
+      <c r="Q47" s="35"/>
+      <c r="S47" s="20" t="str">
+        <f>A113</f>
+        <v>Kilt (Use ION)</v>
+      </c>
+      <c r="T47" s="30"/>
+    </row>
+    <row r="48" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="42" t="s">
+        <v>502</v>
+      </c>
+      <c r="B48" s="50" t="s">
+        <v>373</v>
+      </c>
       <c r="C48" s="20"/>
       <c r="D48" s="21"/>
       <c r="E48" s="36"/>
-      <c r="F48" s="33"/>
-      <c r="G48" s="64"/>
-      <c r="H48" s="145"/>
+      <c r="F48" s="172">
+        <v>2</v>
+      </c>
+      <c r="G48" s="35"/>
+      <c r="H48" s="44">
+        <f>G44*F48</f>
+        <v>8.92</v>
+      </c>
       <c r="I48" s="34"/>
-      <c r="J48" s="148"/>
-      <c r="K48" s="66"/>
+      <c r="J48" s="147" t="str">
+        <f t="shared" si="7"/>
+        <v>cover head to waist only</v>
+      </c>
+      <c r="K48" s="139" t="s">
+        <v>314</v>
+      </c>
       <c r="L48" s="20"/>
       <c r="M48" s="21"/>
       <c r="N48" s="36"/>
       <c r="O48" s="33"/>
-      <c r="P48" s="64"/>
-      <c r="Q48" s="145"/>
-    </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="5" t="s">
+      <c r="P48" s="35"/>
+      <c r="Q48" s="35"/>
+      <c r="S48" t="s">
+        <v>492</v>
+      </c>
+      <c r="T48" s="30"/>
+    </row>
+    <row r="49" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="20"/>
+      <c r="B49" s="40"/>
+      <c r="C49" s="20"/>
+      <c r="D49" s="21"/>
+      <c r="E49" s="171">
+        <f>((72*55)/(36*36))*C44</f>
+        <v>2.0472222222222221</v>
+      </c>
+      <c r="F49" s="33"/>
+      <c r="G49" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="H49" s="65">
+        <f>SUM(H44:H48)</f>
+        <v>31.22</v>
+      </c>
+      <c r="I49" s="34"/>
+      <c r="J49" s="147" t="str">
+        <f t="shared" si="7"/>
+        <v>The Ultimate Hang half bug net 72" x 55" (.67 noseeum)</v>
+      </c>
+      <c r="K49" s="66"/>
+      <c r="L49" s="20"/>
+      <c r="M49" s="21"/>
+      <c r="N49" s="36"/>
+      <c r="O49" s="33"/>
+      <c r="P49" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q49" s="65">
+        <f>SUM(Q44:Q48)</f>
+        <v>38.5</v>
+      </c>
+      <c r="T49" s="30"/>
+    </row>
+    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A50" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="B49" s="38" t="s">
-        <v>430</v>
-      </c>
-      <c r="C49" s="20">
+      <c r="B50" s="54"/>
+      <c r="C50" s="20"/>
+      <c r="D50" s="21"/>
+      <c r="E50" s="36"/>
+      <c r="F50" s="33"/>
+      <c r="G50" s="64"/>
+      <c r="H50" s="144"/>
+      <c r="I50" s="34"/>
+      <c r="J50" s="147"/>
+      <c r="K50" s="66"/>
+      <c r="L50" s="20"/>
+      <c r="M50" s="21"/>
+      <c r="N50" s="36"/>
+      <c r="O50" s="33"/>
+      <c r="P50" s="64"/>
+      <c r="Q50" s="144"/>
+      <c r="T50" s="30"/>
+    </row>
+    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A51" s="60" t="s">
+        <v>410</v>
+      </c>
+      <c r="B51" s="38" t="s">
+        <v>421</v>
+      </c>
+      <c r="C51" s="20">
         <f>(4.85+5.85)/2</f>
         <v>5.35</v>
-      </c>
-      <c r="D49" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="E49" s="36"/>
-      <c r="F49" s="33"/>
-      <c r="G49" s="35">
-        <v>12.84</v>
-      </c>
-      <c r="H49" s="35" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I49" s="34"/>
-      <c r="J49" s="147" t="str">
-        <f t="shared" si="2"/>
-        <v>Back Pack</v>
-      </c>
-      <c r="K49" s="142" t="s">
-        <v>358</v>
-      </c>
-      <c r="L49" s="20">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="M49" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="N49" s="36"/>
-      <c r="O49" s="33">
-        <v>2</v>
-      </c>
-      <c r="P49" s="35">
-        <v>14.5</v>
-      </c>
-      <c r="Q49" s="35">
-        <f t="shared" si="4"/>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A50" s="60" t="s">
-        <v>419</v>
-      </c>
-      <c r="B50" s="38" t="s">
-        <v>431</v>
-      </c>
-      <c r="C50" s="20">
-        <v>3.2</v>
-      </c>
-      <c r="D50" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="E50" s="36"/>
-      <c r="F50" s="33"/>
-      <c r="G50" s="35">
-        <v>5.08</v>
-      </c>
-      <c r="H50" s="35" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I50" s="34"/>
-      <c r="J50" s="148" t="str">
-        <f t="shared" si="2"/>
-        <v>* Work on quantities</v>
-      </c>
-      <c r="K50" s="66" t="s">
-        <v>314</v>
-      </c>
-      <c r="L50" s="20">
-        <v>3.2</v>
-      </c>
-      <c r="M50" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="N50" s="36"/>
-      <c r="O50" s="33"/>
-      <c r="P50" s="35">
-        <v>10</v>
-      </c>
-      <c r="Q50" s="35" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B51" s="38" t="s">
-        <v>432</v>
-      </c>
-      <c r="C51" s="20">
-        <v>6.73</v>
       </c>
       <c r="D51" s="21" t="s">
         <v>159</v>
@@ -6997,42 +7148,45 @@
       <c r="E51" s="36"/>
       <c r="F51" s="33"/>
       <c r="G51" s="35">
-        <v>3.75</v>
+        <v>12.84</v>
       </c>
       <c r="H51" s="35" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I51" s="34"/>
-      <c r="J51" s="148" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K51" s="66" t="s">
-        <v>313</v>
+      <c r="J51" s="146" t="str">
+        <f t="shared" ref="J51:J63" si="8">IF(ISBLANK(A50),"",A50)</f>
+        <v>Back Pack</v>
+      </c>
+      <c r="K51" s="141" t="s">
+        <v>495</v>
       </c>
       <c r="L51" s="20">
-        <v>3.9</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="M51" s="21" t="s">
         <v>159</v>
       </c>
       <c r="N51" s="36"/>
-      <c r="O51" s="33"/>
+      <c r="O51" s="33">
+        <v>0</v>
+      </c>
       <c r="P51" s="35">
-        <v>12.75</v>
+        <v>14.5</v>
       </c>
       <c r="Q51" s="35" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="T51" s="30"/>
+    </row>
+    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B52" s="38" t="s">
-        <v>433</v>
+        <v>422</v>
       </c>
       <c r="C52" s="20">
-        <v>7.9</v>
+        <v>3.2</v>
       </c>
       <c r="D52" s="21" t="s">
         <v>159</v>
@@ -7040,22 +7194,22 @@
       <c r="E52" s="36"/>
       <c r="F52" s="33"/>
       <c r="G52" s="35">
-        <v>12.84</v>
+        <v>5.08</v>
       </c>
       <c r="H52" s="35" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I52" s="34"/>
-      <c r="J52" s="148" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K52" s="142" t="s">
-        <v>312</v>
+      <c r="J52" s="147" t="str">
+        <f t="shared" si="8"/>
+        <v>* Work on quantities</v>
+      </c>
+      <c r="K52" s="66" t="s">
+        <v>493</v>
       </c>
       <c r="L52" s="20">
-        <v>6.1</v>
+        <v>3.2</v>
       </c>
       <c r="M52" s="21" t="s">
         <v>159</v>
@@ -7063,79 +7217,89 @@
       <c r="N52" s="36"/>
       <c r="O52" s="33"/>
       <c r="P52" s="35">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Q52" s="35" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="T52" s="30"/>
+    </row>
+    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B53" s="38" t="s">
-        <v>335</v>
-      </c>
-      <c r="C53" s="20"/>
-      <c r="D53" s="21"/>
+        <v>423</v>
+      </c>
+      <c r="C53" s="20">
+        <v>6.73</v>
+      </c>
+      <c r="D53" s="21" t="s">
+        <v>159</v>
+      </c>
       <c r="E53" s="36"/>
       <c r="F53" s="33"/>
       <c r="G53" s="35">
-        <v>3.96</v>
+        <v>3.75</v>
       </c>
       <c r="H53" s="35" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I53" s="34"/>
-      <c r="J53" s="148" t="str">
-        <f t="shared" si="2"/>
+      <c r="J53" s="147" t="str">
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K53" s="66" t="s">
-        <v>335</v>
-      </c>
-      <c r="L53" s="20"/>
-      <c r="M53" s="21"/>
+        <v>494</v>
+      </c>
+      <c r="L53" s="20">
+        <v>3.9</v>
+      </c>
+      <c r="M53" s="21" t="s">
+        <v>159</v>
+      </c>
       <c r="N53" s="36"/>
-      <c r="O53" s="33">
-        <v>1</v>
+      <c r="O53" s="173">
+        <v>2</v>
       </c>
       <c r="P53" s="35">
-        <v>4.5</v>
+        <v>12.75</v>
       </c>
       <c r="Q53" s="35">
-        <f t="shared" si="4"/>
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v>25.5</v>
+      </c>
+      <c r="T53" s="30"/>
+    </row>
+    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B54" s="38" t="s">
-        <v>351</v>
+        <v>424</v>
       </c>
       <c r="C54" s="20">
-        <v>212.5</v>
+        <v>7.9</v>
       </c>
       <c r="D54" s="21" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E54" s="36"/>
       <c r="F54" s="33"/>
       <c r="G54" s="35">
-        <v>13.91</v>
+        <v>12.84</v>
       </c>
       <c r="H54" s="35" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I54" s="34"/>
-      <c r="J54" s="148" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K54" s="118" t="s">
-        <v>360</v>
+      <c r="J54" s="147" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="K54" s="141" t="s">
+        <v>312</v>
       </c>
       <c r="L54" s="20">
-        <v>10</v>
+        <v>6.1</v>
       </c>
       <c r="M54" s="21" t="s">
         <v>159</v>
@@ -7143,206 +7307,207 @@
       <c r="N54" s="36"/>
       <c r="O54" s="33"/>
       <c r="P54" s="35">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q54" s="35" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B55" s="38"/>
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="T54" s="30"/>
+    </row>
+    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B55" s="38" t="s">
+        <v>332</v>
+      </c>
       <c r="C55" s="20"/>
       <c r="D55" s="21"/>
       <c r="E55" s="36"/>
       <c r="F55" s="33"/>
-      <c r="G55" s="35"/>
+      <c r="G55" s="35">
+        <v>3.96</v>
+      </c>
       <c r="H55" s="35" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I55" s="34"/>
-      <c r="J55" s="148" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K55" s="142" t="s">
-        <v>359</v>
-      </c>
-      <c r="L55" s="20">
-        <v>14.36</v>
-      </c>
-      <c r="M55" s="21" t="s">
-        <v>159</v>
-      </c>
+      <c r="J55" s="147" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="K55" s="66" t="s">
+        <v>332</v>
+      </c>
+      <c r="L55" s="20"/>
+      <c r="M55" s="21"/>
       <c r="N55" s="36"/>
-      <c r="O55" s="33"/>
+      <c r="O55" s="178"/>
       <c r="P55" s="35">
-        <v>12.88</v>
+        <v>4.5</v>
       </c>
       <c r="Q55" s="35" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="T55" s="30"/>
+    </row>
+    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B56" s="38" t="s">
-        <v>336</v>
-      </c>
-      <c r="C56" s="21" t="s">
-        <v>356</v>
-      </c>
-      <c r="D56" s="21"/>
+        <v>348</v>
+      </c>
+      <c r="C56" s="20">
+        <v>212.5</v>
+      </c>
+      <c r="D56" s="21" t="s">
+        <v>161</v>
+      </c>
       <c r="E56" s="36"/>
       <c r="F56" s="33"/>
-      <c r="G56" s="35"/>
+      <c r="G56" s="35">
+        <v>13.91</v>
+      </c>
       <c r="H56" s="35" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I56" s="34"/>
-      <c r="J56" s="148" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K56" s="142" t="s">
-        <v>311</v>
+      <c r="J56" s="147" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="K56" s="117" t="s">
+        <v>355</v>
       </c>
       <c r="L56" s="20">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M56" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="N56" s="3"/>
+      <c r="N56" s="36"/>
       <c r="O56" s="33"/>
       <c r="P56" s="35">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="Q56" s="35" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A57">
-        <v>7</v>
-      </c>
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="T56" s="30"/>
+    </row>
+    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B57" s="38" t="s">
-        <v>422</v>
-      </c>
-      <c r="C57" s="20">
-        <v>1.7</v>
-      </c>
-      <c r="D57" s="21" t="s">
-        <v>161</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="C57" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="D57" s="21"/>
       <c r="E57" s="36"/>
       <c r="F57" s="33"/>
-      <c r="G57" s="35">
-        <v>0.16</v>
-      </c>
+      <c r="G57" s="35"/>
       <c r="H57" s="35" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I57" s="34"/>
-      <c r="J57" s="148">
-        <f t="shared" si="2"/>
-        <v>7</v>
-      </c>
-      <c r="K57" s="66" t="s">
-        <v>420</v>
+      <c r="J57" s="147" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="K57" s="141" t="s">
+        <v>354</v>
       </c>
       <c r="L57" s="20">
-        <v>2.6</v>
+        <v>14.36</v>
       </c>
       <c r="M57" s="21" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="N57" s="36"/>
       <c r="O57" s="33"/>
       <c r="P57" s="35">
-        <v>4.5</v>
+        <v>12.88</v>
       </c>
       <c r="Q57" s="35" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="T57" s="30"/>
+    </row>
+    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>7</v>
+      </c>
       <c r="B58" s="38" t="s">
-        <v>429</v>
+        <v>413</v>
       </c>
       <c r="C58" s="20">
-        <v>0.42</v>
-      </c>
-      <c r="D58" s="21" t="s">
-        <v>161</v>
-      </c>
+        <v>1.7</v>
+      </c>
+      <c r="D58" s="21"/>
       <c r="E58" s="36"/>
-      <c r="F58" s="33">
-        <v>12</v>
-      </c>
-      <c r="G58" s="35">
-        <v>0.16</v>
-      </c>
-      <c r="H58" s="35">
-        <f t="shared" si="1"/>
-        <v>1.92</v>
+      <c r="F58" s="33"/>
+      <c r="G58" s="35"/>
+      <c r="H58" s="35" t="str">
+        <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="I58" s="34"/>
-      <c r="J58" s="148" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K58" s="66" t="s">
-        <v>421</v>
+      <c r="J58" s="147" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="K58" s="141" t="s">
+        <v>311</v>
       </c>
       <c r="L58" s="20">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="M58" s="21" t="s">
-        <v>161</v>
-      </c>
-      <c r="N58" s="36"/>
+        <v>159</v>
+      </c>
+      <c r="N58" s="3"/>
       <c r="O58" s="33"/>
       <c r="P58" s="35">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q58" s="35" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A59">
-        <v>10</v>
-      </c>
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B59" s="38" t="s">
-        <v>423</v>
-      </c>
-      <c r="C59" s="20"/>
+        <v>506</v>
+      </c>
+      <c r="C59" s="20">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="D59" s="21" t="s">
         <v>161</v>
       </c>
       <c r="E59" s="36"/>
-      <c r="F59" s="33"/>
-      <c r="G59" s="35"/>
-      <c r="H59" s="35" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="F59" s="33">
+        <v>10</v>
+      </c>
+      <c r="G59" s="35">
+        <v>0.12</v>
+      </c>
+      <c r="H59" s="35">
+        <f t="shared" si="0"/>
+        <v>1.2</v>
       </c>
       <c r="I59" s="34"/>
-      <c r="J59" s="148">
-        <f t="shared" si="2"/>
-        <v>10</v>
+      <c r="J59" s="147">
+        <f t="shared" si="8"/>
+        <v>7</v>
       </c>
       <c r="K59" s="66" t="s">
-        <v>299</v>
+        <v>411</v>
       </c>
       <c r="L59" s="20">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="M59" s="21" t="s">
         <v>161</v>
@@ -7350,47 +7515,47 @@
       <c r="N59" s="36"/>
       <c r="O59" s="33"/>
       <c r="P59" s="35">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="Q59" s="35" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B60" s="38" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="C60" s="20">
-        <v>3.96</v>
+        <v>0.42</v>
       </c>
       <c r="D60" s="21" t="s">
         <v>161</v>
       </c>
       <c r="E60" s="36"/>
-      <c r="F60" s="33">
-        <v>3</v>
+      <c r="F60" s="175">
+        <v>6</v>
       </c>
       <c r="G60" s="35">
-        <v>0.34</v>
+        <v>0.17</v>
       </c>
       <c r="H60" s="35">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.02</v>
       </c>
       <c r="I60" s="34"/>
-      <c r="J60" s="148">
-        <f t="shared" si="2"/>
-        <v>9</v>
+      <c r="J60" s="147" t="str">
+        <f t="shared" si="8"/>
+        <v/>
       </c>
       <c r="K60" s="66" t="s">
-        <v>298</v>
+        <v>412</v>
       </c>
       <c r="L60" s="20">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="M60" s="21" t="s">
         <v>161</v>
@@ -7398,165 +7563,170 @@
       <c r="N60" s="36"/>
       <c r="O60" s="33"/>
       <c r="P60" s="35">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="Q60" s="35" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="S60" s="10"/>
-    </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>9</v>
+      </c>
       <c r="B61" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="C61" s="20">
-        <v>1.1299999999999999</v>
-      </c>
+        <v>414</v>
+      </c>
+      <c r="C61" s="20"/>
       <c r="D61" s="21" t="s">
         <v>161</v>
       </c>
       <c r="E61" s="36"/>
-      <c r="F61" s="33">
-        <v>14</v>
-      </c>
-      <c r="G61" s="35">
-        <v>0.36</v>
-      </c>
-      <c r="H61" s="35">
-        <f t="shared" si="1"/>
-        <v>5.04</v>
+      <c r="F61" s="33"/>
+      <c r="G61" s="35"/>
+      <c r="H61" s="35" t="str">
+        <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="I61" s="34"/>
-      <c r="J61" s="148" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="J61" s="147">
+        <f t="shared" si="8"/>
+        <v>10</v>
       </c>
       <c r="K61" s="66" t="s">
-        <v>376</v>
-      </c>
-      <c r="L61" s="20"/>
-      <c r="M61" s="21"/>
+        <v>299</v>
+      </c>
+      <c r="L61" s="20">
+        <v>2.33</v>
+      </c>
+      <c r="M61" s="21" t="s">
+        <v>161</v>
+      </c>
       <c r="N61" s="36"/>
       <c r="O61" s="33"/>
       <c r="P61" s="35">
         <v>5</v>
       </c>
       <c r="Q61" s="35" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A62" s="23" t="s">
-        <v>427</v>
-      </c>
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B62" s="38" t="s">
-        <v>342</v>
-      </c>
-      <c r="C62" s="126" t="s">
-        <v>428</v>
-      </c>
-      <c r="D62" s="126"/>
+        <v>415</v>
+      </c>
+      <c r="C62" s="20">
+        <v>3.96</v>
+      </c>
+      <c r="D62" s="21" t="s">
+        <v>161</v>
+      </c>
       <c r="E62" s="36"/>
-      <c r="F62" s="33"/>
-      <c r="G62" s="35"/>
-      <c r="H62" s="35" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="F62" s="175">
+        <v>10</v>
+      </c>
+      <c r="G62" s="35">
+        <v>0.36</v>
+      </c>
+      <c r="H62" s="35">
+        <f t="shared" si="0"/>
+        <v>3.5999999999999996</v>
       </c>
       <c r="I62" s="34"/>
-      <c r="J62" s="149" t="s">
-        <v>464</v>
-      </c>
-      <c r="K62" s="142" t="s">
-        <v>342</v>
+      <c r="J62" s="147">
+        <f t="shared" si="8"/>
+        <v>9</v>
+      </c>
+      <c r="K62" s="66" t="s">
+        <v>298</v>
       </c>
       <c r="L62" s="20">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="M62" s="21" t="s">
         <v>161</v>
       </c>
       <c r="N62" s="36"/>
-      <c r="O62" s="33">
-        <v>3</v>
+      <c r="O62" s="173">
+        <v>1</v>
       </c>
       <c r="P62" s="35">
-        <v>0.65</v>
+        <v>4.75</v>
       </c>
       <c r="Q62" s="35">
-        <f t="shared" si="4"/>
-        <v>1.9500000000000002</v>
-      </c>
-    </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A63" s="23" t="s">
+        <v>418</v>
+      </c>
       <c r="B63" s="38" t="s">
-        <v>349</v>
+        <v>375</v>
       </c>
       <c r="C63" s="20">
-        <v>11.62</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="D63" s="21" t="s">
         <v>161</v>
       </c>
       <c r="E63" s="36"/>
-      <c r="F63" s="33"/>
+      <c r="F63" s="175">
+        <v>6</v>
+      </c>
       <c r="G63" s="35">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="H63" s="35" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+        <v>0.39</v>
+      </c>
+      <c r="H63" s="35">
+        <f t="shared" si="0"/>
+        <v>2.34</v>
       </c>
       <c r="I63" s="34"/>
-      <c r="J63" s="148" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K63" s="66"/>
+      <c r="J63" s="147" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="K63" s="66" t="s">
+        <v>371</v>
+      </c>
       <c r="L63" s="20"/>
       <c r="M63" s="21"/>
       <c r="N63" s="36"/>
       <c r="O63" s="33"/>
-      <c r="P63" s="35"/>
+      <c r="P63" s="35">
+        <v>5</v>
+      </c>
       <c r="Q63" s="35" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A64">
-        <v>5</v>
-      </c>
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B64" s="38" t="s">
-        <v>425</v>
-      </c>
-      <c r="C64" s="20">
-        <v>15.1</v>
-      </c>
-      <c r="D64" s="21" t="s">
-        <v>161</v>
-      </c>
+        <v>339</v>
+      </c>
+      <c r="C64" s="125" t="s">
+        <v>419</v>
+      </c>
+      <c r="D64" s="125"/>
       <c r="E64" s="36"/>
       <c r="F64" s="33"/>
-      <c r="G64" s="35">
-        <v>0.8</v>
-      </c>
+      <c r="G64" s="35"/>
       <c r="H64" s="35" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I64" s="34"/>
-      <c r="J64" s="148">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="K64" s="66" t="s">
-        <v>282</v>
+      <c r="J64" s="148" t="s">
+        <v>454</v>
+      </c>
+      <c r="K64" s="141" t="s">
+        <v>339</v>
       </c>
       <c r="L64" s="20">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="M64" s="21" t="s">
         <v>161</v>
@@ -7564,65 +7734,57 @@
       <c r="N64" s="36"/>
       <c r="O64" s="33"/>
       <c r="P64" s="35">
-        <v>0.9</v>
+        <v>0.65</v>
       </c>
       <c r="Q64" s="35" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>5</v>
+      </c>
       <c r="B65" s="38" t="s">
-        <v>283</v>
+        <v>346</v>
       </c>
       <c r="C65" s="20">
-        <v>8.5</v>
+        <v>11.62</v>
       </c>
       <c r="D65" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="E65" s="127"/>
+      <c r="E65" s="36"/>
       <c r="F65" s="33"/>
       <c r="G65" s="35">
-        <v>0.8</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="H65" s="35" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I65" s="34"/>
-      <c r="J65" s="148" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K65" s="66" t="s">
-        <v>283</v>
-      </c>
-      <c r="L65" s="20">
-        <v>6</v>
-      </c>
-      <c r="M65" s="21" t="s">
-        <v>161</v>
-      </c>
+      <c r="J65" s="147" t="str">
+        <f t="shared" ref="J65:J97" si="9">IF(ISBLANK(A64),"",A64)</f>
+        <v/>
+      </c>
+      <c r="K65" s="66"/>
+      <c r="L65" s="20"/>
+      <c r="M65" s="21"/>
       <c r="N65" s="36"/>
       <c r="O65" s="33"/>
-      <c r="P65" s="35">
-        <v>0.65</v>
-      </c>
+      <c r="P65" s="35"/>
       <c r="Q65" s="35" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A66">
-        <v>9</v>
-      </c>
-      <c r="B66" s="50" t="s">
-        <v>426</v>
+      <c r="B66" s="38" t="s">
+        <v>416</v>
       </c>
       <c r="C66" s="20">
-        <v>1.58</v>
+        <v>15.1</v>
       </c>
       <c r="D66" s="21" t="s">
         <v>161</v>
@@ -7630,22 +7792,22 @@
       <c r="E66" s="36"/>
       <c r="F66" s="33"/>
       <c r="G66" s="35">
-        <v>0.22</v>
+        <v>0.8</v>
       </c>
       <c r="H66" s="35" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I66" s="34"/>
-      <c r="J66" s="148">
-        <f t="shared" si="2"/>
-        <v>9</v>
-      </c>
-      <c r="K66" s="140" t="s">
-        <v>301</v>
+      <c r="J66" s="147">
+        <f t="shared" si="9"/>
+        <v>5</v>
+      </c>
+      <c r="K66" s="66" t="s">
+        <v>282</v>
       </c>
       <c r="L66" s="20">
-        <v>5.4</v>
+        <v>15</v>
       </c>
       <c r="M66" s="21" t="s">
         <v>161</v>
@@ -7653,45 +7815,45 @@
       <c r="N66" s="36"/>
       <c r="O66" s="33"/>
       <c r="P66" s="35">
-        <v>4.5</v>
+        <v>0.9</v>
       </c>
       <c r="Q66" s="35" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>8</v>
-      </c>
-      <c r="B67" s="50" t="s">
-        <v>300</v>
+        <v>9</v>
+      </c>
+      <c r="B67" s="38" t="s">
+        <v>283</v>
       </c>
       <c r="C67" s="20">
-        <v>1.58</v>
+        <v>8.5</v>
       </c>
       <c r="D67" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="E67" s="36"/>
+      <c r="E67" s="126"/>
       <c r="F67" s="33"/>
       <c r="G67" s="35">
-        <v>0.22</v>
+        <v>0.8</v>
       </c>
       <c r="H67" s="35" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I67" s="34"/>
-      <c r="J67" s="148">
-        <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
-      <c r="K67" s="140" t="s">
-        <v>302</v>
+      <c r="J67" s="147" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="K67" s="66" t="s">
+        <v>283</v>
       </c>
       <c r="L67" s="20">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="M67" s="21" t="s">
         <v>161</v>
@@ -7699,510 +7861,508 @@
       <c r="N67" s="36"/>
       <c r="O67" s="33"/>
       <c r="P67" s="35">
-        <v>5</v>
+        <v>0.65</v>
       </c>
       <c r="Q67" s="35" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="68" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B68" s="38" t="s">
-        <v>338</v>
+      <c r="A68">
+        <v>8</v>
+      </c>
+      <c r="B68" s="50" t="s">
+        <v>417</v>
       </c>
       <c r="C68" s="20">
-        <v>14.79</v>
+        <v>1.58</v>
       </c>
       <c r="D68" s="21" t="s">
         <v>161</v>
       </c>
       <c r="E68" s="36"/>
-      <c r="F68" s="33">
-        <v>8</v>
-      </c>
+      <c r="F68" s="33"/>
       <c r="G68" s="35">
-        <v>0.21</v>
-      </c>
-      <c r="H68" s="35">
-        <f t="shared" si="1"/>
-        <v>1.68</v>
+        <v>0.22</v>
+      </c>
+      <c r="H68" s="35" t="str">
+        <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="I68" s="34"/>
-      <c r="J68" s="148" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K68" s="66" t="s">
-        <v>330</v>
+      <c r="J68" s="147">
+        <f t="shared" si="9"/>
+        <v>9</v>
+      </c>
+      <c r="K68" s="139" t="s">
+        <v>301</v>
       </c>
       <c r="L68" s="20">
-        <v>11.2</v>
+        <v>5.4</v>
       </c>
       <c r="M68" s="21" t="s">
-        <v>327</v>
+        <v>161</v>
       </c>
       <c r="N68" s="36"/>
       <c r="O68" s="33"/>
       <c r="P68" s="35">
-        <v>7.75</v>
+        <v>4.5</v>
       </c>
       <c r="Q68" s="35" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="69" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B69" s="38" t="s">
-        <v>341</v>
+      <c r="B69" s="50" t="s">
+        <v>300</v>
       </c>
       <c r="C69" s="20">
-        <v>7</v>
+        <v>1.58</v>
       </c>
       <c r="D69" s="21" t="s">
-        <v>327</v>
+        <v>161</v>
       </c>
       <c r="E69" s="36"/>
-      <c r="F69" s="33">
-        <v>1</v>
-      </c>
+      <c r="F69" s="33"/>
       <c r="G69" s="35">
-        <v>7.49</v>
-      </c>
-      <c r="H69" s="35">
-        <f t="shared" si="1"/>
-        <v>7.49</v>
+        <v>0.22</v>
+      </c>
+      <c r="H69" s="35" t="str">
+        <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="I69" s="34"/>
-      <c r="J69" s="148" t="str">
-        <f t="shared" ref="J69:J114" si="12">IF(ISBLANK(A69),"",A69)</f>
-        <v/>
-      </c>
-      <c r="K69" s="66" t="s">
-        <v>331</v>
+      <c r="J69" s="147">
+        <f t="shared" si="9"/>
+        <v>8</v>
+      </c>
+      <c r="K69" s="139" t="s">
+        <v>302</v>
       </c>
       <c r="L69" s="20">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="M69" s="21" t="s">
-        <v>327</v>
-      </c>
-      <c r="N69" s="3"/>
+        <v>161</v>
+      </c>
+      <c r="N69" s="36"/>
+      <c r="O69" s="33"/>
       <c r="P69" s="35">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Q69" s="35" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B70" s="38" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="C70" s="20">
-        <v>4.4000000000000004</v>
+        <v>14.79</v>
       </c>
       <c r="D70" s="21" t="s">
-        <v>327</v>
+        <v>161</v>
       </c>
       <c r="E70" s="36"/>
       <c r="F70" s="33"/>
       <c r="G70" s="35">
-        <v>9.36</v>
+        <v>0.21</v>
       </c>
       <c r="H70" s="35" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I70" s="34"/>
-      <c r="J70" s="148" t="str">
-        <f t="shared" si="12"/>
+      <c r="J70" s="147" t="str">
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K70" s="66" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="L70" s="20">
-        <v>3.9</v>
+        <v>11.2</v>
       </c>
       <c r="M70" s="21" t="s">
-        <v>327</v>
-      </c>
-      <c r="N70" s="3"/>
+        <v>325</v>
+      </c>
+      <c r="N70" s="36"/>
+      <c r="O70" s="33"/>
       <c r="P70" s="35">
-        <v>5.5</v>
+        <v>7.75</v>
       </c>
       <c r="Q70" s="35" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="71" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B71" s="38" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C71" s="20">
+        <v>7</v>
+      </c>
+      <c r="D71" s="21" t="s">
+        <v>325</v>
+      </c>
+      <c r="E71" s="36"/>
+      <c r="F71" s="33">
+        <v>0</v>
+      </c>
+      <c r="G71" s="35">
+        <v>7.49</v>
+      </c>
+      <c r="H71" s="35" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I71" s="34"/>
+      <c r="J71" s="147" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="K71" s="66" t="s">
+        <v>329</v>
+      </c>
+      <c r="L71" s="20">
+        <v>7.6</v>
+      </c>
+      <c r="M71" s="21" t="s">
+        <v>325</v>
+      </c>
+      <c r="N71" s="3"/>
+      <c r="P71" s="35">
+        <v>9</v>
+      </c>
+      <c r="Q71" s="35" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B72" s="38" t="s">
+        <v>336</v>
+      </c>
+      <c r="C72" s="20">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="D72" s="21" t="s">
+        <v>325</v>
+      </c>
+      <c r="E72" s="36"/>
+      <c r="F72" s="33"/>
+      <c r="G72" s="35">
+        <v>9.36</v>
+      </c>
+      <c r="H72" s="35" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I72" s="34"/>
+      <c r="J72" s="147" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="K72" s="66" t="s">
+        <v>330</v>
+      </c>
+      <c r="L72" s="20">
+        <v>3.9</v>
+      </c>
+      <c r="M72" s="21" t="s">
+        <v>325</v>
+      </c>
+      <c r="N72" s="3"/>
+      <c r="P72" s="35">
+        <v>5.5</v>
+      </c>
+      <c r="Q72" s="35" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B73" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="C73" s="20">
         <v>2.8</v>
       </c>
-      <c r="D71" s="21" t="s">
-        <v>327</v>
-      </c>
-      <c r="E71" s="3"/>
-      <c r="G71" s="35">
-        <v>6.69</v>
-      </c>
-      <c r="H71" s="35" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I71" s="34"/>
-      <c r="J71" s="148" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K71" s="142" t="s">
-        <v>329</v>
-      </c>
-      <c r="L71" s="20">
-        <v>4.5</v>
-      </c>
-      <c r="M71" s="21" t="s">
-        <v>327</v>
-      </c>
-      <c r="N71" s="36"/>
-      <c r="O71" s="33">
-        <v>1</v>
-      </c>
-      <c r="P71" s="35">
-        <v>6.5</v>
-      </c>
-      <c r="Q71" s="35">
-        <f t="shared" si="4"/>
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B72" s="52" t="s">
-        <v>343</v>
-      </c>
-      <c r="C72" s="20">
-        <v>10.3</v>
-      </c>
-      <c r="D72" s="21" t="s">
-        <v>327</v>
-      </c>
-      <c r="E72" s="3"/>
-      <c r="F72">
-        <v>2</v>
-      </c>
-      <c r="G72" s="35">
-        <v>3.21</v>
-      </c>
-      <c r="H72" s="35">
-        <f t="shared" si="1"/>
-        <v>6.42</v>
-      </c>
-      <c r="I72" s="34"/>
-      <c r="J72" s="148" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K72" s="66" t="s">
-        <v>343</v>
-      </c>
-      <c r="L72" s="21" t="s">
-        <v>345</v>
-      </c>
-      <c r="M72" s="21"/>
-      <c r="N72" s="36"/>
-      <c r="O72" s="33"/>
-      <c r="P72" s="35"/>
-      <c r="Q72" s="35" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B73" s="52" t="s">
-        <v>344</v>
-      </c>
-      <c r="C73" s="20">
-        <v>8</v>
-      </c>
       <c r="D73" s="21" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E73" s="3"/>
       <c r="G73" s="35">
-        <v>0.86</v>
+        <v>6.69</v>
       </c>
       <c r="H73" s="35" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I73" s="34"/>
-      <c r="J73" s="148" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K73" s="66" t="s">
-        <v>344</v>
-      </c>
-      <c r="L73" s="21" t="s">
-        <v>345</v>
-      </c>
-      <c r="M73" s="21"/>
+      <c r="J73" s="147" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="K73" s="141" t="s">
+        <v>327</v>
+      </c>
+      <c r="L73" s="20">
+        <v>4.5</v>
+      </c>
+      <c r="M73" s="21" t="s">
+        <v>325</v>
+      </c>
       <c r="N73" s="36"/>
-      <c r="O73" s="33"/>
-      <c r="P73" s="35"/>
-      <c r="Q73" s="35" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+      <c r="O73" s="173">
+        <v>1</v>
+      </c>
+      <c r="P73" s="35">
+        <v>6.5</v>
+      </c>
+      <c r="Q73" s="35">
+        <f t="shared" si="3"/>
+        <v>6.5</v>
       </c>
     </row>
     <row r="74" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B74" s="46" t="s">
-        <v>289</v>
-      </c>
-      <c r="C74" s="20"/>
-      <c r="D74" s="21"/>
+      <c r="B74" s="52" t="s">
+        <v>340</v>
+      </c>
+      <c r="C74" s="20">
+        <v>10.3</v>
+      </c>
+      <c r="D74" s="21" t="s">
+        <v>325</v>
+      </c>
       <c r="E74" s="3"/>
-      <c r="G74" s="35"/>
-      <c r="H74" s="35" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="F74" s="176">
+        <v>2</v>
+      </c>
+      <c r="G74" s="35">
+        <v>3.21</v>
+      </c>
+      <c r="H74" s="35">
+        <f t="shared" si="0"/>
+        <v>6.42</v>
       </c>
       <c r="I74" s="34"/>
-      <c r="J74" s="148" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K74" s="139" t="s">
-        <v>289</v>
-      </c>
-      <c r="L74" s="20"/>
+      <c r="J74" s="147" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="K74" s="66" t="s">
+        <v>340</v>
+      </c>
+      <c r="L74" s="21" t="s">
+        <v>342</v>
+      </c>
       <c r="M74" s="21"/>
-      <c r="N74" s="3"/>
-      <c r="P74" s="30"/>
+      <c r="N74" s="36"/>
+      <c r="O74" s="33"/>
+      <c r="P74" s="35"/>
       <c r="Q74" s="35" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="75" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B75" s="38" t="s">
-        <v>346</v>
+      <c r="B75" s="52" t="s">
+        <v>341</v>
       </c>
       <c r="C75" s="20">
-        <v>4.3</v>
+        <v>8</v>
       </c>
       <c r="D75" s="21" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E75" s="3"/>
       <c r="G75" s="35">
+        <v>0.86</v>
+      </c>
+      <c r="H75" s="35" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I75" s="34"/>
+      <c r="J75" s="147" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="K75" s="66" t="s">
+        <v>341</v>
+      </c>
+      <c r="L75" s="21" t="s">
+        <v>342</v>
+      </c>
+      <c r="M75" s="21"/>
+      <c r="N75" s="36"/>
+      <c r="O75" s="33"/>
+      <c r="P75" s="35"/>
+      <c r="Q75" s="35" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="S75" s="30"/>
+    </row>
+    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B76" s="46" t="s">
+        <v>289</v>
+      </c>
+      <c r="C76" s="20"/>
+      <c r="D76" s="21"/>
+      <c r="E76" s="3"/>
+      <c r="G76" s="35"/>
+      <c r="H76" s="35" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I76" s="51"/>
+      <c r="J76" s="147" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="K76" s="138" t="s">
+        <v>289</v>
+      </c>
+      <c r="L76" s="20"/>
+      <c r="M76" s="21"/>
+      <c r="N76" s="3"/>
+      <c r="P76" s="30"/>
+      <c r="Q76" s="35" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B77" s="38" t="s">
+        <v>343</v>
+      </c>
+      <c r="C77" s="20">
+        <v>4.3</v>
+      </c>
+      <c r="D77" s="21" t="s">
+        <v>325</v>
+      </c>
+      <c r="E77" s="3"/>
+      <c r="F77" s="176">
+        <v>3</v>
+      </c>
+      <c r="G77" s="35">
         <v>2.94</v>
       </c>
-      <c r="H75" s="35" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I75" s="34"/>
-      <c r="J75" s="148" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K75" s="66" t="s">
+      <c r="H77" s="35">
+        <f t="shared" si="0"/>
+        <v>8.82</v>
+      </c>
+      <c r="I77" s="34"/>
+      <c r="J77" s="147" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="K77" s="66" t="s">
         <v>304</v>
       </c>
-      <c r="L75" s="20">
+      <c r="L77" s="20">
         <v>8</v>
       </c>
-      <c r="M75" s="21" t="s">
-        <v>327</v>
-      </c>
-      <c r="N75" s="3"/>
-      <c r="P75" s="35">
+      <c r="M77" s="21" t="s">
+        <v>325</v>
+      </c>
+      <c r="N77" s="3"/>
+      <c r="P77" s="35">
         <v>3.75</v>
       </c>
-      <c r="Q75" s="35" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="S75" s="30"/>
-    </row>
-    <row r="76" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B76" s="38" t="s">
-        <v>347</v>
-      </c>
-      <c r="C76" s="20">
+      <c r="Q77" s="35" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="78" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B78" s="38" t="s">
+        <v>344</v>
+      </c>
+      <c r="C78" s="20">
         <v>1.41</v>
       </c>
-      <c r="D76" s="21" t="s">
+      <c r="D78" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="E76" s="3"/>
-      <c r="G76" s="35">
+      <c r="E78" s="3"/>
+      <c r="F78" s="176">
+        <v>3</v>
+      </c>
+      <c r="G78" s="35">
         <v>0.54</v>
       </c>
-      <c r="H76" s="35" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I76" s="51"/>
-      <c r="J76" s="148" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K76" s="140" t="s">
+      <c r="H78" s="35">
+        <f t="shared" si="0"/>
+        <v>1.62</v>
+      </c>
+      <c r="I78" s="34"/>
+      <c r="J78" s="147" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="K78" s="139" t="s">
         <v>305</v>
       </c>
-      <c r="L76" s="20" t="s">
+      <c r="L78" s="20" t="s">
         <v>303</v>
       </c>
-      <c r="M76" s="21" t="s">
+      <c r="M78" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="N76" s="3"/>
-      <c r="P76" s="35">
+      <c r="N78" s="3"/>
+      <c r="P78" s="35">
         <v>0.95</v>
       </c>
-      <c r="Q76" s="35" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="77" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C77" s="20"/>
-      <c r="D77" s="21"/>
-      <c r="E77" s="3"/>
-      <c r="G77" s="64" t="s">
+      <c r="Q78" s="35" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="S78" s="30"/>
+    </row>
+    <row r="79" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="39" t="s">
+        <v>284</v>
+      </c>
+      <c r="C79" s="20"/>
+      <c r="D79" s="21"/>
+      <c r="E79" s="3"/>
+      <c r="G79" s="64" t="s">
         <v>65</v>
       </c>
-      <c r="H77" s="65">
-        <f>SUM(H49:H76)</f>
-        <v>23.57</v>
-      </c>
-      <c r="I77" s="34"/>
-      <c r="J77" s="148" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K77" s="118"/>
-      <c r="L77" s="20"/>
-      <c r="M77" s="21"/>
-      <c r="N77" s="3"/>
-      <c r="P77" s="64" t="s">
+      <c r="H79" s="65">
+        <f>SUM(H51:H78)</f>
+        <v>25.02</v>
+      </c>
+      <c r="I79" s="34"/>
+      <c r="J79" s="147" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="K79" s="117"/>
+      <c r="L79" s="20"/>
+      <c r="M79" s="21"/>
+      <c r="N79" s="3"/>
+      <c r="P79" s="64" t="s">
         <v>65</v>
       </c>
-      <c r="Q77" s="65">
-        <f>SUM(Q49:Q76)</f>
-        <v>41.95</v>
-      </c>
-    </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A78" s="39" t="s">
-        <v>284</v>
-      </c>
-      <c r="B78" s="40" t="s">
+      <c r="Q79" s="65">
+        <f>SUM(Q51:Q78)</f>
+        <v>36.75</v>
+      </c>
+    </row>
+    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A80" s="43"/>
+      <c r="B80" s="40" t="s">
         <v>308</v>
-      </c>
-      <c r="C78" s="41">
-        <v>1.36</v>
-      </c>
-      <c r="D78" s="42" t="s">
-        <v>161</v>
-      </c>
-      <c r="E78" s="11"/>
-      <c r="F78" s="43">
-        <v>2</v>
-      </c>
-      <c r="G78" s="44">
-        <v>6.15</v>
-      </c>
-      <c r="H78" s="44">
-        <f t="shared" si="1"/>
-        <v>12.3</v>
-      </c>
-      <c r="I78" s="34"/>
-      <c r="J78" s="148" t="str">
-        <f t="shared" si="12"/>
-        <v>Amsteel 7/64</v>
-      </c>
-      <c r="K78" s="143" t="s">
-        <v>308</v>
-      </c>
-      <c r="L78" s="41">
-        <v>1.36</v>
-      </c>
-      <c r="M78" s="42" t="s">
-        <v>327</v>
-      </c>
-      <c r="N78" s="11"/>
-      <c r="O78" s="43">
-        <v>1</v>
-      </c>
-      <c r="P78" s="44">
-        <v>7.5</v>
-      </c>
-      <c r="Q78" s="44">
-        <f t="shared" si="4"/>
-        <v>7.5</v>
-      </c>
-      <c r="S78" s="30"/>
-    </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A79" s="43"/>
-      <c r="B79" s="40" t="s">
-        <v>309</v>
-      </c>
-      <c r="C79" s="41">
-        <v>1.36</v>
-      </c>
-      <c r="D79" s="42" t="s">
-        <v>161</v>
-      </c>
-      <c r="E79" s="11"/>
-      <c r="F79" s="43">
-        <v>1</v>
-      </c>
-      <c r="G79" s="44">
-        <v>6.15</v>
-      </c>
-      <c r="H79" s="44">
-        <f t="shared" si="1"/>
-        <v>6.15</v>
-      </c>
-      <c r="I79" s="34"/>
-      <c r="J79" s="148" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K79" s="143" t="s">
-        <v>309</v>
-      </c>
-      <c r="L79" s="41">
-        <v>1.36</v>
-      </c>
-      <c r="M79" s="42" t="s">
-        <v>327</v>
-      </c>
-      <c r="N79" s="11"/>
-      <c r="O79" s="43">
-        <v>1</v>
-      </c>
-      <c r="P79" s="44">
-        <v>7.5</v>
-      </c>
-      <c r="Q79" s="44">
-        <f t="shared" si="4"/>
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="80" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="39"/>
-      <c r="B80" s="40" t="s">
-        <v>310</v>
       </c>
       <c r="C80" s="41">
         <v>1.36</v>
@@ -8212,28 +8372,28 @@
       </c>
       <c r="E80" s="11"/>
       <c r="F80" s="43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G80" s="44">
-        <v>6.15</v>
+        <v>6.58</v>
       </c>
       <c r="H80" s="44">
-        <f t="shared" si="1"/>
-        <v>6.15</v>
+        <f t="shared" si="0"/>
+        <v>13.16</v>
       </c>
       <c r="I80" s="34"/>
-      <c r="J80" s="148" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K80" s="143" t="s">
-        <v>310</v>
+      <c r="J80" s="147" t="str">
+        <f t="shared" si="9"/>
+        <v>Amsteel 7/64</v>
+      </c>
+      <c r="K80" s="142" t="s">
+        <v>308</v>
       </c>
       <c r="L80" s="41">
         <v>1.36</v>
       </c>
       <c r="M80" s="42" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="N80" s="11"/>
       <c r="O80" s="43">
@@ -8243,957 +8403,983 @@
         <v>7.5</v>
       </c>
       <c r="Q80" s="44">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>7.5</v>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="39"/>
-      <c r="B81" s="40"/>
-      <c r="C81" s="41"/>
-      <c r="D81" s="42"/>
+      <c r="B81" s="40" t="s">
+        <v>309</v>
+      </c>
+      <c r="C81" s="41">
+        <v>1.36</v>
+      </c>
+      <c r="D81" s="42" t="s">
+        <v>161</v>
+      </c>
       <c r="E81" s="11"/>
-      <c r="F81" s="43"/>
-      <c r="G81" s="69" t="s">
+      <c r="F81" s="43">
+        <v>1</v>
+      </c>
+      <c r="G81" s="44">
+        <v>6.58</v>
+      </c>
+      <c r="H81" s="44">
+        <f t="shared" si="0"/>
+        <v>6.58</v>
+      </c>
+      <c r="I81" s="34"/>
+      <c r="J81" s="147" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="K81" s="142" t="s">
+        <v>309</v>
+      </c>
+      <c r="L81" s="41">
+        <v>1.36</v>
+      </c>
+      <c r="M81" s="42" t="s">
+        <v>325</v>
+      </c>
+      <c r="N81" s="11"/>
+      <c r="O81" s="43">
+        <v>1</v>
+      </c>
+      <c r="P81" s="44">
+        <v>7.5</v>
+      </c>
+      <c r="Q81" s="44">
+        <f t="shared" si="3"/>
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="39"/>
+      <c r="B82" s="40" t="s">
+        <v>310</v>
+      </c>
+      <c r="C82" s="41">
+        <v>1.36</v>
+      </c>
+      <c r="D82" s="42" t="s">
+        <v>161</v>
+      </c>
+      <c r="E82" s="11"/>
+      <c r="F82" s="43">
+        <v>1</v>
+      </c>
+      <c r="G82" s="44">
+        <v>6.58</v>
+      </c>
+      <c r="H82" s="44">
+        <f t="shared" si="0"/>
+        <v>6.58</v>
+      </c>
+      <c r="I82" s="34"/>
+      <c r="J82" s="147" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="K82" s="142" t="s">
+        <v>310</v>
+      </c>
+      <c r="L82" s="41">
+        <v>1.36</v>
+      </c>
+      <c r="M82" s="42" t="s">
+        <v>325</v>
+      </c>
+      <c r="N82" s="11"/>
+      <c r="O82" s="43">
+        <v>1</v>
+      </c>
+      <c r="P82" s="44">
+        <v>7.5</v>
+      </c>
+      <c r="Q82" s="44">
+        <f t="shared" si="3"/>
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="45" t="s">
+        <v>285</v>
+      </c>
+      <c r="B83" s="40"/>
+      <c r="C83" s="41"/>
+      <c r="D83" s="42"/>
+      <c r="E83" s="11"/>
+      <c r="F83" s="43"/>
+      <c r="G83" s="69" t="s">
         <v>65</v>
       </c>
-      <c r="H81" s="67">
-        <f>SUM(H78:H80)</f>
-        <v>24.6</v>
-      </c>
-      <c r="I81" s="34"/>
-      <c r="J81" s="148" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K81" s="143"/>
-      <c r="L81" s="41"/>
-      <c r="M81" s="42"/>
-      <c r="N81" s="11"/>
-      <c r="O81" s="43"/>
-      <c r="P81" s="69" t="s">
+      <c r="H83" s="67">
+        <f>SUM(H80:H82)</f>
+        <v>26.32</v>
+      </c>
+      <c r="I83" s="34"/>
+      <c r="J83" s="147" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="K83" s="142"/>
+      <c r="L83" s="41"/>
+      <c r="M83" s="42"/>
+      <c r="N83" s="11"/>
+      <c r="O83" s="43"/>
+      <c r="P83" s="69" t="s">
         <v>65</v>
       </c>
-      <c r="Q81" s="67">
-        <f>SUM(Q78:Q80)</f>
+      <c r="Q83" s="67">
+        <f>SUM(Q80:Q82)</f>
         <v>22.5</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A82" s="45" t="s">
-        <v>285</v>
-      </c>
-      <c r="B82" s="46" t="s">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A84" s="7"/>
+      <c r="B84" s="46" t="s">
         <v>306</v>
       </c>
-      <c r="C82" s="47">
+      <c r="C84" s="47">
         <v>1.9</v>
       </c>
-      <c r="D82" s="48" t="s">
+      <c r="D84" s="48" t="s">
         <v>161</v>
       </c>
-      <c r="E82" s="8"/>
-      <c r="F82" s="7">
+      <c r="E84" s="8"/>
+      <c r="F84" s="7">
         <v>1</v>
       </c>
-      <c r="G82" s="49">
-        <v>4.55</v>
-      </c>
-      <c r="H82" s="49">
-        <f t="shared" si="1"/>
-        <v>4.55</v>
-      </c>
-      <c r="I82" s="34"/>
-      <c r="J82" s="148" t="str">
-        <f t="shared" si="12"/>
+      <c r="G84" s="49">
+        <v>4.87</v>
+      </c>
+      <c r="H84" s="49">
+        <f t="shared" si="0"/>
+        <v>4.87</v>
+      </c>
+      <c r="I84" s="34"/>
+      <c r="J84" s="147" t="str">
+        <f t="shared" si="9"/>
         <v>Shock Cord</v>
       </c>
-      <c r="K82" s="139" t="s">
+      <c r="K84" s="138" t="s">
         <v>306</v>
       </c>
-      <c r="L82" s="47">
+      <c r="L84" s="47">
         <v>1.9</v>
       </c>
-      <c r="M82" s="48" t="s">
-        <v>328</v>
-      </c>
-      <c r="N82" s="8"/>
-      <c r="O82" s="7">
+      <c r="M84" s="48" t="s">
+        <v>326</v>
+      </c>
+      <c r="N84" s="8"/>
+      <c r="O84" s="7">
         <v>1</v>
       </c>
-      <c r="P82" s="49">
+      <c r="P84" s="49">
         <v>5.75</v>
       </c>
-      <c r="Q82" s="49">
-        <f t="shared" si="4"/>
+      <c r="Q84" s="49">
+        <f t="shared" si="3"/>
         <v>5.75</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A83" s="7"/>
-      <c r="B83" s="46" t="s">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A85" s="10"/>
+      <c r="B85" s="46" t="s">
         <v>307</v>
       </c>
-      <c r="C83" s="47">
+      <c r="C85" s="47">
         <v>1.2</v>
       </c>
-      <c r="D83" s="48" t="s">
+      <c r="D85" s="48" t="s">
         <v>161</v>
       </c>
-      <c r="E83" s="8"/>
-      <c r="F83" s="7">
+      <c r="E85" s="8"/>
+      <c r="F85" s="7">
         <v>1</v>
       </c>
-      <c r="G83" s="49">
-        <v>4.55</v>
-      </c>
-      <c r="H83" s="49">
-        <f t="shared" si="1"/>
-        <v>4.55</v>
-      </c>
-      <c r="I83" s="34"/>
-      <c r="J83" s="148" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K83" s="139" t="s">
+      <c r="G85" s="49">
+        <v>4.87</v>
+      </c>
+      <c r="H85" s="49">
+        <f t="shared" si="0"/>
+        <v>4.87</v>
+      </c>
+      <c r="I85" s="34"/>
+      <c r="J85" s="147" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="K85" s="138" t="s">
         <v>307</v>
       </c>
-      <c r="L83" s="47">
+      <c r="L85" s="47">
         <v>1.2</v>
       </c>
-      <c r="M83" s="48" t="s">
-        <v>328</v>
-      </c>
-      <c r="N83" s="8"/>
-      <c r="O83" s="7">
+      <c r="M85" s="48" t="s">
+        <v>326</v>
+      </c>
+      <c r="N85" s="8"/>
+      <c r="O85" s="7">
         <v>1</v>
       </c>
-      <c r="P83" s="49">
+      <c r="P85" s="49">
         <v>5.75</v>
       </c>
-      <c r="Q83" s="49">
-        <f t="shared" si="4"/>
+      <c r="Q85" s="49">
+        <f t="shared" si="3"/>
         <v>5.75</v>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="10"/>
-      <c r="B84" s="54" t="s">
-        <v>373</v>
-      </c>
-      <c r="C84" s="57">
+    <row r="86" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="10"/>
+      <c r="B86" s="54" t="s">
+        <v>368</v>
+      </c>
+      <c r="C86" s="57">
         <v>4.7</v>
       </c>
-      <c r="D84" s="58" t="s">
-        <v>323</v>
-      </c>
-      <c r="E84" s="13"/>
-      <c r="F84" s="10"/>
-      <c r="G84" s="59">
+      <c r="D86" s="58" t="s">
+        <v>321</v>
+      </c>
+      <c r="E86" s="13"/>
+      <c r="F86" s="10"/>
+      <c r="G86" s="59">
         <v>1.61</v>
       </c>
-      <c r="H84" s="59" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I84" s="34"/>
-      <c r="J84" s="148" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K84" s="118" t="s">
-        <v>375</v>
-      </c>
-      <c r="L84" s="57">
+      <c r="H86" s="59" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I86" s="34"/>
+      <c r="J86" s="147" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="K86" s="117" t="s">
+        <v>370</v>
+      </c>
+      <c r="L86" s="57">
         <v>1.9</v>
       </c>
-      <c r="M84" s="58" t="s">
-        <v>327</v>
-      </c>
-      <c r="N84" s="13"/>
-      <c r="O84" s="10"/>
-      <c r="P84" s="59">
+      <c r="M86" s="58" t="s">
+        <v>325</v>
+      </c>
+      <c r="N86" s="13"/>
+      <c r="O86" s="10"/>
+      <c r="P86" s="59">
         <v>2.5</v>
       </c>
-      <c r="Q84" s="59" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="85" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="10"/>
-      <c r="B85" s="54"/>
-      <c r="C85" s="57"/>
-      <c r="D85" s="58"/>
-      <c r="E85" s="13"/>
-      <c r="F85" s="10"/>
-      <c r="G85" s="64" t="s">
+      <c r="Q86" s="59" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="87" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="B87" s="54"/>
+      <c r="C87" s="57"/>
+      <c r="D87" s="58"/>
+      <c r="E87" s="13"/>
+      <c r="F87" s="10"/>
+      <c r="G87" s="64" t="s">
         <v>65</v>
       </c>
-      <c r="H85" s="68">
-        <f>SUM(H82:H84)</f>
-        <v>9.1</v>
-      </c>
-      <c r="I85" s="34"/>
-      <c r="J85" s="148" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K85" s="118"/>
-      <c r="L85" s="57"/>
-      <c r="M85" s="58"/>
-      <c r="N85" s="13"/>
-      <c r="O85" s="10"/>
-      <c r="P85" s="64" t="s">
+      <c r="H87" s="68">
+        <f>SUM(H84:H86)</f>
+        <v>9.74</v>
+      </c>
+      <c r="I87" s="34"/>
+      <c r="J87" s="147" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="K87" s="117"/>
+      <c r="L87" s="57"/>
+      <c r="M87" s="58"/>
+      <c r="N87" s="13"/>
+      <c r="O87" s="10"/>
+      <c r="P87" s="64" t="s">
         <v>65</v>
       </c>
-      <c r="Q85" s="68">
-        <f>SUM(Q82:Q84)</f>
+      <c r="Q87" s="68">
+        <f>SUM(Q84:Q86)</f>
         <v>11.5</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A86" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="B86" s="38" t="s">
-        <v>357</v>
-      </c>
-      <c r="C86" s="20">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A88" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="B88" s="38" t="s">
+        <v>480</v>
+      </c>
+      <c r="C88" s="20">
         <v>0.49</v>
-      </c>
-      <c r="D86" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="E86" s="36">
-        <f>C86*((58*72)/(36*36))</f>
-        <v>1.578888888888889</v>
-      </c>
-      <c r="F86" s="33"/>
-      <c r="G86" s="35">
-        <v>13.38</v>
-      </c>
-      <c r="H86" s="59" t="str">
-        <f t="shared" ref="H86:H115" si="13">IF((G86*F86)=0,"",G86*F86)</f>
-        <v/>
-      </c>
-      <c r="I86" s="34"/>
-      <c r="J86" s="148" t="str">
-        <f t="shared" si="12"/>
-        <v>Sleeping Bag Liner</v>
-      </c>
-      <c r="P86" s="33"/>
-      <c r="Q86" s="59" t="str">
-        <f t="shared" ref="Q86:Q103" si="14">IF((P86*O86)=0,"",P86*O86)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A87" s="5" t="s">
-        <v>365</v>
-      </c>
-      <c r="B87" s="54" t="s">
-        <v>213</v>
-      </c>
-      <c r="C87" s="20">
-        <v>0.67</v>
-      </c>
-      <c r="D87" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="E87" s="36">
-        <f>C87*((58*72)/(36*36))</f>
-        <v>2.1588888888888893</v>
-      </c>
-      <c r="F87" s="33">
-        <v>2</v>
-      </c>
-      <c r="G87" s="35">
-        <v>10.7</v>
-      </c>
-      <c r="H87" s="59">
-        <f t="shared" si="13"/>
-        <v>21.4</v>
-      </c>
-      <c r="I87" s="34"/>
-      <c r="J87" s="148" t="str">
-        <f t="shared" si="12"/>
-        <v>58 x 72</v>
-      </c>
-      <c r="K87" s="66" t="s">
-        <v>291</v>
-      </c>
-      <c r="L87" s="20">
-        <v>0.66</v>
-      </c>
-      <c r="M87" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="N87" s="36">
-        <f t="shared" ref="N87" si="15">L87*$A$5</f>
-        <v>2.145</v>
-      </c>
-      <c r="O87" s="33">
-        <v>2</v>
-      </c>
-      <c r="P87" s="35">
-        <v>12.75</v>
-      </c>
-      <c r="Q87" s="59">
-        <f t="shared" si="14"/>
-        <v>25.5</v>
-      </c>
-    </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A88" s="5"/>
-      <c r="B88" s="38" t="s">
-        <v>214</v>
-      </c>
-      <c r="C88" s="20">
-        <v>0.9</v>
       </c>
       <c r="D88" s="21" t="s">
         <v>159</v>
       </c>
       <c r="E88" s="36">
         <f>C88*((58*72)/(36*36))</f>
-        <v>2.9000000000000004</v>
+        <v>1.578888888888889</v>
       </c>
       <c r="F88" s="33"/>
       <c r="G88" s="35">
-        <v>8.0299999999999994</v>
+        <v>14.32</v>
       </c>
       <c r="H88" s="59" t="str">
-        <f t="shared" ref="H88:H103" si="16">IF((G88*F88)=0,"",G88*F88)</f>
+        <f>IF((G88*F88)=0,"",G88*F88)</f>
         <v/>
       </c>
       <c r="I88" s="34"/>
-      <c r="J88" s="148" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="J88" s="147" t="str">
+        <f t="shared" si="9"/>
+        <v>Sleeping Bag Liner</v>
       </c>
       <c r="P88" s="33"/>
       <c r="Q88" s="59" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="89" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <f t="shared" ref="Q88:Q105" si="10">IF((P88*O88)=0,"",P88*O88)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="5"/>
-      <c r="B89" s="38" t="s">
-        <v>335</v>
-      </c>
-      <c r="C89" s="20"/>
-      <c r="D89" s="21"/>
-      <c r="E89" s="36"/>
+      <c r="B89" s="54" t="s">
+        <v>479</v>
+      </c>
+      <c r="C89" s="20">
+        <v>0.67</v>
+      </c>
+      <c r="D89" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E89" s="36">
+        <f>C89*((58*72)/(36*36))</f>
+        <v>2.1588888888888893</v>
+      </c>
       <c r="F89" s="33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G89" s="35">
-        <v>3.96</v>
+        <v>11.45</v>
       </c>
       <c r="H89" s="59">
-        <f t="shared" si="16"/>
-        <v>3.96</v>
+        <f>IF((G89*F89)=0,"",G89*F89)</f>
+        <v>22.9</v>
       </c>
       <c r="I89" s="34"/>
-      <c r="J89" s="148" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K89" t="s">
-        <v>335</v>
-      </c>
-      <c r="O89">
-        <v>1</v>
-      </c>
-      <c r="P89" s="33">
-        <v>4.5</v>
+      <c r="J89" s="147" t="str">
+        <f t="shared" si="9"/>
+        <v>58 x 72</v>
+      </c>
+      <c r="K89" s="66" t="s">
+        <v>291</v>
+      </c>
+      <c r="L89" s="20">
+        <v>0.66</v>
+      </c>
+      <c r="M89" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="N89" s="36">
+        <f>L89*$A$5</f>
+        <v>2.145</v>
+      </c>
+      <c r="O89" s="33">
+        <v>2</v>
+      </c>
+      <c r="P89" s="35">
+        <v>12.75</v>
       </c>
       <c r="Q89" s="59">
-        <f t="shared" si="14"/>
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="90" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="10"/>
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="5"/>
-      <c r="B90" s="38"/>
-      <c r="C90" s="20"/>
-      <c r="D90" s="21"/>
-      <c r="E90" s="36"/>
+      <c r="B90" s="38" t="s">
+        <v>478</v>
+      </c>
+      <c r="C90" s="20">
+        <v>0.9</v>
+      </c>
+      <c r="D90" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E90" s="36">
+        <f>C90*((58*72)/(36*36))</f>
+        <v>2.9000000000000004</v>
+      </c>
       <c r="F90" s="33"/>
-      <c r="G90" s="64" t="s">
-        <v>65</v>
-      </c>
-      <c r="H90" s="68">
-        <f>SUM(H86:H89)</f>
-        <v>25.36</v>
+      <c r="G90" s="35">
+        <v>8.59</v>
+      </c>
+      <c r="H90" s="59" t="str">
+        <f>IF((G90*F90)=0,"",G90*F90)</f>
+        <v/>
       </c>
       <c r="I90" s="34"/>
-      <c r="J90" s="148" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="P90" s="64" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q90" s="68">
-        <f>SUM(Q86:Q89)</f>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A91" s="5" t="s">
-        <v>366</v>
-      </c>
+      <c r="J90" s="147" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="P90" s="33"/>
+      <c r="Q90" s="59" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+    </row>
+    <row r="91" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="5"/>
       <c r="B91" s="38" t="s">
-        <v>414</v>
-      </c>
-      <c r="C91" s="20">
-        <v>1.3</v>
-      </c>
-      <c r="D91" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="E91" s="36">
-        <f>C91*((12.5*22)/(36*36))</f>
-        <v>0.2758487654320988</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="C91" s="20"/>
+      <c r="D91" s="21"/>
+      <c r="E91" s="36"/>
       <c r="F91" s="33">
         <v>1</v>
       </c>
       <c r="G91" s="35">
-        <v>20.6</v>
+        <v>3.96</v>
       </c>
       <c r="H91" s="59">
-        <f t="shared" si="16"/>
-        <v>20.6</v>
+        <f>IF((G91*F91)=0,"",G91*F91)</f>
+        <v>3.96</v>
       </c>
       <c r="I91" s="34"/>
-      <c r="J91" s="148" t="str">
-        <f t="shared" si="12"/>
-        <v>Food Bag (12.5 x 22)</v>
-      </c>
-      <c r="K91" s="66" t="s">
-        <v>415</v>
-      </c>
-      <c r="L91" s="20">
-        <v>1.43</v>
-      </c>
-      <c r="M91" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="N91" s="36">
-        <f>L91*((12.5*22)/(36*36))</f>
-        <v>0.30343364197530864</v>
-      </c>
-      <c r="O91" s="33">
+      <c r="J91" s="147" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="K91" t="s">
+        <v>332</v>
+      </c>
+      <c r="O91">
         <v>1</v>
       </c>
-      <c r="P91" s="35">
-        <v>27</v>
+      <c r="P91" s="33">
+        <v>4.5</v>
       </c>
       <c r="Q91" s="59">
-        <f t="shared" si="14"/>
-        <v>27</v>
-      </c>
-    </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A92" s="5"/>
-      <c r="B92" s="38" t="s">
-        <v>374</v>
-      </c>
-      <c r="C92" s="20">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="D92" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="E92" s="36">
-        <f>C92*((12.5*22)/(36*36))</f>
-        <v>0.2334104938271605</v>
-      </c>
-      <c r="F92" s="33">
-        <v>1</v>
-      </c>
-      <c r="G92" s="35">
-        <v>6.96</v>
-      </c>
-      <c r="H92" s="59">
-        <f t="shared" si="16"/>
-        <v>6.96</v>
+        <f t="shared" si="10"/>
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="B92" s="38"/>
+      <c r="C92" s="20"/>
+      <c r="D92" s="21"/>
+      <c r="E92" s="36"/>
+      <c r="F92" s="33"/>
+      <c r="G92" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="H92" s="68">
+        <f>SUM(H88:H91)</f>
+        <v>26.86</v>
       </c>
       <c r="I92" s="34"/>
-      <c r="J92" s="148" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="P92" s="35"/>
-      <c r="Q92" s="59" t="str">
-        <f t="shared" si="14"/>
-        <v/>
+      <c r="J92" s="147" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="P92" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q92" s="68">
+        <f>SUM(Q88:Q91)</f>
+        <v>30</v>
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" s="5"/>
       <c r="B93" s="38" t="s">
-        <v>393</v>
-      </c>
-      <c r="C93" s="20"/>
-      <c r="D93" s="21"/>
-      <c r="E93" s="36"/>
+        <v>405</v>
+      </c>
+      <c r="C93" s="20">
+        <v>1.3</v>
+      </c>
+      <c r="D93" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E93" s="36">
+        <f>C93*((12.5*22)/(36*36))</f>
+        <v>0.2758487654320988</v>
+      </c>
       <c r="F93" s="33"/>
-      <c r="G93" s="35"/>
-      <c r="H93" s="59"/>
+      <c r="G93" s="35">
+        <v>20.6</v>
+      </c>
+      <c r="H93" s="59" t="str">
+        <f>IF((G93*F93)=0,"",G93*F93)</f>
+        <v/>
+      </c>
       <c r="I93" s="34"/>
-      <c r="J93" s="148" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="P93" s="35"/>
-      <c r="Q93" s="59"/>
-    </row>
-    <row r="94" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J93" s="147" t="str">
+        <f t="shared" si="9"/>
+        <v>Food Bag (12.5 x 22)</v>
+      </c>
+      <c r="K93" s="66" t="s">
+        <v>406</v>
+      </c>
+      <c r="L93" s="20">
+        <v>1.43</v>
+      </c>
+      <c r="M93" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="N93" s="36">
+        <f>L93*((12.5*22)/(36*36))</f>
+        <v>0.30343364197530864</v>
+      </c>
+      <c r="O93" s="33">
+        <v>1</v>
+      </c>
+      <c r="P93" s="35">
+        <v>27</v>
+      </c>
+      <c r="Q93" s="59">
+        <f t="shared" si="10"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" s="5"/>
       <c r="B94" s="38" t="s">
-        <v>282</v>
+        <v>369</v>
       </c>
       <c r="C94" s="20">
-        <v>15.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="D94" s="21" t="s">
-        <v>161</v>
-      </c>
-      <c r="E94" s="36"/>
+        <v>159</v>
+      </c>
+      <c r="E94" s="36">
+        <f>C94*((12.5*22)/(36*36))</f>
+        <v>0.2334104938271605</v>
+      </c>
       <c r="F94" s="33">
         <v>1</v>
       </c>
       <c r="G94" s="35">
-        <v>0.8</v>
-      </c>
-      <c r="H94" s="59"/>
+        <v>6.96</v>
+      </c>
+      <c r="H94" s="59">
+        <f>IF((G94*F94)=0,"",G94*F94)</f>
+        <v>6.96</v>
+      </c>
       <c r="I94" s="34"/>
-      <c r="J94" s="148" t="str">
-        <f t="shared" si="12"/>
+      <c r="J94" s="147" t="str">
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="P94" s="35"/>
-      <c r="Q94" s="59"/>
-    </row>
-    <row r="95" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Q94" s="59" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" s="5"/>
-      <c r="B95" s="38"/>
+      <c r="B95" s="38" t="s">
+        <v>503</v>
+      </c>
       <c r="C95" s="20"/>
       <c r="D95" s="21"/>
       <c r="E95" s="36"/>
       <c r="F95" s="33"/>
-      <c r="G95" s="64" t="s">
-        <v>65</v>
-      </c>
-      <c r="H95" s="68">
-        <f>SUM(H91:H92)</f>
-        <v>27.560000000000002</v>
-      </c>
+      <c r="G95" s="35"/>
+      <c r="H95" s="59"/>
       <c r="I95" s="34"/>
-      <c r="J95" s="148" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="P95" s="64" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q95" s="68">
-        <f>SUM(Q91:Q92)</f>
-        <v>27</v>
-      </c>
-    </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="J95" s="147" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="P95" s="35"/>
+      <c r="Q95" s="59"/>
+    </row>
+    <row r="96" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="5"/>
-      <c r="B96" s="38"/>
-      <c r="C96" s="20"/>
-      <c r="D96" s="21"/>
+      <c r="B96" s="38" t="s">
+        <v>282</v>
+      </c>
+      <c r="C96" s="20">
+        <v>15.1</v>
+      </c>
+      <c r="D96" s="21" t="s">
+        <v>161</v>
+      </c>
       <c r="E96" s="36"/>
       <c r="F96" s="33"/>
-      <c r="G96" s="64"/>
-      <c r="H96" s="146"/>
+      <c r="G96" s="35">
+        <v>0.8</v>
+      </c>
+      <c r="H96" s="59"/>
       <c r="I96" s="34"/>
-      <c r="J96" s="148"/>
-      <c r="P96" s="64"/>
-      <c r="Q96" s="146"/>
-    </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="J96" s="147" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="P96" s="35"/>
+      <c r="Q96" s="59"/>
+    </row>
+    <row r="97" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="5"/>
       <c r="B97" s="38"/>
       <c r="C97" s="20"/>
       <c r="D97" s="21"/>
       <c r="E97" s="36"/>
       <c r="F97" s="33"/>
-      <c r="G97" s="64"/>
-      <c r="H97" s="146"/>
+      <c r="G97" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="H97" s="68">
+        <f>SUM(H93:H94)</f>
+        <v>6.96</v>
+      </c>
       <c r="I97" s="34"/>
-      <c r="J97" s="148"/>
-      <c r="P97" s="64"/>
-      <c r="Q97" s="146"/>
+      <c r="J97" s="147" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="P97" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q97" s="68">
+        <f>SUM(Q93:Q94)</f>
+        <v>27</v>
+      </c>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A98" s="5" t="s">
-        <v>363</v>
-      </c>
-      <c r="B98" s="38" t="s">
-        <v>362</v>
-      </c>
-      <c r="C98" s="20">
+      <c r="A98" s="5"/>
+      <c r="B98" s="38"/>
+      <c r="C98" s="20"/>
+      <c r="D98" s="21"/>
+      <c r="E98" s="36"/>
+      <c r="F98" s="33"/>
+      <c r="G98" s="64"/>
+      <c r="H98" s="145"/>
+      <c r="I98" s="34"/>
+      <c r="J98" s="147"/>
+      <c r="P98" s="64"/>
+      <c r="Q98" s="145"/>
+    </row>
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A99" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="B99" s="38"/>
+      <c r="C99" s="20"/>
+      <c r="D99" s="21"/>
+      <c r="E99" s="36"/>
+      <c r="F99" s="33"/>
+      <c r="G99" s="64"/>
+      <c r="H99" s="145"/>
+      <c r="I99" s="34"/>
+      <c r="J99" s="147"/>
+      <c r="P99" s="64"/>
+      <c r="Q99" s="145"/>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A100" s="128" t="s">
+        <v>426</v>
+      </c>
+      <c r="B100" s="38" t="s">
+        <v>357</v>
+      </c>
+      <c r="C100" s="20">
         <v>0.51</v>
       </c>
-      <c r="D98" s="21" t="s">
+      <c r="D100" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="E98" s="36">
-        <f>C98*((36*56)/(36*36))</f>
+      <c r="E100" s="36">
+        <f>C100*((36*56)/(36*36))</f>
         <v>0.79333333333333333</v>
       </c>
-      <c r="F98" s="33">
+      <c r="F100" s="33"/>
+      <c r="G100" s="35">
+        <v>20.6</v>
+      </c>
+      <c r="H100" s="59" t="str">
+        <f>IF((G100*F100)=0,"",G100*F100)</f>
+        <v/>
+      </c>
+      <c r="I100" s="34"/>
+      <c r="J100" s="146" t="str">
+        <f t="shared" ref="J100:J108" si="11">IF(ISBLANK(A99),"",A99)</f>
+        <v>Rain Kilt (30L x 48W)</v>
+      </c>
+      <c r="K100" s="66" t="s">
+        <v>357</v>
+      </c>
+      <c r="L100" s="20">
+        <v>0.51</v>
+      </c>
+      <c r="M100" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="N100" s="36">
+        <f>L100*((36*56)/(36*36))</f>
+        <v>0.79333333333333333</v>
+      </c>
+      <c r="O100" s="33">
         <v>2</v>
       </c>
-      <c r="G98" s="35">
-        <v>20.6</v>
-      </c>
-      <c r="H98" s="59">
-        <f t="shared" si="16"/>
-        <v>41.2</v>
-      </c>
-      <c r="I98" s="34"/>
-      <c r="J98" s="147" t="str">
-        <f t="shared" si="12"/>
-        <v>Rain Kilt (30L x 48W)</v>
-      </c>
-      <c r="K98" s="66" t="s">
-        <v>362</v>
-      </c>
-      <c r="L98" s="20">
-        <v>0.51</v>
-      </c>
-      <c r="M98" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="N98" s="36">
-        <f>L98*((36*56)/(36*36))</f>
-        <v>0.79333333333333333</v>
-      </c>
-      <c r="O98" s="33">
-        <v>2</v>
-      </c>
-      <c r="P98" s="35">
+      <c r="P100" s="35">
         <v>20.5</v>
       </c>
-      <c r="Q98" s="59">
-        <f t="shared" si="14"/>
+      <c r="Q100" s="59">
+        <f t="shared" si="10"/>
         <v>41</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A99" s="129" t="s">
-        <v>436</v>
-      </c>
-      <c r="B99" s="38" t="s">
-        <v>374</v>
-      </c>
-      <c r="C99" s="20">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="D99" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="E99" s="36">
-        <f>C99*((36*56)/(36*36))</f>
-        <v>1.7111111111111112</v>
-      </c>
-      <c r="F99" s="33">
-        <v>1</v>
-      </c>
-      <c r="G99" s="35">
-        <v>6.9630000000000001</v>
-      </c>
-      <c r="H99" s="59">
-        <f t="shared" si="16"/>
-        <v>6.9630000000000001</v>
-      </c>
-      <c r="I99" s="34"/>
-      <c r="J99" s="148" t="str">
-        <f t="shared" si="12"/>
-        <v>-OR- 36L x 56W</v>
-      </c>
-      <c r="P99" s="35"/>
-      <c r="Q99" s="59" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A100" s="5"/>
-      <c r="B100" s="38" t="s">
-        <v>395</v>
-      </c>
-      <c r="C100" s="20"/>
-      <c r="D100" s="21"/>
-      <c r="E100" s="36"/>
-      <c r="F100" s="33"/>
-      <c r="G100" s="35"/>
-      <c r="H100" s="59"/>
-      <c r="I100" s="34"/>
-      <c r="J100" s="148" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="P100" s="35"/>
-      <c r="Q100" s="59"/>
-    </row>
-    <row r="101" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" s="5"/>
       <c r="B101" s="38" t="s">
-        <v>401</v>
-      </c>
-      <c r="C101" s="20"/>
-      <c r="D101" s="21"/>
-      <c r="E101" s="36"/>
-      <c r="F101" s="33"/>
-      <c r="G101" s="35"/>
-      <c r="H101" s="59"/>
+        <v>369</v>
+      </c>
+      <c r="C101" s="20">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D101" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E101" s="36">
+        <f>C101*((36*56)/(36*36))</f>
+        <v>1.7111111111111112</v>
+      </c>
+      <c r="F101" s="33">
+        <v>1</v>
+      </c>
+      <c r="G101" s="35">
+        <v>6.9630000000000001</v>
+      </c>
+      <c r="H101" s="59">
+        <f>IF((G101*F101)=0,"",G101*F101)</f>
+        <v>6.9630000000000001</v>
+      </c>
       <c r="I101" s="34"/>
-      <c r="J101" s="148" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="J101" s="147" t="str">
+        <f t="shared" si="11"/>
+        <v>-OR- 36L x 56W</v>
       </c>
       <c r="P101" s="35"/>
-      <c r="Q101" s="59"/>
-    </row>
-    <row r="102" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Q101" s="59" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+    </row>
+    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" s="5"/>
-      <c r="B102" s="38"/>
+      <c r="B102" s="38" t="s">
+        <v>389</v>
+      </c>
       <c r="C102" s="20"/>
       <c r="D102" s="21"/>
       <c r="E102" s="36"/>
       <c r="F102" s="33"/>
-      <c r="G102" s="64" t="s">
-        <v>65</v>
-      </c>
-      <c r="H102" s="68">
-        <f>SUM(H98:H99)</f>
-        <v>48.163000000000004</v>
-      </c>
+      <c r="G102" s="35"/>
+      <c r="H102" s="59"/>
       <c r="I102" s="34"/>
-      <c r="J102" s="148" t="str">
-        <f t="shared" si="12"/>
+      <c r="J102" s="147" t="str">
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="P102" s="35"/>
       <c r="Q102" s="59"/>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A103" s="5" t="s">
-        <v>361</v>
-      </c>
+    <row r="103" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="5"/>
       <c r="B103" s="38" t="s">
-        <v>374</v>
-      </c>
-      <c r="C103" s="20">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="D103" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="E103" s="36">
-        <f>C103*((72*54)/(36*36))</f>
-        <v>3.3000000000000003</v>
-      </c>
-      <c r="F103" s="33">
-        <v>2</v>
-      </c>
-      <c r="G103" s="35">
-        <v>6.96</v>
-      </c>
-      <c r="H103" s="59">
-        <f t="shared" si="16"/>
-        <v>13.92</v>
-      </c>
+        <v>395</v>
+      </c>
+      <c r="C103" s="20"/>
+      <c r="D103" s="21"/>
+      <c r="E103" s="36"/>
+      <c r="F103" s="33"/>
+      <c r="G103" s="35"/>
+      <c r="H103" s="59"/>
       <c r="I103" s="34"/>
       <c r="J103" s="147" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="P103" s="35"/>
+      <c r="Q103" s="59"/>
+    </row>
+    <row r="104" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="B104" s="38"/>
+      <c r="C104" s="20"/>
+      <c r="D104" s="21"/>
+      <c r="E104" s="36"/>
+      <c r="F104" s="33"/>
+      <c r="G104" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="H104" s="68">
+        <f>SUM(H100:H101)</f>
+        <v>6.9630000000000001</v>
+      </c>
+      <c r="I104" s="34"/>
+      <c r="J104" s="147" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="P104" s="35"/>
+      <c r="Q104" s="59"/>
+    </row>
+    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A105" s="60" t="s">
+        <v>363</v>
+      </c>
+      <c r="B105" s="38" t="s">
+        <v>369</v>
+      </c>
+      <c r="C105" s="20">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D105" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E105" s="36">
+        <f>C105*((72*54)/(36*36))</f>
+        <v>3.3000000000000003</v>
+      </c>
+      <c r="F105" s="33">
+        <v>2</v>
+      </c>
+      <c r="G105" s="35">
+        <v>6.96</v>
+      </c>
+      <c r="H105" s="59">
+        <f>IF((G105*F105)=0,"",G105*F105)</f>
+        <v>13.92</v>
+      </c>
+      <c r="I105" s="34"/>
+      <c r="J105" s="146" t="str">
+        <f t="shared" si="11"/>
         <v>Rain Pants</v>
       </c>
-      <c r="K103" t="s">
-        <v>367</v>
-      </c>
-      <c r="N103" s="36">
+      <c r="K105" t="s">
+        <v>362</v>
+      </c>
+      <c r="N105" s="36">
         <f>1.4*((72*54)/(36*36))</f>
         <v>4.1999999999999993</v>
       </c>
-      <c r="O103" s="33">
+      <c r="O105" s="33">
         <v>2</v>
       </c>
-      <c r="P103" s="35">
+      <c r="P105" s="35">
         <v>20</v>
       </c>
-      <c r="Q103" s="59">
-        <f t="shared" si="14"/>
+      <c r="Q105" s="59">
+        <f t="shared" si="10"/>
         <v>40</v>
       </c>
-    </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A104" s="60" t="s">
-        <v>368</v>
-      </c>
-      <c r="B104" s="38" t="s">
-        <v>362</v>
-      </c>
-      <c r="C104" s="20">
-        <v>0.51</v>
-      </c>
-      <c r="D104" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="E104" s="36">
-        <f>C104*((30*48)/(36*36))</f>
-        <v>0.56666666666666665</v>
-      </c>
-      <c r="F104" s="33"/>
-      <c r="G104" s="35">
-        <v>20.6</v>
-      </c>
-      <c r="H104" s="59" t="str">
-        <f t="shared" ref="H104" si="17">IF((G104*F104)=0,"",G104*F104)</f>
-        <v/>
-      </c>
-      <c r="I104" s="34"/>
-      <c r="J104" s="148" t="str">
-        <f t="shared" si="12"/>
-        <v>make pattern</v>
-      </c>
-      <c r="K104" s="66" t="s">
-        <v>362</v>
-      </c>
-      <c r="L104" s="20">
-        <v>0.51</v>
-      </c>
-      <c r="M104" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="N104" s="36">
-        <f>L104*((12.5*22)/(36*36))</f>
-        <v>0.10821759259259259</v>
-      </c>
-      <c r="O104" s="33"/>
-      <c r="P104" s="35">
-        <v>20.5</v>
-      </c>
-      <c r="Q104" s="59" t="str">
-        <f t="shared" ref="Q104" si="18">IF((P104*O104)=0,"",P104*O104)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A105" s="60"/>
-      <c r="B105" s="46" t="s">
-        <v>379</v>
-      </c>
-      <c r="C105" s="20"/>
-      <c r="D105" s="21"/>
-      <c r="E105" s="36"/>
-      <c r="F105" s="33"/>
-      <c r="G105" s="35"/>
-      <c r="H105" s="59"/>
-      <c r="I105" s="34"/>
-      <c r="J105" s="148" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K105" s="66"/>
-      <c r="L105" s="20"/>
-      <c r="M105" s="21"/>
-      <c r="N105" s="36"/>
-      <c r="O105" s="33"/>
-      <c r="P105" s="35"/>
-      <c r="Q105" s="59"/>
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" s="60"/>
-      <c r="B106" s="50" t="s">
-        <v>316</v>
-      </c>
-      <c r="C106" s="20"/>
-      <c r="D106" s="21"/>
-      <c r="E106" s="36"/>
+      <c r="B106" s="38" t="s">
+        <v>357</v>
+      </c>
+      <c r="C106" s="20">
+        <v>0.51</v>
+      </c>
+      <c r="D106" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E106" s="36">
+        <f>C106*((30*48)/(36*36))</f>
+        <v>0.56666666666666665</v>
+      </c>
       <c r="F106" s="33"/>
-      <c r="G106" s="35"/>
-      <c r="H106" s="59"/>
+      <c r="G106" s="35">
+        <v>20.6</v>
+      </c>
+      <c r="H106" s="59" t="str">
+        <f>IF((G106*F106)=0,"",G106*F106)</f>
+        <v/>
+      </c>
       <c r="I106" s="34"/>
-      <c r="J106" s="148" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K106" s="66"/>
-      <c r="L106" s="20"/>
-      <c r="M106" s="21"/>
-      <c r="N106" s="36"/>
+      <c r="J106" s="147" t="str">
+        <f t="shared" si="11"/>
+        <v>make pattern</v>
+      </c>
+      <c r="K106" s="66" t="s">
+        <v>357</v>
+      </c>
+      <c r="L106" s="20">
+        <v>0.51</v>
+      </c>
+      <c r="M106" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="N106" s="36">
+        <f>L106*((12.5*22)/(36*36))</f>
+        <v>0.10821759259259259</v>
+      </c>
       <c r="O106" s="33"/>
-      <c r="P106" s="35"/>
-      <c r="Q106" s="59"/>
-    </row>
-    <row r="107" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P106" s="35">
+        <v>20.5</v>
+      </c>
+      <c r="Q106" s="59" t="str">
+        <f>IF((P106*O106)=0,"",P106*O106)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" s="60"/>
-      <c r="B107" s="38" t="s">
-        <v>335</v>
+      <c r="B107" s="46" t="s">
+        <v>374</v>
       </c>
       <c r="C107" s="20"/>
       <c r="D107" s="21"/>
       <c r="E107" s="36"/>
-      <c r="F107" s="33">
-        <v>1</v>
-      </c>
-      <c r="G107" s="35">
-        <v>3.96</v>
-      </c>
-      <c r="H107" s="59">
-        <f t="shared" ref="H107" si="19">IF((G107*F107)=0,"",G107*F107)</f>
-        <v>3.96</v>
-      </c>
+      <c r="F107" s="33"/>
+      <c r="G107" s="35"/>
+      <c r="H107" s="59"/>
       <c r="I107" s="34"/>
-      <c r="J107" s="148" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K107" t="s">
-        <v>335</v>
-      </c>
-      <c r="O107">
-        <v>1</v>
-      </c>
-      <c r="P107" s="138">
-        <v>4.5</v>
-      </c>
-      <c r="Q107" s="59">
-        <f t="shared" ref="Q107" si="20">IF((P107*O107)=0,"",P107*O107)</f>
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="108" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J107" s="147" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="K107" s="66"/>
+      <c r="L107" s="20"/>
+      <c r="M107" s="21"/>
+      <c r="N107" s="36"/>
+      <c r="O107" s="33"/>
+      <c r="P107" s="35"/>
+      <c r="Q107" s="59"/>
+    </row>
+    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" s="60"/>
-      <c r="B108" s="38"/>
+      <c r="B108" s="50" t="s">
+        <v>314</v>
+      </c>
       <c r="C108" s="20"/>
       <c r="D108" s="21"/>
       <c r="E108" s="36"/>
       <c r="F108" s="33"/>
-      <c r="G108" s="64" t="s">
-        <v>65</v>
-      </c>
-      <c r="H108" s="68">
-        <f>SUM(H103:H107)</f>
-        <v>17.88</v>
-      </c>
+      <c r="G108" s="35"/>
+      <c r="H108" s="59"/>
       <c r="I108" s="34"/>
-      <c r="J108" s="148" t="str">
-        <f t="shared" si="12"/>
+      <c r="J108" s="147" t="str">
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K108" s="66"/>
@@ -9201,20 +9387,13 @@
       <c r="M108" s="21"/>
       <c r="N108" s="36"/>
       <c r="O108" s="33"/>
-      <c r="P108" s="64" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q108" s="68">
-        <f>SUM(Q103:Q107)</f>
-        <v>44.5</v>
-      </c>
+      <c r="P108" s="35"/>
+      <c r="Q108" s="59"/>
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A109" s="18" t="s">
-        <v>369</v>
-      </c>
-      <c r="B109" s="38" t="s">
-        <v>370</v>
+      <c r="A109" s="60"/>
+      <c r="B109" s="50" t="s">
+        <v>477</v>
       </c>
       <c r="C109" s="20"/>
       <c r="D109" s="21"/>
@@ -9223,288 +9402,375 @@
       <c r="G109" s="35"/>
       <c r="H109" s="59"/>
       <c r="I109" s="34"/>
-      <c r="J109" s="147" t="str">
-        <f t="shared" si="12"/>
-        <v>Pack Cover (new pack)</v>
-      </c>
-      <c r="P109" s="33"/>
-      <c r="Q109" s="10"/>
-    </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A110" s="18" t="s">
-        <v>287</v>
-      </c>
-      <c r="B110" s="61" t="s">
-        <v>372</v>
+      <c r="J109" s="147"/>
+      <c r="K109" s="66"/>
+      <c r="L109" s="20"/>
+      <c r="M109" s="21"/>
+      <c r="N109" s="36"/>
+      <c r="O109" s="33"/>
+      <c r="P109" s="35"/>
+      <c r="Q109" s="59"/>
+    </row>
+    <row r="110" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="60"/>
+      <c r="B110" s="38" t="s">
+        <v>332</v>
+      </c>
+      <c r="C110" s="20"/>
+      <c r="D110" s="21"/>
+      <c r="E110" s="36"/>
+      <c r="F110" s="33"/>
+      <c r="G110" s="35">
+        <v>3.96</v>
       </c>
       <c r="H110" s="59" t="str">
-        <f t="shared" si="13"/>
+        <f>IF((G110*F110)=0,"",G110*F110)</f>
         <v/>
       </c>
       <c r="I110" s="34"/>
       <c r="J110" s="147" t="str">
-        <f t="shared" si="12"/>
-        <v>Ditty Bags (See ToDo)</v>
-      </c>
-    </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+        <f t="shared" ref="J110:J117" si="12">IF(ISBLANK(A109),"",A109)</f>
+        <v/>
+      </c>
+      <c r="K110" t="s">
+        <v>332</v>
+      </c>
+      <c r="O110">
+        <v>1</v>
+      </c>
+      <c r="P110" s="137">
+        <v>4.5</v>
+      </c>
+      <c r="Q110" s="59">
+        <f>IF((P110*O110)=0,"",P110*O110)</f>
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="111" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="18" t="s">
-        <v>288</v>
-      </c>
-      <c r="B111" s="38" t="s">
-        <v>371</v>
-      </c>
-      <c r="H111" s="59" t="str">
-        <f t="shared" si="13"/>
-        <v/>
+        <v>364</v>
+      </c>
+      <c r="B111" s="38"/>
+      <c r="C111" s="20"/>
+      <c r="D111" s="21"/>
+      <c r="E111" s="36"/>
+      <c r="F111" s="33"/>
+      <c r="G111" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="H111" s="68">
+        <f>SUM(H105:H110)</f>
+        <v>13.92</v>
       </c>
       <c r="I111" s="34"/>
       <c r="J111" s="147" t="str">
         <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="K111" s="66"/>
+      <c r="L111" s="20"/>
+      <c r="M111" s="21"/>
+      <c r="N111" s="36"/>
+      <c r="O111" s="33"/>
+      <c r="P111" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q111" s="68">
+        <f>SUM(Q105:Q110)</f>
+        <v>44.5</v>
+      </c>
+    </row>
+    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A112" s="18" t="s">
+        <v>287</v>
+      </c>
+      <c r="B112" s="38" t="s">
+        <v>365</v>
+      </c>
+      <c r="C112" s="20"/>
+      <c r="D112" s="21"/>
+      <c r="E112" s="36"/>
+      <c r="F112" s="33"/>
+      <c r="G112" s="35"/>
+      <c r="H112" s="59"/>
+      <c r="I112" s="34"/>
+      <c r="J112" s="146" t="str">
+        <f t="shared" si="12"/>
+        <v>Pack Cover (new pack)</v>
+      </c>
+      <c r="P112" s="33"/>
+      <c r="Q112" s="10"/>
+    </row>
+    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A113" s="18" t="s">
+        <v>288</v>
+      </c>
+      <c r="B113" s="61" t="s">
+        <v>367</v>
+      </c>
+      <c r="H113" s="59" t="str">
+        <f>IF((G113*F113)=0,"",G113*F113)</f>
+        <v/>
+      </c>
+      <c r="I113" s="34"/>
+      <c r="J113" s="146" t="str">
+        <f t="shared" si="12"/>
+        <v>Ditty Bags (See ToDo)</v>
+      </c>
+    </row>
+    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B114" s="38" t="s">
+        <v>366</v>
+      </c>
+      <c r="H114" s="59" t="str">
+        <f>IF((G114*F114)=0,"",G114*F114)</f>
+        <v/>
+      </c>
+      <c r="I114" s="34"/>
+      <c r="J114" s="146" t="str">
+        <f t="shared" si="12"/>
         <v>Kilt (Use ION)</v>
       </c>
     </row>
-    <row r="112" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B112" s="38"/>
-      <c r="H112" s="59" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="I112" s="34"/>
-      <c r="J112" s="148" t="str">
+    <row r="115" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="18" t="s">
+        <v>461</v>
+      </c>
+      <c r="B115" s="38"/>
+      <c r="H115" s="59" t="str">
+        <f>IF((G115*F115)=0,"",G115*F115)</f>
+        <v/>
+      </c>
+      <c r="I115" s="34"/>
+      <c r="J115" s="147" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="Q112" s="20"/>
-    </row>
-    <row r="113" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="18" t="s">
-        <v>471</v>
-      </c>
-      <c r="B113" s="54" t="s">
-        <v>457</v>
-      </c>
-      <c r="C113">
-        <f>C114*F118</f>
+      <c r="Q115" s="20"/>
+    </row>
+    <row r="116" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B116" s="54" t="s">
+        <v>447</v>
+      </c>
+      <c r="C116">
+        <f>C117*F121</f>
         <v>6.8078820000000002</v>
       </c>
-      <c r="D113" t="s">
+      <c r="D116" t="s">
         <v>159</v>
       </c>
-      <c r="E113" s="36">
-        <f>C113*((30*48)/(36*36))</f>
+      <c r="E116" s="36">
+        <f>C116*((30*48)/(36*36))</f>
         <v>7.5643133333333337</v>
       </c>
-      <c r="F113">
+      <c r="F116">
         <v>2</v>
       </c>
-      <c r="G113">
+      <c r="G116">
         <v>29</v>
       </c>
-      <c r="H113" s="59">
-        <f t="shared" si="13"/>
+      <c r="H116" s="59">
+        <f>IF((G116*F116)=0,"",G116*F116)</f>
         <v>58</v>
       </c>
-      <c r="I113" s="34"/>
-      <c r="J113" s="147" t="str">
+      <c r="I116" s="34"/>
+      <c r="J116" s="146" t="str">
         <f t="shared" si="12"/>
         <v>Pullover/hoodie</v>
       </c>
-      <c r="K113" t="s">
-        <v>458</v>
-      </c>
-      <c r="L113">
+      <c r="K116" t="s">
+        <v>448</v>
+      </c>
+      <c r="L116">
         <v>4.8</v>
       </c>
-      <c r="M113" t="s">
+      <c r="M116" t="s">
         <v>159</v>
       </c>
-      <c r="N113" s="36">
+      <c r="N116" s="36">
         <f>1.4*((72*54)/(36*36))</f>
         <v>4.1999999999999993</v>
       </c>
-      <c r="O113">
+      <c r="O116" s="25">
         <v>2</v>
       </c>
-      <c r="P113" s="137">
+      <c r="P116" s="136">
         <v>27.25</v>
       </c>
-      <c r="Q113" s="68">
-        <f t="shared" ref="Q113" si="21">IF((P113*O113)=0,"",P113*O113)</f>
+      <c r="Q116" s="68">
+        <f>IF((P116*O116)=0,"",P116*O116)</f>
         <v>54.5</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B114" s="54" t="s">
-        <v>460</v>
-      </c>
-      <c r="C114">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B117" s="54" t="s">
+        <v>450</v>
+      </c>
+      <c r="C117">
         <v>193</v>
       </c>
-      <c r="D114" t="s">
+      <c r="D117" t="s">
         <v>161</v>
       </c>
-      <c r="I114" s="34"/>
-      <c r="J114" s="144" t="str">
+      <c r="J117" s="143" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="K114" t="s">
-        <v>459</v>
-      </c>
-      <c r="L114">
+      <c r="K117" t="s">
+        <v>449</v>
+      </c>
+      <c r="L117">
         <v>135.62</v>
       </c>
-      <c r="M114" t="s">
+      <c r="M117" t="s">
         <v>161</v>
       </c>
-      <c r="N114" s="36"/>
-    </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B115" s="118">
+      <c r="N117" s="36"/>
+    </row>
+    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A118" s="131" t="s">
+        <v>445</v>
+      </c>
+      <c r="B118" s="117">
         <v>4004</v>
       </c>
-      <c r="C115">
+      <c r="C118">
         <v>119</v>
       </c>
-      <c r="F115">
+      <c r="F118">
         <v>2</v>
       </c>
-      <c r="G115">
+      <c r="G118">
         <v>28</v>
       </c>
-      <c r="H115" s="59">
-        <f t="shared" si="13"/>
+      <c r="H118" s="59">
+        <f>IF((G118*F118)=0,"",G118*F118)</f>
         <v>56</v>
       </c>
-      <c r="I115" s="34"/>
-      <c r="K115" t="s">
-        <v>461</v>
-      </c>
-      <c r="P115" s="137">
+      <c r="K118" t="s">
+        <v>451</v>
+      </c>
+      <c r="P118" s="136">
         <v>20</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A116" s="132" t="s">
-        <v>455</v>
-      </c>
-      <c r="K116" t="s">
-        <v>473</v>
-      </c>
-      <c r="L116">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A119" s="18" t="s">
+        <v>446</v>
+      </c>
+      <c r="K119" t="s">
+        <v>463</v>
+      </c>
+      <c r="L119">
         <v>152.58000000000001</v>
       </c>
-      <c r="M116" t="s">
+      <c r="M119" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="18" t="s">
-        <v>456</v>
-      </c>
-      <c r="L117">
-        <f>L116*F118</f>
+    <row r="120" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L120">
+        <f>L119*F121</f>
         <v>5.38210692</v>
       </c>
-      <c r="M117" t="s">
+      <c r="M120" t="s">
         <v>159</v>
       </c>
-      <c r="O117">
+      <c r="O120">
         <v>2</v>
       </c>
-      <c r="P117" s="137">
+      <c r="P120" s="136">
         <v>31.5</v>
       </c>
-      <c r="Q117" s="59">
-        <f t="shared" ref="Q117:Q118" si="22">IF((P117*O117)=0,"",P117*O117)</f>
+      <c r="Q120" s="59">
+        <f>IF((P120*O120)=0,"",P120*O120)</f>
         <v>63</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="D118" s="133">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="D121" s="132">
         <v>1</v>
       </c>
-      <c r="E118" s="79" t="s">
-        <v>463</v>
-      </c>
-      <c r="F118" s="79">
+      <c r="E121" s="79" t="s">
+        <v>453</v>
+      </c>
+      <c r="F121" s="79">
         <v>3.5274E-2</v>
       </c>
-      <c r="G118" s="80" t="s">
+      <c r="G121" s="80" t="s">
         <v>159</v>
       </c>
-      <c r="K118" s="31" t="s">
-        <v>481</v>
-      </c>
-      <c r="O118">
+      <c r="K121" s="31" t="s">
+        <v>471</v>
+      </c>
+      <c r="O121">
         <v>2</v>
       </c>
-      <c r="P118" s="137">
+      <c r="P121" s="136">
         <v>26.25</v>
       </c>
-      <c r="Q118" s="59">
-        <f t="shared" si="22"/>
+      <c r="Q121" s="59">
+        <f>IF((P121*O121)=0,"",P121*O121)</f>
         <v>52.5</v>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D119" s="134">
+    <row r="122" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D122" s="133">
         <v>28.349499999999999</v>
       </c>
-      <c r="E119" s="135" t="s">
-        <v>463</v>
-      </c>
-      <c r="F119" s="135">
+      <c r="E122" s="134" t="s">
+        <v>453</v>
+      </c>
+      <c r="F122" s="134">
         <v>1</v>
       </c>
-      <c r="G119" s="136" t="s">
+      <c r="G122" s="135" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="K120" s="166"/>
-      <c r="L120" s="66"/>
-      <c r="M120" s="66"/>
-      <c r="N120" s="159"/>
-      <c r="O120" s="66"/>
-      <c r="P120" s="66"/>
-    </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="K121" s="166"/>
-      <c r="L121" s="66"/>
-      <c r="M121" s="66"/>
-      <c r="N121" s="159"/>
-      <c r="O121" s="66"/>
-      <c r="P121" s="66"/>
-    </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="K122" s="166"/>
-      <c r="L122" s="66"/>
-      <c r="M122" s="66"/>
-      <c r="N122" s="159"/>
-      <c r="O122" s="66"/>
-      <c r="P122" s="66"/>
-    </row>
     <row r="123" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="K123" s="166"/>
+      <c r="K123" s="165"/>
       <c r="L123" s="66"/>
       <c r="M123" s="66"/>
-      <c r="N123" s="159"/>
+      <c r="N123" s="158"/>
       <c r="O123" s="66"/>
       <c r="P123" s="66"/>
     </row>
     <row r="124" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="K124" s="166"/>
+      <c r="K124" s="165"/>
       <c r="L124" s="66"/>
       <c r="M124" s="66"/>
-      <c r="N124" s="159"/>
+      <c r="N124" s="158"/>
       <c r="O124" s="66"/>
       <c r="P124" s="66"/>
     </row>
+    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K125" s="165"/>
+      <c r="L125" s="66"/>
+      <c r="M125" s="66"/>
+      <c r="N125" s="158"/>
+      <c r="O125" s="66"/>
+      <c r="P125" s="66"/>
+    </row>
+    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K126" s="165"/>
+      <c r="L126" s="66"/>
+      <c r="M126" s="66"/>
+      <c r="N126" s="158"/>
+      <c r="O126" s="66"/>
+      <c r="P126" s="66"/>
+    </row>
+    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K127" s="165"/>
+      <c r="L127" s="66"/>
+      <c r="M127" s="66"/>
+      <c r="N127" s="158"/>
+      <c r="O127" s="66"/>
+      <c r="P127" s="66"/>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B110" location="ToDo!A19" display="See ToDo" xr:uid="{CE28C4E6-45D1-4C5D-A0AF-3ACF169C0D5B}"/>
+    <hyperlink ref="B113" location="ToDo!A19" display="See ToDo" xr:uid="{CE28C4E6-45D1-4C5D-A0AF-3ACF169C0D5B}"/>
     <hyperlink ref="R31" location="Make!A81" display="L" xr:uid="{F2445477-C9B7-447F-944F-160D21ACEB18}"/>
     <hyperlink ref="R32" location="Make!A85" display="L" xr:uid="{D614D32D-E4C7-4ABC-8AEA-2A0D20F4C1EC}"/>
     <hyperlink ref="R27" location="Make!A90" display="L" xr:uid="{786E7206-F76A-4474-B631-F01E095CA8FB}"/>
@@ -9523,7 +9789,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3D8ADF0-8E94-4902-A1F9-3D27383A1516}">
-  <dimension ref="A1:T31"/>
+  <dimension ref="A1:V31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -9587,8 +9853,8 @@
       <c r="B3" s="16">
         <v>50</v>
       </c>
-      <c r="C3" s="165">
-        <f>(B3-32)*5/9</f>
+      <c r="C3" s="164">
+        <f t="shared" ref="C3:C8" si="0">(B3-32)*5/9</f>
         <v>10</v>
       </c>
       <c r="D3" t="s">
@@ -9602,8 +9868,8 @@
       <c r="B4">
         <v>40</v>
       </c>
-      <c r="C4" s="165">
-        <f t="shared" ref="C4:C8" si="0">(B4-32)*5/9</f>
+      <c r="C4" s="164">
+        <f t="shared" si="0"/>
         <v>4.4444444444444446</v>
       </c>
       <c r="K4" s="26">
@@ -9614,7 +9880,7 @@
         <v>258</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -9624,7 +9890,7 @@
       <c r="B5" s="29">
         <v>30</v>
       </c>
-      <c r="C5" s="165">
+      <c r="C5" s="164">
         <f t="shared" si="0"/>
         <v>-1.1111111111111112</v>
       </c>
@@ -9638,7 +9904,7 @@
         <v>259</v>
       </c>
       <c r="O5" s="20" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="P5">
         <v>32</v>
@@ -9657,7 +9923,7 @@
       <c r="B6" s="29">
         <v>20</v>
       </c>
-      <c r="C6" s="165">
+      <c r="C6" s="164">
         <f t="shared" si="0"/>
         <v>-6.666666666666667</v>
       </c>
@@ -9671,13 +9937,13 @@
         <v>260</v>
       </c>
       <c r="O6" s="20" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="P6">
         <v>16</v>
       </c>
       <c r="Q6" s="20" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="R6">
         <v>8.1999999999999993</v>
@@ -9690,7 +9956,7 @@
       <c r="B7">
         <v>10</v>
       </c>
-      <c r="C7" s="165">
+      <c r="C7" s="164">
         <f t="shared" si="0"/>
         <v>-12.222222222222221</v>
       </c>
@@ -9701,13 +9967,13 @@
         <v>261</v>
       </c>
       <c r="O7" s="20" t="s">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="P7">
         <v>44.8</v>
       </c>
       <c r="Q7" s="20" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="R7">
         <v>26</v>
@@ -9716,7 +9982,7 @@
         <v>22</v>
       </c>
       <c r="T7" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -9726,7 +9992,7 @@
       <c r="B8" s="25">
         <v>-5</v>
       </c>
-      <c r="C8" s="165">
+      <c r="C8" s="164">
         <f t="shared" si="0"/>
         <v>-20.555555555555557</v>
       </c>
@@ -9738,13 +10004,13 @@
         <v>262</v>
       </c>
       <c r="O8" s="20" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="P8">
         <v>4.2</v>
       </c>
       <c r="Q8" s="20" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="R8">
         <v>23</v>
@@ -9753,7 +10019,7 @@
         <v>20</v>
       </c>
       <c r="T8" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -9768,13 +10034,13 @@
         <v>263</v>
       </c>
       <c r="O9" s="20" t="s">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="P9">
         <v>4</v>
       </c>
       <c r="Q9" s="20" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="R9">
         <v>7.3</v>
@@ -9814,7 +10080,7 @@
       </c>
       <c r="O10" s="20"/>
       <c r="Q10" s="20" t="s">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="R10">
         <v>6</v>
@@ -9859,7 +10125,7 @@
         <v>5.9486955449999996</v>
       </c>
       <c r="Q11" s="20" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="R11">
         <v>6</v>
@@ -9884,14 +10150,14 @@
         <f t="shared" ref="M12:M28" si="2">(J12*K12/$K$4)*F12</f>
         <v>0</v>
       </c>
-      <c r="P12" s="130">
+      <c r="P12" s="129">
         <f>SUM(P5:P11)</f>
         <v>101</v>
       </c>
-      <c r="Q12" s="131" t="s">
+      <c r="Q12" s="130" t="s">
         <v>65</v>
       </c>
-      <c r="R12" s="130">
+      <c r="R12" s="129">
         <f>SUM(R5:R11)</f>
         <v>93.2</v>
       </c>
@@ -9936,7 +10202,7 @@
         <v>6</v>
       </c>
       <c r="Q13" s="20" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="R13">
         <f>INT(R12/16)</f>
@@ -9983,7 +10249,7 @@
         <v>5</v>
       </c>
       <c r="Q14" s="20" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="R14">
         <f>R12-(R13*16)</f>
@@ -9994,7 +10260,7 @@
         <v>7</v>
       </c>
       <c r="T14" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -10032,7 +10298,7 @@
         <v>0</v>
       </c>
       <c r="S15" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -10055,7 +10321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>1.2</v>
       </c>
@@ -10091,7 +10357,7 @@
         <v>9.5239799999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>1.6</v>
       </c>
@@ -10126,25 +10392,25 @@
         <f t="shared" si="2"/>
         <v>14.192493900000001</v>
       </c>
-      <c r="O18" s="154" t="s">
-        <v>474</v>
-      </c>
-      <c r="P18" s="155">
+      <c r="O18" s="153" t="s">
+        <v>464</v>
+      </c>
+      <c r="P18" s="154">
         <v>60</v>
       </c>
-      <c r="Q18" s="155" t="s">
-        <v>479</v>
-      </c>
-      <c r="R18" s="156">
-        <f>P18*2*$E$1</f>
-        <v>4.2328799999999998</v>
-      </c>
-      <c r="S18" s="155" t="s">
-        <v>480</v>
-      </c>
-      <c r="T18" s="157"/>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="Q18" s="154" t="s">
+        <v>469</v>
+      </c>
+      <c r="R18" s="155">
+        <f>P18*2*$E$1*$U$23</f>
+        <v>6.8196399999999997</v>
+      </c>
+      <c r="S18" s="154" t="s">
+        <v>470</v>
+      </c>
+      <c r="T18" s="156"/>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>179</v>
       </c>
@@ -10166,25 +10432,25 @@
         <f t="shared" si="2"/>
         <v>3.822222222222222</v>
       </c>
-      <c r="O19" s="158" t="s">
-        <v>475</v>
+      <c r="O19" s="157" t="s">
+        <v>465</v>
       </c>
       <c r="P19" s="66">
         <v>90</v>
       </c>
       <c r="Q19" s="66" t="s">
-        <v>479</v>
-      </c>
-      <c r="R19" s="159">
-        <f t="shared" ref="R19:R22" si="3">P19*2*$E$1</f>
-        <v>6.3493199999999996</v>
+        <v>469</v>
+      </c>
+      <c r="R19" s="158">
+        <f>P19*2*$E$1*$U$23</f>
+        <v>10.22946</v>
       </c>
       <c r="S19" s="66" t="s">
-        <v>480</v>
-      </c>
-      <c r="T19" s="160"/>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+        <v>470</v>
+      </c>
+      <c r="T19" s="159"/>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>148</v>
       </c>
@@ -10206,25 +10472,25 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O20" s="158" t="s">
-        <v>476</v>
+      <c r="O20" s="157" t="s">
+        <v>466</v>
       </c>
       <c r="P20" s="66">
         <v>120</v>
       </c>
       <c r="Q20" s="66" t="s">
-        <v>479</v>
-      </c>
-      <c r="R20" s="159">
-        <f t="shared" si="3"/>
-        <v>8.4657599999999995</v>
+        <v>469</v>
+      </c>
+      <c r="R20" s="158">
+        <f>P20*2*$E$1*$U$23</f>
+        <v>13.639279999999999</v>
       </c>
       <c r="S20" s="66" t="s">
-        <v>480</v>
-      </c>
-      <c r="T20" s="160"/>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+        <v>470</v>
+      </c>
+      <c r="T20" s="159"/>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>0.9</v>
       </c>
@@ -10255,25 +10521,25 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O21" s="158" t="s">
-        <v>478</v>
+      <c r="O21" s="157" t="s">
+        <v>468</v>
       </c>
       <c r="P21" s="66">
         <v>150</v>
       </c>
       <c r="Q21" s="66" t="s">
-        <v>479</v>
-      </c>
-      <c r="R21" s="159">
-        <f t="shared" si="3"/>
-        <v>10.5822</v>
+        <v>469</v>
+      </c>
+      <c r="R21" s="158">
+        <f>P21*2*$E$1*$U$23</f>
+        <v>17.049099999999999</v>
       </c>
       <c r="S21" s="66" t="s">
-        <v>480</v>
-      </c>
-      <c r="T21" s="160"/>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+        <v>470</v>
+      </c>
+      <c r="T21" s="159"/>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>1.1000000000000001</v>
       </c>
@@ -10307,25 +10573,25 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O22" s="161" t="s">
-        <v>477</v>
-      </c>
-      <c r="P22" s="162">
+      <c r="O22" s="160" t="s">
+        <v>467</v>
+      </c>
+      <c r="P22" s="161">
         <v>190</v>
       </c>
-      <c r="Q22" s="162" t="s">
-        <v>479</v>
-      </c>
-      <c r="R22" s="163">
-        <f t="shared" si="3"/>
-        <v>13.404120000000001</v>
-      </c>
-      <c r="S22" s="162" t="s">
-        <v>480</v>
-      </c>
-      <c r="T22" s="164"/>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="Q22" s="161" t="s">
+        <v>469</v>
+      </c>
+      <c r="R22" s="162">
+        <f>P22*2*$E$1*$U$23</f>
+        <v>21.595526666666668</v>
+      </c>
+      <c r="S22" s="161" t="s">
+        <v>470</v>
+      </c>
+      <c r="T22" s="163"/>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="H23" s="3"/>
       <c r="J23" s="7"/>
       <c r="K23" s="7"/>
@@ -10337,8 +10603,18 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T23" s="168" t="s">
+        <v>474</v>
+      </c>
+      <c r="U23">
+        <f>(36*58)/(36*36)</f>
+        <v>1.6111111111111112</v>
+      </c>
+      <c r="V23" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>152</v>
       </c>
@@ -10367,7 +10643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>155</v>
       </c>
@@ -10396,7 +10672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>166</v>
       </c>
@@ -10431,7 +10707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B27">
         <v>3.6</v>
       </c>
@@ -10463,7 +10739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B28">
         <v>5</v>
       </c>
@@ -10495,7 +10771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B29">
         <v>6</v>
       </c>
@@ -10509,7 +10785,7 @@
       <c r="L29" s="12"/>
       <c r="M29" s="12"/>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>181</v>
       </c>
@@ -10517,7 +10793,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
       <c r="F31" s="3"/>
     </row>
   </sheetData>

--- a/AT/Materials.xlsx
+++ b/AT/Materials.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wellspan-my.sharepoint.com/personal/dsmith14_wellspan_org/Documents/Documents/GitHub/dps/AT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="131" documentId="8_{C7F6FACF-983A-4174-A2EA-A87A6F163CFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED8533CD-84E2-4911-A449-642EC21D6D95}"/>
+  <xr:revisionPtr revIDLastSave="146" documentId="8_{C7F6FACF-983A-4174-A2EA-A87A6F163CFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50DEF07D-C02C-47C3-B13E-1918AE72648A}"/>
   <bookViews>
     <workbookView xWindow="885" yWindow="510" windowWidth="27525" windowHeight="15225" activeTab="2" xr2:uid="{362FB22F-6BD6-431B-94C9-F0870D854534}"/>
   </bookViews>
@@ -4564,7 +4564,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{458BE52D-397A-4267-A4EC-33DE3608C71C}">
-  <dimension ref="A1:AB127"/>
+  <dimension ref="A1:AB128"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.28515625" customWidth="1"/>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="F3" s="33"/>
       <c r="G3" s="35">
-        <v>14.98</v>
+        <v>16.03</v>
       </c>
       <c r="H3" s="35" t="str">
         <f>IF((G3*F3)=0,"",G3*F3)</f>
@@ -4728,7 +4728,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="35">
-        <v>9.6300000000000008</v>
+        <v>10.3</v>
       </c>
       <c r="H4" s="35" t="str">
         <f t="shared" ref="H4:H86" si="0">IF((G4*F4)=0,"",G4*F4)</f>
@@ -4979,7 +4979,7 @@
       </c>
       <c r="F9" s="33"/>
       <c r="G9" s="35">
-        <v>6.42</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="H9" s="35" t="str">
         <f t="shared" ref="H9:H26" si="4">IF((G9*F9)=0,"",G9*F9)</f>
@@ -5371,11 +5371,11 @@
         <v>3</v>
       </c>
       <c r="G16" s="35">
-        <v>14.98</v>
+        <v>16.03</v>
       </c>
       <c r="H16" s="35">
         <f t="shared" si="4"/>
-        <v>44.94</v>
+        <v>48.09</v>
       </c>
       <c r="I16" s="34"/>
       <c r="J16" s="146" t="str">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="F19" s="33"/>
       <c r="G19" s="35">
-        <v>6.42</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="H19" s="35" t="str">
         <f t="shared" si="4"/>
@@ -5756,7 +5756,7 @@
       </c>
       <c r="T22" s="82">
         <f>H27</f>
-        <v>93.289999999999992</v>
+        <v>96.44</v>
       </c>
       <c r="U22" s="83">
         <v>5</v>
@@ -5997,7 +5997,7 @@
       </c>
       <c r="H27" s="65">
         <f>SUM(H16:H26)</f>
-        <v>93.289999999999992</v>
+        <v>96.44</v>
       </c>
       <c r="I27" s="34"/>
       <c r="J27" s="146" t="str">
@@ -6092,7 +6092,7 @@
       </c>
       <c r="T28" s="121">
         <f>H97</f>
-        <v>6.96</v>
+        <v>7.45</v>
       </c>
       <c r="U28" s="122">
         <v>11</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="T29" s="121">
         <f>H104</f>
-        <v>6.9630000000000001</v>
+        <v>7.45</v>
       </c>
       <c r="U29" s="122">
         <v>12</v>
@@ -6221,8 +6221,8 @@
         <v>Rain Pants</v>
       </c>
       <c r="T30" s="102">
-        <f>H111</f>
-        <v>13.92</v>
+        <f>H112</f>
+        <v>14.9</v>
       </c>
       <c r="U30" s="103">
         <v>7</v>
@@ -6376,11 +6376,11 @@
         <v>472</v>
       </c>
       <c r="S33" s="149" t="str">
-        <f>A115</f>
+        <f>A116</f>
         <v>Pullover/hoodie</v>
       </c>
       <c r="T33" s="150">
-        <f>Q116</f>
+        <f>Q117</f>
         <v>54.5</v>
       </c>
       <c r="U33" s="151">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="T35" s="116">
         <f>SUM(T21:T33)</f>
-        <v>459.69300000000004</v>
+        <v>464.79999999999995</v>
       </c>
     </row>
     <row r="36" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6625,7 +6625,7 @@
       </c>
       <c r="T38" s="102">
         <f>T27+T30</f>
-        <v>40.78</v>
+        <v>41.76</v>
       </c>
       <c r="U38" s="112" t="s">
         <v>459</v>
@@ -6731,7 +6731,7 @@
       </c>
       <c r="T40" s="82">
         <f>T21+T22</f>
-        <v>140.79</v>
+        <v>143.94</v>
       </c>
       <c r="U40" s="111" t="s">
         <v>458</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="T42" s="118">
         <f>T28+T29</f>
-        <v>13.923</v>
+        <v>14.9</v>
       </c>
       <c r="U42" s="119" t="s">
         <v>407</v>
@@ -6955,7 +6955,7 @@
         <v/>
       </c>
       <c r="S45" s="20" t="str">
-        <f>A111</f>
+        <f>A112</f>
         <v>Pack Cover (new pack)</v>
       </c>
       <c r="T45" s="30"/>
@@ -6995,7 +6995,7 @@
       </c>
       <c r="Q46" s="35"/>
       <c r="S46" s="20" t="str">
-        <f>A112</f>
+        <f>A113</f>
         <v>Ditty Bags (See ToDo)</v>
       </c>
       <c r="T46" s="30"/>
@@ -7031,7 +7031,7 @@
       <c r="P47" s="35"/>
       <c r="Q47" s="35"/>
       <c r="S47" s="20" t="str">
-        <f>A113</f>
+        <f>A114</f>
         <v>Kilt (Use ION)</v>
       </c>
       <c r="T47" s="30"/>
@@ -8972,11 +8972,11 @@
         <v>1</v>
       </c>
       <c r="G94" s="35">
-        <v>6.96</v>
+        <v>7.45</v>
       </c>
       <c r="H94" s="59">
         <f>IF((G94*F94)=0,"",G94*F94)</f>
-        <v>6.96</v>
+        <v>7.45</v>
       </c>
       <c r="I94" s="34"/>
       <c r="J94" s="147" t="str">
@@ -9045,7 +9045,7 @@
       </c>
       <c r="H97" s="68">
         <f>SUM(H93:H94)</f>
-        <v>6.96</v>
+        <v>7.45</v>
       </c>
       <c r="I97" s="34"/>
       <c r="J97" s="147" t="str">
@@ -9117,7 +9117,7 @@
       </c>
       <c r="I100" s="34"/>
       <c r="J100" s="146" t="str">
-        <f t="shared" ref="J100:J108" si="11">IF(ISBLANK(A99),"",A99)</f>
+        <f t="shared" ref="J100:J109" si="11">IF(ISBLANK(A99),"",A99)</f>
         <v>Rain Kilt (30L x 48W)</v>
       </c>
       <c r="K100" s="66" t="s">
@@ -9163,11 +9163,11 @@
         <v>1</v>
       </c>
       <c r="G101" s="35">
-        <v>6.9630000000000001</v>
+        <v>7.45</v>
       </c>
       <c r="H101" s="59">
         <f>IF((G101*F101)=0,"",G101*F101)</f>
-        <v>6.9630000000000001</v>
+        <v>7.45</v>
       </c>
       <c r="I101" s="34"/>
       <c r="J101" s="147" t="str">
@@ -9232,7 +9232,7 @@
       </c>
       <c r="H104" s="68">
         <f>SUM(H100:H101)</f>
-        <v>6.9630000000000001</v>
+        <v>7.45</v>
       </c>
       <c r="I104" s="34"/>
       <c r="J104" s="147" t="str">
@@ -9263,11 +9263,11 @@
         <v>2</v>
       </c>
       <c r="G105" s="35">
-        <v>6.96</v>
+        <v>7.45</v>
       </c>
       <c r="H105" s="59">
         <f>IF((G105*F105)=0,"",G105*F105)</f>
-        <v>13.92</v>
+        <v>14.9</v>
       </c>
       <c r="I105" s="34"/>
       <c r="J105" s="146" t="str">
@@ -9344,9 +9344,7 @@
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" s="60"/>
-      <c r="B107" s="46" t="s">
-        <v>374</v>
-      </c>
+      <c r="B107" s="38"/>
       <c r="C107" s="20"/>
       <c r="D107" s="21"/>
       <c r="E107" s="36"/>
@@ -9354,10 +9352,7 @@
       <c r="G107" s="35"/>
       <c r="H107" s="59"/>
       <c r="I107" s="34"/>
-      <c r="J107" s="147" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
+      <c r="J107" s="147"/>
       <c r="K107" s="66"/>
       <c r="L107" s="20"/>
       <c r="M107" s="21"/>
@@ -9368,8 +9363,8 @@
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" s="60"/>
-      <c r="B108" s="50" t="s">
-        <v>314</v>
+      <c r="B108" s="46" t="s">
+        <v>374</v>
       </c>
       <c r="C108" s="20"/>
       <c r="D108" s="21"/>
@@ -9379,7 +9374,7 @@
       <c r="H108" s="59"/>
       <c r="I108" s="34"/>
       <c r="J108" s="147" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(ISBLANK(A106),"",A106)</f>
         <v/>
       </c>
       <c r="K108" s="66"/>
@@ -9393,7 +9388,7 @@
     <row r="109" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" s="60"/>
       <c r="B109" s="50" t="s">
-        <v>477</v>
+        <v>314</v>
       </c>
       <c r="C109" s="20"/>
       <c r="D109" s="21"/>
@@ -9402,7 +9397,10 @@
       <c r="G109" s="35"/>
       <c r="H109" s="59"/>
       <c r="I109" s="34"/>
-      <c r="J109" s="147"/>
+      <c r="J109" s="147" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
       <c r="K109" s="66"/>
       <c r="L109" s="20"/>
       <c r="M109" s="21"/>
@@ -9411,116 +9409,123 @@
       <c r="P109" s="35"/>
       <c r="Q109" s="59"/>
     </row>
-    <row r="110" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110" s="60"/>
-      <c r="B110" s="38" t="s">
-        <v>332</v>
+      <c r="B110" s="50" t="s">
+        <v>477</v>
       </c>
       <c r="C110" s="20"/>
       <c r="D110" s="21"/>
       <c r="E110" s="36"/>
       <c r="F110" s="33"/>
-      <c r="G110" s="35">
-        <v>3.96</v>
-      </c>
-      <c r="H110" s="59" t="str">
-        <f>IF((G110*F110)=0,"",G110*F110)</f>
-        <v/>
-      </c>
+      <c r="G110" s="35"/>
+      <c r="H110" s="59"/>
       <c r="I110" s="34"/>
-      <c r="J110" s="147" t="str">
-        <f t="shared" ref="J110:J117" si="12">IF(ISBLANK(A109),"",A109)</f>
-        <v/>
-      </c>
-      <c r="K110" t="s">
+      <c r="J110" s="147"/>
+      <c r="K110" s="66"/>
+      <c r="L110" s="20"/>
+      <c r="M110" s="21"/>
+      <c r="N110" s="36"/>
+      <c r="O110" s="33"/>
+      <c r="P110" s="35"/>
+      <c r="Q110" s="59"/>
+    </row>
+    <row r="111" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="60"/>
+      <c r="B111" s="38" t="s">
         <v>332</v>
       </c>
-      <c r="O110">
-        <v>1</v>
-      </c>
-      <c r="P110" s="137">
-        <v>4.5</v>
-      </c>
-      <c r="Q110" s="59">
-        <f>IF((P110*O110)=0,"",P110*O110)</f>
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="111" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="18" t="s">
-        <v>364</v>
-      </c>
-      <c r="B111" s="38"/>
       <c r="C111" s="20"/>
       <c r="D111" s="21"/>
       <c r="E111" s="36"/>
       <c r="F111" s="33"/>
-      <c r="G111" s="64" t="s">
-        <v>65</v>
-      </c>
-      <c r="H111" s="68">
-        <f>SUM(H105:H110)</f>
-        <v>13.92</v>
+      <c r="G111" s="35">
+        <v>3.96</v>
+      </c>
+      <c r="H111" s="59" t="str">
+        <f>IF((G111*F111)=0,"",G111*F111)</f>
+        <v/>
       </c>
       <c r="I111" s="34"/>
       <c r="J111" s="147" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K111" s="66"/>
-      <c r="L111" s="20"/>
-      <c r="M111" s="21"/>
-      <c r="N111" s="36"/>
-      <c r="O111" s="33"/>
-      <c r="P111" s="64" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q111" s="68">
-        <f>SUM(Q105:Q110)</f>
-        <v>44.5</v>
-      </c>
-    </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+        <f t="shared" ref="J111:J118" si="12">IF(ISBLANK(A110),"",A110)</f>
+        <v/>
+      </c>
+      <c r="K111" t="s">
+        <v>332</v>
+      </c>
+      <c r="O111">
+        <v>1</v>
+      </c>
+      <c r="P111" s="137">
+        <v>4.5</v>
+      </c>
+      <c r="Q111" s="59">
+        <f>IF((P111*O111)=0,"",P111*O111)</f>
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="112" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="18" t="s">
-        <v>287</v>
-      </c>
-      <c r="B112" s="38" t="s">
-        <v>365</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="B112" s="38"/>
       <c r="C112" s="20"/>
       <c r="D112" s="21"/>
       <c r="E112" s="36"/>
       <c r="F112" s="33"/>
-      <c r="G112" s="35"/>
-      <c r="H112" s="59"/>
+      <c r="G112" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="H112" s="68">
+        <f>SUM(H105:H111)</f>
+        <v>14.9</v>
+      </c>
       <c r="I112" s="34"/>
-      <c r="J112" s="146" t="str">
+      <c r="J112" s="147" t="str">
         <f t="shared" si="12"/>
-        <v>Pack Cover (new pack)</v>
-      </c>
-      <c r="P112" s="33"/>
-      <c r="Q112" s="10"/>
+        <v/>
+      </c>
+      <c r="K112" s="66"/>
+      <c r="L112" s="20"/>
+      <c r="M112" s="21"/>
+      <c r="N112" s="36"/>
+      <c r="O112" s="33"/>
+      <c r="P112" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q112" s="68">
+        <f>SUM(Q105:Q111)</f>
+        <v>44.5</v>
+      </c>
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113" s="18" t="s">
-        <v>288</v>
-      </c>
-      <c r="B113" s="61" t="s">
-        <v>367</v>
-      </c>
-      <c r="H113" s="59" t="str">
-        <f>IF((G113*F113)=0,"",G113*F113)</f>
-        <v/>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="B113" s="38" t="s">
+        <v>365</v>
+      </c>
+      <c r="C113" s="20"/>
+      <c r="D113" s="21"/>
+      <c r="E113" s="36"/>
+      <c r="F113" s="33"/>
+      <c r="G113" s="35"/>
+      <c r="H113" s="59"/>
       <c r="I113" s="34"/>
       <c r="J113" s="146" t="str">
         <f t="shared" si="12"/>
-        <v>Ditty Bags (See ToDo)</v>
-      </c>
+        <v>Pack Cover (new pack)</v>
+      </c>
+      <c r="P113" s="33"/>
+      <c r="Q113" s="10"/>
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B114" s="38" t="s">
-        <v>366</v>
+      <c r="A114" s="18" t="s">
+        <v>288</v>
+      </c>
+      <c r="B114" s="61" t="s">
+        <v>367</v>
       </c>
       <c r="H114" s="59" t="str">
         <f>IF((G114*F114)=0,"",G114*F114)</f>
@@ -9529,212 +9534,218 @@
       <c r="I114" s="34"/>
       <c r="J114" s="146" t="str">
         <f t="shared" si="12"/>
-        <v>Kilt (Use ION)</v>
-      </c>
-    </row>
-    <row r="115" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="18" t="s">
-        <v>461</v>
-      </c>
-      <c r="B115" s="38"/>
+        <v>Ditty Bags (See ToDo)</v>
+      </c>
+    </row>
+    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B115" s="38" t="s">
+        <v>366</v>
+      </c>
       <c r="H115" s="59" t="str">
         <f>IF((G115*F115)=0,"",G115*F115)</f>
         <v/>
       </c>
       <c r="I115" s="34"/>
-      <c r="J115" s="147" t="str">
+      <c r="J115" s="146" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="Q115" s="20"/>
+        <v>Kilt (Use ION)</v>
+      </c>
     </row>
     <row r="116" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B116" s="54" t="s">
+      <c r="A116" s="18" t="s">
+        <v>461</v>
+      </c>
+      <c r="B116" s="38"/>
+      <c r="H116" s="59" t="str">
+        <f>IF((G116*F116)=0,"",G116*F116)</f>
+        <v/>
+      </c>
+      <c r="I116" s="34"/>
+      <c r="J116" s="147" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="Q116" s="20"/>
+    </row>
+    <row r="117" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B117" s="54" t="s">
         <v>447</v>
       </c>
-      <c r="C116">
-        <f>C117*F121</f>
+      <c r="C117">
+        <f>C118*F122</f>
         <v>6.8078820000000002</v>
       </c>
-      <c r="D116" t="s">
+      <c r="D117" t="s">
         <v>159</v>
       </c>
-      <c r="E116" s="36">
-        <f>C116*((30*48)/(36*36))</f>
+      <c r="E117" s="36">
+        <f>C117*((30*48)/(36*36))</f>
         <v>7.5643133333333337</v>
       </c>
-      <c r="F116">
+      <c r="F117">
         <v>2</v>
       </c>
-      <c r="G116">
+      <c r="G117">
         <v>29</v>
       </c>
-      <c r="H116" s="59">
-        <f>IF((G116*F116)=0,"",G116*F116)</f>
+      <c r="H117" s="59">
+        <f>IF((G117*F117)=0,"",G117*F117)</f>
         <v>58</v>
       </c>
-      <c r="I116" s="34"/>
-      <c r="J116" s="146" t="str">
+      <c r="I117" s="34"/>
+      <c r="J117" s="146" t="str">
         <f t="shared" si="12"/>
         <v>Pullover/hoodie</v>
       </c>
-      <c r="K116" t="s">
+      <c r="K117" t="s">
         <v>448</v>
       </c>
-      <c r="L116">
+      <c r="L117">
         <v>4.8</v>
       </c>
-      <c r="M116" t="s">
+      <c r="M117" t="s">
         <v>159</v>
       </c>
-      <c r="N116" s="36">
+      <c r="N117" s="36">
         <f>1.4*((72*54)/(36*36))</f>
         <v>4.1999999999999993</v>
       </c>
-      <c r="O116" s="25">
+      <c r="O117" s="25">
         <v>2</v>
       </c>
-      <c r="P116" s="136">
+      <c r="P117" s="136">
         <v>27.25</v>
       </c>
-      <c r="Q116" s="68">
-        <f>IF((P116*O116)=0,"",P116*O116)</f>
+      <c r="Q117" s="68">
+        <f>IF((P117*O117)=0,"",P117*O117)</f>
         <v>54.5</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B117" s="54" t="s">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B118" s="54" t="s">
         <v>450</v>
       </c>
-      <c r="C117">
+      <c r="C118">
         <v>193</v>
       </c>
-      <c r="D117" t="s">
+      <c r="D118" t="s">
         <v>161</v>
       </c>
-      <c r="J117" s="143" t="str">
+      <c r="J118" s="143" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="K117" t="s">
+      <c r="K118" t="s">
         <v>449</v>
       </c>
-      <c r="L117">
+      <c r="L118">
         <v>135.62</v>
       </c>
-      <c r="M117" t="s">
+      <c r="M118" t="s">
         <v>161</v>
       </c>
-      <c r="N117" s="36"/>
-    </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A118" s="131" t="s">
+      <c r="N118" s="36"/>
+    </row>
+    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A119" s="131" t="s">
         <v>445</v>
       </c>
-      <c r="B118" s="117">
+      <c r="B119" s="117">
         <v>4004</v>
       </c>
-      <c r="C118">
+      <c r="C119">
         <v>119</v>
       </c>
-      <c r="F118">
+      <c r="F119">
         <v>2</v>
       </c>
-      <c r="G118">
+      <c r="G119">
         <v>28</v>
       </c>
-      <c r="H118" s="59">
-        <f>IF((G118*F118)=0,"",G118*F118)</f>
+      <c r="H119" s="59">
+        <f>IF((G119*F119)=0,"",G119*F119)</f>
         <v>56</v>
       </c>
-      <c r="K118" t="s">
+      <c r="K119" t="s">
         <v>451</v>
       </c>
-      <c r="P118" s="136">
+      <c r="P119" s="136">
         <v>20</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A119" s="18" t="s">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A120" s="18" t="s">
         <v>446</v>
       </c>
-      <c r="K119" t="s">
+      <c r="K120" t="s">
         <v>463</v>
       </c>
-      <c r="L119">
+      <c r="L120">
         <v>152.58000000000001</v>
       </c>
-      <c r="M119" t="s">
+      <c r="M120" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="L120">
-        <f>L119*F121</f>
+    <row r="121" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L121">
+        <f>L120*F122</f>
         <v>5.38210692</v>
       </c>
-      <c r="M120" t="s">
+      <c r="M121" t="s">
         <v>159</v>
-      </c>
-      <c r="O120">
-        <v>2</v>
-      </c>
-      <c r="P120" s="136">
-        <v>31.5</v>
-      </c>
-      <c r="Q120" s="59">
-        <f>IF((P120*O120)=0,"",P120*O120)</f>
-        <v>63</v>
-      </c>
-    </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="D121" s="132">
-        <v>1</v>
-      </c>
-      <c r="E121" s="79" t="s">
-        <v>453</v>
-      </c>
-      <c r="F121" s="79">
-        <v>3.5274E-2</v>
-      </c>
-      <c r="G121" s="80" t="s">
-        <v>159</v>
-      </c>
-      <c r="K121" s="31" t="s">
-        <v>471</v>
       </c>
       <c r="O121">
         <v>2</v>
       </c>
       <c r="P121" s="136">
-        <v>26.25</v>
+        <v>31.5</v>
       </c>
       <c r="Q121" s="59">
         <f>IF((P121*O121)=0,"",P121*O121)</f>
+        <v>63</v>
+      </c>
+    </row>
+    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="D122" s="132">
+        <v>1</v>
+      </c>
+      <c r="E122" s="79" t="s">
+        <v>453</v>
+      </c>
+      <c r="F122" s="79">
+        <v>3.5274E-2</v>
+      </c>
+      <c r="G122" s="80" t="s">
+        <v>159</v>
+      </c>
+      <c r="K122" s="31" t="s">
+        <v>471</v>
+      </c>
+      <c r="O122">
+        <v>2</v>
+      </c>
+      <c r="P122" s="136">
+        <v>26.25</v>
+      </c>
+      <c r="Q122" s="59">
+        <f>IF((P122*O122)=0,"",P122*O122)</f>
         <v>52.5</v>
       </c>
     </row>
-    <row r="122" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D122" s="133">
+    <row r="123" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D123" s="133">
         <v>28.349499999999999</v>
       </c>
-      <c r="E122" s="134" t="s">
+      <c r="E123" s="134" t="s">
         <v>453</v>
       </c>
-      <c r="F122" s="134">
+      <c r="F123" s="134">
         <v>1</v>
       </c>
-      <c r="G122" s="135" t="s">
+      <c r="G123" s="135" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="K123" s="165"/>
-      <c r="L123" s="66"/>
-      <c r="M123" s="66"/>
-      <c r="N123" s="158"/>
-      <c r="O123" s="66"/>
-      <c r="P123" s="66"/>
     </row>
     <row r="124" spans="1:17" x14ac:dyDescent="0.25">
       <c r="K124" s="165"/>
@@ -9768,9 +9779,17 @@
       <c r="O127" s="66"/>
       <c r="P127" s="66"/>
     </row>
+    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K128" s="165"/>
+      <c r="L128" s="66"/>
+      <c r="M128" s="66"/>
+      <c r="N128" s="158"/>
+      <c r="O128" s="66"/>
+      <c r="P128" s="66"/>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B113" location="ToDo!A19" display="See ToDo" xr:uid="{CE28C4E6-45D1-4C5D-A0AF-3ACF169C0D5B}"/>
+    <hyperlink ref="B114" location="ToDo!A19" display="See ToDo" xr:uid="{CE28C4E6-45D1-4C5D-A0AF-3ACF169C0D5B}"/>
     <hyperlink ref="R31" location="Make!A81" display="L" xr:uid="{F2445477-C9B7-447F-944F-160D21ACEB18}"/>
     <hyperlink ref="R32" location="Make!A85" display="L" xr:uid="{D614D32D-E4C7-4ABC-8AEA-2A0D20F4C1EC}"/>
     <hyperlink ref="R27" location="Make!A90" display="L" xr:uid="{786E7206-F76A-4474-B631-F01E095CA8FB}"/>

--- a/AT/Materials.xlsx
+++ b/AT/Materials.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wellspan-my.sharepoint.com/personal/dsmith14_wellspan_org/Documents/Documents/GitHub/dps/AT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="146" documentId="8_{C7F6FACF-983A-4174-A2EA-A87A6F163CFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50DEF07D-C02C-47C3-B13E-1918AE72648A}"/>
+  <xr:revisionPtr revIDLastSave="294" documentId="8_{C7F6FACF-983A-4174-A2EA-A87A6F163CFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24961F34-BEEA-4324-A685-883E5C5F1C51}"/>
   <bookViews>
-    <workbookView xWindow="885" yWindow="510" windowWidth="27525" windowHeight="15225" activeTab="2" xr2:uid="{362FB22F-6BD6-431B-94C9-F0870D854534}"/>
+    <workbookView xWindow="1020" yWindow="465" windowWidth="26910" windowHeight="14100" activeTab="2" xr2:uid="{362FB22F-6BD6-431B-94C9-F0870D854534}"/>
   </bookViews>
   <sheets>
     <sheet name="Materials" sheetId="1" r:id="rId1"/>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="508">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="518">
   <si>
     <t>piping slide</t>
   </si>
@@ -1272,9 +1272,6 @@
     <t>1-3</t>
   </si>
   <si>
-    <t>Order 4</t>
-  </si>
-  <si>
     <t>Order 5</t>
   </si>
   <si>
@@ -1320,9 +1317,6 @@
     <t>Tri-Glide (2)</t>
   </si>
   <si>
-    <t>Tension Lock (6)</t>
-  </si>
-  <si>
     <t>Buckles 1" (2)</t>
   </si>
   <si>
@@ -1597,6 +1591,42 @@
   </si>
   <si>
     <t>Make items above plus</t>
+  </si>
+  <si>
+    <t>Forest Green</t>
+  </si>
+  <si>
+    <t>Brilliant Blue</t>
+  </si>
+  <si>
+    <t>Line lock light</t>
+  </si>
+  <si>
+    <t>Buckles 1/2"</t>
+  </si>
+  <si>
+    <t>Velcro 1/2" per foot</t>
+  </si>
+  <si>
+    <t>Tension Lock 1/2" (6)</t>
+  </si>
+  <si>
+    <t>Extra Xenon make booties with 6oz climashield</t>
+  </si>
+  <si>
+    <t>Hexon 1.2 shorts?</t>
+  </si>
+  <si>
+    <t>see Dutch up booties</t>
+  </si>
+  <si>
+    <t>Xenon rain jacket backpack cover?</t>
+  </si>
+  <si>
+    <t>Kilt Hexon1.2?</t>
+  </si>
+  <si>
+    <t>Compression stuff sack (Dutch web page)</t>
   </si>
 </sst>
 </file>
@@ -1994,7 +2024,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="179">
+  <cellXfs count="181">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2313,20 +2343,28 @@
     <xf numFmtId="2" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3755,7 +3793,7 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
@@ -4254,7 +4292,7 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F39" s="20"/>
       <c r="G39" t="s">
@@ -4564,7 +4602,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{458BE52D-397A-4267-A4EC-33DE3608C71C}">
-  <dimension ref="A1:AB128"/>
+  <dimension ref="A1:AB134"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.28515625" customWidth="1"/>
@@ -4731,12 +4769,12 @@
         <v>10.3</v>
       </c>
       <c r="H4" s="35" t="str">
-        <f t="shared" ref="H4:H86" si="0">IF((G4*F4)=0,"",G4*F4)</f>
+        <f t="shared" ref="H4:H43" si="0">IF((G4*F4)=0,"",G4*F4)</f>
         <v/>
       </c>
       <c r="I4" s="34"/>
       <c r="J4" s="147" t="str">
-        <f t="shared" ref="J4:J40" si="1">IF(ISBLANK(A4),"",A4)</f>
+        <f t="shared" ref="J4:J51" si="1">IF(ISBLANK(A4),"",A4)</f>
         <v>54x78</v>
       </c>
       <c r="K4" t="s">
@@ -4757,7 +4795,7 @@
         <v>12</v>
       </c>
       <c r="Q4" s="35" t="str">
-        <f t="shared" ref="Q4:Q86" si="3">IF((P4*O4)=0,"",P4*O4)</f>
+        <f t="shared" ref="Q4:Q88" si="3">IF((P4*O4)=0,"",P4*O4)</f>
         <v/>
       </c>
       <c r="T4" s="3">
@@ -4765,7 +4803,7 @@
         <v>23.855</v>
       </c>
       <c r="U4" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.25">
@@ -4774,7 +4812,7 @@
         <v>3.25</v>
       </c>
       <c r="B5" s="38" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C5" s="20"/>
       <c r="D5" s="21"/>
@@ -4791,7 +4829,7 @@
         <v>3.25</v>
       </c>
       <c r="K5" s="66" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="L5" s="20"/>
       <c r="M5" s="21"/>
@@ -4808,15 +4846,15 @@
         <v>21.204444444444444</v>
       </c>
       <c r="U5" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B6" s="38" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C6" s="20"/>
       <c r="D6" s="21"/>
@@ -4833,7 +4871,7 @@
         <v>tapperd &amp; sewn waist down</v>
       </c>
       <c r="K6" s="66" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="L6" s="20"/>
       <c r="M6" s="21"/>
@@ -4849,15 +4887,15 @@
         <v>2.8162152777777778</v>
       </c>
       <c r="U6" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B7" s="38" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C7" s="20">
         <v>0.67</v>
@@ -4908,10 +4946,10 @@
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" s="20" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B8" s="38" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C8" s="20">
         <v>0.9</v>
@@ -4923,7 +4961,7 @@
         <f>C8*$A$5*2</f>
         <v>5.8500000000000005</v>
       </c>
-      <c r="F8" s="33">
+      <c r="F8" s="178">
         <v>5</v>
       </c>
       <c r="G8" s="35">
@@ -4962,10 +5000,10 @@
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9" s="21" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B9" s="38" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C9" s="20">
         <v>0.93</v>
@@ -5038,7 +5076,7 @@
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A10" s="21" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B10" s="38" t="s">
         <v>331</v>
@@ -5162,27 +5200,29 @@
       </c>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A12" s="20"/>
+      <c r="A12" s="20" t="s">
+        <v>506</v>
+      </c>
       <c r="B12" s="38" t="s">
         <v>297</v>
       </c>
       <c r="C12" s="20"/>
       <c r="D12" s="21"/>
       <c r="E12" s="36"/>
-      <c r="F12" s="33">
+      <c r="F12" s="178">
         <v>1</v>
       </c>
       <c r="G12" s="35">
-        <v>4.55</v>
+        <v>4.87</v>
       </c>
       <c r="H12" s="35">
         <f t="shared" si="4"/>
-        <v>4.55</v>
+        <v>4.87</v>
       </c>
       <c r="I12" s="34"/>
       <c r="J12" s="147" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Forest Green</v>
       </c>
       <c r="K12" t="s">
         <v>297</v>
@@ -5320,7 +5360,7 @@
       </c>
       <c r="H15" s="65">
         <f>SUM(H3:H14)</f>
-        <v>47.5</v>
+        <v>47.82</v>
       </c>
       <c r="I15" s="34"/>
       <c r="J15" s="147" t="str">
@@ -5367,7 +5407,7 @@
         <f>C16*$A$18</f>
         <v>17.333333333333332</v>
       </c>
-      <c r="F16" s="33">
+      <c r="F16" s="178">
         <v>3</v>
       </c>
       <c r="G16" s="35">
@@ -5421,7 +5461,7 @@
         <v>315</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C17" s="20">
         <v>0.67</v>
@@ -5489,7 +5529,7 @@
         <v>2.8888888888888888</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C18" s="20">
         <v>0.9</v>
@@ -5501,7 +5541,7 @@
         <f>C18*$A$18*2</f>
         <v>5.2</v>
       </c>
-      <c r="F18" s="33">
+      <c r="F18" s="178">
         <v>5</v>
       </c>
       <c r="G18" s="35">
@@ -5542,10 +5582,10 @@
     </row>
     <row r="19" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C19" s="20">
         <v>0.93</v>
@@ -5587,12 +5627,12 @@
         <v>4.5</v>
       </c>
       <c r="S19" s="107" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A20" s="20" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B20" s="38" t="s">
         <v>79</v>
@@ -5600,15 +5640,15 @@
       <c r="C20" s="20"/>
       <c r="D20" s="21"/>
       <c r="E20" s="36"/>
-      <c r="F20" s="33">
+      <c r="F20" s="178">
         <v>1</v>
       </c>
       <c r="G20" s="35">
-        <v>3.96</v>
+        <v>4.87</v>
       </c>
       <c r="H20" s="35">
         <f t="shared" si="4"/>
-        <v>3.96</v>
+        <v>4.87</v>
       </c>
       <c r="I20" s="34"/>
       <c r="J20" s="147" t="str">
@@ -5648,7 +5688,7 @@
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A21" s="20" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B21" s="38" t="s">
         <v>324</v>
@@ -5696,7 +5736,7 @@
       </c>
       <c r="T21" s="82">
         <f>H15</f>
-        <v>47.5</v>
+        <v>47.82</v>
       </c>
       <c r="U21" s="83">
         <v>4</v>
@@ -5756,7 +5796,7 @@
       </c>
       <c r="T22" s="82">
         <f>H27</f>
-        <v>96.44</v>
+        <v>97.070000000000007</v>
       </c>
       <c r="U22" s="83">
         <v>5</v>
@@ -5767,7 +5807,9 @@
       <c r="W22" s="85"/>
     </row>
     <row r="23" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A23" s="20"/>
+      <c r="A23" s="20" t="s">
+        <v>507</v>
+      </c>
       <c r="B23" s="38" t="s">
         <v>320</v>
       </c>
@@ -5789,7 +5831,7 @@
       <c r="I23" s="34"/>
       <c r="J23" s="147" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Brilliant Blue</v>
       </c>
       <c r="K23" s="138" t="s">
         <v>289</v>
@@ -5805,11 +5847,11 @@
       </c>
       <c r="R23" s="5"/>
       <c r="S23" s="86" t="str">
-        <f>A27</f>
+        <f>A28</f>
         <v>Griz Ariel Hammock</v>
       </c>
       <c r="T23" s="87">
-        <f>H37</f>
+        <f>H38</f>
         <v>42.089999999999996</v>
       </c>
       <c r="U23" s="88">
@@ -5852,15 +5894,15 @@
         <v/>
       </c>
       <c r="R24" s="166" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="S24" s="91" t="str">
-        <f>A37</f>
+        <f>A39</f>
         <v>Gathered End Hammock</v>
       </c>
       <c r="T24" s="92">
-        <f>H43</f>
-        <v>38.56</v>
+        <f>H45</f>
+        <v>43.59</v>
       </c>
       <c r="U24" s="93">
         <v>8</v>
@@ -5906,15 +5948,15 @@
         <v>5</v>
       </c>
       <c r="R25" s="166" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="S25" s="91" t="str">
-        <f>A43</f>
+        <f>A46</f>
         <v>Bug Net</v>
       </c>
       <c r="T25" s="92">
-        <f>H49</f>
-        <v>31.22</v>
+        <f>H52</f>
+        <v>35.68</v>
       </c>
       <c r="U25" s="93">
         <v>9</v>
@@ -5936,15 +5978,15 @@
         <v>161</v>
       </c>
       <c r="E26" s="36"/>
-      <c r="F26" s="33">
+      <c r="F26" s="178">
         <v>4</v>
       </c>
       <c r="G26" s="35">
-        <v>0.36</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="H26" s="35">
         <f t="shared" si="4"/>
-        <v>1.44</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="I26" s="34"/>
       <c r="J26" s="147" t="str">
@@ -5964,29 +6006,27 @@
         <v>108.875</v>
       </c>
       <c r="R26" s="166" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="S26" s="96" t="str">
-        <f>A50</f>
+        <f>A53</f>
         <v>Back Pack</v>
       </c>
       <c r="T26" s="97">
-        <f>Q79+H79</f>
-        <v>61.769999999999996</v>
+        <f>Q80+H82</f>
+        <v>72.569999999999993</v>
       </c>
       <c r="U26" s="98">
         <v>6</v>
       </c>
       <c r="V26" s="99" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="W26" s="100"/>
       <c r="X26" s="30"/>
     </row>
     <row r="27" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="5" t="s">
-        <v>272</v>
-      </c>
+      <c r="A27" s="5"/>
       <c r="B27" s="38"/>
       <c r="C27" s="20"/>
       <c r="D27" s="21"/>
@@ -5997,285 +6037,273 @@
       </c>
       <c r="H27" s="65">
         <f>SUM(H16:H26)</f>
-        <v>96.44</v>
+        <v>97.070000000000007</v>
       </c>
       <c r="I27" s="34"/>
-      <c r="J27" s="146" t="str">
+      <c r="J27" s="147" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K27" s="66"/>
+      <c r="L27" s="20"/>
+      <c r="M27" s="21"/>
+      <c r="N27" s="36"/>
+      <c r="O27" s="33"/>
+      <c r="P27" s="64"/>
+      <c r="Q27" s="144"/>
+      <c r="R27" s="166" t="s">
+        <v>470</v>
+      </c>
+      <c r="S27" s="101" t="str">
+        <f>A90</f>
+        <v>Sleeping Bag Liner</v>
+      </c>
+      <c r="T27" s="102">
+        <f>H95</f>
+        <v>26.86</v>
+      </c>
+      <c r="U27" s="103">
+        <v>10</v>
+      </c>
+      <c r="V27" s="104" t="s">
+        <v>280</v>
+      </c>
+      <c r="W27" s="105"/>
+    </row>
+    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B28" s="38"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="36"/>
+      <c r="F28" s="33"/>
+      <c r="G28" s="64"/>
+      <c r="H28" s="144"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="146" t="str">
         <f t="shared" si="1"/>
         <v>Griz Ariel Hammock</v>
       </c>
-      <c r="K27" s="66" t="s">
+      <c r="K28" s="66" t="s">
         <v>290</v>
       </c>
-      <c r="L27" s="20">
+      <c r="L28" s="20">
         <v>1.6</v>
       </c>
-      <c r="M27" s="21" t="s">
+      <c r="M28" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="N27" s="36"/>
-      <c r="O27" s="33">
+      <c r="N28" s="36"/>
+      <c r="O28" s="33">
         <v>3</v>
       </c>
-      <c r="P27" s="35">
+      <c r="P28" s="35">
         <v>7.5</v>
       </c>
-      <c r="Q27" s="35">
+      <c r="Q28" s="35">
         <f t="shared" si="3"/>
         <v>22.5</v>
       </c>
-      <c r="R27" s="166" t="s">
-        <v>472</v>
-      </c>
-      <c r="S27" s="101" t="str">
-        <f>A87</f>
-        <v>Sleeping Bag Liner</v>
-      </c>
-      <c r="T27" s="102">
-        <f>H92</f>
-        <v>26.86</v>
-      </c>
-      <c r="U27" s="103">
-        <v>10</v>
-      </c>
-      <c r="V27" s="104" t="s">
+      <c r="R28" s="166" t="s">
+        <v>470</v>
+      </c>
+      <c r="S28" s="120" t="str">
+        <f>A95</f>
+        <v>Food Bag (12.5 x 22)</v>
+      </c>
+      <c r="T28" s="121">
+        <f>H100</f>
+        <v>7.45</v>
+      </c>
+      <c r="U28" s="122">
+        <v>11</v>
+      </c>
+      <c r="V28" s="117" t="s">
         <v>280</v>
       </c>
-      <c r="W27" s="105"/>
-    </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A28" s="20" t="s">
+      <c r="W28" s="123"/>
+    </row>
+    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A29" s="20" t="s">
         <v>313</v>
       </c>
-      <c r="B28" s="38" t="s">
+      <c r="B29" s="38" t="s">
         <v>279</v>
       </c>
-      <c r="C28" s="20">
+      <c r="C29" s="20">
         <v>1.6</v>
       </c>
-      <c r="D28" s="21" t="s">
+      <c r="D29" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="E28" s="36">
-        <f>$A$29*C28</f>
+      <c r="E29" s="36">
+        <f>$A$30*C29</f>
         <v>5.7925925925925927</v>
       </c>
-      <c r="F28" s="33"/>
-      <c r="G28" s="35">
+      <c r="F29" s="33"/>
+      <c r="G29" s="35">
         <v>6.87</v>
       </c>
-      <c r="H28" s="35" t="str">
+      <c r="H29" s="35" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="I28" s="34"/>
-      <c r="J28" s="147" t="str">
+      <c r="I29" s="34"/>
+      <c r="J29" s="147" t="str">
         <f t="shared" si="1"/>
         <v>102x46</v>
       </c>
-      <c r="K28" s="66"/>
-      <c r="L28" s="20"/>
-      <c r="M28" s="21"/>
-      <c r="N28" s="36"/>
-      <c r="O28" s="33"/>
-      <c r="P28" s="35"/>
-      <c r="Q28" s="35" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="R28" s="166" t="s">
-        <v>472</v>
-      </c>
-      <c r="S28" s="120" t="str">
-        <f>A92</f>
-        <v>Food Bag (12.5 x 22)</v>
-      </c>
-      <c r="T28" s="121">
-        <f>H97</f>
-        <v>7.45</v>
-      </c>
-      <c r="U28" s="122">
-        <v>11</v>
-      </c>
-      <c r="V28" s="117" t="s">
-        <v>280</v>
-      </c>
-      <c r="W28" s="123"/>
-    </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A29" s="37">
-        <f>(102*46)/(36*36)</f>
-        <v>3.6203703703703702</v>
-      </c>
-      <c r="B29" s="38" t="s">
-        <v>334</v>
-      </c>
-      <c r="C29" s="20">
-        <v>1.2</v>
-      </c>
-      <c r="D29" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="E29" s="36">
-        <f>$A$29*C29</f>
-        <v>4.3444444444444441</v>
-      </c>
-      <c r="F29" s="33">
-        <v>3</v>
-      </c>
-      <c r="G29" s="35">
-        <v>7.45</v>
-      </c>
-      <c r="H29" s="35">
-        <f t="shared" si="0"/>
-        <v>22.35</v>
-      </c>
-      <c r="I29" s="34"/>
-      <c r="J29" s="147">
-        <f t="shared" si="1"/>
-        <v>3.6203703703703702</v>
-      </c>
-      <c r="K29" s="66" t="s">
-        <v>79</v>
-      </c>
+      <c r="K29" s="66"/>
       <c r="L29" s="20"/>
       <c r="M29" s="21"/>
       <c r="N29" s="36"/>
-      <c r="O29" s="33">
+      <c r="O29" s="33"/>
+      <c r="P29" s="35"/>
+      <c r="Q29" s="35" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="R29" s="166" t="s">
+        <v>470</v>
+      </c>
+      <c r="S29" s="120" t="str">
+        <f>A102</f>
+        <v>Rain Kilt (30L x 48W)</v>
+      </c>
+      <c r="T29" s="121">
+        <f>H107</f>
+        <v>7.45</v>
+      </c>
+      <c r="U29" s="122">
+        <v>12</v>
+      </c>
+      <c r="V29" s="117" t="s">
+        <v>280</v>
+      </c>
+      <c r="W29" s="123"/>
+    </row>
+    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A30" s="37">
+        <f>(102*46)/(36*36)</f>
+        <v>3.6203703703703702</v>
+      </c>
+      <c r="B30" s="38" t="s">
+        <v>334</v>
+      </c>
+      <c r="C30" s="20">
+        <v>1.2</v>
+      </c>
+      <c r="D30" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E30" s="36">
+        <f>$A$30*C30</f>
+        <v>4.3444444444444441</v>
+      </c>
+      <c r="F30" s="33">
+        <v>3</v>
+      </c>
+      <c r="G30" s="35">
+        <v>7.45</v>
+      </c>
+      <c r="H30" s="35">
+        <f t="shared" si="0"/>
+        <v>22.35</v>
+      </c>
+      <c r="I30" s="34"/>
+      <c r="J30" s="147">
+        <f t="shared" si="1"/>
+        <v>3.6203703703703702</v>
+      </c>
+      <c r="K30" s="66" t="s">
+        <v>79</v>
+      </c>
+      <c r="L30" s="20"/>
+      <c r="M30" s="21"/>
+      <c r="N30" s="36"/>
+      <c r="O30" s="33">
         <v>1</v>
       </c>
-      <c r="P29" s="35">
+      <c r="P30" s="35">
         <v>5.25</v>
       </c>
-      <c r="Q29" s="35">
+      <c r="Q30" s="35">
         <f t="shared" si="3"/>
         <v>5.25</v>
       </c>
-      <c r="R29" s="166" t="s">
-        <v>472</v>
-      </c>
-      <c r="S29" s="120" t="str">
-        <f>A99</f>
-        <v>Rain Kilt (30L x 48W)</v>
-      </c>
-      <c r="T29" s="121">
-        <f>H104</f>
-        <v>7.45</v>
-      </c>
-      <c r="U29" s="122">
-        <v>12</v>
-      </c>
-      <c r="V29" s="117" t="s">
+      <c r="R30" s="166" t="s">
+        <v>470</v>
+      </c>
+      <c r="S30" s="101" t="str">
+        <f>A107</f>
+        <v>Rain Pants</v>
+      </c>
+      <c r="T30" s="102">
+        <f>H115</f>
+        <v>14.9</v>
+      </c>
+      <c r="U30" s="103">
+        <v>7</v>
+      </c>
+      <c r="V30" s="104" t="s">
         <v>280</v>
       </c>
-      <c r="W29" s="123"/>
-    </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A30" s="20" t="s">
+      <c r="W30" s="105"/>
+    </row>
+    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A31" s="20" t="s">
         <v>382</v>
       </c>
-      <c r="B30" s="38" t="s">
+      <c r="B31" s="38" t="s">
         <v>79</v>
       </c>
-      <c r="C30" s="20"/>
-      <c r="D30" s="21"/>
-      <c r="E30" s="36"/>
-      <c r="F30" s="33">
+      <c r="C31" s="20"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="36"/>
+      <c r="F31" s="33">
         <v>1</v>
       </c>
-      <c r="G30" s="35">
+      <c r="G31" s="35">
         <v>3.96</v>
       </c>
-      <c r="H30" s="35">
+      <c r="H31" s="35">
         <f t="shared" si="0"/>
         <v>3.96</v>
-      </c>
-      <c r="I30" s="34"/>
-      <c r="J30" s="147" t="str">
-        <f t="shared" si="1"/>
-        <v>with half bug net</v>
-      </c>
-      <c r="K30" s="66" t="s">
-        <v>322</v>
-      </c>
-      <c r="L30" s="20">
-        <v>3.6</v>
-      </c>
-      <c r="M30" s="21" t="s">
-        <v>321</v>
-      </c>
-      <c r="N30" s="36"/>
-      <c r="O30" s="33"/>
-      <c r="P30" s="35">
-        <v>5.25</v>
-      </c>
-      <c r="Q30" s="35" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="R30" s="166" t="s">
-        <v>472</v>
-      </c>
-      <c r="S30" s="101" t="str">
-        <f>A104</f>
-        <v>Rain Pants</v>
-      </c>
-      <c r="T30" s="102">
-        <f>H112</f>
-        <v>14.9</v>
-      </c>
-      <c r="U30" s="103">
-        <v>7</v>
-      </c>
-      <c r="V30" s="104" t="s">
-        <v>280</v>
-      </c>
-      <c r="W30" s="105"/>
-    </row>
-    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A31" s="20"/>
-      <c r="B31" s="38" t="s">
-        <v>320</v>
-      </c>
-      <c r="C31" s="20">
-        <v>27.49</v>
-      </c>
-      <c r="D31" s="21" t="s">
-        <v>161</v>
-      </c>
-      <c r="E31" s="36"/>
-      <c r="F31" s="33"/>
-      <c r="G31" s="35">
-        <v>2.25</v>
-      </c>
-      <c r="H31" s="35" t="str">
-        <f t="shared" si="0"/>
-        <v/>
       </c>
       <c r="I31" s="34"/>
       <c r="J31" s="147" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="66"/>
-      <c r="L31" s="20"/>
-      <c r="M31" s="21"/>
+        <v>with half bug net</v>
+      </c>
+      <c r="K31" s="66" t="s">
+        <v>322</v>
+      </c>
+      <c r="L31" s="20">
+        <v>3.6</v>
+      </c>
+      <c r="M31" s="21" t="s">
+        <v>321</v>
+      </c>
       <c r="N31" s="36"/>
       <c r="O31" s="33"/>
-      <c r="P31" s="35"/>
+      <c r="P31" s="35">
+        <v>5.25</v>
+      </c>
       <c r="Q31" s="35" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="R31" s="166" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="S31" s="86" t="str">
-        <f>A79</f>
+        <f>A82</f>
         <v>Amsteel 7/64</v>
       </c>
       <c r="T31" s="87">
-        <f>H83</f>
+        <f>H86</f>
         <v>26.32</v>
       </c>
       <c r="U31" s="88">
@@ -6288,20 +6316,19 @@
     </row>
     <row r="32" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A32" s="20"/>
-      <c r="B32" s="52" t="s">
-        <v>345</v>
-      </c>
-      <c r="C32">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="D32" t="s">
+      <c r="B32" s="38" t="s">
+        <v>320</v>
+      </c>
+      <c r="C32" s="20">
+        <v>27.49</v>
+      </c>
+      <c r="D32" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="F32">
-        <v>0</v>
-      </c>
+      <c r="E32" s="36"/>
+      <c r="F32" s="33"/>
       <c r="G32" s="35">
-        <v>1.61</v>
+        <v>2.25</v>
       </c>
       <c r="H32" s="35" t="str">
         <f t="shared" si="0"/>
@@ -6312,9 +6339,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K32" s="117" t="s">
-        <v>427</v>
-      </c>
+      <c r="K32" s="66"/>
       <c r="L32" s="20"/>
       <c r="M32" s="21"/>
       <c r="N32" s="36"/>
@@ -6325,14 +6350,14 @@
         <v/>
       </c>
       <c r="R32" s="166" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="S32" s="86" t="str">
-        <f>A83</f>
+        <f>A86</f>
         <v>Shock Cord</v>
       </c>
       <c r="T32" s="87">
-        <f>H87</f>
+        <f>H90</f>
         <v>9.74</v>
       </c>
       <c r="U32" s="88">
@@ -6346,9 +6371,20 @@
     <row r="33" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="20"/>
       <c r="B33" s="52" t="s">
-        <v>427</v>
-      </c>
-      <c r="G33" s="35"/>
+        <v>345</v>
+      </c>
+      <c r="C33">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D33" t="s">
+        <v>161</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33" s="35">
+        <v>1.61</v>
+      </c>
       <c r="H33" s="35" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -6358,48 +6394,43 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K33" s="140" t="s">
-        <v>351</v>
+      <c r="K33" s="117" t="s">
+        <v>425</v>
       </c>
       <c r="L33" s="20"/>
       <c r="M33" s="21"/>
       <c r="N33" s="36"/>
       <c r="O33" s="33"/>
-      <c r="P33" s="35">
-        <v>7.5</v>
-      </c>
+      <c r="P33" s="35"/>
       <c r="Q33" s="35" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="R33" s="166" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="S33" s="149" t="str">
-        <f>A116</f>
+        <f>A123</f>
         <v>Pullover/hoodie</v>
       </c>
       <c r="T33" s="150">
-        <f>Q117</f>
+        <f>Q123</f>
         <v>54.5</v>
       </c>
       <c r="U33" s="151">
         <v>13</v>
       </c>
       <c r="V33" s="152" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="W33" s="106"/>
     </row>
     <row r="34" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="20"/>
-      <c r="B34" s="53" t="s">
-        <v>352</v>
-      </c>
-      <c r="F34" s="33"/>
-      <c r="G34" s="35">
-        <v>6.15</v>
-      </c>
+      <c r="B34" s="52" t="s">
+        <v>425</v>
+      </c>
+      <c r="G34" s="35"/>
       <c r="H34" s="35" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -6409,159 +6440,154 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K34" s="66" t="s">
-        <v>317</v>
-      </c>
-      <c r="L34" s="20">
-        <v>0.67</v>
-      </c>
-      <c r="M34" s="21" t="s">
-        <v>159</v>
-      </c>
+      <c r="K34" s="140" t="s">
+        <v>351</v>
+      </c>
+      <c r="L34" s="20"/>
+      <c r="M34" s="21"/>
       <c r="N34" s="36"/>
-      <c r="O34" s="33">
-        <v>2</v>
-      </c>
+      <c r="O34" s="33"/>
       <c r="P34" s="35">
-        <v>5.5</v>
-      </c>
-      <c r="Q34" s="35">
+        <v>7.5</v>
+      </c>
+      <c r="Q34" s="35" t="str">
         <f t="shared" si="3"/>
-        <v>11</v>
-      </c>
+        <v/>
+      </c>
+      <c r="T34" s="30"/>
     </row>
     <row r="35" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="20"/>
-      <c r="B35" s="38" t="s">
-        <v>349</v>
-      </c>
-      <c r="C35" s="20">
-        <v>0.67</v>
-      </c>
-      <c r="D35" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="E35" s="36"/>
-      <c r="F35" s="33">
-        <v>3</v>
-      </c>
+      <c r="B35" s="53" t="s">
+        <v>352</v>
+      </c>
+      <c r="F35" s="33"/>
       <c r="G35" s="35">
-        <v>4.46</v>
-      </c>
-      <c r="H35" s="35">
+        <v>6.15</v>
+      </c>
+      <c r="H35" s="35" t="str">
         <f t="shared" si="0"/>
-        <v>13.379999999999999</v>
+        <v/>
       </c>
       <c r="I35" s="34"/>
       <c r="J35" s="147" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K35" s="56" t="s">
-        <v>403</v>
-      </c>
-      <c r="L35" s="20"/>
-      <c r="M35" s="21"/>
+      <c r="K35" s="66" t="s">
+        <v>317</v>
+      </c>
+      <c r="L35" s="20">
+        <v>0.67</v>
+      </c>
+      <c r="M35" s="21" t="s">
+        <v>159</v>
+      </c>
       <c r="N35" s="36"/>
       <c r="O35" s="33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P35" s="35">
-        <v>4.25</v>
+        <v>5.5</v>
       </c>
       <c r="Q35" s="35">
         <f t="shared" si="3"/>
-        <v>4.25</v>
+        <v>11</v>
       </c>
       <c r="S35" s="115" t="s">
         <v>65</v>
       </c>
       <c r="T35" s="116">
         <f>SUM(T21:T33)</f>
-        <v>464.79999999999995</v>
+        <v>486.03999999999996</v>
       </c>
     </row>
     <row r="36" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="20"/>
       <c r="B36" s="38" t="s">
-        <v>401</v>
+        <v>349</v>
       </c>
       <c r="C36" s="20">
-        <v>0.3</v>
+        <v>0.67</v>
       </c>
       <c r="D36" s="21" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E36" s="36"/>
       <c r="F36" s="33">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G36" s="35">
-        <v>0.24</v>
+        <v>4.46</v>
       </c>
       <c r="H36" s="35">
         <f t="shared" si="0"/>
-        <v>2.4</v>
+        <v>13.379999999999999</v>
       </c>
       <c r="I36" s="34"/>
       <c r="J36" s="147" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K36" s="56"/>
+      <c r="K36" s="56" t="s">
+        <v>402</v>
+      </c>
       <c r="L36" s="20"/>
       <c r="M36" s="21"/>
       <c r="N36" s="36"/>
-      <c r="O36" s="33"/>
-      <c r="P36" s="64" t="s">
+      <c r="O36" s="33">
+        <v>1</v>
+      </c>
+      <c r="P36" s="35">
+        <v>4.25</v>
+      </c>
+      <c r="Q36" s="35">
+        <f t="shared" si="3"/>
+        <v>4.25</v>
+      </c>
+      <c r="T36" s="30"/>
+    </row>
+    <row r="37" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="20"/>
+      <c r="B37" s="38" t="s">
+        <v>400</v>
+      </c>
+      <c r="C37" s="20">
+        <v>0.3</v>
+      </c>
+      <c r="D37" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="E37" s="36"/>
+      <c r="F37" s="33">
+        <v>10</v>
+      </c>
+      <c r="G37" s="35">
+        <v>0.24</v>
+      </c>
+      <c r="H37" s="35">
+        <f t="shared" si="0"/>
+        <v>2.4</v>
+      </c>
+      <c r="I37" s="34"/>
+      <c r="J37" s="147" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K37" s="56"/>
+      <c r="L37" s="20"/>
+      <c r="M37" s="21"/>
+      <c r="N37" s="36"/>
+      <c r="O37" s="33"/>
+      <c r="P37" s="64" t="s">
         <v>65</v>
       </c>
-      <c r="Q36" s="65">
-        <f>SUM(Q27:Q35)</f>
+      <c r="Q37" s="65">
+        <f>SUM(Q28:Q36)</f>
         <v>43</v>
       </c>
-      <c r="T36" s="30"/>
-    </row>
-    <row r="37" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="B37" s="55"/>
-      <c r="F37" s="33"/>
-      <c r="G37" s="64" t="s">
-        <v>65</v>
-      </c>
-      <c r="H37" s="65">
-        <f>SUM(H28:H36)</f>
-        <v>42.089999999999996</v>
-      </c>
-      <c r="I37" s="34"/>
-      <c r="J37" s="146" t="str">
-        <f t="shared" si="1"/>
-        <v>Gathered End Hammock</v>
-      </c>
-      <c r="K37" s="66" t="s">
-        <v>290</v>
-      </c>
-      <c r="L37" s="20">
-        <v>1.6</v>
-      </c>
-      <c r="M37" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="N37" s="36"/>
-      <c r="O37" s="33">
-        <v>4</v>
-      </c>
-      <c r="P37" s="35">
-        <v>7.5</v>
-      </c>
-      <c r="Q37" s="35">
-        <f t="shared" si="3"/>
-        <v>30</v>
-      </c>
       <c r="S37" s="169" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="T37" s="108">
         <f>T31+T32+T23</f>
@@ -6571,67 +6597,61 @@
         <v>398</v>
       </c>
       <c r="V37" s="31" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="W37" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="X37" s="30"/>
     </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A38" s="20" t="s">
-        <v>404</v>
-      </c>
-      <c r="B38" s="38" t="s">
-        <v>334</v>
-      </c>
-      <c r="C38" s="20">
-        <v>1.2</v>
-      </c>
-      <c r="D38" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="E38" s="36">
-        <f>$A$39*C38</f>
-        <v>6.1111111111111107</v>
-      </c>
-      <c r="F38" s="33">
-        <v>4</v>
-      </c>
-      <c r="G38" s="35">
-        <v>6.42</v>
-      </c>
-      <c r="H38" s="35">
-        <f t="shared" si="0"/>
-        <v>25.68</v>
+    <row r="38" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="5"/>
+      <c r="B38" s="55"/>
+      <c r="F38" s="33"/>
+      <c r="G38" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="H38" s="65">
+        <f>SUM(H29:H37)</f>
+        <v>42.089999999999996</v>
       </c>
       <c r="I38" s="34"/>
       <c r="J38" s="147" t="str">
         <f t="shared" si="1"/>
-        <v>120x55</v>
-      </c>
-      <c r="K38" s="66"/>
-      <c r="L38" s="20"/>
-      <c r="M38" s="21"/>
+        <v/>
+      </c>
+      <c r="K38" s="66" t="s">
+        <v>290</v>
+      </c>
+      <c r="L38" s="20">
+        <v>1.6</v>
+      </c>
+      <c r="M38" s="21" t="s">
+        <v>159</v>
+      </c>
       <c r="N38" s="36"/>
-      <c r="O38" s="33"/>
-      <c r="P38" s="35"/>
-      <c r="Q38" s="35" t="str">
+      <c r="O38" s="33">
+        <v>4</v>
+      </c>
+      <c r="P38" s="35">
+        <v>7.5</v>
+      </c>
+      <c r="Q38" s="35">
         <f t="shared" si="3"/>
-        <v/>
+        <v>30</v>
       </c>
       <c r="S38" s="170" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="T38" s="102">
         <f>T27+T30</f>
         <v>41.76</v>
       </c>
       <c r="U38" s="112" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="V38" s="31" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="W38" s="3">
         <v>129.33000000000001</v>
@@ -6639,221 +6659,228 @@
       <c r="X38" s="30"/>
     </row>
     <row r="39" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A39" s="37">
-        <f>(120*55)/(36*36)</f>
-        <v>5.0925925925925926</v>
-      </c>
-      <c r="B39" s="38" t="s">
-        <v>279</v>
-      </c>
-      <c r="C39" s="20">
-        <v>1.6</v>
-      </c>
-      <c r="D39" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="E39" s="36">
-        <f>$A$39*C39</f>
-        <v>8.1481481481481488</v>
-      </c>
+      <c r="A39" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="B39" s="55"/>
       <c r="F39" s="33"/>
-      <c r="G39" s="35">
-        <v>6.69</v>
-      </c>
-      <c r="H39" s="35" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="G39" s="64"/>
+      <c r="H39" s="144"/>
       <c r="I39" s="34"/>
-      <c r="J39" s="147">
+      <c r="J39" s="146" t="str">
         <f t="shared" si="1"/>
-        <v>5.0925925925925926</v>
-      </c>
-      <c r="K39" s="66" t="s">
-        <v>79</v>
-      </c>
+        <v>Gathered End Hammock</v>
+      </c>
+      <c r="K39" s="66"/>
       <c r="L39" s="20"/>
       <c r="M39" s="21"/>
       <c r="N39" s="36"/>
-      <c r="O39" s="33">
-        <v>1</v>
-      </c>
-      <c r="P39" s="35">
-        <v>5.25</v>
-      </c>
-      <c r="Q39" s="35">
+      <c r="O39" s="33"/>
+      <c r="P39" s="35"/>
+      <c r="Q39" s="35" t="str">
         <f t="shared" si="3"/>
-        <v>5.25</v>
+        <v/>
       </c>
       <c r="S39" s="110" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="T39" s="97">
         <f>T26+T33</f>
-        <v>116.27</v>
+        <v>127.07</v>
       </c>
       <c r="U39" s="113" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="V39" s="25" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="40" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A40" s="37"/>
+      <c r="A40" s="20" t="s">
+        <v>403</v>
+      </c>
       <c r="B40" s="38" t="s">
-        <v>79</v>
-      </c>
-      <c r="C40" s="20"/>
-      <c r="D40" s="21"/>
-      <c r="E40" s="36"/>
+        <v>334</v>
+      </c>
+      <c r="C40" s="20">
+        <v>1.2</v>
+      </c>
+      <c r="D40" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E40" s="36">
+        <f>$A$41*C40</f>
+        <v>6.1111111111111107</v>
+      </c>
       <c r="F40" s="33">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G40" s="35">
-        <v>3.96</v>
+        <v>7.45</v>
       </c>
       <c r="H40" s="35">
         <f t="shared" si="0"/>
-        <v>3.96</v>
+        <v>29.8</v>
       </c>
       <c r="I40" s="34"/>
       <c r="J40" s="147" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Q40" s="35" t="str">
+        <v>120x55</v>
+      </c>
+      <c r="K40" s="66" t="s">
+        <v>79</v>
+      </c>
+      <c r="L40" s="20"/>
+      <c r="M40" s="21"/>
+      <c r="N40" s="36"/>
+      <c r="O40" s="33">
+        <v>1</v>
+      </c>
+      <c r="P40" s="35">
+        <v>5.25</v>
+      </c>
+      <c r="Q40" s="35">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="S40" s="110" t="s">
-        <v>399</v>
+        <v>5.25</v>
+      </c>
+      <c r="S40" s="179" t="str">
+        <f>"Dutch $"&amp;H82+H15+H27</f>
+        <v>Dutch $180.71</v>
       </c>
       <c r="T40" s="82">
         <f>T21+T22</f>
-        <v>143.94</v>
+        <v>144.89000000000001</v>
       </c>
       <c r="U40" s="111" t="s">
-        <v>458</v>
-      </c>
-      <c r="V40" s="174" t="s">
-        <v>498</v>
-      </c>
-      <c r="W40" s="177">
-        <f>H79</f>
-        <v>25.02</v>
+        <v>456</v>
+      </c>
+      <c r="V40" s="173" t="s">
+        <v>496</v>
+      </c>
+      <c r="W40" s="174">
+        <f>H82</f>
+        <v>35.82</v>
       </c>
     </row>
     <row r="41" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A41" s="37"/>
-      <c r="B41" s="52" t="s">
-        <v>350</v>
+      <c r="A41" s="37">
+        <f>(120*55)/(36*36)</f>
+        <v>5.0925925925925926</v>
+      </c>
+      <c r="B41" s="38" t="s">
+        <v>279</v>
       </c>
       <c r="C41" s="20">
-        <v>27</v>
+        <v>1.6</v>
       </c>
       <c r="D41" s="21" t="s">
-        <v>161</v>
-      </c>
-      <c r="E41" s="36"/>
-      <c r="F41" s="33">
-        <v>0</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="E41" s="36">
+        <f>$A$41*C41</f>
+        <v>8.1481481481481488</v>
+      </c>
+      <c r="F41" s="33"/>
       <c r="G41" s="35">
-        <v>11.45</v>
+        <v>6.69</v>
       </c>
       <c r="H41" s="35" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I41" s="34"/>
-      <c r="J41" s="147"/>
-      <c r="Q41" s="35"/>
+      <c r="J41" s="147">
+        <f t="shared" si="1"/>
+        <v>5.0925925925925926</v>
+      </c>
+      <c r="Q41" s="35" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
       <c r="S41" s="110" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="T41" s="92">
         <f>T25+T24</f>
-        <v>69.78</v>
+        <v>79.27000000000001</v>
       </c>
       <c r="U41" s="124" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="X41" s="30"/>
     </row>
     <row r="42" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="37"/>
       <c r="B42" s="38" t="s">
-        <v>349</v>
-      </c>
-      <c r="C42" s="20">
-        <v>0.67</v>
-      </c>
-      <c r="D42" s="21" t="s">
-        <v>159</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="C42" s="20"/>
+      <c r="D42" s="21"/>
       <c r="E42" s="36"/>
       <c r="F42" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G42" s="35">
-        <v>4.46</v>
+        <v>4.87</v>
       </c>
       <c r="H42" s="35">
-        <f t="shared" ref="H42" si="6">IF((G42*F42)=0,"",G42*F42)</f>
-        <v>8.92</v>
+        <f t="shared" si="0"/>
+        <v>4.87</v>
       </c>
       <c r="I42" s="34"/>
-      <c r="J42" s="147"/>
+      <c r="J42" s="147" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="Q42" s="35"/>
       <c r="S42" s="114" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="T42" s="118">
         <f>T28+T29</f>
         <v>14.9</v>
       </c>
       <c r="U42" s="119" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="43" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="5" t="s">
-        <v>359</v>
-      </c>
-      <c r="B43" s="54"/>
-      <c r="C43" s="20"/>
-      <c r="D43" s="21"/>
+      <c r="A43" s="37"/>
+      <c r="B43" s="52" t="s">
+        <v>350</v>
+      </c>
+      <c r="C43" s="20">
+        <v>27</v>
+      </c>
+      <c r="D43" s="21" t="s">
+        <v>161</v>
+      </c>
       <c r="E43" s="36"/>
       <c r="F43" s="33"/>
-      <c r="G43" s="64" t="s">
-        <v>65</v>
-      </c>
-      <c r="H43" s="63">
-        <f>SUM(H38:H42)</f>
-        <v>38.56</v>
+      <c r="G43" s="35">
+        <v>11.45</v>
+      </c>
+      <c r="H43" s="35" t="str">
+        <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="I43" s="34"/>
       <c r="J43" s="147" t="str">
-        <f>IF(ISBLANK(A41),"",A41)</f>
-        <v/>
-      </c>
-      <c r="P43" s="64" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q43" s="63">
-        <f>SUM(Q37:Q42)</f>
-        <v>35.25</v>
-      </c>
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="Q43" s="35"/>
       <c r="S43" s="127"/>
       <c r="T43" s="30"/>
-    </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A44" s="20" t="s">
-        <v>436</v>
-      </c>
+      <c r="U43" s="30">
+        <f>T40+W40</f>
+        <v>180.71</v>
+      </c>
+    </row>
+    <row r="44" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="37"/>
       <c r="B44" s="38" t="s">
-        <v>501</v>
+        <v>349</v>
       </c>
       <c r="C44" s="20">
         <v>0.67</v>
@@ -6861,206 +6888,209 @@
       <c r="D44" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="E44" s="36">
-        <f>C44*$A$45</f>
-        <v>5.9555555555555566</v>
-      </c>
+      <c r="E44" s="36"/>
       <c r="F44" s="33">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G44" s="35">
         <v>4.46</v>
       </c>
       <c r="H44" s="35">
-        <f t="shared" si="0"/>
-        <v>22.3</v>
+        <f t="shared" ref="H44" si="6">IF((G44*F44)=0,"",G44*F44)</f>
+        <v>8.92</v>
       </c>
       <c r="I44" s="34"/>
-      <c r="J44" s="146" t="str">
-        <f t="shared" ref="J44:J49" si="7">IF(ISBLANK(A43),"",A43)</f>
+      <c r="J44" s="147" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="P44" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q44" s="63">
+        <f>SUM(Q38:Q43)</f>
+        <v>35.25</v>
+      </c>
+      <c r="S44" s="167" t="s">
+        <v>505</v>
+      </c>
+      <c r="T44" s="30"/>
+    </row>
+    <row r="45" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B45" s="54"/>
+      <c r="C45" s="20"/>
+      <c r="D45" s="21"/>
+      <c r="E45" s="36"/>
+      <c r="F45" s="33"/>
+      <c r="G45" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="H45" s="63">
+        <f>SUM(H40:H44)</f>
+        <v>43.59</v>
+      </c>
+      <c r="I45" s="34"/>
+      <c r="J45" s="147" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K45" s="66" t="s">
+        <v>317</v>
+      </c>
+      <c r="L45" s="20">
+        <v>0.67</v>
+      </c>
+      <c r="M45" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="N45" s="36"/>
+      <c r="O45" s="33">
+        <v>7</v>
+      </c>
+      <c r="P45" s="35">
+        <v>5.5</v>
+      </c>
+      <c r="Q45" s="35">
+        <f>IF((P45*O45)=0,"",P45*O45)</f>
+        <v>38.5</v>
+      </c>
+      <c r="S45" s="20" t="str">
+        <f>A116</f>
+        <v>Pack Cover (new pack)</v>
+      </c>
+      <c r="T45" s="30"/>
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A46" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="B46" s="54"/>
+      <c r="C46" s="20"/>
+      <c r="D46" s="21"/>
+      <c r="E46" s="36"/>
+      <c r="F46" s="33"/>
+      <c r="G46" s="64"/>
+      <c r="H46" s="176"/>
+      <c r="I46" s="34"/>
+      <c r="J46" s="146" t="str">
+        <f t="shared" si="1"/>
         <v>Bug Net</v>
       </c>
-      <c r="K44" s="66" t="s">
-        <v>317</v>
-      </c>
-      <c r="L44" s="20">
+      <c r="K46" s="66" t="s">
+        <v>318</v>
+      </c>
+      <c r="L46" s="20">
+        <v>0.9</v>
+      </c>
+      <c r="M46" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="N46" s="36"/>
+      <c r="O46" s="33"/>
+      <c r="P46" s="35">
+        <v>5</v>
+      </c>
+      <c r="Q46" s="35" t="str">
+        <f>IF((P46*O46)=0,"",P46*O46)</f>
+        <v/>
+      </c>
+      <c r="S46" s="20" t="str">
+        <f>A117</f>
+        <v>Ditty Bags (See ToDo)</v>
+      </c>
+      <c r="T46" s="30"/>
+    </row>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A47" s="20" t="s">
+        <v>434</v>
+      </c>
+      <c r="B47" s="38" t="s">
+        <v>499</v>
+      </c>
+      <c r="C47" s="20">
         <v>0.67</v>
       </c>
-      <c r="M44" s="21" t="s">
+      <c r="D47" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="N44" s="36"/>
-      <c r="O44" s="33">
+      <c r="E47" s="36">
+        <f>C47*$A$48</f>
+        <v>5.9555555555555566</v>
+      </c>
+      <c r="F47" s="33">
+        <v>8</v>
+      </c>
+      <c r="G47" s="35">
+        <v>4.46</v>
+      </c>
+      <c r="H47" s="35">
+        <f>IF((G47*F47)=0,"",G47*F47)</f>
+        <v>35.68</v>
+      </c>
+      <c r="I47" s="34"/>
+      <c r="J47" s="147" t="str">
+        <f t="shared" si="1"/>
+        <v>120 x 96</v>
+      </c>
+      <c r="K47" s="66" t="s">
+        <v>316</v>
+      </c>
+      <c r="L47" s="20">
+        <v>0.5</v>
+      </c>
+      <c r="M47" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="N47" s="36">
+        <f>(55*36)/(36*36)</f>
+        <v>1.5277777777777777</v>
+      </c>
+      <c r="O47" s="33">
         <v>7</v>
       </c>
-      <c r="P44" s="35">
-        <v>5.5</v>
-      </c>
-      <c r="Q44" s="35">
-        <f>IF((P44*O44)=0,"",P44*O44)</f>
-        <v>38.5</v>
-      </c>
-      <c r="S44" s="167" t="s">
-        <v>507</v>
-      </c>
-      <c r="T44" s="30"/>
-    </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A45" s="20">
+      <c r="P47" s="35">
+        <v>8.75</v>
+      </c>
+      <c r="Q47" s="35"/>
+      <c r="S47" s="20" t="str">
+        <f>A118</f>
+        <v>Kilt (Use ION)</v>
+      </c>
+      <c r="T47" s="30"/>
+    </row>
+    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A48" s="20">
         <f>(120*96)/(36*36)</f>
         <v>8.8888888888888893</v>
       </c>
-      <c r="B45" s="38" t="s">
+      <c r="B48" s="38" t="s">
         <v>318</v>
       </c>
-      <c r="C45" s="20">
+      <c r="C48" s="20">
         <v>0.9</v>
       </c>
-      <c r="D45" s="21" t="s">
+      <c r="D48" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="E45" s="36">
-        <f>C45*$A$45</f>
+      <c r="E48" s="36">
+        <f>C48*$A$48</f>
         <v>8</v>
       </c>
-      <c r="F45" s="33"/>
-      <c r="G45" s="35">
+      <c r="F48" s="33"/>
+      <c r="G48" s="35">
         <v>4.17</v>
       </c>
-      <c r="H45" s="35" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I45" s="34"/>
-      <c r="J45" s="147" t="str">
-        <f t="shared" si="7"/>
-        <v>120 x 96</v>
-      </c>
-      <c r="K45" s="66" t="s">
-        <v>318</v>
-      </c>
-      <c r="L45" s="20">
-        <v>0.9</v>
-      </c>
-      <c r="M45" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="N45" s="36"/>
-      <c r="O45" s="33"/>
-      <c r="P45" s="35">
-        <v>5</v>
-      </c>
-      <c r="Q45" s="35" t="str">
-        <f>IF((P45*O45)=0,"",P45*O45)</f>
-        <v/>
-      </c>
-      <c r="S45" s="20" t="str">
-        <f>A112</f>
-        <v>Pack Cover (new pack)</v>
-      </c>
-      <c r="T45" s="30"/>
-    </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A46" s="20" t="s">
-        <v>499</v>
-      </c>
-      <c r="B46" s="38"/>
-      <c r="H46" s="35" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I46" s="34"/>
-      <c r="J46" s="147">
-        <f t="shared" si="7"/>
+      <c r="H48" s="35" t="str">
+        <f>IF((G48*F48)=0,"",G48*F48)</f>
+        <v/>
+      </c>
+      <c r="I48" s="34"/>
+      <c r="J48" s="147">
+        <f t="shared" si="1"/>
         <v>8.8888888888888893</v>
       </c>
-      <c r="K46" s="66" t="s">
-        <v>316</v>
-      </c>
-      <c r="L46" s="20">
-        <v>0.5</v>
-      </c>
-      <c r="M46" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="N46" s="36">
-        <f>(55*36)/(36*36)</f>
-        <v>1.5277777777777777</v>
-      </c>
-      <c r="O46" s="33">
-        <v>7</v>
-      </c>
-      <c r="P46" s="35">
-        <v>8.75</v>
-      </c>
-      <c r="Q46" s="35"/>
-      <c r="S46" s="20" t="str">
-        <f>A113</f>
-        <v>Ditty Bags (See ToDo)</v>
-      </c>
-      <c r="T46" s="30"/>
-    </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A47" s="20" t="s">
-        <v>500</v>
-      </c>
-      <c r="B47" s="46" t="s">
-        <v>372</v>
-      </c>
-      <c r="C47" s="20"/>
-      <c r="D47" s="21"/>
-      <c r="E47" s="36"/>
-      <c r="F47" s="33"/>
-      <c r="G47" s="35"/>
-      <c r="H47" s="35" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I47" s="34"/>
-      <c r="J47" s="147" t="str">
-        <f t="shared" si="7"/>
-        <v>Redesign to make it partial</v>
-      </c>
-      <c r="K47" s="138" t="s">
+      <c r="K48" s="138" t="s">
         <v>289</v>
-      </c>
-      <c r="L47" s="20"/>
-      <c r="M47" s="21"/>
-      <c r="N47" s="36"/>
-      <c r="O47" s="33"/>
-      <c r="P47" s="35"/>
-      <c r="Q47" s="35"/>
-      <c r="S47" s="20" t="str">
-        <f>A114</f>
-        <v>Kilt (Use ION)</v>
-      </c>
-      <c r="T47" s="30"/>
-    </row>
-    <row r="48" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="42" t="s">
-        <v>502</v>
-      </c>
-      <c r="B48" s="50" t="s">
-        <v>373</v>
-      </c>
-      <c r="C48" s="20"/>
-      <c r="D48" s="21"/>
-      <c r="E48" s="36"/>
-      <c r="F48" s="172">
-        <v>2</v>
-      </c>
-      <c r="G48" s="35"/>
-      <c r="H48" s="44">
-        <f>G44*F48</f>
-        <v>8.92</v>
-      </c>
-      <c r="I48" s="34"/>
-      <c r="J48" s="147" t="str">
-        <f t="shared" si="7"/>
-        <v>cover head to waist only</v>
-      </c>
-      <c r="K48" s="139" t="s">
-        <v>314</v>
       </c>
       <c r="L48" s="20"/>
       <c r="M48" s="21"/>
@@ -7069,214 +7099,190 @@
       <c r="P48" s="35"/>
       <c r="Q48" s="35"/>
       <c r="S48" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="T48" s="30"/>
     </row>
     <row r="49" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="20"/>
-      <c r="B49" s="40"/>
-      <c r="C49" s="20"/>
-      <c r="D49" s="21"/>
-      <c r="E49" s="171">
-        <f>((72*55)/(36*36))*C44</f>
-        <v>2.0472222222222221</v>
-      </c>
-      <c r="F49" s="33"/>
-      <c r="G49" s="64" t="s">
-        <v>65</v>
-      </c>
-      <c r="H49" s="65">
-        <f>SUM(H44:H48)</f>
-        <v>31.22</v>
+      <c r="A49" s="20" t="s">
+        <v>497</v>
+      </c>
+      <c r="B49" s="38"/>
+      <c r="H49" s="35" t="str">
+        <f>IF((G49*F49)=0,"",G49*F49)</f>
+        <v/>
       </c>
       <c r="I49" s="34"/>
-      <c r="J49" s="147" t="str">
-        <f t="shared" si="7"/>
-        <v>The Ultimate Hang half bug net 72" x 55" (.67 noseeum)</v>
-      </c>
-      <c r="K49" s="66"/>
+      <c r="J49" s="177" t="str">
+        <f t="shared" si="1"/>
+        <v>Redesign to make it partial</v>
+      </c>
+      <c r="K49" s="139" t="s">
+        <v>314</v>
+      </c>
       <c r="L49" s="20"/>
       <c r="M49" s="21"/>
       <c r="N49" s="36"/>
       <c r="O49" s="33"/>
-      <c r="P49" s="64" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q49" s="65">
-        <f>SUM(Q44:Q48)</f>
-        <v>38.5</v>
-      </c>
+      <c r="P49" s="35"/>
+      <c r="Q49" s="35"/>
       <c r="T49" s="30"/>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A50" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="B50" s="54"/>
+    <row r="50" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="20" t="s">
+        <v>498</v>
+      </c>
+      <c r="B50" s="46" t="s">
+        <v>372</v>
+      </c>
       <c r="C50" s="20"/>
       <c r="D50" s="21"/>
       <c r="E50" s="36"/>
       <c r="F50" s="33"/>
-      <c r="G50" s="64"/>
-      <c r="H50" s="144"/>
+      <c r="G50" s="35"/>
+      <c r="H50" s="35" t="str">
+        <f>IF((G50*F50)=0,"",G50*F50)</f>
+        <v/>
+      </c>
       <c r="I50" s="34"/>
-      <c r="J50" s="147"/>
+      <c r="J50" s="177" t="str">
+        <f t="shared" si="1"/>
+        <v>cover head to waist only</v>
+      </c>
       <c r="K50" s="66"/>
       <c r="L50" s="20"/>
       <c r="M50" s="21"/>
       <c r="N50" s="36"/>
       <c r="O50" s="33"/>
-      <c r="P50" s="64"/>
-      <c r="Q50" s="144"/>
+      <c r="P50" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q50" s="65">
+        <f>SUM(Q45:Q49)</f>
+        <v>38.5</v>
+      </c>
       <c r="T50" s="30"/>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A51" s="60" t="s">
-        <v>410</v>
-      </c>
-      <c r="B51" s="38" t="s">
-        <v>421</v>
-      </c>
-      <c r="C51" s="20">
+    <row r="51" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="42" t="s">
+        <v>500</v>
+      </c>
+      <c r="B51" s="50" t="s">
+        <v>373</v>
+      </c>
+      <c r="C51" s="20"/>
+      <c r="D51" s="21"/>
+      <c r="E51" s="36"/>
+      <c r="F51" s="175"/>
+      <c r="G51" s="35"/>
+      <c r="H51" s="35" t="str">
+        <f>IF((G51*F51)=0,"",G51*F51)</f>
+        <v/>
+      </c>
+      <c r="I51" s="34"/>
+      <c r="J51" s="177" t="str">
+        <f t="shared" si="1"/>
+        <v>The Ultimate Hang half bug net 72" x 55" (.67 noseeum)</v>
+      </c>
+      <c r="K51" s="66"/>
+      <c r="L51" s="20"/>
+      <c r="M51" s="21"/>
+      <c r="N51" s="36"/>
+      <c r="O51" s="33"/>
+      <c r="P51" s="64"/>
+      <c r="Q51" s="144"/>
+      <c r="T51" s="30"/>
+    </row>
+    <row r="52" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="20"/>
+      <c r="B52" s="40"/>
+      <c r="C52" s="20"/>
+      <c r="D52" s="21"/>
+      <c r="E52" s="171">
+        <f>((72*55)/(36*36))*C47</f>
+        <v>2.0472222222222221</v>
+      </c>
+      <c r="F52" s="33"/>
+      <c r="G52" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="H52" s="65">
+        <f>SUM(H47:H51)</f>
+        <v>35.68</v>
+      </c>
+      <c r="I52" s="34"/>
+      <c r="J52" s="146" t="str">
+        <f t="shared" ref="J52:J64" si="7">IF(ISBLANK(A53),"",A53)</f>
+        <v>Back Pack</v>
+      </c>
+      <c r="K52" s="141" t="s">
+        <v>493</v>
+      </c>
+      <c r="L52" s="20">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="M52" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="N52" s="36"/>
+      <c r="O52" s="33">
+        <v>0</v>
+      </c>
+      <c r="P52" s="35">
+        <v>14.5</v>
+      </c>
+      <c r="Q52" s="35" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="T52" s="30"/>
+    </row>
+    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A53" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="B53" s="54"/>
+      <c r="C53" s="20"/>
+      <c r="D53" s="21"/>
+      <c r="E53" s="36"/>
+      <c r="F53" s="33"/>
+      <c r="G53" s="64"/>
+      <c r="H53" s="144"/>
+      <c r="I53" s="34"/>
+      <c r="J53" s="147" t="str">
+        <f t="shared" si="7"/>
+        <v>* Work on quantities</v>
+      </c>
+      <c r="K53" s="66" t="s">
+        <v>491</v>
+      </c>
+      <c r="L53" s="20">
+        <v>3.2</v>
+      </c>
+      <c r="M53" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="N53" s="36"/>
+      <c r="O53" s="33"/>
+      <c r="P53" s="35">
+        <v>10</v>
+      </c>
+      <c r="Q53" s="35" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="T53" s="30"/>
+    </row>
+    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A54" s="60" t="s">
+        <v>409</v>
+      </c>
+      <c r="B54" s="38" t="s">
+        <v>419</v>
+      </c>
+      <c r="C54" s="20">
         <f>(4.85+5.85)/2</f>
         <v>5.35</v>
-      </c>
-      <c r="D51" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="E51" s="36"/>
-      <c r="F51" s="33"/>
-      <c r="G51" s="35">
-        <v>12.84</v>
-      </c>
-      <c r="H51" s="35" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I51" s="34"/>
-      <c r="J51" s="146" t="str">
-        <f t="shared" ref="J51:J63" si="8">IF(ISBLANK(A50),"",A50)</f>
-        <v>Back Pack</v>
-      </c>
-      <c r="K51" s="141" t="s">
-        <v>495</v>
-      </c>
-      <c r="L51" s="20">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="M51" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="N51" s="36"/>
-      <c r="O51" s="33">
-        <v>0</v>
-      </c>
-      <c r="P51" s="35">
-        <v>14.5</v>
-      </c>
-      <c r="Q51" s="35" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="T51" s="30"/>
-    </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="B52" s="38" t="s">
-        <v>422</v>
-      </c>
-      <c r="C52" s="20">
-        <v>3.2</v>
-      </c>
-      <c r="D52" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="E52" s="36"/>
-      <c r="F52" s="33"/>
-      <c r="G52" s="35">
-        <v>5.08</v>
-      </c>
-      <c r="H52" s="35" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I52" s="34"/>
-      <c r="J52" s="147" t="str">
-        <f t="shared" si="8"/>
-        <v>* Work on quantities</v>
-      </c>
-      <c r="K52" s="66" t="s">
-        <v>493</v>
-      </c>
-      <c r="L52" s="20">
-        <v>3.2</v>
-      </c>
-      <c r="M52" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="N52" s="36"/>
-      <c r="O52" s="33"/>
-      <c r="P52" s="35">
-        <v>10</v>
-      </c>
-      <c r="Q52" s="35" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="T52" s="30"/>
-    </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="B53" s="38" t="s">
-        <v>423</v>
-      </c>
-      <c r="C53" s="20">
-        <v>6.73</v>
-      </c>
-      <c r="D53" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="E53" s="36"/>
-      <c r="F53" s="33"/>
-      <c r="G53" s="35">
-        <v>3.75</v>
-      </c>
-      <c r="H53" s="35" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I53" s="34"/>
-      <c r="J53" s="147" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K53" s="66" t="s">
-        <v>494</v>
-      </c>
-      <c r="L53" s="20">
-        <v>3.9</v>
-      </c>
-      <c r="M53" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="N53" s="36"/>
-      <c r="O53" s="173">
-        <v>2</v>
-      </c>
-      <c r="P53" s="35">
-        <v>12.75</v>
-      </c>
-      <c r="Q53" s="35">
-        <f t="shared" si="3"/>
-        <v>25.5</v>
-      </c>
-      <c r="T53" s="30"/>
-    </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="B54" s="38" t="s">
-        <v>424</v>
-      </c>
-      <c r="C54" s="20">
-        <v>7.9</v>
       </c>
       <c r="D54" s="21" t="s">
         <v>159</v>
@@ -7287,63 +7293,73 @@
         <v>12.84</v>
       </c>
       <c r="H54" s="35" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="H54:H81" si="8">IF((G54*F54)=0,"",G54*F54)</f>
         <v/>
       </c>
       <c r="I54" s="34"/>
       <c r="J54" s="147" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K54" s="141" t="s">
-        <v>312</v>
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="K54" s="66" t="s">
+        <v>492</v>
       </c>
       <c r="L54" s="20">
-        <v>6.1</v>
+        <v>3.9</v>
       </c>
       <c r="M54" s="21" t="s">
         <v>159</v>
       </c>
       <c r="N54" s="36"/>
-      <c r="O54" s="33"/>
+      <c r="O54" s="172">
+        <v>2</v>
+      </c>
       <c r="P54" s="35">
-        <v>15</v>
-      </c>
-      <c r="Q54" s="35" t="str">
+        <v>12.75</v>
+      </c>
+      <c r="Q54" s="35">
         <f t="shared" si="3"/>
-        <v/>
+        <v>25.5</v>
       </c>
       <c r="T54" s="30"/>
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B55" s="38" t="s">
-        <v>332</v>
-      </c>
-      <c r="C55" s="20"/>
-      <c r="D55" s="21"/>
+        <v>420</v>
+      </c>
+      <c r="C55" s="20">
+        <v>3.2</v>
+      </c>
+      <c r="D55" s="21" t="s">
+        <v>159</v>
+      </c>
       <c r="E55" s="36"/>
       <c r="F55" s="33"/>
       <c r="G55" s="35">
-        <v>3.96</v>
+        <v>5.08</v>
       </c>
       <c r="H55" s="35" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I55" s="34"/>
       <c r="J55" s="147" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K55" s="66" t="s">
-        <v>332</v>
-      </c>
-      <c r="L55" s="20"/>
-      <c r="M55" s="21"/>
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="K55" s="141" t="s">
+        <v>312</v>
+      </c>
+      <c r="L55" s="20">
+        <v>6.1</v>
+      </c>
+      <c r="M55" s="21" t="s">
+        <v>159</v>
+      </c>
       <c r="N55" s="36"/>
-      <c r="O55" s="178"/>
+      <c r="O55" s="33"/>
       <c r="P55" s="35">
-        <v>4.5</v>
+        <v>15</v>
       </c>
       <c r="Q55" s="35" t="str">
         <f t="shared" si="3"/>
@@ -7353,41 +7369,37 @@
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B56" s="38" t="s">
-        <v>348</v>
+        <v>421</v>
       </c>
       <c r="C56" s="20">
-        <v>212.5</v>
+        <v>6.73</v>
       </c>
       <c r="D56" s="21" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E56" s="36"/>
       <c r="F56" s="33"/>
       <c r="G56" s="35">
-        <v>13.91</v>
+        <v>3.75</v>
       </c>
       <c r="H56" s="35" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I56" s="34"/>
       <c r="J56" s="147" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K56" s="117" t="s">
-        <v>355</v>
-      </c>
-      <c r="L56" s="20">
-        <v>10</v>
-      </c>
-      <c r="M56" s="21" t="s">
-        <v>159</v>
-      </c>
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="K56" s="66" t="s">
+        <v>332</v>
+      </c>
+      <c r="L56" s="20"/>
+      <c r="M56" s="21"/>
       <c r="N56" s="36"/>
-      <c r="O56" s="33"/>
+      <c r="O56" s="175"/>
       <c r="P56" s="35">
-        <v>14</v>
+        <v>4.5</v>
       </c>
       <c r="Q56" s="35" t="str">
         <f t="shared" si="3"/>
@@ -7397,29 +7409,33 @@
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B57" s="38" t="s">
-        <v>333</v>
-      </c>
-      <c r="C57" s="21" t="s">
-        <v>353</v>
-      </c>
-      <c r="D57" s="21"/>
+        <v>422</v>
+      </c>
+      <c r="C57" s="20">
+        <v>7.9</v>
+      </c>
+      <c r="D57" s="21" t="s">
+        <v>159</v>
+      </c>
       <c r="E57" s="36"/>
       <c r="F57" s="33"/>
-      <c r="G57" s="35"/>
+      <c r="G57" s="35">
+        <v>12.84</v>
+      </c>
       <c r="H57" s="35" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I57" s="34"/>
       <c r="J57" s="147" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K57" s="141" t="s">
-        <v>354</v>
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="K57" s="117" t="s">
+        <v>355</v>
       </c>
       <c r="L57" s="20">
-        <v>14.36</v>
+        <v>10</v>
       </c>
       <c r="M57" s="21" t="s">
         <v>159</v>
@@ -7427,7 +7443,7 @@
       <c r="N57" s="36"/>
       <c r="O57" s="33"/>
       <c r="P57" s="35">
-        <v>12.88</v>
+        <v>14</v>
       </c>
       <c r="Q57" s="35" t="str">
         <f t="shared" si="3"/>
@@ -7436,41 +7452,38 @@
       <c r="T57" s="30"/>
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A58">
-        <v>7</v>
-      </c>
       <c r="B58" s="38" t="s">
-        <v>413</v>
-      </c>
-      <c r="C58" s="20">
-        <v>1.7</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="C58" s="20"/>
       <c r="D58" s="21"/>
       <c r="E58" s="36"/>
       <c r="F58" s="33"/>
-      <c r="G58" s="35"/>
+      <c r="G58" s="35">
+        <v>3.96</v>
+      </c>
       <c r="H58" s="35" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I58" s="34"/>
       <c r="J58" s="147" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K58" s="141" t="s">
-        <v>311</v>
+        <v>354</v>
       </c>
       <c r="L58" s="20">
-        <v>4</v>
+        <v>14.36</v>
       </c>
       <c r="M58" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="N58" s="3"/>
+      <c r="N58" s="36"/>
       <c r="O58" s="33"/>
       <c r="P58" s="35">
-        <v>8</v>
+        <v>12.88</v>
       </c>
       <c r="Q58" s="35" t="str">
         <f t="shared" si="3"/>
@@ -7479,43 +7492,41 @@
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B59" s="38" t="s">
-        <v>506</v>
+        <v>348</v>
       </c>
       <c r="C59" s="20">
-        <v>0.56000000000000005</v>
+        <v>212.5</v>
       </c>
       <c r="D59" s="21" t="s">
         <v>161</v>
       </c>
       <c r="E59" s="36"/>
-      <c r="F59" s="33">
-        <v>10</v>
-      </c>
+      <c r="F59" s="33"/>
       <c r="G59" s="35">
-        <v>0.12</v>
-      </c>
-      <c r="H59" s="35">
-        <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>13.91</v>
+      </c>
+      <c r="H59" s="35" t="str">
+        <f t="shared" si="8"/>
+        <v/>
       </c>
       <c r="I59" s="34"/>
-      <c r="J59" s="147">
-        <f t="shared" si="8"/>
-        <v>7</v>
-      </c>
-      <c r="K59" s="66" t="s">
-        <v>411</v>
+      <c r="J59" s="147" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="K59" s="141" t="s">
+        <v>311</v>
       </c>
       <c r="L59" s="20">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="M59" s="21" t="s">
-        <v>161</v>
-      </c>
-      <c r="N59" s="36"/>
+        <v>159</v>
+      </c>
+      <c r="N59" s="3"/>
       <c r="O59" s="33"/>
       <c r="P59" s="35">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="Q59" s="35" t="str">
         <f t="shared" si="3"/>
@@ -7523,39 +7534,30 @@
       </c>
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A60">
-        <v>10</v>
-      </c>
       <c r="B60" s="38" t="s">
-        <v>420</v>
-      </c>
-      <c r="C60" s="20">
-        <v>0.42</v>
-      </c>
-      <c r="D60" s="21" t="s">
-        <v>161</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="C60" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="D60" s="21"/>
       <c r="E60" s="36"/>
-      <c r="F60" s="175">
-        <v>6</v>
-      </c>
-      <c r="G60" s="35">
-        <v>0.17</v>
-      </c>
-      <c r="H60" s="35">
-        <f t="shared" si="0"/>
-        <v>1.02</v>
+      <c r="F60" s="33"/>
+      <c r="G60" s="35"/>
+      <c r="H60" s="35" t="str">
+        <f t="shared" si="8"/>
+        <v/>
       </c>
       <c r="I60" s="34"/>
-      <c r="J60" s="147" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+      <c r="J60" s="147">
+        <f t="shared" si="7"/>
+        <v>7</v>
       </c>
       <c r="K60" s="66" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="L60" s="20">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="M60" s="21" t="s">
         <v>161</v>
@@ -7563,7 +7565,7 @@
       <c r="N60" s="36"/>
       <c r="O60" s="33"/>
       <c r="P60" s="35">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="Q60" s="35" t="str">
         <f t="shared" si="3"/>
@@ -7572,32 +7574,32 @@
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B61" s="38" t="s">
-        <v>414</v>
-      </c>
-      <c r="C61" s="20"/>
-      <c r="D61" s="21" t="s">
-        <v>161</v>
-      </c>
+        <v>412</v>
+      </c>
+      <c r="C61" s="20">
+        <v>1.7</v>
+      </c>
+      <c r="D61" s="21"/>
       <c r="E61" s="36"/>
       <c r="F61" s="33"/>
       <c r="G61" s="35"/>
       <c r="H61" s="35" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I61" s="34"/>
-      <c r="J61" s="147">
-        <f t="shared" si="8"/>
-        <v>10</v>
+      <c r="J61" s="147" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="K61" s="66" t="s">
-        <v>299</v>
+        <v>411</v>
       </c>
       <c r="L61" s="20">
-        <v>2.33</v>
+        <v>0.5</v>
       </c>
       <c r="M61" s="21" t="s">
         <v>161</v>
@@ -7605,7 +7607,7 @@
       <c r="N61" s="36"/>
       <c r="O61" s="33"/>
       <c r="P61" s="35">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q61" s="35" t="str">
         <f t="shared" si="3"/>
@@ -7614,127 +7616,129 @@
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B62" s="38" t="s">
-        <v>415</v>
+        <v>504</v>
       </c>
       <c r="C62" s="20">
-        <v>3.96</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="D62" s="21" t="s">
         <v>161</v>
       </c>
       <c r="E62" s="36"/>
-      <c r="F62" s="175">
-        <v>10</v>
-      </c>
+      <c r="F62" s="33"/>
       <c r="G62" s="35">
-        <v>0.36</v>
-      </c>
-      <c r="H62" s="35">
-        <f t="shared" si="0"/>
-        <v>3.5999999999999996</v>
+        <v>0.12</v>
+      </c>
+      <c r="H62" s="35" t="str">
+        <f t="shared" si="8"/>
+        <v/>
       </c>
       <c r="I62" s="34"/>
       <c r="J62" s="147">
-        <f t="shared" si="8"/>
-        <v>9</v>
+        <f t="shared" si="7"/>
+        <v>10</v>
       </c>
       <c r="K62" s="66" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L62" s="20">
-        <v>4</v>
+        <v>2.33</v>
       </c>
       <c r="M62" s="21" t="s">
         <v>161</v>
       </c>
       <c r="N62" s="36"/>
-      <c r="O62" s="173">
+      <c r="O62" s="33"/>
+      <c r="P62" s="35">
+        <v>5</v>
+      </c>
+      <c r="Q62" s="35" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>10</v>
+      </c>
+      <c r="B63" s="38" t="s">
+        <v>418</v>
+      </c>
+      <c r="C63" s="20">
+        <v>0.42</v>
+      </c>
+      <c r="D63" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="E63" s="36"/>
+      <c r="F63" s="178">
+        <v>12</v>
+      </c>
+      <c r="G63" s="35">
+        <v>0.17</v>
+      </c>
+      <c r="H63" s="35">
+        <f t="shared" si="8"/>
+        <v>2.04</v>
+      </c>
+      <c r="I63" s="34"/>
+      <c r="J63" s="147">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="K63" s="66" t="s">
+        <v>298</v>
+      </c>
+      <c r="L63" s="20">
+        <v>4</v>
+      </c>
+      <c r="M63" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="N63" s="36"/>
+      <c r="O63" s="172">
         <v>1</v>
       </c>
-      <c r="P62" s="35">
+      <c r="P63" s="35">
         <v>4.75</v>
       </c>
-      <c r="Q62" s="35">
+      <c r="Q63" s="35">
         <f t="shared" si="3"/>
         <v>4.75</v>
       </c>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A63" s="23" t="s">
-        <v>418</v>
-      </c>
-      <c r="B63" s="38" t="s">
-        <v>375</v>
-      </c>
-      <c r="C63" s="20">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="D63" s="21" t="s">
+    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>9</v>
+      </c>
+      <c r="B64" s="38" t="s">
+        <v>413</v>
+      </c>
+      <c r="C64" s="20"/>
+      <c r="D64" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="E63" s="36"/>
-      <c r="F63" s="175">
-        <v>6</v>
-      </c>
-      <c r="G63" s="35">
-        <v>0.39</v>
-      </c>
-      <c r="H63" s="35">
-        <f t="shared" si="0"/>
-        <v>2.34</v>
-      </c>
-      <c r="I63" s="34"/>
-      <c r="J63" s="147" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K63" s="66" t="s">
-        <v>371</v>
-      </c>
-      <c r="L63" s="20"/>
-      <c r="M63" s="21"/>
-      <c r="N63" s="36"/>
-      <c r="O63" s="33"/>
-      <c r="P63" s="35">
-        <v>5</v>
-      </c>
-      <c r="Q63" s="35" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="B64" s="38" t="s">
-        <v>339</v>
-      </c>
-      <c r="C64" s="125" t="s">
-        <v>419</v>
-      </c>
-      <c r="D64" s="125"/>
       <c r="E64" s="36"/>
-      <c r="F64" s="33"/>
+      <c r="F64" s="175"/>
       <c r="G64" s="35"/>
       <c r="H64" s="35" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I64" s="34"/>
-      <c r="J64" s="148" t="s">
-        <v>454</v>
-      </c>
-      <c r="K64" s="141" t="s">
-        <v>339</v>
-      </c>
-      <c r="L64" s="20">
-        <v>33</v>
-      </c>
-      <c r="M64" s="21" t="s">
-        <v>161</v>
-      </c>
+      <c r="J64" s="147" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="K64" s="66" t="s">
+        <v>371</v>
+      </c>
+      <c r="L64" s="20"/>
+      <c r="M64" s="21"/>
       <c r="N64" s="36"/>
       <c r="O64" s="33"/>
       <c r="P64" s="35">
-        <v>0.65</v>
+        <v>5</v>
       </c>
       <c r="Q64" s="35" t="str">
         <f t="shared" si="3"/>
@@ -7742,118 +7746,114 @@
       </c>
     </row>
     <row r="65" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A65">
-        <v>5</v>
-      </c>
       <c r="B65" s="38" t="s">
-        <v>346</v>
+        <v>511</v>
       </c>
       <c r="C65" s="20">
-        <v>11.62</v>
+        <v>3.96</v>
       </c>
       <c r="D65" s="21" t="s">
         <v>161</v>
       </c>
       <c r="E65" s="36"/>
-      <c r="F65" s="33"/>
+      <c r="F65" s="178">
+        <v>6</v>
+      </c>
       <c r="G65" s="35">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="H65" s="35" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <v>0.24</v>
+      </c>
+      <c r="H65" s="35">
+        <f t="shared" si="8"/>
+        <v>1.44</v>
       </c>
       <c r="I65" s="34"/>
-      <c r="J65" s="147" t="str">
-        <f t="shared" ref="J65:J97" si="9">IF(ISBLANK(A64),"",A64)</f>
-        <v/>
-      </c>
-      <c r="K65" s="66"/>
-      <c r="L65" s="20"/>
-      <c r="M65" s="21"/>
+      <c r="J65" s="148" t="s">
+        <v>452</v>
+      </c>
+      <c r="K65" s="141" t="s">
+        <v>339</v>
+      </c>
+      <c r="L65" s="20">
+        <v>33</v>
+      </c>
+      <c r="M65" s="21" t="s">
+        <v>161</v>
+      </c>
       <c r="N65" s="36"/>
       <c r="O65" s="33"/>
-      <c r="P65" s="35"/>
+      <c r="P65" s="35">
+        <v>0.65</v>
+      </c>
       <c r="Q65" s="35" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A66" s="23" t="s">
+        <v>416</v>
+      </c>
       <c r="B66" s="38" t="s">
-        <v>416</v>
+        <v>508</v>
       </c>
       <c r="C66" s="20">
-        <v>15.1</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="D66" s="21" t="s">
         <v>161</v>
       </c>
       <c r="E66" s="36"/>
-      <c r="F66" s="33"/>
+      <c r="F66" s="178">
+        <v>6</v>
+      </c>
       <c r="G66" s="35">
-        <v>0.8</v>
-      </c>
-      <c r="H66" s="35" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H66" s="35">
+        <f t="shared" si="8"/>
+        <v>1.7399999999999998</v>
       </c>
       <c r="I66" s="34"/>
-      <c r="J66" s="147">
-        <f t="shared" si="9"/>
-        <v>5</v>
-      </c>
-      <c r="K66" s="66" t="s">
-        <v>282</v>
-      </c>
-      <c r="L66" s="20">
-        <v>15</v>
-      </c>
-      <c r="M66" s="21" t="s">
-        <v>161</v>
-      </c>
+      <c r="J66" s="147" t="str">
+        <f>IF(ISBLANK(A67),"",A67)</f>
+        <v/>
+      </c>
+      <c r="K66" s="66"/>
+      <c r="L66" s="20"/>
+      <c r="M66" s="21"/>
       <c r="N66" s="36"/>
       <c r="O66" s="33"/>
-      <c r="P66" s="35">
-        <v>0.9</v>
-      </c>
+      <c r="P66" s="35"/>
       <c r="Q66" s="35" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A67">
-        <v>9</v>
-      </c>
       <c r="B67" s="38" t="s">
-        <v>283</v>
-      </c>
-      <c r="C67" s="20">
-        <v>8.5</v>
-      </c>
-      <c r="D67" s="21" t="s">
-        <v>161</v>
-      </c>
-      <c r="E67" s="126"/>
-      <c r="F67" s="33"/>
-      <c r="G67" s="35">
-        <v>0.8</v>
-      </c>
+        <v>339</v>
+      </c>
+      <c r="C67" s="125" t="s">
+        <v>417</v>
+      </c>
+      <c r="D67" s="125"/>
+      <c r="E67" s="36"/>
+      <c r="F67" s="175"/>
+      <c r="G67" s="35"/>
       <c r="H67" s="35" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I67" s="34"/>
       <c r="J67" s="147" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(ISBLANK(A67),"",A67)</f>
         <v/>
       </c>
       <c r="K67" s="66" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L67" s="20">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="M67" s="21" t="s">
         <v>161</v>
@@ -7861,7 +7861,7 @@
       <c r="N67" s="36"/>
       <c r="O67" s="33"/>
       <c r="P67" s="35">
-        <v>0.65</v>
+        <v>0.9</v>
       </c>
       <c r="Q67" s="35" t="str">
         <f t="shared" si="3"/>
@@ -7870,36 +7870,36 @@
     </row>
     <row r="68" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>8</v>
-      </c>
-      <c r="B68" s="50" t="s">
-        <v>417</v>
+        <v>5</v>
+      </c>
+      <c r="B68" s="38" t="s">
+        <v>346</v>
       </c>
       <c r="C68" s="20">
-        <v>1.58</v>
+        <v>11.62</v>
       </c>
       <c r="D68" s="21" t="s">
         <v>161</v>
       </c>
       <c r="E68" s="36"/>
-      <c r="F68" s="33"/>
+      <c r="F68" s="175"/>
       <c r="G68" s="35">
-        <v>0.22</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="H68" s="35" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I68" s="34"/>
       <c r="J68" s="147">
-        <f t="shared" si="9"/>
-        <v>9</v>
-      </c>
-      <c r="K68" s="139" t="s">
-        <v>301</v>
+        <f t="shared" ref="J68:J113" si="9">IF(ISBLANK(A68),"",A68)</f>
+        <v>5</v>
+      </c>
+      <c r="K68" s="66" t="s">
+        <v>283</v>
       </c>
       <c r="L68" s="20">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="M68" s="21" t="s">
         <v>161</v>
@@ -7907,7 +7907,7 @@
       <c r="N68" s="36"/>
       <c r="O68" s="33"/>
       <c r="P68" s="35">
-        <v>4.5</v>
+        <v>0.65</v>
       </c>
       <c r="Q68" s="35" t="str">
         <f t="shared" si="3"/>
@@ -7915,34 +7915,34 @@
       </c>
     </row>
     <row r="69" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B69" s="50" t="s">
-        <v>300</v>
+      <c r="B69" s="38" t="s">
+        <v>414</v>
       </c>
       <c r="C69" s="20">
-        <v>1.58</v>
+        <v>15.1</v>
       </c>
       <c r="D69" s="21" t="s">
         <v>161</v>
       </c>
       <c r="E69" s="36"/>
-      <c r="F69" s="33"/>
+      <c r="F69" s="175"/>
       <c r="G69" s="35">
-        <v>0.22</v>
+        <v>0.8</v>
       </c>
       <c r="H69" s="35" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I69" s="34"/>
-      <c r="J69" s="147">
+      <c r="J69" s="147" t="str">
         <f t="shared" si="9"/>
-        <v>8</v>
+        <v/>
       </c>
       <c r="K69" s="139" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L69" s="20">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="M69" s="21" t="s">
         <v>161</v>
@@ -7950,7 +7950,7 @@
       <c r="N69" s="36"/>
       <c r="O69" s="33"/>
       <c r="P69" s="35">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="Q69" s="35" t="str">
         <f t="shared" si="3"/>
@@ -7958,42 +7958,47 @@
       </c>
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>9</v>
+      </c>
       <c r="B70" s="38" t="s">
-        <v>335</v>
+        <v>509</v>
       </c>
       <c r="C70" s="20">
-        <v>14.79</v>
+        <v>4.47</v>
       </c>
       <c r="D70" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="E70" s="36"/>
-      <c r="F70" s="33"/>
+      <c r="E70" s="126"/>
+      <c r="F70" s="178">
+        <v>8</v>
+      </c>
       <c r="G70" s="35">
-        <v>0.21</v>
-      </c>
-      <c r="H70" s="35" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <v>0.39</v>
+      </c>
+      <c r="H70" s="35">
+        <f t="shared" si="8"/>
+        <v>3.12</v>
       </c>
       <c r="I70" s="34"/>
-      <c r="J70" s="147" t="str">
+      <c r="J70" s="147">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K70" s="66" t="s">
-        <v>328</v>
+        <v>9</v>
+      </c>
+      <c r="K70" s="139" t="s">
+        <v>302</v>
       </c>
       <c r="L70" s="20">
-        <v>11.2</v>
+        <v>6.2</v>
       </c>
       <c r="M70" s="21" t="s">
-        <v>325</v>
+        <v>161</v>
       </c>
       <c r="N70" s="36"/>
       <c r="O70" s="33"/>
       <c r="P70" s="35">
-        <v>7.75</v>
+        <v>5</v>
       </c>
       <c r="Q70" s="35" t="str">
         <f t="shared" si="3"/>
@@ -8001,43 +8006,47 @@
       </c>
     </row>
     <row r="71" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B71" s="38" t="s">
-        <v>338</v>
+      <c r="A71">
+        <v>8</v>
+      </c>
+      <c r="B71" s="50" t="s">
+        <v>415</v>
       </c>
       <c r="C71" s="20">
-        <v>7</v>
+        <v>1.58</v>
       </c>
       <c r="D71" s="21" t="s">
-        <v>325</v>
+        <v>161</v>
       </c>
       <c r="E71" s="36"/>
-      <c r="F71" s="33">
-        <v>0</v>
+      <c r="F71" s="178">
+        <v>6</v>
       </c>
       <c r="G71" s="35">
-        <v>7.49</v>
-      </c>
-      <c r="H71" s="35" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <v>0.24</v>
+      </c>
+      <c r="H71" s="35">
+        <f t="shared" si="8"/>
+        <v>1.44</v>
       </c>
       <c r="I71" s="34"/>
-      <c r="J71" s="147" t="str">
+      <c r="J71" s="147">
         <f t="shared" si="9"/>
-        <v/>
+        <v>8</v>
       </c>
       <c r="K71" s="66" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L71" s="20">
-        <v>7.6</v>
+        <v>11.2</v>
       </c>
       <c r="M71" s="21" t="s">
         <v>325</v>
       </c>
-      <c r="N71" s="3"/>
+      <c r="N71" s="36"/>
+      <c r="O71" s="33"/>
       <c r="P71" s="35">
-        <v>9</v>
+        <v>7.75</v>
       </c>
       <c r="Q71" s="35" t="str">
         <f t="shared" si="3"/>
@@ -8045,22 +8054,22 @@
       </c>
     </row>
     <row r="72" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B72" s="38" t="s">
-        <v>336</v>
+      <c r="B72" s="50" t="s">
+        <v>300</v>
       </c>
       <c r="C72" s="20">
-        <v>4.4000000000000004</v>
+        <v>1.58</v>
       </c>
       <c r="D72" s="21" t="s">
-        <v>325</v>
+        <v>161</v>
       </c>
       <c r="E72" s="36"/>
-      <c r="F72" s="33"/>
+      <c r="F72" s="175"/>
       <c r="G72" s="35">
-        <v>9.36</v>
+        <v>0.22</v>
       </c>
       <c r="H72" s="35" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I72" s="34"/>
@@ -8069,17 +8078,17 @@
         <v/>
       </c>
       <c r="K72" s="66" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="L72" s="20">
-        <v>3.9</v>
+        <v>7.6</v>
       </c>
       <c r="M72" s="21" t="s">
         <v>325</v>
       </c>
       <c r="N72" s="3"/>
       <c r="P72" s="35">
-        <v>5.5</v>
+        <v>9</v>
       </c>
       <c r="Q72" s="35" t="str">
         <f t="shared" si="3"/>
@@ -8088,20 +8097,21 @@
     </row>
     <row r="73" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B73" s="38" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C73" s="20">
-        <v>2.8</v>
+        <v>14.79</v>
       </c>
       <c r="D73" s="21" t="s">
-        <v>325</v>
-      </c>
-      <c r="E73" s="3"/>
+        <v>161</v>
+      </c>
+      <c r="E73" s="36"/>
+      <c r="F73" s="175"/>
       <c r="G73" s="35">
-        <v>6.69</v>
+        <v>0.21</v>
       </c>
       <c r="H73" s="35" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I73" s="34"/>
@@ -8109,84 +8119,86 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="K73" s="141" t="s">
-        <v>327</v>
+      <c r="K73" s="66" t="s">
+        <v>330</v>
       </c>
       <c r="L73" s="20">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="M73" s="21" t="s">
         <v>325</v>
       </c>
-      <c r="N73" s="36"/>
-      <c r="O73" s="173">
-        <v>1</v>
-      </c>
+      <c r="N73" s="3"/>
       <c r="P73" s="35">
-        <v>6.5</v>
-      </c>
-      <c r="Q73" s="35">
+        <v>5.5</v>
+      </c>
+      <c r="Q73" s="35" t="str">
         <f t="shared" si="3"/>
-        <v>6.5</v>
+        <v/>
       </c>
     </row>
     <row r="74" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B74" s="52" t="s">
-        <v>340</v>
+      <c r="B74" s="38" t="s">
+        <v>338</v>
       </c>
       <c r="C74" s="20">
-        <v>10.3</v>
+        <v>7</v>
       </c>
       <c r="D74" s="21" t="s">
         <v>325</v>
       </c>
-      <c r="E74" s="3"/>
-      <c r="F74" s="176">
-        <v>2</v>
-      </c>
+      <c r="E74" s="36"/>
+      <c r="F74" s="175"/>
       <c r="G74" s="35">
-        <v>3.21</v>
-      </c>
-      <c r="H74" s="35">
-        <f t="shared" si="0"/>
-        <v>6.42</v>
+        <v>7.49</v>
+      </c>
+      <c r="H74" s="35" t="str">
+        <f t="shared" si="8"/>
+        <v/>
       </c>
       <c r="I74" s="34"/>
       <c r="J74" s="147" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="K74" s="66" t="s">
-        <v>340</v>
-      </c>
-      <c r="L74" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="M74" s="21"/>
+      <c r="K74" s="141" t="s">
+        <v>327</v>
+      </c>
+      <c r="L74" s="20">
+        <v>4.5</v>
+      </c>
+      <c r="M74" s="21" t="s">
+        <v>325</v>
+      </c>
       <c r="N74" s="36"/>
-      <c r="O74" s="33"/>
-      <c r="P74" s="35"/>
-      <c r="Q74" s="35" t="str">
+      <c r="O74" s="172">
+        <v>1</v>
+      </c>
+      <c r="P74" s="35">
+        <v>6.5</v>
+      </c>
+      <c r="Q74" s="35">
         <f t="shared" si="3"/>
-        <v/>
+        <v>6.5</v>
       </c>
     </row>
     <row r="75" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B75" s="52" t="s">
-        <v>341</v>
+      <c r="B75" s="38" t="s">
+        <v>336</v>
       </c>
       <c r="C75" s="20">
-        <v>8</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="D75" s="21" t="s">
         <v>325</v>
       </c>
-      <c r="E75" s="3"/>
+      <c r="E75" s="36"/>
+      <c r="F75" s="175"/>
       <c r="G75" s="35">
-        <v>0.86</v>
+        <v>9.36</v>
       </c>
       <c r="H75" s="35" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I75" s="34"/>
@@ -8195,7 +8207,7 @@
         <v/>
       </c>
       <c r="K75" s="66" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="L75" s="21" t="s">
         <v>342</v>
@@ -8211,15 +8223,22 @@
       <c r="S75" s="30"/>
     </row>
     <row r="76" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B76" s="46" t="s">
-        <v>289</v>
-      </c>
-      <c r="C76" s="20"/>
-      <c r="D76" s="21"/>
+      <c r="B76" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="C76" s="20">
+        <v>2.8</v>
+      </c>
+      <c r="D76" s="21" t="s">
+        <v>325</v>
+      </c>
       <c r="E76" s="3"/>
-      <c r="G76" s="35"/>
+      <c r="F76" s="10"/>
+      <c r="G76" s="35">
+        <v>6.69</v>
+      </c>
       <c r="H76" s="35" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I76" s="51"/>
@@ -8227,100 +8246,97 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="K76" s="138" t="s">
-        <v>289</v>
-      </c>
-      <c r="L76" s="20"/>
+      <c r="K76" s="66" t="s">
+        <v>341</v>
+      </c>
+      <c r="L76" s="21" t="s">
+        <v>342</v>
+      </c>
       <c r="M76" s="21"/>
-      <c r="N76" s="3"/>
-      <c r="P76" s="30"/>
+      <c r="N76" s="36"/>
+      <c r="O76" s="33"/>
+      <c r="P76" s="35"/>
       <c r="Q76" s="35" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="77" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B77" s="38" t="s">
-        <v>343</v>
+      <c r="B77" s="52" t="s">
+        <v>340</v>
       </c>
       <c r="C77" s="20">
-        <v>4.3</v>
+        <v>10.3</v>
       </c>
       <c r="D77" s="21" t="s">
         <v>325</v>
       </c>
       <c r="E77" s="3"/>
-      <c r="F77" s="176">
-        <v>3</v>
+      <c r="F77" s="9">
+        <v>2</v>
       </c>
       <c r="G77" s="35">
-        <v>2.94</v>
+        <v>3.43</v>
       </c>
       <c r="H77" s="35">
-        <f t="shared" si="0"/>
-        <v>8.82</v>
+        <f t="shared" si="8"/>
+        <v>6.86</v>
       </c>
       <c r="I77" s="34"/>
       <c r="J77" s="147" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="K77" s="66" t="s">
-        <v>304</v>
-      </c>
-      <c r="L77" s="20">
-        <v>8</v>
-      </c>
-      <c r="M77" s="21" t="s">
-        <v>325</v>
-      </c>
+      <c r="K77" s="138" t="s">
+        <v>289</v>
+      </c>
+      <c r="L77" s="20"/>
+      <c r="M77" s="21"/>
       <c r="N77" s="3"/>
-      <c r="P77" s="35">
-        <v>3.75</v>
-      </c>
+      <c r="P77" s="30"/>
       <c r="Q77" s="35" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B78" s="38" t="s">
-        <v>344</v>
+    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B78" s="52" t="s">
+        <v>510</v>
       </c>
       <c r="C78" s="20">
-        <v>1.41</v>
+        <v>8</v>
       </c>
       <c r="D78" s="21" t="s">
-        <v>161</v>
+        <v>325</v>
       </c>
       <c r="E78" s="3"/>
-      <c r="F78" s="176">
-        <v>3</v>
+      <c r="F78" s="9">
+        <v>4</v>
       </c>
       <c r="G78" s="35">
-        <v>0.54</v>
+        <v>0.92</v>
       </c>
       <c r="H78" s="35">
-        <f t="shared" si="0"/>
-        <v>1.62</v>
+        <f t="shared" si="8"/>
+        <v>3.68</v>
       </c>
       <c r="I78" s="34"/>
       <c r="J78" s="147" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="K78" s="139" t="s">
-        <v>305</v>
-      </c>
-      <c r="L78" s="20" t="s">
-        <v>303</v>
+      <c r="K78" s="66" t="s">
+        <v>304</v>
+      </c>
+      <c r="L78" s="20">
+        <v>8</v>
       </c>
       <c r="M78" s="21" t="s">
-        <v>161</v>
+        <v>325</v>
       </c>
       <c r="N78" s="3"/>
       <c r="P78" s="35">
-        <v>0.95</v>
+        <v>3.75</v>
       </c>
       <c r="Q78" s="35" t="str">
         <f t="shared" si="3"/>
@@ -8329,161 +8345,133 @@
       <c r="S78" s="30"/>
     </row>
     <row r="79" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="39" t="s">
-        <v>284</v>
+      <c r="B79" s="46" t="s">
+        <v>289</v>
       </c>
       <c r="C79" s="20"/>
       <c r="D79" s="21"/>
       <c r="E79" s="3"/>
-      <c r="G79" s="64" t="s">
-        <v>65</v>
-      </c>
-      <c r="H79" s="65">
-        <f>SUM(H51:H78)</f>
-        <v>25.02</v>
+      <c r="F79" s="10"/>
+      <c r="G79" s="35"/>
+      <c r="H79" s="35" t="str">
+        <f t="shared" si="8"/>
+        <v/>
       </c>
       <c r="I79" s="34"/>
       <c r="J79" s="147" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="K79" s="117"/>
-      <c r="L79" s="20"/>
-      <c r="M79" s="21"/>
+      <c r="K79" s="139" t="s">
+        <v>305</v>
+      </c>
+      <c r="L79" s="20" t="s">
+        <v>303</v>
+      </c>
+      <c r="M79" s="21" t="s">
+        <v>161</v>
+      </c>
       <c r="N79" s="3"/>
-      <c r="P79" s="64" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q79" s="65">
-        <f>SUM(Q51:Q78)</f>
-        <v>36.75</v>
-      </c>
-    </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A80" s="43"/>
-      <c r="B80" s="40" t="s">
-        <v>308</v>
-      </c>
-      <c r="C80" s="41">
-        <v>1.36</v>
-      </c>
-      <c r="D80" s="42" t="s">
-        <v>161</v>
-      </c>
-      <c r="E80" s="11"/>
-      <c r="F80" s="43">
-        <v>2</v>
-      </c>
-      <c r="G80" s="44">
-        <v>6.58</v>
-      </c>
-      <c r="H80" s="44">
-        <f t="shared" si="0"/>
-        <v>13.16</v>
+      <c r="P79" s="35">
+        <v>0.95</v>
+      </c>
+      <c r="Q79" s="35" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="80" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B80" s="38" t="s">
+        <v>343</v>
+      </c>
+      <c r="C80" s="20">
+        <v>4.3</v>
+      </c>
+      <c r="D80" s="21" t="s">
+        <v>325</v>
+      </c>
+      <c r="E80" s="3"/>
+      <c r="F80" s="9">
+        <v>4</v>
+      </c>
+      <c r="G80" s="35">
+        <v>3.15</v>
+      </c>
+      <c r="H80" s="35">
+        <f t="shared" si="8"/>
+        <v>12.6</v>
       </c>
       <c r="I80" s="34"/>
       <c r="J80" s="147" t="str">
         <f t="shared" si="9"/>
-        <v>Amsteel 7/64</v>
-      </c>
-      <c r="K80" s="142" t="s">
-        <v>308</v>
-      </c>
-      <c r="L80" s="41">
-        <v>1.36</v>
-      </c>
-      <c r="M80" s="42" t="s">
-        <v>325</v>
-      </c>
-      <c r="N80" s="11"/>
-      <c r="O80" s="43">
-        <v>1</v>
-      </c>
-      <c r="P80" s="44">
-        <v>7.5</v>
-      </c>
-      <c r="Q80" s="44">
-        <f t="shared" si="3"/>
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A81" s="39"/>
-      <c r="B81" s="40" t="s">
-        <v>309</v>
-      </c>
-      <c r="C81" s="41">
-        <v>1.36</v>
-      </c>
-      <c r="D81" s="42" t="s">
+        <v/>
+      </c>
+      <c r="K80" s="117"/>
+      <c r="L80" s="20"/>
+      <c r="M80" s="21"/>
+      <c r="N80" s="3"/>
+      <c r="P80" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q80" s="65">
+        <f>SUM(Q52:Q79)</f>
+        <v>36.75</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="38" t="s">
+        <v>344</v>
+      </c>
+      <c r="C81" s="20">
+        <v>1.41</v>
+      </c>
+      <c r="D81" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="E81" s="11"/>
-      <c r="F81" s="43">
-        <v>1</v>
-      </c>
-      <c r="G81" s="44">
-        <v>6.58</v>
-      </c>
-      <c r="H81" s="44">
-        <f t="shared" si="0"/>
-        <v>6.58</v>
+      <c r="E81" s="3"/>
+      <c r="F81" s="9">
+        <v>5</v>
+      </c>
+      <c r="G81" s="35">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="H81" s="35">
+        <f t="shared" si="8"/>
+        <v>2.9</v>
       </c>
       <c r="I81" s="34"/>
       <c r="J81" s="147" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="K81" s="142" t="s">
-        <v>309</v>
-      </c>
-      <c r="L81" s="41">
-        <v>1.36</v>
-      </c>
-      <c r="M81" s="42" t="s">
-        <v>325</v>
-      </c>
-      <c r="N81" s="11"/>
-      <c r="O81" s="43">
-        <v>1</v>
-      </c>
-      <c r="P81" s="44">
-        <v>7.5</v>
-      </c>
-      <c r="Q81" s="44">
-        <f t="shared" si="3"/>
-        <v>7.5</v>
-      </c>
+      <c r="K81" s="117"/>
+      <c r="L81" s="20"/>
+      <c r="M81" s="21"/>
+      <c r="N81" s="3"/>
+      <c r="P81" s="64"/>
+      <c r="Q81" s="144"/>
     </row>
     <row r="82" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="39"/>
-      <c r="B82" s="40" t="s">
-        <v>310</v>
-      </c>
-      <c r="C82" s="41">
-        <v>1.36</v>
-      </c>
-      <c r="D82" s="42" t="s">
-        <v>161</v>
-      </c>
-      <c r="E82" s="11"/>
-      <c r="F82" s="43">
-        <v>1</v>
-      </c>
-      <c r="G82" s="44">
-        <v>6.58</v>
-      </c>
-      <c r="H82" s="44">
-        <f t="shared" si="0"/>
-        <v>6.58</v>
+      <c r="A82" s="39" t="s">
+        <v>284</v>
+      </c>
+      <c r="C82" s="20"/>
+      <c r="D82" s="21"/>
+      <c r="E82" s="3"/>
+      <c r="G82" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="H82" s="65">
+        <f>SUM(H54:H81)</f>
+        <v>35.82</v>
       </c>
       <c r="I82" s="34"/>
-      <c r="J82" s="147" t="str">
+      <c r="J82" s="146" t="str">
         <f t="shared" si="9"/>
-        <v/>
+        <v>Amsteel 7/64</v>
       </c>
       <c r="K82" s="142" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="L82" s="41">
         <v>1.36</v>
@@ -8503,422 +8491,453 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="45" t="s">
-        <v>285</v>
-      </c>
-      <c r="B83" s="40"/>
-      <c r="C83" s="41"/>
-      <c r="D83" s="42"/>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A83" s="43"/>
+      <c r="B83" s="40" t="s">
+        <v>308</v>
+      </c>
+      <c r="C83" s="41">
+        <v>1.36</v>
+      </c>
+      <c r="D83" s="42" t="s">
+        <v>161</v>
+      </c>
       <c r="E83" s="11"/>
-      <c r="F83" s="43"/>
-      <c r="G83" s="69" t="s">
-        <v>65</v>
-      </c>
-      <c r="H83" s="67">
-        <f>SUM(H80:H82)</f>
-        <v>26.32</v>
+      <c r="F83" s="43">
+        <v>2</v>
+      </c>
+      <c r="G83" s="44">
+        <v>6.58</v>
+      </c>
+      <c r="H83" s="44">
+        <f>IF((G83*F83)=0,"",G83*F83)</f>
+        <v>13.16</v>
       </c>
       <c r="I83" s="34"/>
       <c r="J83" s="147" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="K83" s="142"/>
-      <c r="L83" s="41"/>
-      <c r="M83" s="42"/>
+      <c r="K83" s="142" t="s">
+        <v>309</v>
+      </c>
+      <c r="L83" s="41">
+        <v>1.36</v>
+      </c>
+      <c r="M83" s="42" t="s">
+        <v>325</v>
+      </c>
       <c r="N83" s="11"/>
-      <c r="O83" s="43"/>
-      <c r="P83" s="69" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q83" s="67">
-        <f>SUM(Q80:Q82)</f>
-        <v>22.5</v>
-      </c>
-    </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A84" s="7"/>
-      <c r="B84" s="46" t="s">
-        <v>306</v>
-      </c>
-      <c r="C84" s="47">
-        <v>1.9</v>
-      </c>
-      <c r="D84" s="48" t="s">
+      <c r="O83" s="43">
+        <v>1</v>
+      </c>
+      <c r="P83" s="44">
+        <v>7.5</v>
+      </c>
+      <c r="Q83" s="44">
+        <f t="shared" si="3"/>
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="39"/>
+      <c r="B84" s="40" t="s">
+        <v>309</v>
+      </c>
+      <c r="C84" s="41">
+        <v>1.36</v>
+      </c>
+      <c r="D84" s="42" t="s">
         <v>161</v>
       </c>
-      <c r="E84" s="8"/>
-      <c r="F84" s="7">
+      <c r="E84" s="11"/>
+      <c r="F84" s="43">
         <v>1</v>
       </c>
-      <c r="G84" s="49">
-        <v>4.87</v>
-      </c>
-      <c r="H84" s="49">
-        <f t="shared" si="0"/>
-        <v>4.87</v>
+      <c r="G84" s="44">
+        <v>6.58</v>
+      </c>
+      <c r="H84" s="44">
+        <f>IF((G84*F84)=0,"",G84*F84)</f>
+        <v>6.58</v>
       </c>
       <c r="I84" s="34"/>
       <c r="J84" s="147" t="str">
         <f t="shared" si="9"/>
-        <v>Shock Cord</v>
-      </c>
-      <c r="K84" s="138" t="s">
-        <v>306</v>
-      </c>
-      <c r="L84" s="47">
-        <v>1.9</v>
-      </c>
-      <c r="M84" s="48" t="s">
-        <v>326</v>
-      </c>
-      <c r="N84" s="8"/>
-      <c r="O84" s="7">
+        <v/>
+      </c>
+      <c r="K84" s="142" t="s">
+        <v>310</v>
+      </c>
+      <c r="L84" s="41">
+        <v>1.36</v>
+      </c>
+      <c r="M84" s="42" t="s">
+        <v>325</v>
+      </c>
+      <c r="N84" s="11"/>
+      <c r="O84" s="43">
         <v>1</v>
       </c>
-      <c r="P84" s="49">
-        <v>5.75</v>
-      </c>
-      <c r="Q84" s="49">
+      <c r="P84" s="44">
+        <v>7.5</v>
+      </c>
+      <c r="Q84" s="44">
         <f t="shared" si="3"/>
-        <v>5.75</v>
-      </c>
-    </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A85" s="10"/>
-      <c r="B85" s="46" t="s">
-        <v>307</v>
-      </c>
-      <c r="C85" s="47">
-        <v>1.2</v>
-      </c>
-      <c r="D85" s="48" t="s">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="39"/>
+      <c r="B85" s="40" t="s">
+        <v>310</v>
+      </c>
+      <c r="C85" s="41">
+        <v>1.36</v>
+      </c>
+      <c r="D85" s="42" t="s">
         <v>161</v>
       </c>
-      <c r="E85" s="8"/>
-      <c r="F85" s="7">
+      <c r="E85" s="11"/>
+      <c r="F85" s="43">
         <v>1</v>
       </c>
-      <c r="G85" s="49">
-        <v>4.87</v>
-      </c>
-      <c r="H85" s="49">
-        <f t="shared" si="0"/>
-        <v>4.87</v>
+      <c r="G85" s="44">
+        <v>6.58</v>
+      </c>
+      <c r="H85" s="44">
+        <f>IF((G85*F85)=0,"",G85*F85)</f>
+        <v>6.58</v>
       </c>
       <c r="I85" s="34"/>
       <c r="J85" s="147" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="K85" s="138" t="s">
-        <v>307</v>
-      </c>
-      <c r="L85" s="47">
-        <v>1.2</v>
-      </c>
-      <c r="M85" s="48" t="s">
+      <c r="K85" s="142"/>
+      <c r="L85" s="41"/>
+      <c r="M85" s="42"/>
+      <c r="N85" s="11"/>
+      <c r="O85" s="43"/>
+      <c r="P85" s="69" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q85" s="67">
+        <f>SUM(Q82:Q84)</f>
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="45" t="s">
+        <v>285</v>
+      </c>
+      <c r="B86" s="40"/>
+      <c r="C86" s="41"/>
+      <c r="D86" s="42"/>
+      <c r="E86" s="11"/>
+      <c r="F86" s="43"/>
+      <c r="G86" s="69" t="s">
+        <v>65</v>
+      </c>
+      <c r="H86" s="67">
+        <f>SUM(H83:H85)</f>
+        <v>26.32</v>
+      </c>
+      <c r="I86" s="34"/>
+      <c r="J86" s="146" t="str">
+        <f t="shared" si="9"/>
+        <v>Shock Cord</v>
+      </c>
+      <c r="K86" s="138" t="s">
+        <v>306</v>
+      </c>
+      <c r="L86" s="47">
+        <v>1.9</v>
+      </c>
+      <c r="M86" s="48" t="s">
         <v>326</v>
       </c>
-      <c r="N85" s="8"/>
-      <c r="O85" s="7">
+      <c r="N86" s="8"/>
+      <c r="O86" s="7">
         <v>1</v>
       </c>
-      <c r="P85" s="49">
+      <c r="P86" s="49">
         <v>5.75</v>
       </c>
-      <c r="Q85" s="49">
+      <c r="Q86" s="49">
         <f t="shared" si="3"/>
         <v>5.75</v>
       </c>
     </row>
-    <row r="86" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="10"/>
-      <c r="B86" s="54" t="s">
-        <v>368</v>
-      </c>
-      <c r="C86" s="57">
-        <v>4.7</v>
-      </c>
-      <c r="D86" s="58" t="s">
-        <v>321</v>
-      </c>
-      <c r="E86" s="13"/>
-      <c r="F86" s="10"/>
-      <c r="G86" s="59">
-        <v>1.61</v>
-      </c>
-      <c r="H86" s="59" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I86" s="34"/>
-      <c r="J86" s="147" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K86" s="117" t="s">
-        <v>370</v>
-      </c>
-      <c r="L86" s="57">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A87" s="7"/>
+      <c r="B87" s="46" t="s">
+        <v>306</v>
+      </c>
+      <c r="C87" s="47">
         <v>1.9</v>
       </c>
-      <c r="M86" s="58" t="s">
-        <v>325</v>
-      </c>
-      <c r="N86" s="13"/>
-      <c r="O86" s="10"/>
-      <c r="P86" s="59">
-        <v>2.5</v>
-      </c>
-      <c r="Q86" s="59" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="87" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="B87" s="54"/>
-      <c r="C87" s="57"/>
-      <c r="D87" s="58"/>
-      <c r="E87" s="13"/>
-      <c r="F87" s="10"/>
-      <c r="G87" s="64" t="s">
-        <v>65</v>
-      </c>
-      <c r="H87" s="68">
-        <f>SUM(H84:H86)</f>
-        <v>9.74</v>
+      <c r="D87" s="48" t="s">
+        <v>161</v>
+      </c>
+      <c r="E87" s="8"/>
+      <c r="F87" s="7">
+        <v>1</v>
+      </c>
+      <c r="G87" s="49">
+        <v>4.87</v>
+      </c>
+      <c r="H87" s="49">
+        <f>IF((G87*F87)=0,"",G87*F87)</f>
+        <v>4.87</v>
       </c>
       <c r="I87" s="34"/>
       <c r="J87" s="147" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="K87" s="117"/>
-      <c r="L87" s="57"/>
-      <c r="M87" s="58"/>
-      <c r="N87" s="13"/>
-      <c r="O87" s="10"/>
-      <c r="P87" s="64" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q87" s="68">
-        <f>SUM(Q84:Q86)</f>
-        <v>11.5</v>
-      </c>
-    </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A88" s="5" t="s">
-        <v>360</v>
-      </c>
-      <c r="B88" s="38" t="s">
-        <v>480</v>
-      </c>
-      <c r="C88" s="20">
-        <v>0.49</v>
-      </c>
-      <c r="D88" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="E88" s="36">
-        <f>C88*((58*72)/(36*36))</f>
-        <v>1.578888888888889</v>
-      </c>
-      <c r="F88" s="33"/>
-      <c r="G88" s="35">
-        <v>14.32</v>
-      </c>
-      <c r="H88" s="59" t="str">
+      <c r="K87" s="138" t="s">
+        <v>307</v>
+      </c>
+      <c r="L87" s="47">
+        <v>1.2</v>
+      </c>
+      <c r="M87" s="48" t="s">
+        <v>326</v>
+      </c>
+      <c r="N87" s="8"/>
+      <c r="O87" s="7">
+        <v>1</v>
+      </c>
+      <c r="P87" s="49">
+        <v>5.75</v>
+      </c>
+      <c r="Q87" s="49">
+        <f t="shared" si="3"/>
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="10"/>
+      <c r="B88" s="46" t="s">
+        <v>307</v>
+      </c>
+      <c r="C88" s="47">
+        <v>1.2</v>
+      </c>
+      <c r="D88" s="48" t="s">
+        <v>161</v>
+      </c>
+      <c r="E88" s="8"/>
+      <c r="F88" s="7">
+        <v>1</v>
+      </c>
+      <c r="G88" s="49">
+        <v>4.87</v>
+      </c>
+      <c r="H88" s="49">
         <f>IF((G88*F88)=0,"",G88*F88)</f>
-        <v/>
+        <v>4.87</v>
       </c>
       <c r="I88" s="34"/>
       <c r="J88" s="147" t="str">
         <f t="shared" si="9"/>
-        <v>Sleeping Bag Liner</v>
-      </c>
-      <c r="P88" s="33"/>
+        <v/>
+      </c>
+      <c r="K88" s="117" t="s">
+        <v>370</v>
+      </c>
+      <c r="L88" s="57">
+        <v>1.9</v>
+      </c>
+      <c r="M88" s="58" t="s">
+        <v>325</v>
+      </c>
+      <c r="N88" s="13"/>
+      <c r="O88" s="10"/>
+      <c r="P88" s="59">
+        <v>2.5</v>
+      </c>
       <c r="Q88" s="59" t="str">
-        <f t="shared" ref="Q88:Q105" si="10">IF((P88*O88)=0,"",P88*O88)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A89" s="5"/>
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="89" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="10"/>
       <c r="B89" s="54" t="s">
-        <v>479</v>
-      </c>
-      <c r="C89" s="20">
-        <v>0.67</v>
-      </c>
-      <c r="D89" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="E89" s="36">
-        <f>C89*((58*72)/(36*36))</f>
-        <v>2.1588888888888893</v>
-      </c>
-      <c r="F89" s="33">
-        <v>2</v>
-      </c>
-      <c r="G89" s="35">
-        <v>11.45</v>
-      </c>
-      <c r="H89" s="59">
+        <v>368</v>
+      </c>
+      <c r="C89" s="57">
+        <v>4.7</v>
+      </c>
+      <c r="D89" s="58" t="s">
+        <v>321</v>
+      </c>
+      <c r="E89" s="13"/>
+      <c r="F89" s="10"/>
+      <c r="G89" s="59">
+        <v>1.61</v>
+      </c>
+      <c r="H89" s="59" t="str">
         <f>IF((G89*F89)=0,"",G89*F89)</f>
-        <v>22.9</v>
+        <v/>
       </c>
       <c r="I89" s="34"/>
       <c r="J89" s="147" t="str">
         <f t="shared" si="9"/>
-        <v>58 x 72</v>
-      </c>
-      <c r="K89" s="66" t="s">
-        <v>291</v>
-      </c>
-      <c r="L89" s="20">
-        <v>0.66</v>
-      </c>
-      <c r="M89" s="21" t="s">
+        <v/>
+      </c>
+      <c r="K89" s="117"/>
+      <c r="L89" s="57"/>
+      <c r="M89" s="58"/>
+      <c r="N89" s="13"/>
+      <c r="O89" s="10"/>
+      <c r="P89" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q89" s="68">
+        <f>SUM(Q86:Q88)</f>
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="B90" s="54"/>
+      <c r="C90" s="57"/>
+      <c r="D90" s="58"/>
+      <c r="E90" s="13"/>
+      <c r="F90" s="10"/>
+      <c r="G90" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="H90" s="68">
+        <f>SUM(H87:H89)</f>
+        <v>9.74</v>
+      </c>
+      <c r="I90" s="34"/>
+      <c r="J90" s="146" t="str">
+        <f t="shared" si="9"/>
+        <v>Sleeping Bag Liner</v>
+      </c>
+      <c r="K90" s="117"/>
+      <c r="L90" s="57"/>
+      <c r="M90" s="58"/>
+      <c r="N90" s="13"/>
+      <c r="O90" s="10"/>
+      <c r="P90" s="64"/>
+      <c r="Q90" s="145"/>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A91" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="B91" s="38" t="s">
+        <v>478</v>
+      </c>
+      <c r="C91" s="20">
+        <v>0.49</v>
+      </c>
+      <c r="D91" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="N89" s="36">
-        <f>L89*$A$5</f>
-        <v>2.145</v>
-      </c>
-      <c r="O89" s="33">
-        <v>2</v>
-      </c>
-      <c r="P89" s="35">
-        <v>12.75</v>
-      </c>
-      <c r="Q89" s="59">
-        <f t="shared" si="10"/>
-        <v>25.5</v>
-      </c>
-    </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A90" s="5"/>
-      <c r="B90" s="38" t="s">
-        <v>478</v>
-      </c>
-      <c r="C90" s="20">
-        <v>0.9</v>
-      </c>
-      <c r="D90" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="E90" s="36">
-        <f>C90*((58*72)/(36*36))</f>
-        <v>2.9000000000000004</v>
-      </c>
-      <c r="F90" s="33"/>
-      <c r="G90" s="35">
-        <v>8.59</v>
-      </c>
-      <c r="H90" s="59" t="str">
-        <f>IF((G90*F90)=0,"",G90*F90)</f>
-        <v/>
-      </c>
-      <c r="I90" s="34"/>
-      <c r="J90" s="147" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="P90" s="33"/>
-      <c r="Q90" s="59" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="91" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="5"/>
-      <c r="B91" s="38" t="s">
-        <v>332</v>
-      </c>
-      <c r="C91" s="20"/>
-      <c r="D91" s="21"/>
-      <c r="E91" s="36"/>
-      <c r="F91" s="33">
-        <v>1</v>
-      </c>
+      <c r="E91" s="36">
+        <f>C91*((58*72)/(36*36))</f>
+        <v>1.578888888888889</v>
+      </c>
+      <c r="F91" s="33"/>
       <c r="G91" s="35">
-        <v>3.96</v>
-      </c>
-      <c r="H91" s="59">
+        <v>14.32</v>
+      </c>
+      <c r="H91" s="59" t="str">
         <f>IF((G91*F91)=0,"",G91*F91)</f>
-        <v>3.96</v>
+        <v/>
       </c>
       <c r="I91" s="34"/>
       <c r="J91" s="147" t="str">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K91" t="s">
-        <v>332</v>
-      </c>
-      <c r="O91">
-        <v>1</v>
-      </c>
-      <c r="P91" s="33">
-        <v>4.5</v>
-      </c>
-      <c r="Q91" s="59">
-        <f t="shared" si="10"/>
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="92" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="5" t="s">
-        <v>361</v>
-      </c>
-      <c r="B92" s="38"/>
-      <c r="C92" s="20"/>
-      <c r="D92" s="21"/>
-      <c r="E92" s="36"/>
-      <c r="F92" s="33"/>
-      <c r="G92" s="64" t="s">
-        <v>65</v>
-      </c>
-      <c r="H92" s="68">
-        <f>SUM(H88:H91)</f>
-        <v>26.86</v>
+        <v>58 x 72</v>
+      </c>
+      <c r="P91" s="33"/>
+      <c r="Q91" s="59" t="str">
+        <f t="shared" ref="Q91:Q108" si="10">IF((P91*O91)=0,"",P91*O91)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A92" s="5"/>
+      <c r="B92" s="54" t="s">
+        <v>477</v>
+      </c>
+      <c r="C92" s="20">
+        <v>0.67</v>
+      </c>
+      <c r="D92" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E92" s="36">
+        <f>C92*((58*72)/(36*36))</f>
+        <v>2.1588888888888893</v>
+      </c>
+      <c r="F92" s="33">
+        <v>2</v>
+      </c>
+      <c r="G92" s="35">
+        <v>11.45</v>
+      </c>
+      <c r="H92" s="59">
+        <f>IF((G92*F92)=0,"",G92*F92)</f>
+        <v>22.9</v>
       </c>
       <c r="I92" s="34"/>
       <c r="J92" s="147" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="P92" s="64" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q92" s="68">
-        <f>SUM(Q88:Q91)</f>
-        <v>30</v>
+      <c r="K92" s="66" t="s">
+        <v>291</v>
+      </c>
+      <c r="L92" s="20">
+        <v>0.66</v>
+      </c>
+      <c r="M92" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="N92" s="36">
+        <f>L92*$A$5</f>
+        <v>2.145</v>
+      </c>
+      <c r="O92" s="33">
+        <v>2</v>
+      </c>
+      <c r="P92" s="35">
+        <v>12.75</v>
+      </c>
+      <c r="Q92" s="59">
+        <f t="shared" si="10"/>
+        <v>25.5</v>
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" s="5"/>
       <c r="B93" s="38" t="s">
-        <v>405</v>
+        <v>476</v>
       </c>
       <c r="C93" s="20">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="D93" s="21" t="s">
         <v>159</v>
       </c>
       <c r="E93" s="36">
-        <f>C93*((12.5*22)/(36*36))</f>
-        <v>0.2758487654320988</v>
+        <f>C93*((58*72)/(36*36))</f>
+        <v>2.9000000000000004</v>
       </c>
       <c r="F93" s="33"/>
       <c r="G93" s="35">
-        <v>20.6</v>
+        <v>8.59</v>
       </c>
       <c r="H93" s="59" t="str">
         <f>IF((G93*F93)=0,"",G93*F93)</f>
@@ -8927,124 +8946,155 @@
       <c r="I93" s="34"/>
       <c r="J93" s="147" t="str">
         <f t="shared" si="9"/>
-        <v>Food Bag (12.5 x 22)</v>
-      </c>
-      <c r="K93" s="66" t="s">
-        <v>406</v>
-      </c>
-      <c r="L93" s="20">
-        <v>1.43</v>
-      </c>
-      <c r="M93" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="N93" s="36">
-        <f>L93*((12.5*22)/(36*36))</f>
-        <v>0.30343364197530864</v>
-      </c>
-      <c r="O93" s="33">
-        <v>1</v>
-      </c>
-      <c r="P93" s="35">
-        <v>27</v>
-      </c>
-      <c r="Q93" s="59">
+        <v/>
+      </c>
+      <c r="P93" s="33"/>
+      <c r="Q93" s="59" t="str">
         <f t="shared" si="10"/>
-        <v>27</v>
-      </c>
-    </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+        <v/>
+      </c>
+    </row>
+    <row r="94" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="5"/>
       <c r="B94" s="38" t="s">
-        <v>369</v>
-      </c>
-      <c r="C94" s="20">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="D94" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="E94" s="36">
-        <f>C94*((12.5*22)/(36*36))</f>
-        <v>0.2334104938271605</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="C94" s="20"/>
+      <c r="D94" s="21"/>
+      <c r="E94" s="36"/>
       <c r="F94" s="33">
         <v>1</v>
       </c>
       <c r="G94" s="35">
-        <v>7.45</v>
+        <v>3.96</v>
       </c>
       <c r="H94" s="59">
         <f>IF((G94*F94)=0,"",G94*F94)</f>
-        <v>7.45</v>
+        <v>3.96</v>
       </c>
       <c r="I94" s="34"/>
       <c r="J94" s="147" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="P94" s="35"/>
-      <c r="Q94" s="59" t="str">
+      <c r="K94" t="s">
+        <v>332</v>
+      </c>
+      <c r="O94">
+        <v>1</v>
+      </c>
+      <c r="P94" s="33">
+        <v>4.5</v>
+      </c>
+      <c r="Q94" s="59">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A95" s="5"/>
-      <c r="B95" s="38" t="s">
-        <v>503</v>
-      </c>
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="B95" s="38"/>
       <c r="C95" s="20"/>
       <c r="D95" s="21"/>
       <c r="E95" s="36"/>
       <c r="F95" s="33"/>
-      <c r="G95" s="35"/>
-      <c r="H95" s="59"/>
+      <c r="G95" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="H95" s="68">
+        <f>SUM(H91:H94)</f>
+        <v>26.86</v>
+      </c>
       <c r="I95" s="34"/>
-      <c r="J95" s="147" t="str">
+      <c r="J95" s="146" t="str">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="P95" s="35"/>
-      <c r="Q95" s="59"/>
-    </row>
-    <row r="96" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>Food Bag (12.5 x 22)</v>
+      </c>
+      <c r="P95" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q95" s="68">
+        <f>SUM(Q91:Q94)</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" s="5"/>
       <c r="B96" s="38" t="s">
-        <v>282</v>
+        <v>404</v>
       </c>
       <c r="C96" s="20">
-        <v>15.1</v>
+        <v>1.3</v>
       </c>
       <c r="D96" s="21" t="s">
-        <v>161</v>
-      </c>
-      <c r="E96" s="36"/>
+        <v>159</v>
+      </c>
+      <c r="E96" s="36">
+        <f>C96*((12.5*22)/(36*36))</f>
+        <v>0.2758487654320988</v>
+      </c>
       <c r="F96" s="33"/>
       <c r="G96" s="35">
-        <v>0.8</v>
-      </c>
-      <c r="H96" s="59"/>
+        <v>20.6</v>
+      </c>
+      <c r="H96" s="59" t="str">
+        <f>IF((G96*F96)=0,"",G96*F96)</f>
+        <v/>
+      </c>
       <c r="I96" s="34"/>
       <c r="J96" s="147" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="P96" s="35"/>
-      <c r="Q96" s="59"/>
-    </row>
-    <row r="97" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K96" s="66" t="s">
+        <v>405</v>
+      </c>
+      <c r="L96" s="20">
+        <v>1.43</v>
+      </c>
+      <c r="M96" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="N96" s="36">
+        <f>L96*((12.5*22)/(36*36))</f>
+        <v>0.30343364197530864</v>
+      </c>
+      <c r="O96" s="33">
+        <v>1</v>
+      </c>
+      <c r="P96" s="35">
+        <v>27</v>
+      </c>
+      <c r="Q96" s="59">
+        <f t="shared" si="10"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" s="5"/>
-      <c r="B97" s="38"/>
-      <c r="C97" s="20"/>
-      <c r="D97" s="21"/>
-      <c r="E97" s="36"/>
-      <c r="F97" s="33"/>
-      <c r="G97" s="64" t="s">
-        <v>65</v>
-      </c>
-      <c r="H97" s="68">
-        <f>SUM(H93:H94)</f>
+      <c r="B97" s="38" t="s">
+        <v>369</v>
+      </c>
+      <c r="C97" s="20">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D97" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E97" s="36">
+        <f>C97*((12.5*22)/(36*36))</f>
+        <v>0.2334104938271605</v>
+      </c>
+      <c r="F97" s="33">
+        <v>1</v>
+      </c>
+      <c r="G97" s="35">
+        <v>7.45</v>
+      </c>
+      <c r="H97" s="59">
+        <f>IF((G97*F97)=0,"",G97*F97)</f>
         <v>7.45</v>
       </c>
       <c r="I97" s="34"/>
@@ -9052,368 +9102,376 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="P97" s="64" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q97" s="68">
-        <f>SUM(Q93:Q94)</f>
-        <v>27</v>
+      <c r="P97" s="35"/>
+      <c r="Q97" s="59" t="str">
+        <f t="shared" si="10"/>
+        <v/>
       </c>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" s="5"/>
-      <c r="B98" s="38"/>
+      <c r="B98" s="38" t="s">
+        <v>501</v>
+      </c>
       <c r="C98" s="20"/>
       <c r="D98" s="21"/>
       <c r="E98" s="36"/>
       <c r="F98" s="33"/>
-      <c r="G98" s="64"/>
-      <c r="H98" s="145"/>
+      <c r="G98" s="35"/>
+      <c r="H98" s="59"/>
       <c r="I98" s="34"/>
-      <c r="J98" s="147"/>
-      <c r="P98" s="64"/>
-      <c r="Q98" s="145"/>
-    </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A99" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="B99" s="38"/>
-      <c r="C99" s="20"/>
-      <c r="D99" s="21"/>
+      <c r="J98" s="147" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="P98" s="35"/>
+      <c r="Q98" s="59"/>
+    </row>
+    <row r="99" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="5"/>
+      <c r="B99" s="38" t="s">
+        <v>282</v>
+      </c>
+      <c r="C99" s="20">
+        <v>15.1</v>
+      </c>
+      <c r="D99" s="21" t="s">
+        <v>161</v>
+      </c>
       <c r="E99" s="36"/>
       <c r="F99" s="33"/>
-      <c r="G99" s="64"/>
-      <c r="H99" s="145"/>
+      <c r="G99" s="35">
+        <v>0.8</v>
+      </c>
+      <c r="H99" s="59"/>
       <c r="I99" s="34"/>
-      <c r="J99" s="147"/>
-      <c r="P99" s="64"/>
-      <c r="Q99" s="145"/>
-    </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A100" s="128" t="s">
-        <v>426</v>
-      </c>
-      <c r="B100" s="38" t="s">
-        <v>357</v>
-      </c>
-      <c r="C100" s="20">
-        <v>0.51</v>
-      </c>
-      <c r="D100" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="E100" s="36">
-        <f>C100*((36*56)/(36*36))</f>
-        <v>0.79333333333333333</v>
-      </c>
+      <c r="J99" s="147" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="P99" s="35"/>
+      <c r="Q99" s="59"/>
+    </row>
+    <row r="100" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="5"/>
+      <c r="B100" s="38"/>
+      <c r="C100" s="20"/>
+      <c r="D100" s="21"/>
+      <c r="E100" s="36"/>
       <c r="F100" s="33"/>
-      <c r="G100" s="35">
-        <v>20.6</v>
-      </c>
-      <c r="H100" s="59" t="str">
-        <f>IF((G100*F100)=0,"",G100*F100)</f>
-        <v/>
+      <c r="G100" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="H100" s="68">
+        <f>SUM(H96:H97)</f>
+        <v>7.45</v>
       </c>
       <c r="I100" s="34"/>
-      <c r="J100" s="146" t="str">
-        <f t="shared" ref="J100:J109" si="11">IF(ISBLANK(A99),"",A99)</f>
-        <v>Rain Kilt (30L x 48W)</v>
-      </c>
-      <c r="K100" s="66" t="s">
-        <v>357</v>
-      </c>
-      <c r="L100" s="20">
-        <v>0.51</v>
-      </c>
-      <c r="M100" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="N100" s="36">
-        <f>L100*((36*56)/(36*36))</f>
-        <v>0.79333333333333333</v>
-      </c>
-      <c r="O100" s="33">
-        <v>2</v>
-      </c>
-      <c r="P100" s="35">
-        <v>20.5</v>
-      </c>
-      <c r="Q100" s="59">
-        <f t="shared" si="10"/>
-        <v>41</v>
+      <c r="J100" s="147" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="P100" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q100" s="68">
+        <f>SUM(Q96:Q97)</f>
+        <v>27</v>
       </c>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" s="5"/>
-      <c r="B101" s="38" t="s">
-        <v>369</v>
-      </c>
-      <c r="C101" s="20">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="D101" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="E101" s="36">
-        <f>C101*((36*56)/(36*36))</f>
-        <v>1.7111111111111112</v>
-      </c>
-      <c r="F101" s="33">
-        <v>1</v>
-      </c>
-      <c r="G101" s="35">
-        <v>7.45</v>
-      </c>
-      <c r="H101" s="59">
-        <f>IF((G101*F101)=0,"",G101*F101)</f>
-        <v>7.45</v>
-      </c>
+      <c r="B101" s="38"/>
+      <c r="C101" s="20"/>
+      <c r="D101" s="21"/>
+      <c r="E101" s="36"/>
+      <c r="F101" s="33"/>
+      <c r="G101" s="64"/>
+      <c r="H101" s="145"/>
       <c r="I101" s="34"/>
       <c r="J101" s="147" t="str">
-        <f t="shared" si="11"/>
-        <v>-OR- 36L x 56W</v>
-      </c>
-      <c r="P101" s="35"/>
-      <c r="Q101" s="59" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="P101" s="64"/>
+      <c r="Q101" s="145"/>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A102" s="5"/>
-      <c r="B102" s="38" t="s">
-        <v>389</v>
-      </c>
+      <c r="A102" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="B102" s="38"/>
       <c r="C102" s="20"/>
       <c r="D102" s="21"/>
       <c r="E102" s="36"/>
       <c r="F102" s="33"/>
-      <c r="G102" s="35"/>
-      <c r="H102" s="59"/>
+      <c r="G102" s="64"/>
+      <c r="H102" s="145"/>
       <c r="I102" s="34"/>
-      <c r="J102" s="147" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="P102" s="35"/>
-      <c r="Q102" s="59"/>
-    </row>
-    <row r="103" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="5"/>
+      <c r="J102" s="146" t="str">
+        <f t="shared" si="9"/>
+        <v>Rain Kilt (30L x 48W)</v>
+      </c>
+      <c r="P102" s="64"/>
+      <c r="Q102" s="145"/>
+    </row>
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A103" s="128" t="s">
+        <v>424</v>
+      </c>
       <c r="B103" s="38" t="s">
-        <v>395</v>
-      </c>
-      <c r="C103" s="20"/>
-      <c r="D103" s="21"/>
-      <c r="E103" s="36"/>
+        <v>357</v>
+      </c>
+      <c r="C103" s="20">
+        <v>0.51</v>
+      </c>
+      <c r="D103" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E103" s="36">
+        <f>C103*((36*56)/(36*36))</f>
+        <v>0.79333333333333333</v>
+      </c>
       <c r="F103" s="33"/>
-      <c r="G103" s="35"/>
-      <c r="H103" s="59"/>
+      <c r="G103" s="35">
+        <v>20.6</v>
+      </c>
+      <c r="H103" s="59" t="str">
+        <f>IF((G103*F103)=0,"",G103*F103)</f>
+        <v/>
+      </c>
       <c r="I103" s="34"/>
       <c r="J103" s="147" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="P103" s="35"/>
-      <c r="Q103" s="59"/>
-    </row>
-    <row r="104" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="5" t="s">
-        <v>356</v>
-      </c>
-      <c r="B104" s="38"/>
-      <c r="C104" s="20"/>
-      <c r="D104" s="21"/>
-      <c r="E104" s="36"/>
-      <c r="F104" s="33"/>
-      <c r="G104" s="64" t="s">
-        <v>65</v>
-      </c>
-      <c r="H104" s="68">
-        <f>SUM(H100:H101)</f>
+        <f t="shared" si="9"/>
+        <v>-OR- 36L x 56W</v>
+      </c>
+      <c r="K103" s="66" t="s">
+        <v>357</v>
+      </c>
+      <c r="L103" s="20">
+        <v>0.51</v>
+      </c>
+      <c r="M103" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="N103" s="36">
+        <f>L103*((36*56)/(36*36))</f>
+        <v>0.79333333333333333</v>
+      </c>
+      <c r="O103" s="33">
+        <v>2</v>
+      </c>
+      <c r="P103" s="35">
+        <v>20.5</v>
+      </c>
+      <c r="Q103" s="59">
+        <f t="shared" si="10"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A104" s="5"/>
+      <c r="B104" s="38" t="s">
+        <v>369</v>
+      </c>
+      <c r="C104" s="20">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D104" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E104" s="36">
+        <f>C104*((36*56)/(36*36))</f>
+        <v>1.7111111111111112</v>
+      </c>
+      <c r="F104" s="33">
+        <v>1</v>
+      </c>
+      <c r="G104" s="35">
+        <v>7.45</v>
+      </c>
+      <c r="H104" s="59">
+        <f>IF((G104*F104)=0,"",G104*F104)</f>
         <v>7.45</v>
       </c>
       <c r="I104" s="34"/>
       <c r="J104" s="147" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="P104" s="35"/>
-      <c r="Q104" s="59"/>
+      <c r="Q104" s="59" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A105" s="60" t="s">
-        <v>363</v>
-      </c>
+      <c r="A105" s="5"/>
       <c r="B105" s="38" t="s">
-        <v>369</v>
-      </c>
-      <c r="C105" s="20">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="D105" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="E105" s="36">
-        <f>C105*((72*54)/(36*36))</f>
-        <v>3.3000000000000003</v>
-      </c>
-      <c r="F105" s="33">
-        <v>2</v>
-      </c>
-      <c r="G105" s="35">
-        <v>7.45</v>
-      </c>
-      <c r="H105" s="59">
-        <f>IF((G105*F105)=0,"",G105*F105)</f>
-        <v>14.9</v>
-      </c>
+        <v>389</v>
+      </c>
+      <c r="C105" s="20"/>
+      <c r="D105" s="21"/>
+      <c r="E105" s="36"/>
+      <c r="F105" s="33"/>
+      <c r="G105" s="35"/>
+      <c r="H105" s="59"/>
       <c r="I105" s="34"/>
-      <c r="J105" s="146" t="str">
-        <f t="shared" si="11"/>
-        <v>Rain Pants</v>
-      </c>
-      <c r="K105" t="s">
-        <v>362</v>
-      </c>
-      <c r="N105" s="36">
-        <f>1.4*((72*54)/(36*36))</f>
-        <v>4.1999999999999993</v>
-      </c>
-      <c r="O105" s="33">
-        <v>2</v>
-      </c>
-      <c r="P105" s="35">
-        <v>20</v>
-      </c>
-      <c r="Q105" s="59">
-        <f t="shared" si="10"/>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A106" s="60"/>
+      <c r="J105" s="147" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="P105" s="35"/>
+      <c r="Q105" s="59"/>
+    </row>
+    <row r="106" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="5"/>
       <c r="B106" s="38" t="s">
-        <v>357</v>
-      </c>
-      <c r="C106" s="20">
-        <v>0.51</v>
-      </c>
-      <c r="D106" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="E106" s="36">
-        <f>C106*((30*48)/(36*36))</f>
-        <v>0.56666666666666665</v>
-      </c>
+        <v>395</v>
+      </c>
+      <c r="C106" s="20"/>
+      <c r="D106" s="21"/>
+      <c r="E106" s="36"/>
       <c r="F106" s="33"/>
-      <c r="G106" s="35">
-        <v>20.6</v>
-      </c>
-      <c r="H106" s="59" t="str">
-        <f>IF((G106*F106)=0,"",G106*F106)</f>
-        <v/>
-      </c>
+      <c r="G106" s="35"/>
+      <c r="H106" s="59"/>
       <c r="I106" s="34"/>
       <c r="J106" s="147" t="str">
-        <f t="shared" si="11"/>
-        <v>make pattern</v>
-      </c>
-      <c r="K106" s="66" t="s">
-        <v>357</v>
-      </c>
-      <c r="L106" s="20">
-        <v>0.51</v>
-      </c>
-      <c r="M106" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="N106" s="36">
-        <f>L106*((12.5*22)/(36*36))</f>
-        <v>0.10821759259259259</v>
-      </c>
-      <c r="O106" s="33"/>
-      <c r="P106" s="35">
-        <v>20.5</v>
-      </c>
-      <c r="Q106" s="59" t="str">
-        <f>IF((P106*O106)=0,"",P106*O106)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A107" s="60"/>
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="P106" s="35"/>
+      <c r="Q106" s="59"/>
+    </row>
+    <row r="107" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="5" t="s">
+        <v>356</v>
+      </c>
       <c r="B107" s="38"/>
       <c r="C107" s="20"/>
       <c r="D107" s="21"/>
       <c r="E107" s="36"/>
       <c r="F107" s="33"/>
-      <c r="G107" s="35"/>
-      <c r="H107" s="59"/>
+      <c r="G107" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="H107" s="68">
+        <f>SUM(H103:H104)</f>
+        <v>7.45</v>
+      </c>
       <c r="I107" s="34"/>
-      <c r="J107" s="147"/>
-      <c r="K107" s="66"/>
-      <c r="L107" s="20"/>
-      <c r="M107" s="21"/>
-      <c r="N107" s="36"/>
-      <c r="O107" s="33"/>
+      <c r="J107" s="146" t="str">
+        <f t="shared" si="9"/>
+        <v>Rain Pants</v>
+      </c>
       <c r="P107" s="35"/>
       <c r="Q107" s="59"/>
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A108" s="60"/>
-      <c r="B108" s="46" t="s">
-        <v>374</v>
-      </c>
-      <c r="C108" s="20"/>
-      <c r="D108" s="21"/>
-      <c r="E108" s="36"/>
-      <c r="F108" s="33"/>
-      <c r="G108" s="35"/>
-      <c r="H108" s="59"/>
+      <c r="A108" s="60" t="s">
+        <v>363</v>
+      </c>
+      <c r="B108" s="38" t="s">
+        <v>369</v>
+      </c>
+      <c r="C108" s="20">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D108" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E108" s="36">
+        <f>C108*((72*54)/(36*36))</f>
+        <v>3.3000000000000003</v>
+      </c>
+      <c r="F108" s="33">
+        <v>2</v>
+      </c>
+      <c r="G108" s="35">
+        <v>7.45</v>
+      </c>
+      <c r="H108" s="59">
+        <f>IF((G108*F108)=0,"",G108*F108)</f>
+        <v>14.9</v>
+      </c>
       <c r="I108" s="34"/>
       <c r="J108" s="147" t="str">
-        <f>IF(ISBLANK(A106),"",A106)</f>
-        <v/>
-      </c>
-      <c r="K108" s="66"/>
-      <c r="L108" s="20"/>
-      <c r="M108" s="21"/>
-      <c r="N108" s="36"/>
-      <c r="O108" s="33"/>
-      <c r="P108" s="35"/>
-      <c r="Q108" s="59"/>
+        <f t="shared" si="9"/>
+        <v>make pattern</v>
+      </c>
+      <c r="K108" t="s">
+        <v>362</v>
+      </c>
+      <c r="N108" s="36">
+        <f>1.4*((72*54)/(36*36))</f>
+        <v>4.1999999999999993</v>
+      </c>
+      <c r="O108" s="33">
+        <v>2</v>
+      </c>
+      <c r="P108" s="35">
+        <v>20</v>
+      </c>
+      <c r="Q108" s="59">
+        <f t="shared" si="10"/>
+        <v>40</v>
+      </c>
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" s="60"/>
-      <c r="B109" s="50" t="s">
-        <v>314</v>
-      </c>
-      <c r="C109" s="20"/>
-      <c r="D109" s="21"/>
-      <c r="E109" s="36"/>
+      <c r="B109" s="38" t="s">
+        <v>357</v>
+      </c>
+      <c r="C109" s="20">
+        <v>0.51</v>
+      </c>
+      <c r="D109" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E109" s="36">
+        <f>C109*((30*48)/(36*36))</f>
+        <v>0.56666666666666665</v>
+      </c>
       <c r="F109" s="33"/>
-      <c r="G109" s="35"/>
-      <c r="H109" s="59"/>
+      <c r="G109" s="35">
+        <v>20.6</v>
+      </c>
+      <c r="H109" s="59" t="str">
+        <f>IF((G109*F109)=0,"",G109*F109)</f>
+        <v/>
+      </c>
       <c r="I109" s="34"/>
       <c r="J109" s="147" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K109" s="66"/>
-      <c r="L109" s="20"/>
-      <c r="M109" s="21"/>
-      <c r="N109" s="36"/>
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="K109" s="66" t="s">
+        <v>357</v>
+      </c>
+      <c r="L109" s="20">
+        <v>0.51</v>
+      </c>
+      <c r="M109" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="N109" s="36">
+        <f>L109*((12.5*22)/(36*36))</f>
+        <v>0.10821759259259259</v>
+      </c>
       <c r="O109" s="33"/>
-      <c r="P109" s="35"/>
-      <c r="Q109" s="59"/>
+      <c r="P109" s="35">
+        <v>20.5</v>
+      </c>
+      <c r="Q109" s="59" t="str">
+        <f>IF((P109*O109)=0,"",P109*O109)</f>
+        <v/>
+      </c>
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A110" s="60"/>
-      <c r="B110" s="50" t="s">
-        <v>477</v>
-      </c>
+      <c r="A110" s="180" t="s">
+        <v>512</v>
+      </c>
+      <c r="B110" s="38"/>
       <c r="C110" s="20"/>
       <c r="D110" s="21"/>
       <c r="E110" s="36"/>
@@ -9421,7 +9479,10 @@
       <c r="G110" s="35"/>
       <c r="H110" s="59"/>
       <c r="I110" s="34"/>
-      <c r="J110" s="147"/>
+      <c r="J110" s="147" t="str">
+        <f t="shared" si="9"/>
+        <v>Extra Xenon make booties with 6oz climashield</v>
+      </c>
       <c r="K110" s="66"/>
       <c r="L110" s="20"/>
       <c r="M110" s="21"/>
@@ -9430,60 +9491,46 @@
       <c r="P110" s="35"/>
       <c r="Q110" s="59"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="60"/>
-      <c r="B111" s="38" t="s">
-        <v>332</v>
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A111" s="180" t="s">
+        <v>514</v>
+      </c>
+      <c r="B111" s="46" t="s">
+        <v>374</v>
       </c>
       <c r="C111" s="20"/>
       <c r="D111" s="21"/>
       <c r="E111" s="36"/>
       <c r="F111" s="33"/>
-      <c r="G111" s="35">
-        <v>3.96</v>
-      </c>
-      <c r="H111" s="59" t="str">
-        <f>IF((G111*F111)=0,"",G111*F111)</f>
-        <v/>
-      </c>
+      <c r="G111" s="35"/>
+      <c r="H111" s="59"/>
       <c r="I111" s="34"/>
       <c r="J111" s="147" t="str">
-        <f t="shared" ref="J111:J118" si="12">IF(ISBLANK(A110),"",A110)</f>
-        <v/>
-      </c>
-      <c r="K111" t="s">
-        <v>332</v>
-      </c>
-      <c r="O111">
-        <v>1</v>
-      </c>
-      <c r="P111" s="137">
-        <v>4.5</v>
-      </c>
-      <c r="Q111" s="59">
-        <f>IF((P111*O111)=0,"",P111*O111)</f>
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="112" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="18" t="s">
-        <v>364</v>
-      </c>
-      <c r="B112" s="38"/>
+        <f t="shared" si="9"/>
+        <v>see Dutch up booties</v>
+      </c>
+      <c r="K111" s="66"/>
+      <c r="L111" s="20"/>
+      <c r="M111" s="21"/>
+      <c r="N111" s="36"/>
+      <c r="O111" s="33"/>
+      <c r="P111" s="35"/>
+      <c r="Q111" s="59"/>
+    </row>
+    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A112" s="60"/>
+      <c r="B112" s="50" t="s">
+        <v>314</v>
+      </c>
       <c r="C112" s="20"/>
       <c r="D112" s="21"/>
       <c r="E112" s="36"/>
       <c r="F112" s="33"/>
-      <c r="G112" s="64" t="s">
-        <v>65</v>
-      </c>
-      <c r="H112" s="68">
-        <f>SUM(H105:H111)</f>
-        <v>14.9</v>
-      </c>
+      <c r="G112" s="35"/>
+      <c r="H112" s="59"/>
       <c r="I112" s="34"/>
       <c r="J112" s="147" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K112" s="66"/>
@@ -9491,20 +9538,13 @@
       <c r="M112" s="21"/>
       <c r="N112" s="36"/>
       <c r="O112" s="33"/>
-      <c r="P112" s="64" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q112" s="68">
-        <f>SUM(Q105:Q111)</f>
-        <v>44.5</v>
-      </c>
+      <c r="P112" s="35"/>
+      <c r="Q112" s="59"/>
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A113" s="18" t="s">
-        <v>287</v>
-      </c>
-      <c r="B113" s="38" t="s">
-        <v>365</v>
+      <c r="A113" s="60"/>
+      <c r="B113" s="50" t="s">
+        <v>475</v>
       </c>
       <c r="C113" s="20"/>
       <c r="D113" s="21"/>
@@ -9513,283 +9553,388 @@
       <c r="G113" s="35"/>
       <c r="H113" s="59"/>
       <c r="I113" s="34"/>
-      <c r="J113" s="146" t="str">
-        <f t="shared" si="12"/>
-        <v>Pack Cover (new pack)</v>
-      </c>
-      <c r="P113" s="33"/>
-      <c r="Q113" s="10"/>
-    </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A114" s="18" t="s">
-        <v>288</v>
-      </c>
-      <c r="B114" s="61" t="s">
-        <v>367</v>
+      <c r="J113" s="147" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="K113" s="66"/>
+      <c r="L113" s="20"/>
+      <c r="M113" s="21"/>
+      <c r="N113" s="36"/>
+      <c r="O113" s="33"/>
+      <c r="P113" s="35"/>
+      <c r="Q113" s="59"/>
+    </row>
+    <row r="114" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="60"/>
+      <c r="B114" s="38" t="s">
+        <v>332</v>
+      </c>
+      <c r="C114" s="20"/>
+      <c r="D114" s="21"/>
+      <c r="E114" s="36"/>
+      <c r="F114" s="33"/>
+      <c r="G114" s="35">
+        <v>3.96</v>
       </c>
       <c r="H114" s="59" t="str">
         <f>IF((G114*F114)=0,"",G114*F114)</f>
         <v/>
       </c>
       <c r="I114" s="34"/>
-      <c r="J114" s="146" t="str">
-        <f t="shared" si="12"/>
-        <v>Ditty Bags (See ToDo)</v>
-      </c>
-    </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B115" s="38" t="s">
+      <c r="J114" s="147" t="str">
+        <f>IF(ISBLANK(A115),"",A115)</f>
+        <v/>
+      </c>
+      <c r="K114" t="s">
+        <v>332</v>
+      </c>
+      <c r="O114">
+        <v>1</v>
+      </c>
+      <c r="P114" s="137">
+        <v>4.5</v>
+      </c>
+      <c r="Q114" s="59">
+        <f>IF((P114*O114)=0,"",P114*O114)</f>
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="115" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="60"/>
+      <c r="B115" s="38"/>
+      <c r="C115" s="20"/>
+      <c r="D115" s="21"/>
+      <c r="E115" s="36"/>
+      <c r="F115" s="33"/>
+      <c r="G115" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="H115" s="68">
+        <f>SUM(H108:H114)</f>
+        <v>14.9</v>
+      </c>
+      <c r="I115" s="34"/>
+      <c r="J115" s="147"/>
+      <c r="K115" s="66"/>
+      <c r="L115" s="20"/>
+      <c r="M115" s="21"/>
+      <c r="N115" s="36"/>
+      <c r="O115" s="33"/>
+      <c r="P115" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q115" s="68">
+        <f>SUM(Q108:Q114)</f>
+        <v>44.5</v>
+      </c>
+    </row>
+    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A116" s="18" t="s">
+        <v>364</v>
+      </c>
+      <c r="B116" s="38" t="s">
+        <v>365</v>
+      </c>
+      <c r="C116" s="20"/>
+      <c r="D116" s="21"/>
+      <c r="E116" s="36"/>
+      <c r="F116" s="33"/>
+      <c r="G116" s="35"/>
+      <c r="H116" s="59"/>
+      <c r="I116" s="34"/>
+      <c r="J116" s="147"/>
+      <c r="P116" s="33"/>
+      <c r="Q116" s="10"/>
+    </row>
+    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A117" s="18" t="s">
+        <v>287</v>
+      </c>
+      <c r="B117" s="61" t="s">
+        <v>367</v>
+      </c>
+      <c r="H117" s="59" t="str">
+        <f>IF((G117*F117)=0,"",G117*F117)</f>
+        <v/>
+      </c>
+      <c r="I117" s="34"/>
+      <c r="J117" s="147"/>
+    </row>
+    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A118" s="18" t="s">
+        <v>288</v>
+      </c>
+      <c r="B118" s="38" t="s">
         <v>366</v>
       </c>
-      <c r="H115" s="59" t="str">
-        <f>IF((G115*F115)=0,"",G115*F115)</f>
-        <v/>
-      </c>
-      <c r="I115" s="34"/>
-      <c r="J115" s="146" t="str">
-        <f t="shared" si="12"/>
-        <v>Kilt (Use ION)</v>
-      </c>
-    </row>
-    <row r="116" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="18" t="s">
-        <v>461</v>
-      </c>
-      <c r="B116" s="38"/>
-      <c r="H116" s="59" t="str">
-        <f>IF((G116*F116)=0,"",G116*F116)</f>
-        <v/>
-      </c>
-      <c r="I116" s="34"/>
-      <c r="J116" s="147" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="Q116" s="20"/>
-    </row>
-    <row r="117" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B117" s="54" t="s">
-        <v>447</v>
-      </c>
-      <c r="C117">
-        <f>C118*F122</f>
+      <c r="H118" s="59" t="str">
+        <f>IF((G118*F118)=0,"",G118*F118)</f>
+        <v/>
+      </c>
+      <c r="J118" s="147"/>
+    </row>
+    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A119" s="18" t="s">
+        <v>516</v>
+      </c>
+      <c r="B119" s="38"/>
+      <c r="H119" s="59"/>
+      <c r="J119" s="147"/>
+    </row>
+    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A120" s="18" t="s">
+        <v>517</v>
+      </c>
+      <c r="B120" s="38"/>
+      <c r="H120" s="59"/>
+      <c r="J120" s="147"/>
+    </row>
+    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A121" s="18" t="s">
+        <v>513</v>
+      </c>
+      <c r="B121" s="38"/>
+      <c r="H121" s="59"/>
+      <c r="J121" s="147"/>
+    </row>
+    <row r="122" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="18" t="s">
+        <v>515</v>
+      </c>
+      <c r="B122" s="38"/>
+      <c r="H122" s="59" t="str">
+        <f>IF((G122*F122)=0,"",G122*F122)</f>
+        <v/>
+      </c>
+      <c r="J122" s="147"/>
+      <c r="Q122" s="20"/>
+    </row>
+    <row r="123" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A123" s="18" t="s">
+        <v>459</v>
+      </c>
+      <c r="B123" s="54" t="s">
+        <v>445</v>
+      </c>
+      <c r="C123">
+        <f>C124*F128</f>
         <v>6.8078820000000002</v>
       </c>
-      <c r="D117" t="s">
+      <c r="D123" t="s">
         <v>159</v>
       </c>
-      <c r="E117" s="36">
-        <f>C117*((30*48)/(36*36))</f>
+      <c r="E123" s="36">
+        <f>C123*((30*48)/(36*36))</f>
         <v>7.5643133333333337</v>
       </c>
-      <c r="F117">
+      <c r="F123">
         <v>2</v>
       </c>
-      <c r="G117">
+      <c r="G123">
         <v>29</v>
       </c>
-      <c r="H117" s="59">
-        <f>IF((G117*F117)=0,"",G117*F117)</f>
+      <c r="H123" s="59">
+        <f>IF((G123*F123)=0,"",G123*F123)</f>
         <v>58</v>
       </c>
-      <c r="I117" s="34"/>
-      <c r="J117" s="146" t="str">
-        <f t="shared" si="12"/>
+      <c r="J123" s="146" t="str">
+        <f>IF(ISBLANK(A123),"",A123)</f>
         <v>Pullover/hoodie</v>
       </c>
-      <c r="K117" t="s">
-        <v>448</v>
-      </c>
-      <c r="L117">
+      <c r="K123" t="s">
+        <v>446</v>
+      </c>
+      <c r="L123">
         <v>4.8</v>
       </c>
-      <c r="M117" t="s">
+      <c r="M123" t="s">
         <v>159</v>
       </c>
-      <c r="N117" s="36">
+      <c r="N123" s="36">
         <f>1.4*((72*54)/(36*36))</f>
         <v>4.1999999999999993</v>
       </c>
-      <c r="O117" s="25">
+      <c r="O123" s="25">
         <v>2</v>
       </c>
-      <c r="P117" s="136">
+      <c r="P123" s="136">
         <v>27.25</v>
       </c>
-      <c r="Q117" s="68">
-        <f>IF((P117*O117)=0,"",P117*O117)</f>
+      <c r="Q123" s="68">
+        <f>IF((P123*O123)=0,"",P123*O123)</f>
         <v>54.5</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B118" s="54" t="s">
-        <v>450</v>
-      </c>
-      <c r="C118">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B124" s="54" t="s">
+        <v>448</v>
+      </c>
+      <c r="C124">
         <v>193</v>
       </c>
-      <c r="D118" t="s">
+      <c r="D124" t="s">
         <v>161</v>
       </c>
-      <c r="J118" s="143" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K118" t="s">
+      <c r="J124" s="143" t="str">
+        <f>IF(ISBLANK(A124),"",A124)</f>
+        <v/>
+      </c>
+      <c r="K124" t="s">
+        <v>447</v>
+      </c>
+      <c r="L124">
+        <v>135.62</v>
+      </c>
+      <c r="M124" t="s">
+        <v>161</v>
+      </c>
+      <c r="N124" s="36"/>
+    </row>
+    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B125" s="117">
+        <v>4004</v>
+      </c>
+      <c r="C125">
+        <v>119</v>
+      </c>
+      <c r="F125">
+        <v>2</v>
+      </c>
+      <c r="G125">
+        <v>28</v>
+      </c>
+      <c r="H125" s="59">
+        <f>IF((G125*F125)=0,"",G125*F125)</f>
+        <v>56</v>
+      </c>
+      <c r="K125" t="s">
         <v>449</v>
       </c>
-      <c r="L118">
-        <v>135.62</v>
-      </c>
-      <c r="M118" t="s">
+      <c r="P125" s="136">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A126" s="131" t="s">
+        <v>443</v>
+      </c>
+      <c r="K126" t="s">
+        <v>461</v>
+      </c>
+      <c r="L126">
+        <v>152.58000000000001</v>
+      </c>
+      <c r="M126" t="s">
         <v>161</v>
       </c>
-      <c r="N118" s="36"/>
-    </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A119" s="131" t="s">
-        <v>445</v>
-      </c>
-      <c r="B119" s="117">
-        <v>4004</v>
-      </c>
-      <c r="C119">
-        <v>119</v>
-      </c>
-      <c r="F119">
+    </row>
+    <row r="127" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A127" s="18" t="s">
+        <v>444</v>
+      </c>
+      <c r="L127">
+        <f>L126*F128</f>
+        <v>5.38210692</v>
+      </c>
+      <c r="M127" t="s">
+        <v>159</v>
+      </c>
+      <c r="O127">
         <v>2</v>
       </c>
-      <c r="G119">
-        <v>28</v>
-      </c>
-      <c r="H119" s="59">
-        <f>IF((G119*F119)=0,"",G119*F119)</f>
-        <v>56</v>
-      </c>
-      <c r="K119" t="s">
+      <c r="P127" s="136">
+        <v>31.5</v>
+      </c>
+      <c r="Q127" s="59">
+        <f>IF((P127*O127)=0,"",P127*O127)</f>
+        <v>63</v>
+      </c>
+    </row>
+    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="D128" s="132">
+        <v>1</v>
+      </c>
+      <c r="E128" s="79" t="s">
         <v>451</v>
       </c>
-      <c r="P119" s="136">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A120" s="18" t="s">
-        <v>446</v>
-      </c>
-      <c r="K120" t="s">
-        <v>463</v>
-      </c>
-      <c r="L120">
-        <v>152.58000000000001</v>
-      </c>
-      <c r="M120" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="121" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="L121">
-        <f>L120*F122</f>
-        <v>5.38210692</v>
-      </c>
-      <c r="M121" t="s">
+      <c r="F128" s="79">
+        <v>3.5274E-2</v>
+      </c>
+      <c r="G128" s="80" t="s">
         <v>159</v>
       </c>
-      <c r="O121">
+      <c r="K128" s="31" t="s">
+        <v>469</v>
+      </c>
+      <c r="O128">
         <v>2</v>
       </c>
-      <c r="P121" s="136">
-        <v>31.5</v>
-      </c>
-      <c r="Q121" s="59">
-        <f>IF((P121*O121)=0,"",P121*O121)</f>
-        <v>63</v>
-      </c>
-    </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="D122" s="132">
+      <c r="P128" s="136">
+        <v>26.25</v>
+      </c>
+      <c r="Q128" s="59">
+        <f>IF((P128*O128)=0,"",P128*O128)</f>
+        <v>52.5</v>
+      </c>
+    </row>
+    <row r="129" spans="4:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D129" s="133">
+        <v>28.349499999999999</v>
+      </c>
+      <c r="E129" s="134" t="s">
+        <v>451</v>
+      </c>
+      <c r="F129" s="134">
         <v>1</v>
       </c>
-      <c r="E122" s="79" t="s">
-        <v>453</v>
-      </c>
-      <c r="F122" s="79">
-        <v>3.5274E-2</v>
-      </c>
-      <c r="G122" s="80" t="s">
+      <c r="G129" s="135" t="s">
         <v>159</v>
       </c>
-      <c r="K122" s="31" t="s">
-        <v>471</v>
-      </c>
-      <c r="O122">
-        <v>2</v>
-      </c>
-      <c r="P122" s="136">
-        <v>26.25</v>
-      </c>
-      <c r="Q122" s="59">
-        <f>IF((P122*O122)=0,"",P122*O122)</f>
-        <v>52.5</v>
-      </c>
-    </row>
-    <row r="123" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D123" s="133">
-        <v>28.349499999999999</v>
-      </c>
-      <c r="E123" s="134" t="s">
-        <v>453</v>
-      </c>
-      <c r="F123" s="134">
-        <v>1</v>
-      </c>
-      <c r="G123" s="135" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="K124" s="165"/>
-      <c r="L124" s="66"/>
-      <c r="M124" s="66"/>
-      <c r="N124" s="158"/>
-      <c r="O124" s="66"/>
-      <c r="P124" s="66"/>
-    </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="K125" s="165"/>
-      <c r="L125" s="66"/>
-      <c r="M125" s="66"/>
-      <c r="N125" s="158"/>
-      <c r="O125" s="66"/>
-      <c r="P125" s="66"/>
-    </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="K126" s="165"/>
-      <c r="L126" s="66"/>
-      <c r="M126" s="66"/>
-      <c r="N126" s="158"/>
-      <c r="O126" s="66"/>
-      <c r="P126" s="66"/>
-    </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="K127" s="165"/>
-      <c r="L127" s="66"/>
-      <c r="M127" s="66"/>
-      <c r="N127" s="158"/>
-      <c r="O127" s="66"/>
-      <c r="P127" s="66"/>
-    </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="K128" s="165"/>
-      <c r="L128" s="66"/>
-      <c r="M128" s="66"/>
-      <c r="N128" s="158"/>
-      <c r="O128" s="66"/>
-      <c r="P128" s="66"/>
+    </row>
+    <row r="130" spans="4:16" x14ac:dyDescent="0.25">
+      <c r="K130" s="165"/>
+      <c r="L130" s="66"/>
+      <c r="M130" s="66"/>
+      <c r="N130" s="158"/>
+      <c r="O130" s="66"/>
+      <c r="P130" s="66"/>
+    </row>
+    <row r="131" spans="4:16" x14ac:dyDescent="0.25">
+      <c r="K131" s="165"/>
+      <c r="L131" s="66"/>
+      <c r="M131" s="66"/>
+      <c r="N131" s="158"/>
+      <c r="O131" s="66"/>
+      <c r="P131" s="66"/>
+    </row>
+    <row r="132" spans="4:16" x14ac:dyDescent="0.25">
+      <c r="K132" s="165"/>
+      <c r="L132" s="66"/>
+      <c r="M132" s="66"/>
+      <c r="N132" s="158"/>
+      <c r="O132" s="66"/>
+      <c r="P132" s="66"/>
+    </row>
+    <row r="133" spans="4:16" x14ac:dyDescent="0.25">
+      <c r="K133" s="165"/>
+      <c r="L133" s="66"/>
+      <c r="M133" s="66"/>
+      <c r="N133" s="158"/>
+      <c r="O133" s="66"/>
+      <c r="P133" s="66"/>
+    </row>
+    <row r="134" spans="4:16" x14ac:dyDescent="0.25">
+      <c r="K134" s="165"/>
+      <c r="L134" s="66"/>
+      <c r="M134" s="66"/>
+      <c r="N134" s="158"/>
+      <c r="O134" s="66"/>
+      <c r="P134" s="66"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B114" location="ToDo!A19" display="See ToDo" xr:uid="{CE28C4E6-45D1-4C5D-A0AF-3ACF169C0D5B}"/>
+    <hyperlink ref="B117" location="ToDo!A19" display="See ToDo" xr:uid="{CE28C4E6-45D1-4C5D-A0AF-3ACF169C0D5B}"/>
     <hyperlink ref="R31" location="Make!A81" display="L" xr:uid="{F2445477-C9B7-447F-944F-160D21ACEB18}"/>
     <hyperlink ref="R32" location="Make!A85" display="L" xr:uid="{D614D32D-E4C7-4ABC-8AEA-2A0D20F4C1EC}"/>
     <hyperlink ref="R27" location="Make!A90" display="L" xr:uid="{786E7206-F76A-4474-B631-F01E095CA8FB}"/>
@@ -9899,7 +10044,7 @@
         <v>258</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -9923,7 +10068,7 @@
         <v>259</v>
       </c>
       <c r="O5" s="20" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="P5">
         <v>32</v>
@@ -9956,13 +10101,13 @@
         <v>260</v>
       </c>
       <c r="O6" s="20" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="P6">
         <v>16</v>
       </c>
       <c r="Q6" s="20" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="R6">
         <v>8.1999999999999993</v>
@@ -9986,7 +10131,7 @@
         <v>261</v>
       </c>
       <c r="O7" s="20" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="P7">
         <v>44.8</v>
@@ -10001,7 +10146,7 @@
         <v>22</v>
       </c>
       <c r="T7" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -10023,7 +10168,7 @@
         <v>262</v>
       </c>
       <c r="O8" s="20" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="P8">
         <v>4.2</v>
@@ -10038,7 +10183,7 @@
         <v>20</v>
       </c>
       <c r="T8" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -10053,13 +10198,13 @@
         <v>263</v>
       </c>
       <c r="O9" s="20" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="P9">
         <v>4</v>
       </c>
       <c r="Q9" s="20" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="R9">
         <v>7.3</v>
@@ -10099,7 +10244,7 @@
       </c>
       <c r="O10" s="20"/>
       <c r="Q10" s="20" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="R10">
         <v>6</v>
@@ -10144,7 +10289,7 @@
         <v>5.9486955449999996</v>
       </c>
       <c r="Q11" s="20" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="R11">
         <v>6</v>
@@ -10221,7 +10366,7 @@
         <v>6</v>
       </c>
       <c r="Q13" s="20" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="R13">
         <f>INT(R12/16)</f>
@@ -10268,7 +10413,7 @@
         <v>5</v>
       </c>
       <c r="Q14" s="20" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="R14">
         <f>R12-(R13*16)</f>
@@ -10279,7 +10424,7 @@
         <v>7</v>
       </c>
       <c r="T14" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -10317,7 +10462,7 @@
         <v>0</v>
       </c>
       <c r="S15" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -10412,20 +10557,20 @@
         <v>14.192493900000001</v>
       </c>
       <c r="O18" s="153" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="P18" s="154">
         <v>60</v>
       </c>
       <c r="Q18" s="154" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="R18" s="155">
         <f>P18*2*$E$1*$U$23</f>
         <v>6.8196399999999997</v>
       </c>
       <c r="S18" s="154" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="T18" s="156"/>
     </row>
@@ -10452,20 +10597,20 @@
         <v>3.822222222222222</v>
       </c>
       <c r="O19" s="157" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="P19" s="66">
         <v>90</v>
       </c>
       <c r="Q19" s="66" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="R19" s="158">
         <f>P19*2*$E$1*$U$23</f>
         <v>10.22946</v>
       </c>
       <c r="S19" s="66" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="T19" s="159"/>
     </row>
@@ -10492,20 +10637,20 @@
         <v>0</v>
       </c>
       <c r="O20" s="157" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="P20" s="66">
         <v>120</v>
       </c>
       <c r="Q20" s="66" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="R20" s="158">
         <f>P20*2*$E$1*$U$23</f>
         <v>13.639279999999999</v>
       </c>
       <c r="S20" s="66" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="T20" s="159"/>
     </row>
@@ -10541,20 +10686,20 @@
         <v>0</v>
       </c>
       <c r="O21" s="157" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="P21" s="66">
         <v>150</v>
       </c>
       <c r="Q21" s="66" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="R21" s="158">
         <f>P21*2*$E$1*$U$23</f>
         <v>17.049099999999999</v>
       </c>
       <c r="S21" s="66" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="T21" s="159"/>
     </row>
@@ -10593,20 +10738,20 @@
         <v>0</v>
       </c>
       <c r="O22" s="160" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="P22" s="161">
         <v>190</v>
       </c>
       <c r="Q22" s="161" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="R22" s="162">
         <f>P22*2*$E$1*$U$23</f>
         <v>21.595526666666668</v>
       </c>
       <c r="S22" s="161" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="T22" s="163"/>
     </row>
@@ -10623,14 +10768,14 @@
         <v>0</v>
       </c>
       <c r="T23" s="168" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="U23">
         <f>(36*58)/(36*36)</f>
         <v>1.6111111111111112</v>
       </c>
       <c r="V23" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.25">

--- a/AT/Materials.xlsx
+++ b/AT/Materials.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wellspan-my.sharepoint.com/personal/dsmith14_wellspan_org/Documents/Documents/GitHub/dps/AT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="294" documentId="8_{C7F6FACF-983A-4174-A2EA-A87A6F163CFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24961F34-BEEA-4324-A685-883E5C5F1C51}"/>
+  <xr:revisionPtr revIDLastSave="56" documentId="13_ncr:1_{1DDBCB49-8FEC-4B57-AB8A-23D32742197E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A554B33-2EAE-4A87-8277-9920800F319B}"/>
   <bookViews>
-    <workbookView xWindow="1020" yWindow="465" windowWidth="26910" windowHeight="14100" activeTab="2" xr2:uid="{362FB22F-6BD6-431B-94C9-F0870D854534}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="26010" windowHeight="13875" activeTab="2" xr2:uid="{362FB22F-6BD6-431B-94C9-F0870D854534}"/>
   </bookViews>
   <sheets>
     <sheet name="Materials" sheetId="1" r:id="rId1"/>
     <sheet name="ToDo" sheetId="2" r:id="rId2"/>
     <sheet name="Make" sheetId="4" r:id="rId3"/>
     <sheet name="Notes" sheetId="3" r:id="rId4"/>
+    <sheet name="Dutch Thread colors" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -73,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="542">
   <si>
     <t>piping slide</t>
   </si>
@@ -1272,9 +1273,6 @@
     <t>1-3</t>
   </si>
   <si>
-    <t>Order 5</t>
-  </si>
-  <si>
     <t>mini plastic hook (3/32)</t>
   </si>
   <si>
@@ -1488,9 +1486,6 @@
     <t>L</t>
   </si>
   <si>
-    <t>Order 6</t>
-  </si>
-  <si>
     <t>36x58</t>
   </si>
   <si>
@@ -1627,6 +1622,84 @@
   </si>
   <si>
     <t>Compression stuff sack (Dutch web page)</t>
+  </si>
+  <si>
+    <t>Hexon 1.2 (Forest green)</t>
+  </si>
+  <si>
+    <t>Black</t>
+  </si>
+  <si>
+    <t>Salmon</t>
+  </si>
+  <si>
+    <t>Green</t>
+  </si>
+  <si>
+    <t>Yellow/Orange</t>
+  </si>
+  <si>
+    <t>Poppy Red</t>
+  </si>
+  <si>
+    <t>Brick Red</t>
+  </si>
+  <si>
+    <t>Navy Blue</t>
+  </si>
+  <si>
+    <t>Deep Blue</t>
+  </si>
+  <si>
+    <t>Lime Green</t>
+  </si>
+  <si>
+    <t>Bright Orange</t>
+  </si>
+  <si>
+    <t>Deep Purple</t>
+  </si>
+  <si>
+    <t>Dark Olive</t>
+  </si>
+  <si>
+    <t>Bright Yellow</t>
+  </si>
+  <si>
+    <t>Kevlar Yellow</t>
+  </si>
+  <si>
+    <t>Olive Green</t>
+  </si>
+  <si>
+    <t>Coyote Brown</t>
+  </si>
+  <si>
+    <t>Olive Brown</t>
+  </si>
+  <si>
+    <t>Charcoal Gray</t>
+  </si>
+  <si>
+    <t>Titanium Gray</t>
+  </si>
+  <si>
+    <t>Moss Green</t>
+  </si>
+  <si>
+    <t>Moroccan Blue</t>
+  </si>
+  <si>
+    <t>Burnt Orange</t>
+  </si>
+  <si>
+    <t>Dutchware Thread Colors</t>
+  </si>
+  <si>
+    <t>with above order</t>
+  </si>
+  <si>
+    <t>plus compression sack</t>
   </si>
 </sst>
 </file>
@@ -3793,7 +3866,7 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
@@ -4292,7 +4365,7 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F39" s="20"/>
       <c r="G39" t="s">
@@ -4602,7 +4675,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{458BE52D-397A-4267-A4EC-33DE3608C71C}">
-  <dimension ref="A1:AB134"/>
+  <dimension ref="A1:AB135"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.28515625" customWidth="1"/>
@@ -4803,7 +4876,7 @@
         <v>23.855</v>
       </c>
       <c r="U4" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.25">
@@ -4812,7 +4885,7 @@
         <v>3.25</v>
       </c>
       <c r="B5" s="38" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C5" s="20"/>
       <c r="D5" s="21"/>
@@ -4829,7 +4902,7 @@
         <v>3.25</v>
       </c>
       <c r="K5" s="66" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="L5" s="20"/>
       <c r="M5" s="21"/>
@@ -4846,15 +4919,15 @@
         <v>21.204444444444444</v>
       </c>
       <c r="U5" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B6" s="38" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C6" s="20"/>
       <c r="D6" s="21"/>
@@ -4871,7 +4944,7 @@
         <v>tapperd &amp; sewn waist down</v>
       </c>
       <c r="K6" s="66" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="L6" s="20"/>
       <c r="M6" s="21"/>
@@ -4887,15 +4960,15 @@
         <v>2.8162152777777778</v>
       </c>
       <c r="U6" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B7" s="38" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C7" s="20">
         <v>0.67</v>
@@ -4946,10 +5019,10 @@
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" s="20" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B8" s="38" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C8" s="20">
         <v>0.9</v>
@@ -5000,10 +5073,10 @@
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9" s="21" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B9" s="38" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C9" s="20">
         <v>0.93</v>
@@ -5076,7 +5149,7 @@
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A10" s="21" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B10" s="38" t="s">
         <v>331</v>
@@ -5201,7 +5274,7 @@
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A12" s="20" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B12" s="38" t="s">
         <v>297</v>
@@ -5461,7 +5534,7 @@
         <v>315</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C17" s="20">
         <v>0.67</v>
@@ -5529,7 +5602,7 @@
         <v>2.8888888888888888</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C18" s="20">
         <v>0.9</v>
@@ -5582,10 +5655,10 @@
     </row>
     <row r="19" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C19" s="20">
         <v>0.93</v>
@@ -5627,12 +5700,12 @@
         <v>4.5</v>
       </c>
       <c r="S19" s="107" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A20" s="20" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B20" s="38" t="s">
         <v>79</v>
@@ -5688,7 +5761,7 @@
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A21" s="20" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B21" s="38" t="s">
         <v>324</v>
@@ -5808,7 +5881,7 @@
     </row>
     <row r="23" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A23" s="20" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B23" s="38" t="s">
         <v>320</v>
@@ -5894,7 +5967,7 @@
         <v/>
       </c>
       <c r="R24" s="166" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="S24" s="91" t="str">
         <f>A39</f>
@@ -5902,7 +5975,7 @@
       </c>
       <c r="T24" s="92">
         <f>H45</f>
-        <v>43.59</v>
+        <v>40.22</v>
       </c>
       <c r="U24" s="93">
         <v>8</v>
@@ -5948,7 +6021,7 @@
         <v>5</v>
       </c>
       <c r="R25" s="166" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="S25" s="91" t="str">
         <f>A46</f>
@@ -5956,7 +6029,7 @@
       </c>
       <c r="T25" s="92">
         <f>H52</f>
-        <v>35.68</v>
+        <v>31.22</v>
       </c>
       <c r="U25" s="93">
         <v>9</v>
@@ -6006,7 +6079,7 @@
         <v>108.875</v>
       </c>
       <c r="R26" s="166" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="S26" s="96" t="str">
         <f>A53</f>
@@ -6020,7 +6093,7 @@
         <v>6</v>
       </c>
       <c r="V26" s="99" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="W26" s="100"/>
       <c r="X26" s="30"/>
@@ -6052,7 +6125,7 @@
       <c r="P27" s="64"/>
       <c r="Q27" s="144"/>
       <c r="R27" s="166" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="S27" s="101" t="str">
         <f>A90</f>
@@ -6107,7 +6180,7 @@
         <v>22.5</v>
       </c>
       <c r="R28" s="166" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="S28" s="120" t="str">
         <f>A95</f>
@@ -6115,7 +6188,7 @@
       </c>
       <c r="T28" s="121">
         <f>H100</f>
-        <v>7.45</v>
+        <v>6.71</v>
       </c>
       <c r="U28" s="122">
         <v>11</v>
@@ -6166,15 +6239,15 @@
         <v/>
       </c>
       <c r="R29" s="166" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="S29" s="120" t="str">
         <f>A102</f>
         <v>Rain Kilt (30L x 48W)</v>
       </c>
       <c r="T29" s="121">
-        <f>H107</f>
-        <v>7.45</v>
+        <f>H108</f>
+        <v>17.8</v>
       </c>
       <c r="U29" s="122">
         <v>12</v>
@@ -6234,14 +6307,14 @@
         <v>5.25</v>
       </c>
       <c r="R30" s="166" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="S30" s="101" t="str">
-        <f>A107</f>
+        <f>A108</f>
         <v>Rain Pants</v>
       </c>
       <c r="T30" s="102">
-        <f>H115</f>
+        <f>H116</f>
         <v>14.9</v>
       </c>
       <c r="U30" s="103">
@@ -6296,7 +6369,7 @@
         <v/>
       </c>
       <c r="R31" s="166" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="S31" s="86" t="str">
         <f>A82</f>
@@ -6350,7 +6423,7 @@
         <v/>
       </c>
       <c r="R32" s="166" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="S32" s="86" t="str">
         <f>A86</f>
@@ -6395,7 +6468,7 @@
         <v/>
       </c>
       <c r="K33" s="117" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="L33" s="20"/>
       <c r="M33" s="21"/>
@@ -6407,28 +6480,28 @@
         <v/>
       </c>
       <c r="R33" s="166" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="S33" s="149" t="str">
-        <f>A123</f>
+        <f>A124</f>
         <v>Pullover/hoodie</v>
       </c>
       <c r="T33" s="150">
-        <f>Q123</f>
+        <f>Q124</f>
         <v>54.5</v>
       </c>
       <c r="U33" s="151">
         <v>13</v>
       </c>
       <c r="V33" s="152" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="W33" s="106"/>
     </row>
     <row r="34" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="20"/>
       <c r="B34" s="52" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G34" s="35"/>
       <c r="H34" s="35" t="str">
@@ -6499,7 +6572,7 @@
       </c>
       <c r="T35" s="116">
         <f>SUM(T21:T33)</f>
-        <v>486.03999999999996</v>
+        <v>487.82</v>
       </c>
     </row>
     <row r="36" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6530,7 +6603,7 @@
         <v/>
       </c>
       <c r="K36" s="56" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="L36" s="20"/>
       <c r="M36" s="21"/>
@@ -6550,7 +6623,7 @@
     <row r="37" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="20"/>
       <c r="B37" s="38" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C37" s="20">
         <v>0.3</v>
@@ -6587,7 +6660,7 @@
         <v>43</v>
       </c>
       <c r="S37" s="169" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="T37" s="108">
         <f>T31+T32+T23</f>
@@ -6597,10 +6670,10 @@
         <v>398</v>
       </c>
       <c r="V37" s="31" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="W37" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="X37" s="30"/>
     </row>
@@ -6641,17 +6714,17 @@
         <v>30</v>
       </c>
       <c r="S38" s="170" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="T38" s="102">
         <f>T27+T30</f>
         <v>41.76</v>
       </c>
       <c r="U38" s="112" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="V38" s="31" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="W38" s="3">
         <v>129.33000000000001</v>
@@ -6682,25 +6755,25 @@
         <v/>
       </c>
       <c r="S39" s="110" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="T39" s="97">
         <f>T26+T33</f>
         <v>127.07</v>
       </c>
       <c r="U39" s="113" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="V39" s="25" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A40" s="20" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B40" s="38" t="s">
-        <v>334</v>
+        <v>516</v>
       </c>
       <c r="C40" s="20">
         <v>1.2</v>
@@ -6716,11 +6789,11 @@
         <v>4</v>
       </c>
       <c r="G40" s="35">
-        <v>7.45</v>
+        <v>6.71</v>
       </c>
       <c r="H40" s="35">
         <f t="shared" si="0"/>
-        <v>29.8</v>
+        <v>26.84</v>
       </c>
       <c r="I40" s="34"/>
       <c r="J40" s="147" t="str">
@@ -6752,10 +6825,10 @@
         <v>144.89000000000001</v>
       </c>
       <c r="U40" s="111" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="V40" s="173" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="W40" s="174">
         <f>H82</f>
@@ -6797,15 +6870,16 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="S41" s="110" t="s">
-        <v>399</v>
+      <c r="S41" s="110" t="str">
+        <f>"Dutch $"&amp;T41+T42</f>
+        <v>Dutch $95.95</v>
       </c>
       <c r="T41" s="92">
         <f>T25+T24</f>
-        <v>79.27000000000001</v>
+        <v>71.44</v>
       </c>
       <c r="U41" s="124" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="X41" s="30"/>
     </row>
@@ -6818,14 +6892,14 @@
       <c r="D42" s="21"/>
       <c r="E42" s="36"/>
       <c r="F42" s="33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G42" s="35">
         <v>4.87</v>
       </c>
-      <c r="H42" s="35">
+      <c r="H42" s="35" t="str">
         <f t="shared" si="0"/>
-        <v>4.87</v>
+        <v/>
       </c>
       <c r="I42" s="34"/>
       <c r="J42" s="147" t="str">
@@ -6834,14 +6908,14 @@
       </c>
       <c r="Q42" s="35"/>
       <c r="S42" s="114" t="s">
-        <v>471</v>
+        <v>540</v>
       </c>
       <c r="T42" s="118">
         <f>T28+T29</f>
-        <v>14.9</v>
+        <v>24.51</v>
       </c>
       <c r="U42" s="119" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="43" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6871,11 +6945,11 @@
       </c>
       <c r="Q43" s="35"/>
       <c r="S43" s="127"/>
-      <c r="T43" s="30"/>
-      <c r="U43" s="30">
-        <f>T40+W40</f>
-        <v>180.71</v>
-      </c>
+      <c r="T43" s="30">
+        <f>T41+T42</f>
+        <v>95.95</v>
+      </c>
+      <c r="U43" s="30"/>
     </row>
     <row r="44" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="37"/>
@@ -6888,16 +6962,19 @@
       <c r="D44" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="E44" s="36"/>
+      <c r="E44" s="36">
+        <f>C44*F44</f>
+        <v>2.0100000000000002</v>
+      </c>
       <c r="F44" s="33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G44" s="35">
         <v>4.46</v>
       </c>
       <c r="H44" s="35">
         <f t="shared" ref="H44" si="6">IF((G44*F44)=0,"",G44*F44)</f>
-        <v>8.92</v>
+        <v>13.379999999999999</v>
       </c>
       <c r="I44" s="34"/>
       <c r="J44" s="147" t="str">
@@ -6912,7 +6989,7 @@
         <v>35.25</v>
       </c>
       <c r="S44" s="167" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="T44" s="30"/>
     </row>
@@ -6927,7 +7004,7 @@
       </c>
       <c r="H45" s="63">
         <f>SUM(H40:H44)</f>
-        <v>43.59</v>
+        <v>40.22</v>
       </c>
       <c r="I45" s="34"/>
       <c r="J45" s="147" t="str">
@@ -6955,7 +7032,7 @@
         <v>38.5</v>
       </c>
       <c r="S45" s="20" t="str">
-        <f>A116</f>
+        <f>A117</f>
         <v>Pack Cover (new pack)</v>
       </c>
       <c r="T45" s="30"/>
@@ -6995,17 +7072,17 @@
         <v/>
       </c>
       <c r="S46" s="20" t="str">
-        <f>A117</f>
+        <f>A118</f>
         <v>Ditty Bags (See ToDo)</v>
       </c>
       <c r="T46" s="30"/>
     </row>
     <row r="47" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A47" s="20" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B47" s="38" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C47" s="20">
         <v>0.67</v>
@@ -7018,14 +7095,14 @@
         <v>5.9555555555555566</v>
       </c>
       <c r="F47" s="33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G47" s="35">
         <v>4.46</v>
       </c>
       <c r="H47" s="35">
         <f>IF((G47*F47)=0,"",G47*F47)</f>
-        <v>35.68</v>
+        <v>31.22</v>
       </c>
       <c r="I47" s="34"/>
       <c r="J47" s="147" t="str">
@@ -7053,7 +7130,7 @@
       </c>
       <c r="Q47" s="35"/>
       <c r="S47" s="20" t="str">
-        <f>A118</f>
+        <f>A119</f>
         <v>Kilt (Use ION)</v>
       </c>
       <c r="T47" s="30"/>
@@ -7099,13 +7176,13 @@
       <c r="P48" s="35"/>
       <c r="Q48" s="35"/>
       <c r="S48" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="T48" s="30"/>
     </row>
     <row r="49" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="20" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B49" s="38"/>
       <c r="H49" s="35" t="str">
@@ -7126,11 +7203,14 @@
       <c r="O49" s="33"/>
       <c r="P49" s="35"/>
       <c r="Q49" s="35"/>
+      <c r="S49" s="18" t="s">
+        <v>515</v>
+      </c>
       <c r="T49" s="30"/>
     </row>
     <row r="50" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="20" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B50" s="46" t="s">
         <v>372</v>
@@ -7161,11 +7241,14 @@
         <f>SUM(Q45:Q49)</f>
         <v>38.5</v>
       </c>
+      <c r="S50" s="18" t="s">
+        <v>511</v>
+      </c>
       <c r="T50" s="30"/>
     </row>
     <row r="51" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="42" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B51" s="50" t="s">
         <v>373</v>
@@ -7191,6 +7274,9 @@
       <c r="O51" s="33"/>
       <c r="P51" s="64"/>
       <c r="Q51" s="144"/>
+      <c r="S51" s="18" t="s">
+        <v>513</v>
+      </c>
       <c r="T51" s="30"/>
     </row>
     <row r="52" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7208,7 +7294,7 @@
       </c>
       <c r="H52" s="65">
         <f>SUM(H47:H51)</f>
-        <v>35.68</v>
+        <v>31.22</v>
       </c>
       <c r="I52" s="34"/>
       <c r="J52" s="146" t="str">
@@ -7216,7 +7302,7 @@
         <v>Back Pack</v>
       </c>
       <c r="K52" s="141" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="L52" s="20">
         <v>4.4000000000000004</v>
@@ -7234,6 +7320,9 @@
       <c r="Q52" s="35" t="str">
         <f t="shared" si="3"/>
         <v/>
+      </c>
+      <c r="S52" s="18" t="s">
+        <v>514</v>
       </c>
       <c r="T52" s="30"/>
     </row>
@@ -7254,7 +7343,7 @@
         <v>* Work on quantities</v>
       </c>
       <c r="K53" s="66" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="L53" s="20">
         <v>3.2</v>
@@ -7275,10 +7364,10 @@
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A54" s="60" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B54" s="38" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C54" s="20">
         <f>(4.85+5.85)/2</f>
@@ -7302,7 +7391,7 @@
         <v/>
       </c>
       <c r="K54" s="66" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="L54" s="20">
         <v>3.9</v>
@@ -7325,7 +7414,7 @@
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B55" s="38" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C55" s="20">
         <v>3.2</v>
@@ -7369,7 +7458,7 @@
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B56" s="38" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C56" s="20">
         <v>6.73</v>
@@ -7409,7 +7498,7 @@
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B57" s="38" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C57" s="20">
         <v>7.9</v>
@@ -7554,7 +7643,7 @@
         <v>7</v>
       </c>
       <c r="K60" s="66" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="L60" s="20">
         <v>2.6</v>
@@ -7577,7 +7666,7 @@
         <v>7</v>
       </c>
       <c r="B61" s="38" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C61" s="20">
         <v>1.7</v>
@@ -7596,7 +7685,7 @@
         <v/>
       </c>
       <c r="K61" s="66" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L61" s="20">
         <v>0.5</v>
@@ -7616,7 +7705,7 @@
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B62" s="38" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C62" s="20">
         <v>0.56000000000000005</v>
@@ -7662,7 +7751,7 @@
         <v>10</v>
       </c>
       <c r="B63" s="38" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C63" s="20">
         <v>0.42</v>
@@ -7712,7 +7801,7 @@
         <v>9</v>
       </c>
       <c r="B64" s="38" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C64" s="20"/>
       <c r="D64" s="21" t="s">
@@ -7747,7 +7836,7 @@
     </row>
     <row r="65" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B65" s="38" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C65" s="20">
         <v>3.96</v>
@@ -7768,7 +7857,7 @@
       </c>
       <c r="I65" s="34"/>
       <c r="J65" s="148" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K65" s="141" t="s">
         <v>339</v>
@@ -7791,10 +7880,10 @@
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A66" s="23" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B66" s="38" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C66" s="20">
         <v>1.1299999999999999</v>
@@ -7834,7 +7923,7 @@
         <v>339</v>
       </c>
       <c r="C67" s="125" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D67" s="125"/>
       <c r="E67" s="36"/>
@@ -7892,7 +7981,7 @@
       </c>
       <c r="I68" s="34"/>
       <c r="J68" s="147">
-        <f t="shared" ref="J68:J113" si="9">IF(ISBLANK(A68),"",A68)</f>
+        <f t="shared" ref="J68:J114" si="9">IF(ISBLANK(A68),"",A68)</f>
         <v>5</v>
       </c>
       <c r="K68" s="66" t="s">
@@ -7916,7 +8005,7 @@
     </row>
     <row r="69" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B69" s="38" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C69" s="20">
         <v>15.1</v>
@@ -7962,7 +8051,7 @@
         <v>9</v>
       </c>
       <c r="B70" s="38" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C70" s="20">
         <v>4.47</v>
@@ -8010,7 +8099,7 @@
         <v>8</v>
       </c>
       <c r="B71" s="50" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C71" s="20">
         <v>1.58</v>
@@ -8301,7 +8390,7 @@
     </row>
     <row r="78" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B78" s="52" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C78" s="20">
         <v>8</v>
@@ -8835,7 +8924,7 @@
         <v>360</v>
       </c>
       <c r="B91" s="38" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C91" s="20">
         <v>0.49</v>
@@ -8862,14 +8951,14 @@
       </c>
       <c r="P91" s="33"/>
       <c r="Q91" s="59" t="str">
-        <f t="shared" ref="Q91:Q108" si="10">IF((P91*O91)=0,"",P91*O91)</f>
+        <f t="shared" ref="Q91:Q109" si="10">IF((P91*O91)=0,"",P91*O91)</f>
         <v/>
       </c>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" s="5"/>
       <c r="B92" s="54" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C92" s="20">
         <v>0.67</v>
@@ -8923,7 +9012,7 @@
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" s="5"/>
       <c r="B93" s="38" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C93" s="20">
         <v>0.9</v>
@@ -9023,7 +9112,7 @@
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" s="5"/>
       <c r="B96" s="38" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C96" s="20">
         <v>1.3</v>
@@ -9049,7 +9138,7 @@
         <v/>
       </c>
       <c r="K96" s="66" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="L96" s="20">
         <v>1.43</v>
@@ -9091,11 +9180,11 @@
         <v>1</v>
       </c>
       <c r="G97" s="35">
-        <v>7.45</v>
+        <v>6.71</v>
       </c>
       <c r="H97" s="59">
         <f>IF((G97*F97)=0,"",G97*F97)</f>
-        <v>7.45</v>
+        <v>6.71</v>
       </c>
       <c r="I97" s="34"/>
       <c r="J97" s="147" t="str">
@@ -9111,7 +9200,7 @@
     <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" s="5"/>
       <c r="B98" s="38" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C98" s="20"/>
       <c r="D98" s="21"/>
@@ -9164,7 +9253,7 @@
       </c>
       <c r="H100" s="68">
         <f>SUM(H96:H97)</f>
-        <v>7.45</v>
+        <v>6.71</v>
       </c>
       <c r="I100" s="34"/>
       <c r="J100" s="147" t="str">
@@ -9217,7 +9306,7 @@
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" s="128" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B103" s="38" t="s">
         <v>357</v>
@@ -9270,7 +9359,9 @@
       </c>
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A104" s="5"/>
+      <c r="A104" s="5" t="s">
+        <v>541</v>
+      </c>
       <c r="B104" s="38" t="s">
         <v>369</v>
       </c>
@@ -9285,19 +9376,19 @@
         <v>1.7111111111111112</v>
       </c>
       <c r="F104" s="33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G104" s="35">
-        <v>7.45</v>
+        <v>6.71</v>
       </c>
       <c r="H104" s="59">
         <f>IF((G104*F104)=0,"",G104*F104)</f>
-        <v>7.45</v>
+        <v>13.42</v>
       </c>
       <c r="I104" s="34"/>
       <c r="J104" s="147" t="str">
         <f t="shared" si="9"/>
-        <v/>
+        <v>plus compression sack</v>
       </c>
       <c r="P104" s="35"/>
       <c r="Q104" s="59" t="str">
@@ -9315,7 +9406,10 @@
       <c r="E105" s="36"/>
       <c r="F105" s="33"/>
       <c r="G105" s="35"/>
-      <c r="H105" s="59"/>
+      <c r="H105" s="59" t="str">
+        <f t="shared" ref="H105:H107" si="11">IF((G105*F105)=0,"",G105*F105)</f>
+        <v/>
+      </c>
       <c r="I105" s="34"/>
       <c r="J105" s="147" t="str">
         <f t="shared" si="9"/>
@@ -9324,7 +9418,7 @@
       <c r="P105" s="35"/>
       <c r="Q105" s="59"/>
     </row>
-    <row r="106" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" s="5"/>
       <c r="B106" s="38" t="s">
         <v>395</v>
@@ -9334,7 +9428,10 @@
       <c r="E106" s="36"/>
       <c r="F106" s="33"/>
       <c r="G106" s="35"/>
-      <c r="H106" s="59"/>
+      <c r="H106" s="59" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
       <c r="I106" s="34"/>
       <c r="J106" s="147" t="str">
         <f t="shared" si="9"/>
@@ -9344,160 +9441,157 @@
       <c r="Q106" s="59"/>
     </row>
     <row r="107" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="5" t="s">
-        <v>356</v>
-      </c>
-      <c r="B107" s="38"/>
+      <c r="A107" s="5"/>
+      <c r="B107" s="38" t="s">
+        <v>332</v>
+      </c>
       <c r="C107" s="20"/>
       <c r="D107" s="21"/>
       <c r="E107" s="36"/>
-      <c r="F107" s="33"/>
-      <c r="G107" s="64" t="s">
+      <c r="F107" s="33">
+        <v>1</v>
+      </c>
+      <c r="G107" s="35">
+        <v>4.38</v>
+      </c>
+      <c r="H107" s="59">
+        <f t="shared" si="11"/>
+        <v>4.38</v>
+      </c>
+      <c r="I107" s="34"/>
+      <c r="J107" s="147"/>
+      <c r="P107" s="35"/>
+      <c r="Q107" s="59"/>
+    </row>
+    <row r="108" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="B108" s="38"/>
+      <c r="C108" s="20"/>
+      <c r="D108" s="21"/>
+      <c r="E108" s="36"/>
+      <c r="F108" s="33"/>
+      <c r="G108" s="64" t="s">
         <v>65</v>
       </c>
-      <c r="H107" s="68">
-        <f>SUM(H103:H104)</f>
-        <v>7.45</v>
-      </c>
-      <c r="I107" s="34"/>
-      <c r="J107" s="146" t="str">
+      <c r="H108" s="68">
+        <f>SUM(H103:H107)</f>
+        <v>17.8</v>
+      </c>
+      <c r="I108" s="34"/>
+      <c r="J108" s="146" t="str">
         <f t="shared" si="9"/>
         <v>Rain Pants</v>
       </c>
-      <c r="P107" s="35"/>
-      <c r="Q107" s="59"/>
-    </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A108" s="60" t="s">
+      <c r="P108" s="35"/>
+      <c r="Q108" s="59"/>
+    </row>
+    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A109" s="60" t="s">
         <v>363</v>
       </c>
-      <c r="B108" s="38" t="s">
+      <c r="B109" s="38" t="s">
         <v>369</v>
       </c>
-      <c r="C108" s="20">
+      <c r="C109" s="20">
         <v>1.1000000000000001</v>
-      </c>
-      <c r="D108" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="E108" s="36">
-        <f>C108*((72*54)/(36*36))</f>
-        <v>3.3000000000000003</v>
-      </c>
-      <c r="F108" s="33">
-        <v>2</v>
-      </c>
-      <c r="G108" s="35">
-        <v>7.45</v>
-      </c>
-      <c r="H108" s="59">
-        <f>IF((G108*F108)=0,"",G108*F108)</f>
-        <v>14.9</v>
-      </c>
-      <c r="I108" s="34"/>
-      <c r="J108" s="147" t="str">
-        <f t="shared" si="9"/>
-        <v>make pattern</v>
-      </c>
-      <c r="K108" t="s">
-        <v>362</v>
-      </c>
-      <c r="N108" s="36">
-        <f>1.4*((72*54)/(36*36))</f>
-        <v>4.1999999999999993</v>
-      </c>
-      <c r="O108" s="33">
-        <v>2</v>
-      </c>
-      <c r="P108" s="35">
-        <v>20</v>
-      </c>
-      <c r="Q108" s="59">
-        <f t="shared" si="10"/>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A109" s="60"/>
-      <c r="B109" s="38" t="s">
-        <v>357</v>
-      </c>
-      <c r="C109" s="20">
-        <v>0.51</v>
       </c>
       <c r="D109" s="21" t="s">
         <v>159</v>
       </c>
       <c r="E109" s="36">
-        <f>C109*((30*48)/(36*36))</f>
-        <v>0.56666666666666665</v>
-      </c>
-      <c r="F109" s="33"/>
+        <f>C109*((72*54)/(36*36))</f>
+        <v>3.3000000000000003</v>
+      </c>
+      <c r="F109" s="33">
+        <v>2</v>
+      </c>
       <c r="G109" s="35">
-        <v>20.6</v>
-      </c>
-      <c r="H109" s="59" t="str">
+        <v>7.45</v>
+      </c>
+      <c r="H109" s="59">
         <f>IF((G109*F109)=0,"",G109*F109)</f>
-        <v/>
+        <v>14.9</v>
       </c>
       <c r="I109" s="34"/>
       <c r="J109" s="147" t="str">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K109" s="66" t="s">
+        <v>make pattern</v>
+      </c>
+      <c r="K109" t="s">
+        <v>362</v>
+      </c>
+      <c r="N109" s="36">
+        <f>1.4*((72*54)/(36*36))</f>
+        <v>4.1999999999999993</v>
+      </c>
+      <c r="O109" s="33">
+        <v>2</v>
+      </c>
+      <c r="P109" s="35">
+        <v>20</v>
+      </c>
+      <c r="Q109" s="59">
+        <f t="shared" si="10"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A110" s="60"/>
+      <c r="B110" s="38" t="s">
         <v>357</v>
       </c>
-      <c r="L109" s="20">
+      <c r="C110" s="20">
         <v>0.51</v>
       </c>
-      <c r="M109" s="21" t="s">
+      <c r="D110" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="N109" s="36">
-        <f>L109*((12.5*22)/(36*36))</f>
-        <v>0.10821759259259259</v>
-      </c>
-      <c r="O109" s="33"/>
-      <c r="P109" s="35">
-        <v>20.5</v>
-      </c>
-      <c r="Q109" s="59" t="str">
-        <f>IF((P109*O109)=0,"",P109*O109)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A110" s="180" t="s">
-        <v>512</v>
-      </c>
-      <c r="B110" s="38"/>
-      <c r="C110" s="20"/>
-      <c r="D110" s="21"/>
-      <c r="E110" s="36"/>
+      <c r="E110" s="36">
+        <f>C110*((30*48)/(36*36))</f>
+        <v>0.56666666666666665</v>
+      </c>
       <c r="F110" s="33"/>
-      <c r="G110" s="35"/>
-      <c r="H110" s="59"/>
+      <c r="G110" s="35">
+        <v>20.6</v>
+      </c>
+      <c r="H110" s="59" t="str">
+        <f>IF((G110*F110)=0,"",G110*F110)</f>
+        <v/>
+      </c>
       <c r="I110" s="34"/>
       <c r="J110" s="147" t="str">
         <f t="shared" si="9"/>
-        <v>Extra Xenon make booties with 6oz climashield</v>
-      </c>
-      <c r="K110" s="66"/>
-      <c r="L110" s="20"/>
-      <c r="M110" s="21"/>
-      <c r="N110" s="36"/>
+        <v/>
+      </c>
+      <c r="K110" s="66" t="s">
+        <v>357</v>
+      </c>
+      <c r="L110" s="20">
+        <v>0.51</v>
+      </c>
+      <c r="M110" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="N110" s="36">
+        <f>L110*((12.5*22)/(36*36))</f>
+        <v>0.10821759259259259</v>
+      </c>
       <c r="O110" s="33"/>
-      <c r="P110" s="35"/>
-      <c r="Q110" s="59"/>
+      <c r="P110" s="35">
+        <v>20.5</v>
+      </c>
+      <c r="Q110" s="59" t="str">
+        <f>IF((P110*O110)=0,"",P110*O110)</f>
+        <v/>
+      </c>
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111" s="180" t="s">
-        <v>514</v>
-      </c>
-      <c r="B111" s="46" t="s">
-        <v>374</v>
-      </c>
+        <v>510</v>
+      </c>
+      <c r="B111" s="38"/>
       <c r="C111" s="20"/>
       <c r="D111" s="21"/>
       <c r="E111" s="36"/>
@@ -9507,7 +9601,7 @@
       <c r="I111" s="34"/>
       <c r="J111" s="147" t="str">
         <f t="shared" si="9"/>
-        <v>see Dutch up booties</v>
+        <v>Extra Xenon make booties with 6oz climashield</v>
       </c>
       <c r="K111" s="66"/>
       <c r="L111" s="20"/>
@@ -9518,9 +9612,11 @@
       <c r="Q111" s="59"/>
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A112" s="60"/>
-      <c r="B112" s="50" t="s">
-        <v>314</v>
+      <c r="A112" s="180" t="s">
+        <v>512</v>
+      </c>
+      <c r="B112" s="46" t="s">
+        <v>374</v>
       </c>
       <c r="C112" s="20"/>
       <c r="D112" s="21"/>
@@ -9531,7 +9627,7 @@
       <c r="I112" s="34"/>
       <c r="J112" s="147" t="str">
         <f t="shared" si="9"/>
-        <v/>
+        <v>see Dutch up booties</v>
       </c>
       <c r="K112" s="66"/>
       <c r="L112" s="20"/>
@@ -9544,7 +9640,7 @@
     <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113" s="60"/>
       <c r="B113" s="50" t="s">
-        <v>475</v>
+        <v>314</v>
       </c>
       <c r="C113" s="20"/>
       <c r="D113" s="21"/>
@@ -9565,126 +9661,142 @@
       <c r="P113" s="35"/>
       <c r="Q113" s="59"/>
     </row>
-    <row r="114" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114" s="60"/>
-      <c r="B114" s="38" t="s">
-        <v>332</v>
+      <c r="B114" s="50" t="s">
+        <v>473</v>
       </c>
       <c r="C114" s="20"/>
       <c r="D114" s="21"/>
       <c r="E114" s="36"/>
       <c r="F114" s="33"/>
-      <c r="G114" s="35">
-        <v>3.96</v>
-      </c>
-      <c r="H114" s="59" t="str">
-        <f>IF((G114*F114)=0,"",G114*F114)</f>
-        <v/>
-      </c>
+      <c r="G114" s="35"/>
+      <c r="H114" s="59"/>
       <c r="I114" s="34"/>
       <c r="J114" s="147" t="str">
-        <f>IF(ISBLANK(A115),"",A115)</f>
-        <v/>
-      </c>
-      <c r="K114" t="s">
-        <v>332</v>
-      </c>
-      <c r="O114">
-        <v>1</v>
-      </c>
-      <c r="P114" s="137">
-        <v>4.5</v>
-      </c>
-      <c r="Q114" s="59">
-        <f>IF((P114*O114)=0,"",P114*O114)</f>
-        <v>4.5</v>
-      </c>
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="K114" s="66"/>
+      <c r="L114" s="20"/>
+      <c r="M114" s="21"/>
+      <c r="N114" s="36"/>
+      <c r="O114" s="33"/>
+      <c r="P114" s="35"/>
+      <c r="Q114" s="59"/>
     </row>
     <row r="115" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="60"/>
-      <c r="B115" s="38"/>
+      <c r="B115" s="38" t="s">
+        <v>332</v>
+      </c>
       <c r="C115" s="20"/>
       <c r="D115" s="21"/>
       <c r="E115" s="36"/>
       <c r="F115" s="33"/>
-      <c r="G115" s="64" t="s">
-        <v>65</v>
-      </c>
-      <c r="H115" s="68">
-        <f>SUM(H108:H114)</f>
-        <v>14.9</v>
+      <c r="G115" s="35">
+        <v>3.96</v>
+      </c>
+      <c r="H115" s="59" t="str">
+        <f>IF((G115*F115)=0,"",G115*F115)</f>
+        <v/>
       </c>
       <c r="I115" s="34"/>
-      <c r="J115" s="147"/>
-      <c r="K115" s="66"/>
-      <c r="L115" s="20"/>
-      <c r="M115" s="21"/>
-      <c r="N115" s="36"/>
-      <c r="O115" s="33"/>
-      <c r="P115" s="64" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q115" s="68">
-        <f>SUM(Q108:Q114)</f>
-        <v>44.5</v>
-      </c>
-    </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A116" s="18" t="s">
-        <v>364</v>
-      </c>
-      <c r="B116" s="38" t="s">
-        <v>365</v>
-      </c>
+      <c r="J115" s="147" t="str">
+        <f>IF(ISBLANK(A116),"",A116)</f>
+        <v/>
+      </c>
+      <c r="K115" t="s">
+        <v>332</v>
+      </c>
+      <c r="O115">
+        <v>1</v>
+      </c>
+      <c r="P115" s="137">
+        <v>4.5</v>
+      </c>
+      <c r="Q115" s="59">
+        <f>IF((P115*O115)=0,"",P115*O115)</f>
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="116" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="60"/>
+      <c r="B116" s="38"/>
       <c r="C116" s="20"/>
       <c r="D116" s="21"/>
       <c r="E116" s="36"/>
       <c r="F116" s="33"/>
-      <c r="G116" s="35"/>
-      <c r="H116" s="59"/>
+      <c r="G116" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="H116" s="68">
+        <f>SUM(H109:H115)</f>
+        <v>14.9</v>
+      </c>
       <c r="I116" s="34"/>
       <c r="J116" s="147"/>
-      <c r="P116" s="33"/>
-      <c r="Q116" s="10"/>
+      <c r="K116" s="66"/>
+      <c r="L116" s="20"/>
+      <c r="M116" s="21"/>
+      <c r="N116" s="36"/>
+      <c r="O116" s="33"/>
+      <c r="P116" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q116" s="68">
+        <f>SUM(Q109:Q115)</f>
+        <v>44.5</v>
+      </c>
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A117" s="18" t="s">
-        <v>287</v>
-      </c>
-      <c r="B117" s="61" t="s">
-        <v>367</v>
-      </c>
-      <c r="H117" s="59" t="str">
-        <f>IF((G117*F117)=0,"",G117*F117)</f>
-        <v/>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="B117" s="38" t="s">
+        <v>365</v>
+      </c>
+      <c r="C117" s="20"/>
+      <c r="D117" s="21"/>
+      <c r="E117" s="36"/>
+      <c r="F117" s="33"/>
+      <c r="G117" s="35"/>
+      <c r="H117" s="59"/>
       <c r="I117" s="34"/>
       <c r="J117" s="147"/>
+      <c r="P117" s="33"/>
+      <c r="Q117" s="10"/>
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A118" s="18" t="s">
-        <v>288</v>
-      </c>
-      <c r="B118" s="38" t="s">
-        <v>366</v>
+        <v>287</v>
+      </c>
+      <c r="B118" s="61" t="s">
+        <v>367</v>
       </c>
       <c r="H118" s="59" t="str">
         <f>IF((G118*F118)=0,"",G118*F118)</f>
         <v/>
       </c>
+      <c r="I118" s="34"/>
       <c r="J118" s="147"/>
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A119" s="18" t="s">
-        <v>516</v>
-      </c>
-      <c r="B119" s="38"/>
-      <c r="H119" s="59"/>
+        <v>288</v>
+      </c>
+      <c r="B119" s="38" t="s">
+        <v>366</v>
+      </c>
+      <c r="H119" s="59" t="str">
+        <f>IF((G119*F119)=0,"",G119*F119)</f>
+        <v/>
+      </c>
       <c r="J119" s="147"/>
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120" s="18" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="B120" s="38"/>
       <c r="H120" s="59"/>
@@ -9692,215 +9804,215 @@
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A121" s="18" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B121" s="38"/>
       <c r="H121" s="59"/>
       <c r="J121" s="147"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A122" s="18" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="B122" s="38"/>
-      <c r="H122" s="59" t="str">
-        <f>IF((G122*F122)=0,"",G122*F122)</f>
-        <v/>
-      </c>
+      <c r="H122" s="59"/>
       <c r="J122" s="147"/>
-      <c r="Q122" s="20"/>
     </row>
     <row r="123" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="18" t="s">
-        <v>459</v>
-      </c>
-      <c r="B123" s="54" t="s">
+        <v>513</v>
+      </c>
+      <c r="B123" s="38"/>
+      <c r="H123" s="59" t="str">
+        <f>IF((G123*F123)=0,"",G123*F123)</f>
+        <v/>
+      </c>
+      <c r="J123" s="147"/>
+      <c r="Q123" s="20"/>
+    </row>
+    <row r="124" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A124" s="18" t="s">
+        <v>458</v>
+      </c>
+      <c r="B124" s="54" t="s">
+        <v>444</v>
+      </c>
+      <c r="C124">
+        <f>C125*F129</f>
+        <v>6.8078820000000002</v>
+      </c>
+      <c r="D124" t="s">
+        <v>159</v>
+      </c>
+      <c r="E124" s="36">
+        <f>C124*((30*48)/(36*36))</f>
+        <v>7.5643133333333337</v>
+      </c>
+      <c r="F124">
+        <v>2</v>
+      </c>
+      <c r="G124">
+        <v>29</v>
+      </c>
+      <c r="H124" s="59">
+        <f>IF((G124*F124)=0,"",G124*F124)</f>
+        <v>58</v>
+      </c>
+      <c r="J124" s="146" t="str">
+        <f>IF(ISBLANK(A124),"",A124)</f>
+        <v>Pullover/hoodie</v>
+      </c>
+      <c r="K124" t="s">
         <v>445</v>
       </c>
-      <c r="C123">
-        <f>C124*F128</f>
-        <v>6.8078820000000002</v>
-      </c>
-      <c r="D123" t="s">
+      <c r="L124">
+        <v>4.8</v>
+      </c>
+      <c r="M124" t="s">
         <v>159</v>
       </c>
-      <c r="E123" s="36">
-        <f>C123*((30*48)/(36*36))</f>
-        <v>7.5643133333333337</v>
-      </c>
-      <c r="F123">
-        <v>2</v>
-      </c>
-      <c r="G123">
-        <v>29</v>
-      </c>
-      <c r="H123" s="59">
-        <f>IF((G123*F123)=0,"",G123*F123)</f>
-        <v>58</v>
-      </c>
-      <c r="J123" s="146" t="str">
-        <f>IF(ISBLANK(A123),"",A123)</f>
-        <v>Pullover/hoodie</v>
-      </c>
-      <c r="K123" t="s">
-        <v>446</v>
-      </c>
-      <c r="L123">
-        <v>4.8</v>
-      </c>
-      <c r="M123" t="s">
-        <v>159</v>
-      </c>
-      <c r="N123" s="36">
+      <c r="N124" s="36">
         <f>1.4*((72*54)/(36*36))</f>
         <v>4.1999999999999993</v>
       </c>
-      <c r="O123" s="25">
+      <c r="O124" s="25">
         <v>2</v>
       </c>
-      <c r="P123" s="136">
+      <c r="P124" s="136">
         <v>27.25</v>
       </c>
-      <c r="Q123" s="68">
-        <f>IF((P123*O123)=0,"",P123*O123)</f>
+      <c r="Q124" s="68">
+        <f>IF((P124*O124)=0,"",P124*O124)</f>
         <v>54.5</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B124" s="54" t="s">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B125" s="54" t="s">
+        <v>447</v>
+      </c>
+      <c r="C125">
+        <v>193</v>
+      </c>
+      <c r="D125" t="s">
+        <v>161</v>
+      </c>
+      <c r="J125" s="143" t="str">
+        <f>IF(ISBLANK(A125),"",A125)</f>
+        <v/>
+      </c>
+      <c r="K125" t="s">
+        <v>446</v>
+      </c>
+      <c r="L125">
+        <v>135.62</v>
+      </c>
+      <c r="M125" t="s">
+        <v>161</v>
+      </c>
+      <c r="N125" s="36"/>
+    </row>
+    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B126" s="117">
+        <v>4004</v>
+      </c>
+      <c r="C126">
+        <v>119</v>
+      </c>
+      <c r="F126">
+        <v>2</v>
+      </c>
+      <c r="G126">
+        <v>28</v>
+      </c>
+      <c r="H126" s="59">
+        <f>IF((G126*F126)=0,"",G126*F126)</f>
+        <v>56</v>
+      </c>
+      <c r="K126" t="s">
         <v>448</v>
       </c>
-      <c r="C124">
-        <v>193</v>
-      </c>
-      <c r="D124" t="s">
+      <c r="P126" s="136">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A127" s="131" t="s">
+        <v>442</v>
+      </c>
+      <c r="K127" t="s">
+        <v>460</v>
+      </c>
+      <c r="L127">
+        <v>152.58000000000001</v>
+      </c>
+      <c r="M127" t="s">
         <v>161</v>
       </c>
-      <c r="J124" s="143" t="str">
-        <f>IF(ISBLANK(A124),"",A124)</f>
-        <v/>
-      </c>
-      <c r="K124" t="s">
-        <v>447</v>
-      </c>
-      <c r="L124">
-        <v>135.62</v>
-      </c>
-      <c r="M124" t="s">
-        <v>161</v>
-      </c>
-      <c r="N124" s="36"/>
-    </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B125" s="117">
-        <v>4004</v>
-      </c>
-      <c r="C125">
-        <v>119</v>
-      </c>
-      <c r="F125">
-        <v>2</v>
-      </c>
-      <c r="G125">
-        <v>28</v>
-      </c>
-      <c r="H125" s="59">
-        <f>IF((G125*F125)=0,"",G125*F125)</f>
-        <v>56</v>
-      </c>
-      <c r="K125" t="s">
-        <v>449</v>
-      </c>
-      <c r="P125" s="136">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A126" s="131" t="s">
+    </row>
+    <row r="128" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A128" s="18" t="s">
         <v>443</v>
       </c>
-      <c r="K126" t="s">
-        <v>461</v>
-      </c>
-      <c r="L126">
-        <v>152.58000000000001</v>
-      </c>
-      <c r="M126" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="127" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="18" t="s">
-        <v>444</v>
-      </c>
-      <c r="L127">
-        <f>L126*F128</f>
+      <c r="L128">
+        <f>L127*F129</f>
         <v>5.38210692</v>
       </c>
-      <c r="M127" t="s">
+      <c r="M128" t="s">
         <v>159</v>
-      </c>
-      <c r="O127">
-        <v>2</v>
-      </c>
-      <c r="P127" s="136">
-        <v>31.5</v>
-      </c>
-      <c r="Q127" s="59">
-        <f>IF((P127*O127)=0,"",P127*O127)</f>
-        <v>63</v>
-      </c>
-    </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="D128" s="132">
-        <v>1</v>
-      </c>
-      <c r="E128" s="79" t="s">
-        <v>451</v>
-      </c>
-      <c r="F128" s="79">
-        <v>3.5274E-2</v>
-      </c>
-      <c r="G128" s="80" t="s">
-        <v>159</v>
-      </c>
-      <c r="K128" s="31" t="s">
-        <v>469</v>
       </c>
       <c r="O128">
         <v>2</v>
       </c>
       <c r="P128" s="136">
-        <v>26.25</v>
+        <v>31.5</v>
       </c>
       <c r="Q128" s="59">
         <f>IF((P128*O128)=0,"",P128*O128)</f>
+        <v>63</v>
+      </c>
+    </row>
+    <row r="129" spans="4:17" x14ac:dyDescent="0.25">
+      <c r="D129" s="132">
+        <v>1</v>
+      </c>
+      <c r="E129" s="79" t="s">
+        <v>450</v>
+      </c>
+      <c r="F129" s="79">
+        <v>3.5274E-2</v>
+      </c>
+      <c r="G129" s="80" t="s">
+        <v>159</v>
+      </c>
+      <c r="K129" s="31" t="s">
+        <v>468</v>
+      </c>
+      <c r="O129">
+        <v>2</v>
+      </c>
+      <c r="P129" s="136">
+        <v>26.25</v>
+      </c>
+      <c r="Q129" s="59">
+        <f>IF((P129*O129)=0,"",P129*O129)</f>
         <v>52.5</v>
       </c>
     </row>
-    <row r="129" spans="4:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D129" s="133">
+    <row r="130" spans="4:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D130" s="133">
         <v>28.349499999999999</v>
       </c>
-      <c r="E129" s="134" t="s">
-        <v>451</v>
-      </c>
-      <c r="F129" s="134">
+      <c r="E130" s="134" t="s">
+        <v>450</v>
+      </c>
+      <c r="F130" s="134">
         <v>1</v>
       </c>
-      <c r="G129" s="135" t="s">
+      <c r="G130" s="135" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="130" spans="4:16" x14ac:dyDescent="0.25">
-      <c r="K130" s="165"/>
-      <c r="L130" s="66"/>
-      <c r="M130" s="66"/>
-      <c r="N130" s="158"/>
-      <c r="O130" s="66"/>
-      <c r="P130" s="66"/>
-    </row>
-    <row r="131" spans="4:16" x14ac:dyDescent="0.25">
+    <row r="131" spans="4:17" x14ac:dyDescent="0.25">
       <c r="K131" s="165"/>
       <c r="L131" s="66"/>
       <c r="M131" s="66"/>
@@ -9908,7 +10020,7 @@
       <c r="O131" s="66"/>
       <c r="P131" s="66"/>
     </row>
-    <row r="132" spans="4:16" x14ac:dyDescent="0.25">
+    <row r="132" spans="4:17" x14ac:dyDescent="0.25">
       <c r="K132" s="165"/>
       <c r="L132" s="66"/>
       <c r="M132" s="66"/>
@@ -9916,7 +10028,7 @@
       <c r="O132" s="66"/>
       <c r="P132" s="66"/>
     </row>
-    <row r="133" spans="4:16" x14ac:dyDescent="0.25">
+    <row r="133" spans="4:17" x14ac:dyDescent="0.25">
       <c r="K133" s="165"/>
       <c r="L133" s="66"/>
       <c r="M133" s="66"/>
@@ -9924,7 +10036,7 @@
       <c r="O133" s="66"/>
       <c r="P133" s="66"/>
     </row>
-    <row r="134" spans="4:16" x14ac:dyDescent="0.25">
+    <row r="134" spans="4:17" x14ac:dyDescent="0.25">
       <c r="K134" s="165"/>
       <c r="L134" s="66"/>
       <c r="M134" s="66"/>
@@ -9932,9 +10044,17 @@
       <c r="O134" s="66"/>
       <c r="P134" s="66"/>
     </row>
+    <row r="135" spans="4:17" x14ac:dyDescent="0.25">
+      <c r="K135" s="165"/>
+      <c r="L135" s="66"/>
+      <c r="M135" s="66"/>
+      <c r="N135" s="158"/>
+      <c r="O135" s="66"/>
+      <c r="P135" s="66"/>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B117" location="ToDo!A19" display="See ToDo" xr:uid="{CE28C4E6-45D1-4C5D-A0AF-3ACF169C0D5B}"/>
+    <hyperlink ref="B118" location="ToDo!A19" display="See ToDo" xr:uid="{CE28C4E6-45D1-4C5D-A0AF-3ACF169C0D5B}"/>
     <hyperlink ref="R31" location="Make!A81" display="L" xr:uid="{F2445477-C9B7-447F-944F-160D21ACEB18}"/>
     <hyperlink ref="R32" location="Make!A85" display="L" xr:uid="{D614D32D-E4C7-4ABC-8AEA-2A0D20F4C1EC}"/>
     <hyperlink ref="R27" location="Make!A90" display="L" xr:uid="{786E7206-F76A-4474-B631-F01E095CA8FB}"/>
@@ -9957,9 +10077,10 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
-    <col min="2" max="2" width="6.5703125" customWidth="1"/>
-    <col min="3" max="3" width="7.5703125" customWidth="1"/>
-    <col min="5" max="5" width="7.140625" customWidth="1"/>
+    <col min="2" max="2" width="7.5703125" customWidth="1"/>
+    <col min="3" max="3" width="9.42578125" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" customWidth="1"/>
+    <col min="5" max="5" width="8.7109375" customWidth="1"/>
     <col min="6" max="6" width="7.28515625" customWidth="1"/>
     <col min="7" max="7" width="5.42578125" customWidth="1"/>
     <col min="8" max="8" width="8" customWidth="1"/>
@@ -10044,7 +10165,7 @@
         <v>258</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -10068,7 +10189,7 @@
         <v>259</v>
       </c>
       <c r="O5" s="20" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="P5">
         <v>32</v>
@@ -10101,13 +10222,13 @@
         <v>260</v>
       </c>
       <c r="O6" s="20" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="P6">
         <v>16</v>
       </c>
       <c r="Q6" s="20" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="R6">
         <v>8.1999999999999993</v>
@@ -10131,7 +10252,7 @@
         <v>261</v>
       </c>
       <c r="O7" s="20" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="P7">
         <v>44.8</v>
@@ -10146,7 +10267,7 @@
         <v>22</v>
       </c>
       <c r="T7" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -10168,7 +10289,7 @@
         <v>262</v>
       </c>
       <c r="O8" s="20" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="P8">
         <v>4.2</v>
@@ -10183,7 +10304,7 @@
         <v>20</v>
       </c>
       <c r="T8" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -10198,13 +10319,13 @@
         <v>263</v>
       </c>
       <c r="O9" s="20" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="P9">
         <v>4</v>
       </c>
       <c r="Q9" s="20" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="R9">
         <v>7.3</v>
@@ -10244,7 +10365,7 @@
       </c>
       <c r="O10" s="20"/>
       <c r="Q10" s="20" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="R10">
         <v>6</v>
@@ -10289,7 +10410,7 @@
         <v>5.9486955449999996</v>
       </c>
       <c r="Q11" s="20" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="R11">
         <v>6</v>
@@ -10366,7 +10487,7 @@
         <v>6</v>
       </c>
       <c r="Q13" s="20" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="R13">
         <f>INT(R12/16)</f>
@@ -10413,7 +10534,7 @@
         <v>5</v>
       </c>
       <c r="Q14" s="20" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="R14">
         <f>R12-(R13*16)</f>
@@ -10424,7 +10545,7 @@
         <v>7</v>
       </c>
       <c r="T14" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -10462,7 +10583,7 @@
         <v>0</v>
       </c>
       <c r="S15" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -10557,20 +10678,20 @@
         <v>14.192493900000001</v>
       </c>
       <c r="O18" s="153" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="P18" s="154">
         <v>60</v>
       </c>
       <c r="Q18" s="154" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="R18" s="155">
         <f>P18*2*$E$1*$U$23</f>
         <v>6.8196399999999997</v>
       </c>
       <c r="S18" s="154" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="T18" s="156"/>
     </row>
@@ -10597,20 +10718,20 @@
         <v>3.822222222222222</v>
       </c>
       <c r="O19" s="157" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="P19" s="66">
         <v>90</v>
       </c>
       <c r="Q19" s="66" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="R19" s="158">
         <f>P19*2*$E$1*$U$23</f>
         <v>10.22946</v>
       </c>
       <c r="S19" s="66" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="T19" s="159"/>
     </row>
@@ -10637,20 +10758,20 @@
         <v>0</v>
       </c>
       <c r="O20" s="157" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="P20" s="66">
         <v>120</v>
       </c>
       <c r="Q20" s="66" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="R20" s="158">
         <f>P20*2*$E$1*$U$23</f>
         <v>13.639279999999999</v>
       </c>
       <c r="S20" s="66" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="T20" s="159"/>
     </row>
@@ -10686,20 +10807,20 @@
         <v>0</v>
       </c>
       <c r="O21" s="157" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="P21" s="66">
         <v>150</v>
       </c>
       <c r="Q21" s="66" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="R21" s="158">
         <f>P21*2*$E$1*$U$23</f>
         <v>17.049099999999999</v>
       </c>
       <c r="S21" s="66" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="T21" s="159"/>
     </row>
@@ -10738,20 +10859,20 @@
         <v>0</v>
       </c>
       <c r="O22" s="160" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="P22" s="161">
         <v>190</v>
       </c>
       <c r="Q22" s="161" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="R22" s="162">
         <f>P22*2*$E$1*$U$23</f>
         <v>21.595526666666668</v>
       </c>
       <c r="S22" s="161" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="T22" s="163"/>
     </row>
@@ -10768,14 +10889,14 @@
         <v>0</v>
       </c>
       <c r="T23" s="168" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="U23">
         <f>(36*58)/(36*36)</f>
         <v>1.6111111111111112</v>
       </c>
       <c r="V23" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.25">
@@ -10964,4 +11085,215 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9E0C7C5-BD41-49D3-9542-8FC0DD02235F}">
+  <dimension ref="A1:B25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="14.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1274</v>
+      </c>
+      <c r="B2" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>221</v>
+      </c>
+      <c r="B4" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>2557</v>
+      </c>
+      <c r="B5" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>309</v>
+      </c>
+      <c r="B6" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>315</v>
+      </c>
+      <c r="B7" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>336</v>
+      </c>
+      <c r="B8" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>351</v>
+      </c>
+      <c r="B9" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>3529</v>
+      </c>
+      <c r="B10" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>3644</v>
+      </c>
+      <c r="B11" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>386</v>
+      </c>
+      <c r="B12" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>417</v>
+      </c>
+      <c r="B13" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>472</v>
+      </c>
+      <c r="B14" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>555</v>
+      </c>
+      <c r="B15" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>580</v>
+      </c>
+      <c r="B16" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>582</v>
+      </c>
+      <c r="B17" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>672</v>
+      </c>
+      <c r="B18" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>676</v>
+      </c>
+      <c r="B19" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>701</v>
+      </c>
+      <c r="B20" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>7568</v>
+      </c>
+      <c r="B21" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>824</v>
+      </c>
+      <c r="B22" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>967</v>
+      </c>
+      <c r="B23" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>968</v>
+      </c>
+      <c r="B24" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>982</v>
+      </c>
+      <c r="B25" t="s">
+        <v>538</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataConsolidate/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/AT/Materials.xlsx
+++ b/AT/Materials.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wellspan-my.sharepoint.com/personal/dsmith14_wellspan_org/Documents/Documents/GitHub/dps/AT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="56" documentId="13_ncr:1_{1DDBCB49-8FEC-4B57-AB8A-23D32742197E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A554B33-2EAE-4A87-8277-9920800F319B}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="13_ncr:1_{1DDBCB49-8FEC-4B57-AB8A-23D32742197E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8FFA329-58C7-4F77-AB01-4279663EAF09}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="26010" windowHeight="13875" activeTab="2" xr2:uid="{362FB22F-6BD6-431B-94C9-F0870D854534}"/>
+    <workbookView xWindow="2310" yWindow="1170" windowWidth="25440" windowHeight="14655" activeTab="3" xr2:uid="{362FB22F-6BD6-431B-94C9-F0870D854534}"/>
   </bookViews>
   <sheets>
     <sheet name="Materials" sheetId="1" r:id="rId1"/>
@@ -475,9 +475,6 @@
     <t>Spider 1" webbing - lightest webbing 10'</t>
   </si>
   <si>
-    <t>Climashield APEX</t>
-  </si>
-  <si>
     <t>2.5 oz</t>
   </si>
   <si>
@@ -1700,6 +1697,9 @@
   </si>
   <si>
     <t>plus compression sack</t>
+  </si>
+  <si>
+    <t>Climashield APEX ratings</t>
   </si>
 </sst>
 </file>
@@ -3022,7 +3022,7 @@
       </c>
       <c r="J9" s="3"/>
       <c r="K9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -3319,7 +3319,7 @@
         <v>34</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
@@ -3367,7 +3367,7 @@
         <v>34</v>
       </c>
       <c r="K20" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -3718,7 +3718,7 @@
         <v>61</v>
       </c>
       <c r="M33" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
@@ -3766,10 +3766,10 @@
         <v>61</v>
       </c>
       <c r="L35" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="M35" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
@@ -3866,7 +3866,7 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
@@ -4011,16 +4011,16 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>250</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>251</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>252</v>
       </c>
       <c r="C15" s="1"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -4118,7 +4118,7 @@
         <v>122</v>
       </c>
       <c r="F27" s="21" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -4132,18 +4132,18 @@
         <v>122</v>
       </c>
       <c r="G28" s="18" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="G29" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>3</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>65</v>
@@ -4151,13 +4151,13 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F30" s="20" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G30" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H30">
         <v>5</v>
@@ -4170,18 +4170,18 @@
         <v>22.5</v>
       </c>
       <c r="K30" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F31" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G31" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H31">
         <v>3</v>
@@ -4196,16 +4196,16 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>191</v>
+      </c>
+      <c r="B32" t="s">
         <v>192</v>
       </c>
-      <c r="B32" t="s">
-        <v>193</v>
-      </c>
       <c r="F32" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G32" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H32">
         <v>3</v>
@@ -4220,16 +4220,16 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B33" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F33" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G33" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H33">
         <v>3</v>
@@ -4244,22 +4244,22 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>186</v>
+      </c>
+      <c r="B34" t="s">
         <v>187</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>188</v>
       </c>
-      <c r="C34" t="s">
-        <v>189</v>
-      </c>
       <c r="D34" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F34" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G34" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H34">
         <v>5</v>
@@ -4274,16 +4274,16 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C35" t="s">
         <v>58</v>
       </c>
       <c r="F35" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G35" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H35">
         <v>5</v>
@@ -4298,13 +4298,13 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F36" s="20" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G36" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I36" s="30">
         <v>6.5</v>
@@ -4316,19 +4316,19 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B37" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C37" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F37" s="20" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G37" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H37">
         <v>4</v>
@@ -4343,11 +4343,11 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F38" s="20"/>
       <c r="G38" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H38">
         <v>1</v>
@@ -4360,16 +4360,16 @@
         <v>3.7</v>
       </c>
       <c r="K38" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F39" s="20"/>
       <c r="G39" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I39" s="30">
         <v>4.25</v>
@@ -4382,7 +4382,7 @@
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="F40" s="20"/>
       <c r="G40" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I40" s="30">
         <v>5.5</v>
@@ -4392,13 +4392,13 @@
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="F41" s="20"/>
       <c r="G41" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I41" s="30">
         <v>5.5</v>
@@ -4408,16 +4408,16 @@
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B42" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F42" s="20"/>
       <c r="G42" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H42">
         <v>4</v>
@@ -4430,22 +4430,22 @@
         <v>19</v>
       </c>
       <c r="K42" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C43" s="30">
         <v>13.5</v>
       </c>
       <c r="D43" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F43" s="20"/>
       <c r="G43" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I43" s="30">
         <v>2.1</v>
@@ -4455,22 +4455,22 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C44" s="30">
         <v>13.5</v>
       </c>
       <c r="D44" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F44" s="20"/>
       <c r="G44" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I44" s="30">
         <v>2.1</v>
@@ -4482,17 +4482,17 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C45" s="30">
         <v>13.5</v>
       </c>
       <c r="D45" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F45" s="20"/>
       <c r="G45" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="I45" s="30">
         <v>3.75</v>
@@ -4504,17 +4504,17 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C46" s="30">
         <v>13.5</v>
       </c>
       <c r="D46" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F46" s="20"/>
       <c r="G46" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I46" s="30">
         <v>7</v>
@@ -4526,10 +4526,10 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="F47" s="20" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G47" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H47">
         <v>2</v>
@@ -4542,18 +4542,18 @@
         <v>12.5</v>
       </c>
       <c r="K47" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B48" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F48" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G48" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H48">
         <v>1</v>
@@ -4566,18 +4566,18 @@
         <v>12</v>
       </c>
       <c r="K48" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="49" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F49" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G49" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H49">
         <v>2</v>
@@ -4590,18 +4590,18 @@
         <v>27</v>
       </c>
       <c r="K49" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="50" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F50" s="20" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G50" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I50" s="30">
         <v>3.9</v>
@@ -4611,7 +4611,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="L50" s="30">
         <f>J30+J38+SUM(J40:J43)+SUM(J47:J50)</f>
@@ -4620,11 +4620,11 @@
     </row>
     <row r="51" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F51" s="20"/>
       <c r="G51" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I51" s="30">
         <v>2</v>
@@ -4636,7 +4636,7 @@
     </row>
     <row r="52" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F52" s="20"/>
       <c r="I52" s="30"/>
@@ -4647,12 +4647,12 @@
     </row>
     <row r="53" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="54" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
   </sheetData>
@@ -4706,14 +4706,14 @@
   <sheetData>
     <row r="1" spans="1:28" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B1" s="18" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C1" s="18"/>
       <c r="D1" s="18"/>
       <c r="E1" s="18"/>
       <c r="I1" s="34"/>
       <c r="K1" s="18" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="L1" s="18"/>
       <c r="M1" s="18"/>
@@ -4722,40 +4722,40 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>65</v>
       </c>
       <c r="I2" s="34"/>
       <c r="K2" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="M2" s="4"/>
       <c r="N2" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Q2" s="4" t="s">
         <v>65</v>
@@ -4765,16 +4765,16 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B3" s="38" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C3" s="20">
         <v>6</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E3" s="36">
         <f>C3*$A$5</f>
@@ -4794,13 +4794,13 @@
         <v>Top Quilt</v>
       </c>
       <c r="K3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L3" s="20">
         <v>5</v>
       </c>
       <c r="M3" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N3" s="36">
         <f>L3*$A$5</f>
@@ -4820,16 +4820,16 @@
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" s="20" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B4" s="38" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C4" s="20">
         <v>3.6</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E4" s="36">
         <f>C4*$A$5</f>
@@ -4851,13 +4851,13 @@
         <v>54x78</v>
       </c>
       <c r="K4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L4" s="20">
         <v>3.6</v>
       </c>
       <c r="M4" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N4" s="36">
         <f t="shared" ref="N4:N10" si="2">L4*$A$5</f>
@@ -4876,7 +4876,7 @@
         <v>23.855</v>
       </c>
       <c r="U4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.25">
@@ -4885,7 +4885,7 @@
         <v>3.25</v>
       </c>
       <c r="B5" s="38" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C5" s="20"/>
       <c r="D5" s="21"/>
@@ -4902,7 +4902,7 @@
         <v>3.25</v>
       </c>
       <c r="K5" s="66" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="L5" s="20"/>
       <c r="M5" s="21"/>
@@ -4919,15 +4919,15 @@
         <v>21.204444444444444</v>
       </c>
       <c r="U5" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B6" s="38" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C6" s="20"/>
       <c r="D6" s="21"/>
@@ -4944,7 +4944,7 @@
         <v>tapperd &amp; sewn waist down</v>
       </c>
       <c r="K6" s="66" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="L6" s="20"/>
       <c r="M6" s="21"/>
@@ -4960,21 +4960,21 @@
         <v>2.8162152777777778</v>
       </c>
       <c r="U6" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B7" s="38" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C7" s="20">
         <v>0.67</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E7" s="36">
         <f>C7*$A$5*2</f>
@@ -4994,13 +4994,13 @@
         <v>make 2nd top quilt 3.5oz</v>
       </c>
       <c r="K7" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L7" s="20">
         <v>0.66</v>
       </c>
       <c r="M7" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N7" s="36">
         <f t="shared" si="2"/>
@@ -5019,16 +5019,16 @@
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" s="20" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B8" s="38" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C8" s="20">
         <v>0.9</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E8" s="36">
         <f>C8*$A$5*2</f>
@@ -5050,13 +5050,13 @@
         <v>and use current 5oz UQ</v>
       </c>
       <c r="K8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="L8" s="20">
         <v>0.9</v>
       </c>
       <c r="M8" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N8" s="36">
         <f t="shared" si="2"/>
@@ -5073,16 +5073,16 @@
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9" s="21" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B9" s="38" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C9" s="20">
         <v>0.93</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E9" s="36">
         <f>C9*$A$5*2</f>
@@ -5102,13 +5102,13 @@
         <v>3yd 6oz &amp; 2 yd 3.5oz</v>
       </c>
       <c r="K9" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="L9" s="20">
         <v>1</v>
       </c>
       <c r="M9" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N9" s="36">
         <f t="shared" si="2"/>
@@ -5123,42 +5123,42 @@
         <v/>
       </c>
       <c r="U9" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="V9" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="V9" s="2" t="s">
-        <v>380</v>
-      </c>
       <c r="W9" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="Y9" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="Z9" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="Z9" s="2" t="s">
+      <c r="AA9" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="AA9" s="2" t="s">
+      <c r="AB9" s="2" t="s">
         <v>392</v>
-      </c>
-      <c r="AB9" s="2" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A10" s="21" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B10" s="38" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C10" s="20">
         <v>1.05</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E10" s="36">
         <f>C10*$A$5*2</f>
@@ -5178,7 +5178,7 @@
         <v>add 1/2yd 6oz to 3.5oz TQ</v>
       </c>
       <c r="K10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="L10" s="20">
         <v>1.1000000000000001</v>
@@ -5199,7 +5199,7 @@
         <v/>
       </c>
       <c r="S10" s="70" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="T10" s="75">
         <f>SUM(U10:AB10)</f>
@@ -5215,7 +5215,7 @@
     <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11" s="20"/>
       <c r="B11" s="38" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C11" s="20"/>
       <c r="D11" s="21"/>
@@ -5234,7 +5234,7 @@
         <v/>
       </c>
       <c r="K11" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="L11" s="20"/>
       <c r="M11" s="21"/>
@@ -5250,7 +5250,7 @@
         <v>5.25</v>
       </c>
       <c r="S11" s="70" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="T11" s="75">
         <f t="shared" ref="T11:T17" si="5">SUM(U11:AB11)</f>
@@ -5274,10 +5274,10 @@
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A12" s="20" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C12" s="20"/>
       <c r="D12" s="21"/>
@@ -5298,7 +5298,7 @@
         <v>Forest Green</v>
       </c>
       <c r="K12" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="L12" s="20"/>
       <c r="M12" s="21"/>
@@ -5312,7 +5312,7 @@
         <v/>
       </c>
       <c r="S12" s="71" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="T12" s="75">
         <f t="shared" si="5"/>
@@ -5337,7 +5337,7 @@
     <row r="13" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A13" s="20"/>
       <c r="B13" s="46" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C13" s="20"/>
       <c r="D13" s="21"/>
@@ -5354,7 +5354,7 @@
         <v/>
       </c>
       <c r="K13" s="138" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="L13" s="20"/>
       <c r="M13" s="21"/>
@@ -5365,7 +5365,7 @@
       </c>
       <c r="Q13" s="35"/>
       <c r="S13" s="71" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="T13" s="75">
         <f t="shared" si="5"/>
@@ -5378,7 +5378,7 @@
     <row r="14" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="20"/>
       <c r="B14" s="50" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="21"/>
@@ -5397,7 +5397,7 @@
         <v/>
       </c>
       <c r="K14" s="139" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="L14" s="20"/>
       <c r="M14" s="21"/>
@@ -5408,7 +5408,7 @@
       <c r="P14" s="35"/>
       <c r="Q14" s="35"/>
       <c r="S14" s="72" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="T14" s="75">
         <f t="shared" si="5"/>
@@ -5453,7 +5453,7 @@
         <v>104.625</v>
       </c>
       <c r="S15" s="73" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="T15" s="75">
         <f t="shared" si="5"/>
@@ -5465,16 +5465,16 @@
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C16" s="20">
         <v>6</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E16" s="36">
         <f>C16*$A$18</f>
@@ -5496,13 +5496,13 @@
         <v>Under Quilt</v>
       </c>
       <c r="K16" s="66" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L16" s="20">
         <v>5</v>
       </c>
       <c r="M16" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N16" s="36"/>
       <c r="O16" s="33">
@@ -5516,7 +5516,7 @@
         <v>35.625</v>
       </c>
       <c r="S16" s="74" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="T16" s="75">
         <f t="shared" si="5"/>
@@ -5531,16 +5531,16 @@
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A17" s="20" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C17" s="20">
         <v>0.67</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E17" s="36">
         <f>C17*$A$18*2</f>
@@ -5560,13 +5560,13 @@
         <v>78x48</v>
       </c>
       <c r="K17" s="66" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L17" s="20">
         <v>0.66</v>
       </c>
       <c r="M17" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N17" s="36">
         <f>L17*$A$5</f>
@@ -5583,7 +5583,7 @@
         <v>63.75</v>
       </c>
       <c r="S17" s="74" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="T17" s="75">
         <f t="shared" si="5"/>
@@ -5602,13 +5602,13 @@
         <v>2.8888888888888888</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C18" s="20">
         <v>0.9</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E18" s="36">
         <f>C18*$A$18*2</f>
@@ -5630,13 +5630,13 @@
         <v>2.8888888888888888</v>
       </c>
       <c r="K18" s="66" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="L18" s="20">
         <v>0.9</v>
       </c>
       <c r="M18" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N18" s="36">
         <f>L18*$A$5</f>
@@ -5655,16 +5655,16 @@
     </row>
     <row r="19" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C19" s="20">
         <v>0.93</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E19" s="36">
         <f>C19*$A$5*2</f>
@@ -5684,7 +5684,7 @@
         <v>make this a TQ. See above</v>
       </c>
       <c r="K19" s="66" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="L19" s="20"/>
       <c r="M19" s="21"/>
@@ -5700,12 +5700,12 @@
         <v>4.5</v>
       </c>
       <c r="S19" s="107" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A20" s="20" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B20" s="38" t="s">
         <v>79</v>
@@ -5729,13 +5729,13 @@
         <v>future if 5oz UQ is not warm</v>
       </c>
       <c r="K20" s="66" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="L20" s="20">
         <v>6.6</v>
       </c>
       <c r="M20" s="21" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="N20" s="36"/>
       <c r="O20" s="33"/>
@@ -5754,23 +5754,23 @@
         <v>65</v>
       </c>
       <c r="U20" s="78" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="V20" s="79"/>
       <c r="W20" s="80"/>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A21" s="20" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C21" s="20">
         <v>49.9</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G21" s="35">
         <v>4.01</v>
@@ -5785,13 +5785,13 @@
         <v>Xenon waterproof for bottom</v>
       </c>
       <c r="K21" s="66" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="L21" s="20">
         <v>5</v>
       </c>
       <c r="M21" s="21" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="N21" s="36"/>
       <c r="O21" s="33"/>
@@ -5815,20 +5815,20 @@
         <v>4</v>
       </c>
       <c r="V21" s="84" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="W21" s="85"/>
     </row>
     <row r="22" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A22" s="20"/>
       <c r="B22" s="38" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C22" s="20">
         <v>43.94</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E22" s="36"/>
       <c r="F22" s="33"/>
@@ -5845,13 +5845,13 @@
         <v/>
       </c>
       <c r="K22" s="66" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="L22" s="20">
         <v>3.6</v>
       </c>
       <c r="M22" s="21" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="N22" s="36"/>
       <c r="O22" s="33"/>
@@ -5875,22 +5875,22 @@
         <v>5</v>
       </c>
       <c r="V22" s="84" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="W22" s="85"/>
     </row>
     <row r="23" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A23" s="20" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C23" s="20">
         <v>27.49</v>
       </c>
       <c r="D23" s="21" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E23" s="36"/>
       <c r="F23" s="33"/>
@@ -5907,7 +5907,7 @@
         <v>Brilliant Blue</v>
       </c>
       <c r="K23" s="138" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="L23" s="20"/>
       <c r="M23" s="21"/>
@@ -5931,14 +5931,14 @@
         <v>3</v>
       </c>
       <c r="V23" s="89" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="W23" s="90"/>
     </row>
     <row r="24" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A24" s="20"/>
       <c r="B24" s="46" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C24" s="20"/>
       <c r="D24" s="21"/>
@@ -5955,7 +5955,7 @@
         <v/>
       </c>
       <c r="K24" s="139" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="L24" s="20"/>
       <c r="M24" s="21"/>
@@ -5967,7 +5967,7 @@
         <v/>
       </c>
       <c r="R24" s="166" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="S24" s="91" t="str">
         <f>A39</f>
@@ -5981,14 +5981,14 @@
         <v>8</v>
       </c>
       <c r="V24" s="94" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="W24" s="95"/>
     </row>
     <row r="25" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="20"/>
       <c r="B25" s="50" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C25" s="20"/>
       <c r="D25" s="21"/>
@@ -6005,7 +6005,7 @@
         <v/>
       </c>
       <c r="K25" s="66" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="L25" s="20"/>
       <c r="M25" s="21"/>
@@ -6021,7 +6021,7 @@
         <v>5</v>
       </c>
       <c r="R25" s="166" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="S25" s="91" t="str">
         <f>A46</f>
@@ -6035,20 +6035,20 @@
         <v>9</v>
       </c>
       <c r="V25" s="94" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="W25" s="95"/>
     </row>
     <row r="26" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="20"/>
       <c r="B26" s="38" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C26" s="20">
         <v>1.1299999999999999</v>
       </c>
       <c r="D26" s="21" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E26" s="36"/>
       <c r="F26" s="178">
@@ -6079,7 +6079,7 @@
         <v>108.875</v>
       </c>
       <c r="R26" s="166" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="S26" s="96" t="str">
         <f>A53</f>
@@ -6093,7 +6093,7 @@
         <v>6</v>
       </c>
       <c r="V26" s="99" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="W26" s="100"/>
       <c r="X26" s="30"/>
@@ -6125,7 +6125,7 @@
       <c r="P27" s="64"/>
       <c r="Q27" s="144"/>
       <c r="R27" s="166" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="S27" s="101" t="str">
         <f>A90</f>
@@ -6139,13 +6139,13 @@
         <v>10</v>
       </c>
       <c r="V27" s="104" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="W27" s="105"/>
     </row>
     <row r="28" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B28" s="38"/>
       <c r="C28" s="20"/>
@@ -6160,13 +6160,13 @@
         <v>Griz Ariel Hammock</v>
       </c>
       <c r="K28" s="66" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="L28" s="20">
         <v>1.6</v>
       </c>
       <c r="M28" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N28" s="36"/>
       <c r="O28" s="33">
@@ -6180,7 +6180,7 @@
         <v>22.5</v>
       </c>
       <c r="R28" s="166" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="S28" s="120" t="str">
         <f>A95</f>
@@ -6194,22 +6194,22 @@
         <v>11</v>
       </c>
       <c r="V28" s="117" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="W28" s="123"/>
     </row>
     <row r="29" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A29" s="20" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C29" s="20">
         <v>1.6</v>
       </c>
       <c r="D29" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E29" s="36">
         <f>$A$30*C29</f>
@@ -6239,7 +6239,7 @@
         <v/>
       </c>
       <c r="R29" s="166" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="S29" s="120" t="str">
         <f>A102</f>
@@ -6253,7 +6253,7 @@
         <v>12</v>
       </c>
       <c r="V29" s="117" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="W29" s="123"/>
     </row>
@@ -6263,13 +6263,13 @@
         <v>3.6203703703703702</v>
       </c>
       <c r="B30" s="38" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C30" s="20">
         <v>1.2</v>
       </c>
       <c r="D30" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E30" s="36">
         <f>$A$30*C30</f>
@@ -6307,7 +6307,7 @@
         <v>5.25</v>
       </c>
       <c r="R30" s="166" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="S30" s="101" t="str">
         <f>A108</f>
@@ -6321,13 +6321,13 @@
         <v>7</v>
       </c>
       <c r="V30" s="104" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="W30" s="105"/>
     </row>
     <row r="31" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A31" s="20" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B31" s="38" t="s">
         <v>79</v>
@@ -6351,13 +6351,13 @@
         <v>with half bug net</v>
       </c>
       <c r="K31" s="66" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="L31" s="20">
         <v>3.6</v>
       </c>
       <c r="M31" s="21" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="N31" s="36"/>
       <c r="O31" s="33"/>
@@ -6369,7 +6369,7 @@
         <v/>
       </c>
       <c r="R31" s="166" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="S31" s="86" t="str">
         <f>A82</f>
@@ -6383,20 +6383,20 @@
         <v>1</v>
       </c>
       <c r="V31" s="89" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="W31" s="90"/>
     </row>
     <row r="32" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A32" s="20"/>
       <c r="B32" s="38" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C32" s="20">
         <v>27.49</v>
       </c>
       <c r="D32" s="21" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E32" s="36"/>
       <c r="F32" s="33"/>
@@ -6423,7 +6423,7 @@
         <v/>
       </c>
       <c r="R32" s="166" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="S32" s="86" t="str">
         <f>A86</f>
@@ -6437,20 +6437,20 @@
         <v>2</v>
       </c>
       <c r="V32" s="89" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="W32" s="90"/>
     </row>
     <row r="33" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="20"/>
       <c r="B33" s="52" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C33">
         <v>5.0999999999999996</v>
       </c>
       <c r="D33" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -6468,7 +6468,7 @@
         <v/>
       </c>
       <c r="K33" s="117" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="L33" s="20"/>
       <c r="M33" s="21"/>
@@ -6480,7 +6480,7 @@
         <v/>
       </c>
       <c r="R33" s="166" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="S33" s="149" t="str">
         <f>A124</f>
@@ -6494,14 +6494,14 @@
         <v>13</v>
       </c>
       <c r="V33" s="152" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="W33" s="106"/>
     </row>
     <row r="34" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="20"/>
       <c r="B34" s="52" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="G34" s="35"/>
       <c r="H34" s="35" t="str">
@@ -6514,7 +6514,7 @@
         <v/>
       </c>
       <c r="K34" s="140" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="L34" s="20"/>
       <c r="M34" s="21"/>
@@ -6532,7 +6532,7 @@
     <row r="35" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="20"/>
       <c r="B35" s="53" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F35" s="33"/>
       <c r="G35" s="35">
@@ -6548,13 +6548,13 @@
         <v/>
       </c>
       <c r="K35" s="66" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="L35" s="20">
         <v>0.67</v>
       </c>
       <c r="M35" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N35" s="36"/>
       <c r="O35" s="33">
@@ -6578,13 +6578,13 @@
     <row r="36" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="20"/>
       <c r="B36" s="38" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C36" s="20">
         <v>0.67</v>
       </c>
       <c r="D36" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E36" s="36"/>
       <c r="F36" s="33">
@@ -6603,7 +6603,7 @@
         <v/>
       </c>
       <c r="K36" s="56" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="L36" s="20"/>
       <c r="M36" s="21"/>
@@ -6623,13 +6623,13 @@
     <row r="37" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="20"/>
       <c r="B37" s="38" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C37" s="20">
         <v>0.3</v>
       </c>
       <c r="D37" s="21" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E37" s="36"/>
       <c r="F37" s="33">
@@ -6660,20 +6660,20 @@
         <v>43</v>
       </c>
       <c r="S37" s="169" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="T37" s="108">
         <f>T31+T32+T23</f>
         <v>78.150000000000006</v>
       </c>
       <c r="U37" s="109" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="V37" s="31" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="W37" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="X37" s="30"/>
     </row>
@@ -6694,13 +6694,13 @@
         <v/>
       </c>
       <c r="K38" s="66" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="L38" s="20">
         <v>1.6</v>
       </c>
       <c r="M38" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N38" s="36"/>
       <c r="O38" s="33">
@@ -6714,17 +6714,17 @@
         <v>30</v>
       </c>
       <c r="S38" s="170" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="T38" s="102">
         <f>T27+T30</f>
         <v>41.76</v>
       </c>
       <c r="U38" s="112" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="V38" s="31" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="W38" s="3">
         <v>129.33000000000001</v>
@@ -6733,7 +6733,7 @@
     </row>
     <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B39" s="55"/>
       <c r="F39" s="33"/>
@@ -6755,31 +6755,31 @@
         <v/>
       </c>
       <c r="S39" s="110" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="T39" s="97">
         <f>T26+T33</f>
         <v>127.07</v>
       </c>
       <c r="U39" s="113" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="V39" s="25" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A40" s="20" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B40" s="38" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C40" s="20">
         <v>1.2</v>
       </c>
       <c r="D40" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E40" s="36">
         <f>$A$41*C40</f>
@@ -6825,10 +6825,10 @@
         <v>144.89000000000001</v>
       </c>
       <c r="U40" s="111" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="V40" s="173" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="W40" s="174">
         <f>H82</f>
@@ -6841,13 +6841,13 @@
         <v>5.0925925925925926</v>
       </c>
       <c r="B41" s="38" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C41" s="20">
         <v>1.6</v>
       </c>
       <c r="D41" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E41" s="36">
         <f>$A$41*C41</f>
@@ -6879,7 +6879,7 @@
         <v>71.44</v>
       </c>
       <c r="U41" s="124" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="X41" s="30"/>
     </row>
@@ -6908,26 +6908,26 @@
       </c>
       <c r="Q42" s="35"/>
       <c r="S42" s="114" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="T42" s="118">
         <f>T28+T29</f>
         <v>24.51</v>
       </c>
       <c r="U42" s="119" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="43" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="37"/>
       <c r="B43" s="52" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C43" s="20">
         <v>27</v>
       </c>
       <c r="D43" s="21" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E43" s="36"/>
       <c r="F43" s="33"/>
@@ -6954,13 +6954,13 @@
     <row r="44" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="37"/>
       <c r="B44" s="38" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C44" s="20">
         <v>0.67</v>
       </c>
       <c r="D44" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E44" s="36">
         <f>C44*F44</f>
@@ -6989,7 +6989,7 @@
         <v>35.25</v>
       </c>
       <c r="S44" s="167" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="T44" s="30"/>
     </row>
@@ -7012,13 +7012,13 @@
         <v/>
       </c>
       <c r="K45" s="66" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="L45" s="20">
         <v>0.67</v>
       </c>
       <c r="M45" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N45" s="36"/>
       <c r="O45" s="33">
@@ -7039,7 +7039,7 @@
     </row>
     <row r="46" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B46" s="54"/>
       <c r="C46" s="20"/>
@@ -7054,13 +7054,13 @@
         <v>Bug Net</v>
       </c>
       <c r="K46" s="66" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="L46" s="20">
         <v>0.9</v>
       </c>
       <c r="M46" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N46" s="36"/>
       <c r="O46" s="33"/>
@@ -7079,16 +7079,16 @@
     </row>
     <row r="47" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A47" s="20" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B47" s="38" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C47" s="20">
         <v>0.67</v>
       </c>
       <c r="D47" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E47" s="36">
         <f>C47*$A$48</f>
@@ -7110,13 +7110,13 @@
         <v>120 x 96</v>
       </c>
       <c r="K47" s="66" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="L47" s="20">
         <v>0.5</v>
       </c>
       <c r="M47" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N47" s="36">
         <f>(55*36)/(36*36)</f>
@@ -7141,13 +7141,13 @@
         <v>8.8888888888888893</v>
       </c>
       <c r="B48" s="38" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C48" s="20">
         <v>0.9</v>
       </c>
       <c r="D48" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E48" s="36">
         <f>C48*$A$48</f>
@@ -7167,7 +7167,7 @@
         <v>8.8888888888888893</v>
       </c>
       <c r="K48" s="138" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="L48" s="20"/>
       <c r="M48" s="21"/>
@@ -7176,13 +7176,13 @@
       <c r="P48" s="35"/>
       <c r="Q48" s="35"/>
       <c r="S48" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="T48" s="30"/>
     </row>
     <row r="49" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="20" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B49" s="38"/>
       <c r="H49" s="35" t="str">
@@ -7195,7 +7195,7 @@
         <v>Redesign to make it partial</v>
       </c>
       <c r="K49" s="139" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="L49" s="20"/>
       <c r="M49" s="21"/>
@@ -7204,16 +7204,16 @@
       <c r="P49" s="35"/>
       <c r="Q49" s="35"/>
       <c r="S49" s="18" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="T49" s="30"/>
     </row>
     <row r="50" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="20" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B50" s="46" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C50" s="20"/>
       <c r="D50" s="21"/>
@@ -7242,16 +7242,16 @@
         <v>38.5</v>
       </c>
       <c r="S50" s="18" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="T50" s="30"/>
     </row>
     <row r="51" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="42" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B51" s="50" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C51" s="20"/>
       <c r="D51" s="21"/>
@@ -7275,7 +7275,7 @@
       <c r="P51" s="64"/>
       <c r="Q51" s="144"/>
       <c r="S51" s="18" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="T51" s="30"/>
     </row>
@@ -7302,13 +7302,13 @@
         <v>Back Pack</v>
       </c>
       <c r="K52" s="141" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="L52" s="20">
         <v>4.4000000000000004</v>
       </c>
       <c r="M52" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N52" s="36"/>
       <c r="O52" s="33">
@@ -7322,13 +7322,13 @@
         <v/>
       </c>
       <c r="S52" s="18" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="T52" s="30"/>
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B53" s="54"/>
       <c r="C53" s="20"/>
@@ -7343,13 +7343,13 @@
         <v>* Work on quantities</v>
       </c>
       <c r="K53" s="66" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="L53" s="20">
         <v>3.2</v>
       </c>
       <c r="M53" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N53" s="36"/>
       <c r="O53" s="33"/>
@@ -7364,17 +7364,17 @@
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A54" s="60" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B54" s="38" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C54" s="20">
         <f>(4.85+5.85)/2</f>
         <v>5.35</v>
       </c>
       <c r="D54" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E54" s="36"/>
       <c r="F54" s="33"/>
@@ -7391,13 +7391,13 @@
         <v/>
       </c>
       <c r="K54" s="66" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="L54" s="20">
         <v>3.9</v>
       </c>
       <c r="M54" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N54" s="36"/>
       <c r="O54" s="172">
@@ -7414,13 +7414,13 @@
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B55" s="38" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C55" s="20">
         <v>3.2</v>
       </c>
       <c r="D55" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E55" s="36"/>
       <c r="F55" s="33"/>
@@ -7437,13 +7437,13 @@
         <v/>
       </c>
       <c r="K55" s="141" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="L55" s="20">
         <v>6.1</v>
       </c>
       <c r="M55" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N55" s="36"/>
       <c r="O55" s="33"/>
@@ -7458,13 +7458,13 @@
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B56" s="38" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C56" s="20">
         <v>6.73</v>
       </c>
       <c r="D56" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E56" s="36"/>
       <c r="F56" s="33"/>
@@ -7481,7 +7481,7 @@
         <v/>
       </c>
       <c r="K56" s="66" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="L56" s="20"/>
       <c r="M56" s="21"/>
@@ -7498,13 +7498,13 @@
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B57" s="38" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C57" s="20">
         <v>7.9</v>
       </c>
       <c r="D57" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E57" s="36"/>
       <c r="F57" s="33"/>
@@ -7521,13 +7521,13 @@
         <v/>
       </c>
       <c r="K57" s="117" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="L57" s="20">
         <v>10</v>
       </c>
       <c r="M57" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N57" s="36"/>
       <c r="O57" s="33"/>
@@ -7542,7 +7542,7 @@
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B58" s="38" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C58" s="20"/>
       <c r="D58" s="21"/>
@@ -7561,13 +7561,13 @@
         <v/>
       </c>
       <c r="K58" s="141" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L58" s="20">
         <v>14.36</v>
       </c>
       <c r="M58" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N58" s="36"/>
       <c r="O58" s="33"/>
@@ -7581,13 +7581,13 @@
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B59" s="38" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C59" s="20">
         <v>212.5</v>
       </c>
       <c r="D59" s="21" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E59" s="36"/>
       <c r="F59" s="33"/>
@@ -7604,13 +7604,13 @@
         <v/>
       </c>
       <c r="K59" s="141" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="L59" s="20">
         <v>4</v>
       </c>
       <c r="M59" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N59" s="3"/>
       <c r="O59" s="33"/>
@@ -7624,10 +7624,10 @@
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B60" s="38" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C60" s="21" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D60" s="21"/>
       <c r="E60" s="36"/>
@@ -7643,13 +7643,13 @@
         <v>7</v>
       </c>
       <c r="K60" s="66" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="L60" s="20">
         <v>2.6</v>
       </c>
       <c r="M60" s="21" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="N60" s="36"/>
       <c r="O60" s="33"/>
@@ -7666,7 +7666,7 @@
         <v>7</v>
       </c>
       <c r="B61" s="38" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C61" s="20">
         <v>1.7</v>
@@ -7685,13 +7685,13 @@
         <v/>
       </c>
       <c r="K61" s="66" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="L61" s="20">
         <v>0.5</v>
       </c>
       <c r="M61" s="21" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="N61" s="36"/>
       <c r="O61" s="33"/>
@@ -7705,13 +7705,13 @@
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B62" s="38" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C62" s="20">
         <v>0.56000000000000005</v>
       </c>
       <c r="D62" s="21" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E62" s="36"/>
       <c r="F62" s="33"/>
@@ -7728,13 +7728,13 @@
         <v>10</v>
       </c>
       <c r="K62" s="66" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="L62" s="20">
         <v>2.33</v>
       </c>
       <c r="M62" s="21" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="N62" s="36"/>
       <c r="O62" s="33"/>
@@ -7751,13 +7751,13 @@
         <v>10</v>
       </c>
       <c r="B63" s="38" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C63" s="20">
         <v>0.42</v>
       </c>
       <c r="D63" s="21" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E63" s="36"/>
       <c r="F63" s="178">
@@ -7776,13 +7776,13 @@
         <v>9</v>
       </c>
       <c r="K63" s="66" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="L63" s="20">
         <v>4</v>
       </c>
       <c r="M63" s="21" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="N63" s="36"/>
       <c r="O63" s="172">
@@ -7801,11 +7801,11 @@
         <v>9</v>
       </c>
       <c r="B64" s="38" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C64" s="20"/>
       <c r="D64" s="21" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E64" s="36"/>
       <c r="F64" s="175"/>
@@ -7820,7 +7820,7 @@
         <v/>
       </c>
       <c r="K64" s="66" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="L64" s="20"/>
       <c r="M64" s="21"/>
@@ -7836,13 +7836,13 @@
     </row>
     <row r="65" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B65" s="38" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C65" s="20">
         <v>3.96</v>
       </c>
       <c r="D65" s="21" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E65" s="36"/>
       <c r="F65" s="178">
@@ -7857,16 +7857,16 @@
       </c>
       <c r="I65" s="34"/>
       <c r="J65" s="148" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="K65" s="141" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="L65" s="20">
         <v>33</v>
       </c>
       <c r="M65" s="21" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="N65" s="36"/>
       <c r="O65" s="33"/>
@@ -7880,16 +7880,16 @@
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A66" s="23" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B66" s="38" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C66" s="20">
         <v>1.1299999999999999</v>
       </c>
       <c r="D66" s="21" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E66" s="36"/>
       <c r="F66" s="178">
@@ -7920,10 +7920,10 @@
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B67" s="38" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C67" s="125" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D67" s="125"/>
       <c r="E67" s="36"/>
@@ -7939,13 +7939,13 @@
         <v/>
       </c>
       <c r="K67" s="66" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="L67" s="20">
         <v>15</v>
       </c>
       <c r="M67" s="21" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="N67" s="36"/>
       <c r="O67" s="33"/>
@@ -7962,13 +7962,13 @@
         <v>5</v>
       </c>
       <c r="B68" s="38" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C68" s="20">
         <v>11.62</v>
       </c>
       <c r="D68" s="21" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E68" s="36"/>
       <c r="F68" s="175"/>
@@ -7985,13 +7985,13 @@
         <v>5</v>
       </c>
       <c r="K68" s="66" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L68" s="20">
         <v>6</v>
       </c>
       <c r="M68" s="21" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="N68" s="36"/>
       <c r="O68" s="33"/>
@@ -8005,13 +8005,13 @@
     </row>
     <row r="69" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B69" s="38" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C69" s="20">
         <v>15.1</v>
       </c>
       <c r="D69" s="21" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E69" s="36"/>
       <c r="F69" s="175"/>
@@ -8028,13 +8028,13 @@
         <v/>
       </c>
       <c r="K69" s="139" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="L69" s="20">
         <v>5.4</v>
       </c>
       <c r="M69" s="21" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="N69" s="36"/>
       <c r="O69" s="33"/>
@@ -8051,13 +8051,13 @@
         <v>9</v>
       </c>
       <c r="B70" s="38" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C70" s="20">
         <v>4.47</v>
       </c>
       <c r="D70" s="21" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E70" s="126"/>
       <c r="F70" s="178">
@@ -8076,13 +8076,13 @@
         <v>9</v>
       </c>
       <c r="K70" s="139" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L70" s="20">
         <v>6.2</v>
       </c>
       <c r="M70" s="21" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="N70" s="36"/>
       <c r="O70" s="33"/>
@@ -8099,13 +8099,13 @@
         <v>8</v>
       </c>
       <c r="B71" s="50" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C71" s="20">
         <v>1.58</v>
       </c>
       <c r="D71" s="21" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E71" s="36"/>
       <c r="F71" s="178">
@@ -8124,13 +8124,13 @@
         <v>8</v>
       </c>
       <c r="K71" s="66" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="L71" s="20">
         <v>11.2</v>
       </c>
       <c r="M71" s="21" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="N71" s="36"/>
       <c r="O71" s="33"/>
@@ -8144,13 +8144,13 @@
     </row>
     <row r="72" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B72" s="50" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C72" s="20">
         <v>1.58</v>
       </c>
       <c r="D72" s="21" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E72" s="36"/>
       <c r="F72" s="175"/>
@@ -8167,13 +8167,13 @@
         <v/>
       </c>
       <c r="K72" s="66" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L72" s="20">
         <v>7.6</v>
       </c>
       <c r="M72" s="21" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="N72" s="3"/>
       <c r="P72" s="35">
@@ -8186,13 +8186,13 @@
     </row>
     <row r="73" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B73" s="38" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C73" s="20">
         <v>14.79</v>
       </c>
       <c r="D73" s="21" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E73" s="36"/>
       <c r="F73" s="175"/>
@@ -8209,13 +8209,13 @@
         <v/>
       </c>
       <c r="K73" s="66" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="L73" s="20">
         <v>3.9</v>
       </c>
       <c r="M73" s="21" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="N73" s="3"/>
       <c r="P73" s="35">
@@ -8228,13 +8228,13 @@
     </row>
     <row r="74" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B74" s="38" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C74" s="20">
         <v>7</v>
       </c>
       <c r="D74" s="21" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E74" s="36"/>
       <c r="F74" s="175"/>
@@ -8251,13 +8251,13 @@
         <v/>
       </c>
       <c r="K74" s="141" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="L74" s="20">
         <v>4.5</v>
       </c>
       <c r="M74" s="21" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="N74" s="36"/>
       <c r="O74" s="172">
@@ -8273,13 +8273,13 @@
     </row>
     <row r="75" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B75" s="38" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C75" s="20">
         <v>4.4000000000000004</v>
       </c>
       <c r="D75" s="21" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E75" s="36"/>
       <c r="F75" s="175"/>
@@ -8296,10 +8296,10 @@
         <v/>
       </c>
       <c r="K75" s="66" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="L75" s="21" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="M75" s="21"/>
       <c r="N75" s="36"/>
@@ -8313,13 +8313,13 @@
     </row>
     <row r="76" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B76" s="38" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C76" s="20">
         <v>2.8</v>
       </c>
       <c r="D76" s="21" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E76" s="3"/>
       <c r="F76" s="10"/>
@@ -8336,10 +8336,10 @@
         <v/>
       </c>
       <c r="K76" s="66" t="s">
+        <v>340</v>
+      </c>
+      <c r="L76" s="21" t="s">
         <v>341</v>
-      </c>
-      <c r="L76" s="21" t="s">
-        <v>342</v>
       </c>
       <c r="M76" s="21"/>
       <c r="N76" s="36"/>
@@ -8352,13 +8352,13 @@
     </row>
     <row r="77" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B77" s="52" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C77" s="20">
         <v>10.3</v>
       </c>
       <c r="D77" s="21" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E77" s="3"/>
       <c r="F77" s="9">
@@ -8377,7 +8377,7 @@
         <v/>
       </c>
       <c r="K77" s="138" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="L77" s="20"/>
       <c r="M77" s="21"/>
@@ -8390,13 +8390,13 @@
     </row>
     <row r="78" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B78" s="52" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C78" s="20">
         <v>8</v>
       </c>
       <c r="D78" s="21" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E78" s="3"/>
       <c r="F78" s="9">
@@ -8415,13 +8415,13 @@
         <v/>
       </c>
       <c r="K78" s="66" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="L78" s="20">
         <v>8</v>
       </c>
       <c r="M78" s="21" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="N78" s="3"/>
       <c r="P78" s="35">
@@ -8435,7 +8435,7 @@
     </row>
     <row r="79" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B79" s="46" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C79" s="20"/>
       <c r="D79" s="21"/>
@@ -8452,13 +8452,13 @@
         <v/>
       </c>
       <c r="K79" s="139" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="L79" s="20" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="M79" s="21" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="N79" s="3"/>
       <c r="P79" s="35">
@@ -8471,13 +8471,13 @@
     </row>
     <row r="80" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B80" s="38" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C80" s="20">
         <v>4.3</v>
       </c>
       <c r="D80" s="21" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E80" s="3"/>
       <c r="F80" s="9">
@@ -8509,13 +8509,13 @@
     </row>
     <row r="81" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B81" s="38" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C81" s="20">
         <v>1.41</v>
       </c>
       <c r="D81" s="21" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E81" s="3"/>
       <c r="F81" s="9">
@@ -8542,7 +8542,7 @@
     </row>
     <row r="82" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="39" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C82" s="20"/>
       <c r="D82" s="21"/>
@@ -8560,13 +8560,13 @@
         <v>Amsteel 7/64</v>
       </c>
       <c r="K82" s="142" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L82" s="41">
         <v>1.36</v>
       </c>
       <c r="M82" s="42" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="N82" s="11"/>
       <c r="O82" s="43">
@@ -8583,13 +8583,13 @@
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" s="43"/>
       <c r="B83" s="40" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C83" s="41">
         <v>1.36</v>
       </c>
       <c r="D83" s="42" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E83" s="11"/>
       <c r="F83" s="43">
@@ -8608,13 +8608,13 @@
         <v/>
       </c>
       <c r="K83" s="142" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L83" s="41">
         <v>1.36</v>
       </c>
       <c r="M83" s="42" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="N83" s="11"/>
       <c r="O83" s="43">
@@ -8631,13 +8631,13 @@
     <row r="84" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="39"/>
       <c r="B84" s="40" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C84" s="41">
         <v>1.36</v>
       </c>
       <c r="D84" s="42" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E84" s="11"/>
       <c r="F84" s="43">
@@ -8656,13 +8656,13 @@
         <v/>
       </c>
       <c r="K84" s="142" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="L84" s="41">
         <v>1.36</v>
       </c>
       <c r="M84" s="42" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="N84" s="11"/>
       <c r="O84" s="43">
@@ -8679,13 +8679,13 @@
     <row r="85" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="39"/>
       <c r="B85" s="40" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C85" s="41">
         <v>1.36</v>
       </c>
       <c r="D85" s="42" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E85" s="11"/>
       <c r="F85" s="43">
@@ -8718,7 +8718,7 @@
     </row>
     <row r="86" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="45" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B86" s="40"/>
       <c r="C86" s="41"/>
@@ -8738,13 +8738,13 @@
         <v>Shock Cord</v>
       </c>
       <c r="K86" s="138" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="L86" s="47">
         <v>1.9</v>
       </c>
       <c r="M86" s="48" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="N86" s="8"/>
       <c r="O86" s="7">
@@ -8761,13 +8761,13 @@
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="7"/>
       <c r="B87" s="46" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C87" s="47">
         <v>1.9</v>
       </c>
       <c r="D87" s="48" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E87" s="8"/>
       <c r="F87" s="7">
@@ -8786,13 +8786,13 @@
         <v/>
       </c>
       <c r="K87" s="138" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="L87" s="47">
         <v>1.2</v>
       </c>
       <c r="M87" s="48" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="N87" s="8"/>
       <c r="O87" s="7">
@@ -8809,13 +8809,13 @@
     <row r="88" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="10"/>
       <c r="B88" s="46" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C88" s="47">
         <v>1.2</v>
       </c>
       <c r="D88" s="48" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E88" s="8"/>
       <c r="F88" s="7">
@@ -8834,13 +8834,13 @@
         <v/>
       </c>
       <c r="K88" s="117" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="L88" s="57">
         <v>1.9</v>
       </c>
       <c r="M88" s="58" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="N88" s="13"/>
       <c r="O88" s="10"/>
@@ -8855,13 +8855,13 @@
     <row r="89" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="10"/>
       <c r="B89" s="54" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C89" s="57">
         <v>4.7</v>
       </c>
       <c r="D89" s="58" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E89" s="13"/>
       <c r="F89" s="10"/>
@@ -8892,7 +8892,7 @@
     </row>
     <row r="90" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B90" s="54"/>
       <c r="C90" s="57"/>
@@ -8921,16 +8921,16 @@
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B91" s="38" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C91" s="20">
         <v>0.49</v>
       </c>
       <c r="D91" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E91" s="36">
         <f>C91*((58*72)/(36*36))</f>
@@ -8958,13 +8958,13 @@
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" s="5"/>
       <c r="B92" s="54" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C92" s="20">
         <v>0.67</v>
       </c>
       <c r="D92" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E92" s="36">
         <f>C92*((58*72)/(36*36))</f>
@@ -8986,13 +8986,13 @@
         <v/>
       </c>
       <c r="K92" s="66" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L92" s="20">
         <v>0.66</v>
       </c>
       <c r="M92" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N92" s="36">
         <f>L92*$A$5</f>
@@ -9012,13 +9012,13 @@
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" s="5"/>
       <c r="B93" s="38" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C93" s="20">
         <v>0.9</v>
       </c>
       <c r="D93" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E93" s="36">
         <f>C93*((58*72)/(36*36))</f>
@@ -9046,7 +9046,7 @@
     <row r="94" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="5"/>
       <c r="B94" s="38" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C94" s="20"/>
       <c r="D94" s="21"/>
@@ -9067,7 +9067,7 @@
         <v/>
       </c>
       <c r="K94" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="O94">
         <v>1</v>
@@ -9082,7 +9082,7 @@
     </row>
     <row r="95" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B95" s="38"/>
       <c r="C95" s="20"/>
@@ -9112,13 +9112,13 @@
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" s="5"/>
       <c r="B96" s="38" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C96" s="20">
         <v>1.3</v>
       </c>
       <c r="D96" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E96" s="36">
         <f>C96*((12.5*22)/(36*36))</f>
@@ -9138,13 +9138,13 @@
         <v/>
       </c>
       <c r="K96" s="66" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="L96" s="20">
         <v>1.43</v>
       </c>
       <c r="M96" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N96" s="36">
         <f>L96*((12.5*22)/(36*36))</f>
@@ -9164,13 +9164,13 @@
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" s="5"/>
       <c r="B97" s="38" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C97" s="20">
         <v>1.1000000000000001</v>
       </c>
       <c r="D97" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E97" s="36">
         <f>C97*((12.5*22)/(36*36))</f>
@@ -9200,7 +9200,7 @@
     <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" s="5"/>
       <c r="B98" s="38" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C98" s="20"/>
       <c r="D98" s="21"/>
@@ -9219,13 +9219,13 @@
     <row r="99" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="5"/>
       <c r="B99" s="38" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C99" s="20">
         <v>15.1</v>
       </c>
       <c r="D99" s="21" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E99" s="36"/>
       <c r="F99" s="33"/>
@@ -9287,7 +9287,7 @@
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B102" s="38"/>
       <c r="C102" s="20"/>
@@ -9306,16 +9306,16 @@
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" s="128" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B103" s="38" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C103" s="20">
         <v>0.51</v>
       </c>
       <c r="D103" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E103" s="36">
         <f>C103*((36*56)/(36*36))</f>
@@ -9335,13 +9335,13 @@
         <v>-OR- 36L x 56W</v>
       </c>
       <c r="K103" s="66" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="L103" s="20">
         <v>0.51</v>
       </c>
       <c r="M103" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N103" s="36">
         <f>L103*((36*56)/(36*36))</f>
@@ -9360,16 +9360,16 @@
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B104" s="38" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C104" s="20">
         <v>1.1000000000000001</v>
       </c>
       <c r="D104" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E104" s="36">
         <f>C104*((36*56)/(36*36))</f>
@@ -9399,7 +9399,7 @@
     <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" s="5"/>
       <c r="B105" s="38" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C105" s="20"/>
       <c r="D105" s="21"/>
@@ -9421,7 +9421,7 @@
     <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" s="5"/>
       <c r="B106" s="38" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C106" s="20"/>
       <c r="D106" s="21"/>
@@ -9443,7 +9443,7 @@
     <row r="107" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="5"/>
       <c r="B107" s="38" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C107" s="20"/>
       <c r="D107" s="21"/>
@@ -9465,7 +9465,7 @@
     </row>
     <row r="108" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="5" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B108" s="38"/>
       <c r="C108" s="20"/>
@@ -9489,16 +9489,16 @@
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" s="60" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B109" s="38" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C109" s="20">
         <v>1.1000000000000001</v>
       </c>
       <c r="D109" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E109" s="36">
         <f>C109*((72*54)/(36*36))</f>
@@ -9520,7 +9520,7 @@
         <v>make pattern</v>
       </c>
       <c r="K109" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="N109" s="36">
         <f>1.4*((72*54)/(36*36))</f>
@@ -9540,13 +9540,13 @@
     <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110" s="60"/>
       <c r="B110" s="38" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C110" s="20">
         <v>0.51</v>
       </c>
       <c r="D110" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E110" s="36">
         <f>C110*((30*48)/(36*36))</f>
@@ -9566,13 +9566,13 @@
         <v/>
       </c>
       <c r="K110" s="66" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="L110" s="20">
         <v>0.51</v>
       </c>
       <c r="M110" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N110" s="36">
         <f>L110*((12.5*22)/(36*36))</f>
@@ -9589,7 +9589,7 @@
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111" s="180" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B111" s="38"/>
       <c r="C111" s="20"/>
@@ -9613,10 +9613,10 @@
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A112" s="180" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B112" s="46" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C112" s="20"/>
       <c r="D112" s="21"/>
@@ -9640,7 +9640,7 @@
     <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113" s="60"/>
       <c r="B113" s="50" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C113" s="20"/>
       <c r="D113" s="21"/>
@@ -9664,7 +9664,7 @@
     <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114" s="60"/>
       <c r="B114" s="50" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C114" s="20"/>
       <c r="D114" s="21"/>
@@ -9688,7 +9688,7 @@
     <row r="115" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="60"/>
       <c r="B115" s="38" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C115" s="20"/>
       <c r="D115" s="21"/>
@@ -9707,7 +9707,7 @@
         <v/>
       </c>
       <c r="K115" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="O115">
         <v>1</v>
@@ -9751,10 +9751,10 @@
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A117" s="18" t="s">
+        <v>363</v>
+      </c>
+      <c r="B117" s="38" t="s">
         <v>364</v>
-      </c>
-      <c r="B117" s="38" t="s">
-        <v>365</v>
       </c>
       <c r="C117" s="20"/>
       <c r="D117" s="21"/>
@@ -9769,10 +9769,10 @@
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A118" s="18" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B118" s="61" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H118" s="59" t="str">
         <f>IF((G118*F118)=0,"",G118*F118)</f>
@@ -9783,10 +9783,10 @@
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A119" s="18" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B119" s="38" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H119" s="59" t="str">
         <f>IF((G119*F119)=0,"",G119*F119)</f>
@@ -9796,7 +9796,7 @@
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120" s="18" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B120" s="38"/>
       <c r="H120" s="59"/>
@@ -9804,7 +9804,7 @@
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A121" s="18" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B121" s="38"/>
       <c r="H121" s="59"/>
@@ -9812,7 +9812,7 @@
     </row>
     <row r="122" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A122" s="18" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B122" s="38"/>
       <c r="H122" s="59"/>
@@ -9820,7 +9820,7 @@
     </row>
     <row r="123" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="18" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B123" s="38"/>
       <c r="H123" s="59" t="str">
@@ -9832,17 +9832,17 @@
     </row>
     <row r="124" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="18" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B124" s="54" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C124">
         <f>C125*F129</f>
         <v>6.8078820000000002</v>
       </c>
       <c r="D124" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E124" s="36">
         <f>C124*((30*48)/(36*36))</f>
@@ -9863,13 +9863,13 @@
         <v>Pullover/hoodie</v>
       </c>
       <c r="K124" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="L124">
         <v>4.8</v>
       </c>
       <c r="M124" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N124" s="36">
         <f>1.4*((72*54)/(36*36))</f>
@@ -9888,26 +9888,26 @@
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B125" s="54" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C125">
         <v>193</v>
       </c>
       <c r="D125" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J125" s="143" t="str">
         <f>IF(ISBLANK(A125),"",A125)</f>
         <v/>
       </c>
       <c r="K125" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="L125">
         <v>135.62</v>
       </c>
       <c r="M125" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="N125" s="36"/>
     </row>
@@ -9929,7 +9929,7 @@
         <v>56</v>
       </c>
       <c r="K126" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="P126" s="136">
         <v>20</v>
@@ -9937,28 +9937,28 @@
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127" s="131" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="K127" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="L127">
         <v>152.58000000000001</v>
       </c>
       <c r="M127" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="128" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="18" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="L128">
         <f>L127*F129</f>
         <v>5.38210692</v>
       </c>
       <c r="M128" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O128">
         <v>2</v>
@@ -9976,16 +9976,16 @@
         <v>1</v>
       </c>
       <c r="E129" s="79" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F129" s="79">
         <v>3.5274E-2</v>
       </c>
       <c r="G129" s="80" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K129" s="31" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="O129">
         <v>2</v>
@@ -10003,13 +10003,13 @@
         <v>28.349499999999999</v>
       </c>
       <c r="E130" s="134" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F130" s="134">
         <v>1</v>
       </c>
       <c r="G130" s="135" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="131" spans="4:17" x14ac:dyDescent="0.25">
@@ -10092,48 +10092,48 @@
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>133</v>
+        <v>541</v>
       </c>
       <c r="D1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E1">
         <v>3.5274E-2</v>
       </c>
       <c r="F1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G1" t="s">
         <v>159</v>
-      </c>
-      <c r="G1" t="s">
-        <v>160</v>
       </c>
       <c r="H1">
         <v>28.349499999999999</v>
       </c>
       <c r="I1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B2" s="24" t="s">
+        <v>138</v>
+      </c>
+      <c r="C2" s="24" t="s">
         <v>139</v>
-      </c>
-      <c r="C2" s="24" t="s">
-        <v>140</v>
       </c>
       <c r="E2">
         <f>2.72*H1</f>
         <v>77.110640000000004</v>
       </c>
       <c r="G2" s="31" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B3" s="16">
         <v>50</v>
@@ -10143,12 +10143,12 @@
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B4">
         <v>40</v>
@@ -10162,15 +10162,15 @@
         <v>1296</v>
       </c>
       <c r="L4" s="26" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="29" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B5" s="29">
         <v>30</v>
@@ -10180,16 +10180,16 @@
         <v>-1.1111111111111112</v>
       </c>
       <c r="D5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K5" s="7">
         <v>54</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="O5" s="20" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="P5">
         <v>32</v>
@@ -10203,7 +10203,7 @@
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="29" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B6" s="29">
         <v>20</v>
@@ -10213,22 +10213,22 @@
         <v>-6.666666666666667</v>
       </c>
       <c r="D6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K6" s="7">
         <v>78</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="O6" s="20" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="P6">
         <v>16</v>
       </c>
       <c r="Q6" s="20" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="R6">
         <v>8.1999999999999993</v>
@@ -10236,7 +10236,7 @@
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B7">
         <v>10</v>
@@ -10249,16 +10249,16 @@
         <v>1.83</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O7" s="20" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="P7">
         <v>44.8</v>
       </c>
       <c r="Q7" s="20" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="R7">
         <v>26</v>
@@ -10267,12 +10267,12 @@
         <v>22</v>
       </c>
       <c r="T7" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="25" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B8" s="25">
         <v>-5</v>
@@ -10286,16 +10286,16 @@
         <v>3.25</v>
       </c>
       <c r="L8" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="O8" s="20" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="P8">
         <v>4.2</v>
       </c>
       <c r="Q8" s="20" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="R8">
         <v>23</v>
@@ -10304,28 +10304,28 @@
         <v>20</v>
       </c>
       <c r="T8" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="E9" s="22" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K9" s="9">
         <f>K8*K7</f>
         <v>5.9474999999999998</v>
       </c>
       <c r="L9" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O9" s="20" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P9">
         <v>4</v>
       </c>
       <c r="Q9" s="20" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="R9">
         <v>7.3</v>
@@ -10333,39 +10333,39 @@
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J10" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="K10" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="K10" s="4" t="s">
-        <v>260</v>
-      </c>
       <c r="L10" s="32" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="M10" s="32" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O10" s="20"/>
       <c r="Q10" s="20" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="R10">
         <v>6</v>
@@ -10373,13 +10373,13 @@
     </row>
     <row r="11" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B11" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C11" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E11">
         <v>51.89</v>
@@ -10389,7 +10389,7 @@
         <v>1.83036786</v>
       </c>
       <c r="G11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H11" s="3">
         <f>F11*2</f>
@@ -10410,7 +10410,7 @@
         <v>5.9486955449999996</v>
       </c>
       <c r="Q11" s="20" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="R11">
         <v>6</v>
@@ -10418,10 +10418,10 @@
     </row>
     <row r="12" spans="1:20" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>143</v>
+      </c>
+      <c r="B12" t="s">
         <v>144</v>
-      </c>
-      <c r="B12" t="s">
-        <v>145</v>
       </c>
       <c r="F12" s="3"/>
       <c r="H12" s="3"/>
@@ -10452,7 +10452,7 @@
         <v>67</v>
       </c>
       <c r="B13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E13">
         <v>31.48</v>
@@ -10462,7 +10462,7 @@
         <v>1.1104255199999999</v>
       </c>
       <c r="G13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H13" s="3">
         <f>F13*5</f>
@@ -10487,7 +10487,7 @@
         <v>6</v>
       </c>
       <c r="Q13" s="20" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="R13">
         <f>INT(R12/16)</f>
@@ -10499,7 +10499,7 @@
         <v>90</v>
       </c>
       <c r="B14" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E14">
         <v>43</v>
@@ -10509,7 +10509,7 @@
         <v>1.5167820000000001</v>
       </c>
       <c r="G14" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H14" s="3">
         <f>F14*5</f>
@@ -10534,7 +10534,7 @@
         <v>5</v>
       </c>
       <c r="Q14" s="20" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="R14">
         <f>R12-(R13*16)</f>
@@ -10545,18 +10545,18 @@
         <v>7</v>
       </c>
       <c r="T14" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B15" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E15">
         <v>51.89</v>
@@ -10566,7 +10566,7 @@
         <v>1.83036786</v>
       </c>
       <c r="G15" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H15" s="3">
         <f>F15*3</f>
@@ -10583,15 +10583,15 @@
         <v>0</v>
       </c>
       <c r="S15" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>145</v>
+      </c>
+      <c r="B16" t="s">
         <v>146</v>
-      </c>
-      <c r="B16" t="s">
-        <v>147</v>
       </c>
       <c r="F16" s="3"/>
       <c r="H16" s="3"/>
@@ -10611,7 +10611,7 @@
         <v>1.2</v>
       </c>
       <c r="B17" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E17">
         <v>54</v>
@@ -10621,7 +10621,7 @@
         <v>1.9047959999999999</v>
       </c>
       <c r="G17" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H17" s="3">
         <f>F17*4</f>
@@ -10647,7 +10647,7 @@
         <v>1.6</v>
       </c>
       <c r="B18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E18">
         <v>80.47</v>
@@ -10657,7 +10657,7 @@
         <v>2.8384987800000001</v>
       </c>
       <c r="G18" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H18" s="3">
         <f>F18*3</f>
@@ -10678,26 +10678,26 @@
         <v>14.192493900000001</v>
       </c>
       <c r="O18" s="153" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="P18" s="154">
         <v>60</v>
       </c>
       <c r="Q18" s="154" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="R18" s="155">
         <f>P18*2*$E$1*$U$23</f>
         <v>6.8196399999999997</v>
       </c>
       <c r="S18" s="154" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="T18" s="156"/>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F19" s="3">
         <v>1.2</v>
@@ -10718,32 +10718,32 @@
         <v>3.822222222222222</v>
       </c>
       <c r="O19" s="157" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="P19" s="66">
         <v>90</v>
       </c>
       <c r="Q19" s="66" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="R19" s="158">
         <f>P19*2*$E$1*$U$23</f>
         <v>10.22946</v>
       </c>
       <c r="S19" s="66" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="T19" s="159"/>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>147</v>
+      </c>
+      <c r="B20" t="s">
         <v>148</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>149</v>
-      </c>
-      <c r="C20" t="s">
-        <v>150</v>
       </c>
       <c r="F20" s="3"/>
       <c r="H20" s="3"/>
@@ -10758,20 +10758,20 @@
         <v>0</v>
       </c>
       <c r="O20" s="157" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="P20" s="66">
         <v>120</v>
       </c>
       <c r="Q20" s="66" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="R20" s="158">
         <f>P20*2*$E$1*$U$23</f>
         <v>13.639279999999999</v>
       </c>
       <c r="S20" s="66" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="T20" s="159"/>
     </row>
@@ -10780,10 +10780,10 @@
         <v>0.9</v>
       </c>
       <c r="B21" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C21" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E21">
         <v>44.59</v>
@@ -10793,7 +10793,7 @@
         <v>1.57286766</v>
       </c>
       <c r="G21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H21" s="3"/>
       <c r="J21" s="7"/>
@@ -10807,20 +10807,20 @@
         <v>0</v>
       </c>
       <c r="O21" s="157" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="P21" s="66">
         <v>150</v>
       </c>
       <c r="Q21" s="66" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="R21" s="158">
         <f>P21*2*$E$1*$U$23</f>
         <v>17.049099999999999</v>
       </c>
       <c r="S21" s="66" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="T21" s="159"/>
     </row>
@@ -10829,7 +10829,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="B22" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C22">
         <v>4000</v>
@@ -10842,7 +10842,7 @@
         <v>2.0532995399999998</v>
       </c>
       <c r="G22" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H22" s="3">
         <f>F22*8</f>
@@ -10859,20 +10859,20 @@
         <v>0</v>
       </c>
       <c r="O22" s="160" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="P22" s="161">
         <v>190</v>
       </c>
       <c r="Q22" s="161" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="R22" s="162">
         <f>P22*2*$E$1*$U$23</f>
         <v>21.595526666666668</v>
       </c>
       <c r="S22" s="161" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="T22" s="163"/>
     </row>
@@ -10889,25 +10889,25 @@
         <v>0</v>
       </c>
       <c r="T23" s="168" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="U23">
         <f>(36*58)/(36*36)</f>
         <v>1.6111111111111112</v>
       </c>
       <c r="V23" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>151</v>
+      </c>
+      <c r="B24" t="s">
         <v>152</v>
       </c>
-      <c r="B24" t="s">
-        <v>153</v>
-      </c>
       <c r="D24" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E24">
         <v>90</v>
@@ -10930,13 +10930,13 @@
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B25" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D25" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E25">
         <v>135</v>
@@ -10959,13 +10959,13 @@
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B26">
         <v>2.5</v>
       </c>
       <c r="D26" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E26">
         <v>119.44</v>
@@ -10975,7 +10975,7 @@
         <v>4.2131265600000001</v>
       </c>
       <c r="G26" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H26" s="3">
         <f>F26*2</f>
@@ -10997,7 +10997,7 @@
         <v>3.6</v>
       </c>
       <c r="D27" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E27">
         <v>180</v>
@@ -11007,7 +11007,7 @@
         <v>6.3493199999999996</v>
       </c>
       <c r="G27" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H27" s="3">
         <f>F27*2</f>
@@ -11029,7 +11029,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E28">
         <v>238.88</v>
@@ -11039,7 +11039,7 @@
         <v>8.4262531200000002</v>
       </c>
       <c r="G28" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H28" s="3">
         <f>F28*2</f>
@@ -11061,7 +11061,7 @@
         <v>6</v>
       </c>
       <c r="D29" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F29" s="3"/>
       <c r="H29" s="3"/>
@@ -11072,10 +11072,10 @@
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>180</v>
+      </c>
+      <c r="C30" t="s">
         <v>181</v>
-      </c>
-      <c r="C30" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.25">
@@ -11097,7 +11097,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -11105,7 +11105,7 @@
         <v>1274</v>
       </c>
       <c r="B2" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -11113,7 +11113,7 @@
         <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -11121,7 +11121,7 @@
         <v>221</v>
       </c>
       <c r="B4" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -11129,7 +11129,7 @@
         <v>2557</v>
       </c>
       <c r="B5" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -11137,7 +11137,7 @@
         <v>309</v>
       </c>
       <c r="B6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -11145,7 +11145,7 @@
         <v>315</v>
       </c>
       <c r="B7" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -11153,7 +11153,7 @@
         <v>336</v>
       </c>
       <c r="B8" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -11161,7 +11161,7 @@
         <v>351</v>
       </c>
       <c r="B9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -11169,7 +11169,7 @@
         <v>3529</v>
       </c>
       <c r="B10" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -11177,7 +11177,7 @@
         <v>3644</v>
       </c>
       <c r="B11" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -11185,7 +11185,7 @@
         <v>386</v>
       </c>
       <c r="B12" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -11193,7 +11193,7 @@
         <v>417</v>
       </c>
       <c r="B13" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -11201,7 +11201,7 @@
         <v>472</v>
       </c>
       <c r="B14" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -11209,7 +11209,7 @@
         <v>555</v>
       </c>
       <c r="B15" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -11217,7 +11217,7 @@
         <v>580</v>
       </c>
       <c r="B16" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -11225,7 +11225,7 @@
         <v>582</v>
       </c>
       <c r="B17" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -11233,7 +11233,7 @@
         <v>672</v>
       </c>
       <c r="B18" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -11241,7 +11241,7 @@
         <v>676</v>
       </c>
       <c r="B19" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -11249,7 +11249,7 @@
         <v>701</v>
       </c>
       <c r="B20" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -11257,7 +11257,7 @@
         <v>7568</v>
       </c>
       <c r="B21" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -11265,7 +11265,7 @@
         <v>824</v>
       </c>
       <c r="B22" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -11273,7 +11273,7 @@
         <v>967</v>
       </c>
       <c r="B23" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -11281,7 +11281,7 @@
         <v>968</v>
       </c>
       <c r="B24" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -11289,7 +11289,7 @@
         <v>982</v>
       </c>
       <c r="B25" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
   </sheetData>
